--- a/Programme_vols_mensuel_2027-2028.xlsx
+++ b/Programme_vols_mensuel_2027-2028.xlsx
@@ -11,7 +11,7 @@
     <sheet name="Programme de vols" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Programme de vols'!$B$1:$L$38</definedName>
+    <definedName function="false" hidden="false" localSheetId="0" name="_xlnm.Print_Area" vbProcedure="false">'Programme de vols'!$B$1:$L$39</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -28,6 +28,20 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
+    <comment ref="B62" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Saisir la date du vol (dans l'annee avril 2027 - mars 2028).
+Nb de rotations : 1 par defaut, 2 pour une double rotation le meme jour.
+Les 3 premieres lignes sont des exemples : les supprimer avant exploitation.</t>
+        </r>
+      </text>
+    </comment>
     <comment ref="C4" authorId="0">
       <text>
         <r>
@@ -36,8 +50,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Liste deroulante : avril 2027 -&gt; mars 2028.
-Pilote la grille ET le recapitulatif.</t>
+          <t xml:space="preserve">Liste deroulante : avril 2027 -&gt; mars 2028.</t>
         </r>
       </text>
     </comment>
@@ -49,8 +62,7 @@
             <rFont val="Arial"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">Liste deroulante : 12 routes.
-Pilote uniquement la grille.</t>
+          <t xml:space="preserve">Liste deroulante : les 12 routes exploitees.</t>
         </r>
       </text>
     </comment>
@@ -59,12 +71,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="80">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="90">
   <si>
     <t xml:space="preserve">PROGRAMME DE VOLS MENSUEL - ANNEE D'EXPLOITATION AVRIL 2027 / MARS 2028</t>
   </si>
   <si>
-    <t xml:space="preserve">Feuille unique : les deux filtres ci-dessous (Mois et Route) pilotent la grille. Le recapitulatif ne suit que le filtre Mois. Toutes les valeurs sont calculees par formule a partir des semaines types saisies dans la zone de parametres (bas de feuille).</t>
+    <t xml:space="preserve">Feuille unique : les deux filtres ci-dessous (Mois et Route) pilotent la grille. Le recapitulatif ne suit que le filtre Mois. Chaque route a une semaine type pouvant melanger plusieurs types avion (un type par jour), a laquelle s'ajoutent les vols additionnels dates saisis en bas de feuille. Tout est calcule par formule.</t>
   </si>
   <si>
     <t xml:space="preserve">REPERES CALCULES</t>
@@ -76,7 +88,7 @@
     <t xml:space="preserve">avril 2027</t>
   </si>
   <si>
-    <t xml:space="preserve">&lt;-- listes deroulantes</t>
+    <t xml:space="preserve">&lt;-- liste deroulante : pilote la grille ET le recapitulatif</t>
   </si>
   <si>
     <t xml:space="preserve">1er jour du mois</t>
@@ -88,13 +100,16 @@
     <t xml:space="preserve">NOSRUN</t>
   </si>
   <si>
+    <t xml:space="preserve">&lt;-- liste deroulante : pilote la grille uniquement</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dernier jour du mois</t>
   </si>
   <si>
     <t xml:space="preserve">GRILLE MENSUELLE  -  type avion opere par semaine et par jour (filtres Mois + Route)</t>
   </si>
   <si>
-    <t xml:space="preserve">Lundi de la semaine 1</t>
+    <t xml:space="preserve">Lundi semaine 1</t>
   </si>
   <si>
     <t xml:space="preserve">Semaine</t>
@@ -121,21 +136,24 @@
     <t xml:space="preserve">J7 - Dimanche</t>
   </si>
   <si>
-    <t xml:space="preserve">Type avion (route filtree)</t>
+    <t xml:space="preserve">Type(s) avion</t>
   </si>
   <si>
     <t xml:space="preserve">Semaine 1</t>
   </si>
   <si>
-    <t xml:space="preserve">Rotations / semaine (route filtree)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total rotations du mois (route filtree)</t>
+    <t xml:space="preserve">Rotations / semaine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total rotations mois</t>
   </si>
   <si>
     <t xml:space="preserve">Semaine 2</t>
   </si>
   <si>
+    <t xml:space="preserve">(route filtree)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Semaine 3</t>
   </si>
   <si>
@@ -154,7 +172,7 @@
     <t xml:space="preserve">Nb de semaines calendaires du mois</t>
   </si>
   <si>
-    <t xml:space="preserve">Semaines partielles de debut / fin de mois incluses : seuls les jours reellement compris dans le mois sont dates, donc comptes.</t>
+    <t xml:space="preserve">Lecture d'une cellule : "778" = vol de la semaine type  |  "778 (+A320)" = semaine type + vol additionnel  |  "(+A320)" = vol additionnel seul (bordure rouge). Semaines partielles incluses.</t>
   </si>
   <si>
     <t xml:space="preserve">RECAPITULATIF MENSUEL - TOUTES ROUTES  (depend uniquement du filtre Mois)</t>
@@ -163,142 +181,166 @@
     <t xml:space="preserve">Route</t>
   </si>
   <si>
+    <t xml:space="preserve">Semaine type (jours J1-J7)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rotations/semaine</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nb de semaines/occurrences dans le mois</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total rotations du mois</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dont semaine type</t>
+  </si>
+  <si>
+    <t xml:space="preserve">dont vols additionnels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total 77W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total 778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Total A320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TOTAL GENERAL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Methode : pour chaque jour d'operation de la semaine type, le nombre d'occurrences de ce jour dans le mois est compte a partir des dates reelles de la grille (ligne "Occurrences du jour dans le mois", semaines partielles incluses). Total rotations du mois = semaine type + vols additionnels dates du mois. La colonne "Nb de semaines/occurrences" indique le nombre de semaines calendaires couvertes par le mois ; les colonnes Total 77W / 778 / A320 ventilent le total du mois par type avion (semaine type + vols additionnels).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) SEMAINES TYPES PAR ROUTE (saisie unique, valable pour les 12 mois)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cellules en BLEU = saisie utilisateur. Pour chaque jour J1-J7, choisir dans la liste deroulante le TYPE AVION opere ce jour-la (77W / 778 / A320), ou laisser la cellule vide s'il n'y a pas d'operation. Une meme route peut donc utiliser plusieurs types avion dans la semaine (ex. CDGRUN : 77W les jours impairs, 778 les jours pairs). Toute modification recalcule immediatement la grille et le recapitulatif, pour les 12 mois. Valeurs livrees = exemples a ajuster (NOSRUN = 3/7 en A320 sur J1/J4/J6, conforme a l'exemple fourni).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rot./sem. (auto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Type(s) avion (auto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Couleur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mois (liste)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1er jour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Types avion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDGRUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">77W</t>
+  </si>
+  <si>
+    <t xml:space="preserve">778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CDGDZA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mai 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BKKRUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">juin 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DZARUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">juillet 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MRURUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">aout 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">septembre 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RUNTNR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">octobre 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JNBRUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">novembre 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CPTRUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decembre 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIERUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">janvier 2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">RRGRUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fevrier 2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TMMRUN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mars 2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2) VOLS ADDITIONNELS (en plus de la semaine type)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une ligne = un vol supplementaire date (charter, renfort saisonnier, fret...). Il s'ajoute a la semaine type de la route, sur n'importe quel jour, y compris un jour deja opere ou un jour hors semaine type. Il apparait dans la grille entre parentheses avec un + et une bordure rouge, et il est compte dans le recapitulatif du mois concerne.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date du vol</t>
+  </si>
+  <si>
     <t xml:space="preserve">Type avion</t>
   </si>
   <si>
-    <t xml:space="preserve">Semaine type (jours J1-J7)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rotations/semaine</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nb de semaines/occurrences dans le mois</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total rotations du mois</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TOTAL GENERAL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Methode de calcul : pour chaque jour d'operation de la semaine type, le nombre d'occurrences de ce jour dans le mois est compte via les dates reelles de la grille (ligne "Occurrences du jour dans le mois", semaines partielles incluses). Total rotations du mois = somme de ces occurrences. La colonne "Nb de semaines/occurrences" indique le nombre de semaines calendaires couvertes par le mois.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ZONE DE PARAMETRES - SEMAINES TYPES PAR ROUTE (saisie unique, valable pour les 12 mois)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cellules en BLEU = saisie utilisateur. Type avion : liste deroulante (77W / 778 / A320). Jours J1-J7 : saisir 1 si la route opere ce jour-la, 0 sinon. Toute modification recalcule immediatement la grille et le recapitulatif, pour les 12 mois. Valeurs livrees = exemples a ajuster (NOSRUN = 3/7 A320 sur J1/J4/J6, conforme a l'exemple fourni).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J4</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J6</t>
-  </si>
-  <si>
-    <t xml:space="preserve">J7</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rot./sem. (auto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Couleur</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mois (liste)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1er jour</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Types avion</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDGRUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">77W</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CDGDZA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mai 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BKKRUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">juin 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A320</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DZARUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">juillet 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MRURUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">aout 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">septembre 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RUNTNR</t>
-  </si>
-  <si>
-    <t xml:space="preserve">octobre 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JNBRUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">novembre 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CPTRUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decembre 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIERUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">janvier 2028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">RRGRUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fevrier 2028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TMMRUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mars 2028</t>
+    <t xml:space="preserve">Nb de rotations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Commentaire (libre)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cle technique (auto)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXEMPLE a supprimer - vol supplementaire un mercredi (jour hors semaine type)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXEMPLE a supprimer - rotation doublee un samedi (jour deja opere)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">EXEMPLE a supprimer - 2 rotations fret supplementaires</t>
   </si>
 </sst>
 </file>
@@ -312,7 +354,7 @@
     <numFmt numFmtId="167" formatCode="dd/mm"/>
     <numFmt numFmtId="168" formatCode="General"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="24">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -423,6 +465,22 @@
       <charset val="1"/>
     </font>
     <font>
+      <i val="true"/>
+      <sz val="8"/>
+      <color rgb="FF808080"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="9"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
@@ -438,16 +496,31 @@
       <charset val="1"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color rgb="FF0000FF"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <b val="true"/>
-      <sz val="9"/>
+      <sz val="8"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FF0000FF"/>
+      <i val="true"/>
+      <sz val="9"/>
+      <color rgb="FF595959"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFA6A6A6"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -458,7 +531,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="21">
+  <fills count="22">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -579,6 +652,12 @@
         <bgColor rgb="FFA6A6A6"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA6A6A6"/>
+        <bgColor rgb="FF8FAADC"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="3">
     <border diagonalUp="false" diagonalDown="false">
@@ -642,7 +721,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="58">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -711,6 +790,10 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -723,7 +806,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -731,11 +814,63 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="17" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -743,51 +878,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="6" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="166" fontId="7" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="17" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="15" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -799,51 +890,67 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="16" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="16" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="18" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="18" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="19" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="19" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="21" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="166" fontId="19" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -856,7 +963,24 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="24">
+  <dxfs count="25">
+    <dxf>
+      <border diagonalUp="false" diagonalDown="false">
+        <left style="medium">
+          <color rgb="FFC00000"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFC00000"/>
+        </right>
+        <top style="medium">
+          <color rgb="FFC00000"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FFC00000"/>
+        </bottom>
+        <diagonal/>
+      </border>
+    </dxf>
     <dxf>
       <font>
         <name val="Arial"/>
@@ -1222,7 +1346,7 @@
     <indexedColors>
       <rgbColor rgb="FF000000"/>
       <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
+      <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FFE7E6E6"/>
@@ -1461,18 +1585,19 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:P54"/>
+  <dimension ref="B1:P101"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="3"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="15" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1500,10 +1625,10 @@
       <c r="I2" s="2"/>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="K3" s="3" t="s">
+      <c r="N3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="3"/>
+      <c r="O3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="4" t="s">
@@ -1516,11 +1641,11 @@
       <c r="E4" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="K4" s="7" t="s">
+      <c r="N4" s="7" t="s">
         <v>6</v>
       </c>
-      <c r="L4" s="8" t="n">
-        <f aca="false">INDEX($O$43:$O$54,MATCH($C$4,$N$43:$N$54,0))</f>
+      <c r="O4" s="8" t="n">
+        <f aca="false">INDEX($O$45:$O$56,MATCH($C$4,$N$45:$N$56,0))</f>
         <v>46478</v>
       </c>
     </row>
@@ -1533,19 +1658,19 @@
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="K5" s="7" t="s">
         <v>9</v>
       </c>
-      <c r="L5" s="8" t="n">
-        <f aca="false">EOMONTH($L$4,0)</f>
+      <c r="N5" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <f aca="false">EOMONTH($O$4,0)</f>
         <v>46507</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B6" s="9" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="9"/>
@@ -1554,84 +1679,84 @@
       <c r="G6" s="9"/>
       <c r="H6" s="9"/>
       <c r="I6" s="9"/>
-      <c r="K6" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="L6" s="8" t="n">
-        <f aca="false">$L$4-WEEKDAY($L$4,3)</f>
+      <c r="N6" s="7" t="s">
+        <v>12</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <f aca="false">$O$4-WEEKDAY($O$4,3)</f>
         <v>46475</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="10" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C7" s="10" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H7" s="10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>19</v>
-      </c>
-      <c r="K7" s="7" t="s">
         <v>20</v>
       </c>
-      <c r="L7" s="11" t="str">
-        <f aca="false">IFERROR(INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),"")</f>
-        <v>A320</v>
+      <c r="N7" s="7" t="s">
+        <v>21</v>
+      </c>
+      <c r="O7" s="11" t="str">
+        <f aca="false">IFERROR(INDEX($C$25:$C$36,MATCH($C$5,$B$25:$B$36,0)),"")</f>
+        <v>A320(3)</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B8" s="12" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C8" s="13" t="str">
-        <f aca="false">IF(C9="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),1)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(C9="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),1)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C9)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,C9)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C9)=1,IFERROR(INDEX($D$62:$D$101,MATCH(C9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C9)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(C9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C9)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="D8" s="13" t="str">
-        <f aca="false">IF(D9="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),2)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(D9="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),2)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D9)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,D9)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D9)=1,IFERROR(INDEX($D$62:$D$101,MATCH(D9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D9)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(D9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D9)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="E8" s="13" t="str">
-        <f aca="false">IF(E9="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),3)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(E9="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),3)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E9)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,E9)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E9)=1,IFERROR(INDEX($D$62:$D$101,MATCH(E9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E9)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(E9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E9)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="F8" s="13" t="str">
-        <f aca="false">IF(F9="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),4)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(F9="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),4)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F9)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,F9)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F9)=1,IFERROR(INDEX($D$62:$D$101,MATCH(F9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F9)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(F9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F9)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="G8" s="13" t="str">
-        <f aca="false">IF(G9="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),5)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(G9="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),5)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G9)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,G9)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G9)=1,IFERROR(INDEX($D$62:$D$101,MATCH(G9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G9)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(G9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G9)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="H8" s="13" t="str">
-        <f aca="false">IF(H9="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),6)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(H9="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),6)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H9)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,H9)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H9)=1,IFERROR(INDEX($D$62:$D$101,MATCH(H9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H9)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(H9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H9)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="I8" s="13" t="str">
-        <f aca="false">IF(I9="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),7)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
-        <v/>
-      </c>
-      <c r="K8" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="L8" s="14" t="n">
-        <f aca="false">IFERROR(SUM(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),0)),"")</f>
+        <f aca="false">IF(I9="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),7)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I9)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,I9)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I9)=1,IFERROR(INDEX($D$62:$D$101,MATCH(I9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I9)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(I9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I9)&amp;" vols")&amp;")")))</f>
+        <v/>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>23</v>
+      </c>
+      <c r="O8" s="14" t="n">
+        <f aca="false">IFERROR(INDEX($E$25:$E$36,MATCH($C$5,$B$25:$B$36,0)),"")</f>
         <v>3</v>
       </c>
     </row>
@@ -1641,72 +1766,75 @@
         <v>du 01/04 au 04/04</v>
       </c>
       <c r="C9" s="16" t="str">
-        <f aca="false">IF(OR($L$6+0&lt;$L$4,$L$6+0&gt;$L$5),"",$L$6+0)</f>
+        <f aca="false">IF(OR($O$6+0&lt;$O$4,$O$6+0&gt;$O$5),"",$O$6+0)</f>
         <v/>
       </c>
       <c r="D9" s="16" t="str">
-        <f aca="false">IF(OR($L$6+1&lt;$L$4,$L$6+1&gt;$L$5),"",$L$6+1)</f>
+        <f aca="false">IF(OR($O$6+1&lt;$O$4,$O$6+1&gt;$O$5),"",$O$6+1)</f>
         <v/>
       </c>
       <c r="E9" s="16" t="str">
-        <f aca="false">IF(OR($L$6+2&lt;$L$4,$L$6+2&gt;$L$5),"",$L$6+2)</f>
+        <f aca="false">IF(OR($O$6+2&lt;$O$4,$O$6+2&gt;$O$5),"",$O$6+2)</f>
         <v/>
       </c>
       <c r="F9" s="16" t="n">
-        <f aca="false">IF(OR($L$6+3&lt;$L$4,$L$6+3&gt;$L$5),"",$L$6+3)</f>
+        <f aca="false">IF(OR($O$6+3&lt;$O$4,$O$6+3&gt;$O$5),"",$O$6+3)</f>
         <v>46478</v>
       </c>
       <c r="G9" s="16" t="n">
-        <f aca="false">IF(OR($L$6+4&lt;$L$4,$L$6+4&gt;$L$5),"",$L$6+4)</f>
+        <f aca="false">IF(OR($O$6+4&lt;$O$4,$O$6+4&gt;$O$5),"",$O$6+4)</f>
         <v>46479</v>
       </c>
       <c r="H9" s="16" t="n">
-        <f aca="false">IF(OR($L$6+5&lt;$L$4,$L$6+5&gt;$L$5),"",$L$6+5)</f>
+        <f aca="false">IF(OR($O$6+5&lt;$O$4,$O$6+5&gt;$O$5),"",$O$6+5)</f>
         <v>46480</v>
       </c>
       <c r="I9" s="16" t="n">
-        <f aca="false">IF(OR($L$6+6&lt;$L$4,$L$6+6&gt;$L$5),"",$L$6+6)</f>
+        <f aca="false">IF(OR($O$6+6&lt;$O$4,$O$6+6&gt;$O$5),"",$O$6+6)</f>
         <v>46481</v>
       </c>
-      <c r="K9" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="L9" s="14" t="n">
+      <c r="N9" s="7" t="s">
+        <v>24</v>
+      </c>
+      <c r="O9" s="14" t="n">
         <f aca="false">IFERROR(INDEX($G$25:$G$36,MATCH($C$5,$B$25:$B$36,0)),"")</f>
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B10" s="12" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C10" s="13" t="str">
-        <f aca="false">IF(C11="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),1)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(C11="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),1)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C11)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,C11)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C11)=1,IFERROR(INDEX($D$62:$D$101,MATCH(C11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C11)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(C11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C11)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="D10" s="13" t="str">
-        <f aca="false">IF(D11="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),2)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(D11="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),2)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D11)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,D11)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D11)=1,IFERROR(INDEX($D$62:$D$101,MATCH(D11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D11)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(D11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D11)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="E10" s="13" t="str">
-        <f aca="false">IF(E11="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),3)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
-        <v/>
+        <f aca="false">IF(E11="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),3)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E11)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,E11)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E11)=1,IFERROR(INDEX($D$62:$D$101,MATCH(E11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E11)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(E11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E11)&amp;" vols")&amp;")")))</f>
+        <v>(+A320)</v>
       </c>
       <c r="F10" s="13" t="str">
-        <f aca="false">IF(F11="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),4)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(F11="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),4)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F11)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,F11)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F11)=1,IFERROR(INDEX($D$62:$D$101,MATCH(F11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F11)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(F11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F11)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="G10" s="13" t="str">
-        <f aca="false">IF(G11="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),5)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(G11="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),5)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G11)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,G11)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G11)=1,IFERROR(INDEX($D$62:$D$101,MATCH(G11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G11)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(G11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G11)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="H10" s="13" t="str">
-        <f aca="false">IF(H11="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),6)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
-        <v>A320</v>
+        <f aca="false">IF(H11="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),6)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H11)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,H11)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H11)=1,IFERROR(INDEX($D$62:$D$101,MATCH(H11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H11)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(H11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H11)&amp;" vols")&amp;")")))</f>
+        <v>A320 (+A320)</v>
       </c>
       <c r="I10" s="13" t="str">
-        <f aca="false">IF(I11="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),7)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
-        <v/>
+        <f aca="false">IF(I11="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),7)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I11)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,I11)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I11)=1,IFERROR(INDEX($D$62:$D$101,MATCH(I11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I11)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(I11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I11)&amp;" vols")&amp;")")))</f>
+        <v/>
+      </c>
+      <c r="N10" s="17" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1715,64 +1843,64 @@
         <v>du 05/04 au 11/04</v>
       </c>
       <c r="C11" s="16" t="n">
-        <f aca="false">IF(OR($L$6+7&lt;$L$4,$L$6+7&gt;$L$5),"",$L$6+7)</f>
+        <f aca="false">IF(OR($O$6+7&lt;$O$4,$O$6+7&gt;$O$5),"",$O$6+7)</f>
         <v>46482</v>
       </c>
       <c r="D11" s="16" t="n">
-        <f aca="false">IF(OR($L$6+8&lt;$L$4,$L$6+8&gt;$L$5),"",$L$6+8)</f>
+        <f aca="false">IF(OR($O$6+8&lt;$O$4,$O$6+8&gt;$O$5),"",$O$6+8)</f>
         <v>46483</v>
       </c>
       <c r="E11" s="16" t="n">
-        <f aca="false">IF(OR($L$6+9&lt;$L$4,$L$6+9&gt;$L$5),"",$L$6+9)</f>
+        <f aca="false">IF(OR($O$6+9&lt;$O$4,$O$6+9&gt;$O$5),"",$O$6+9)</f>
         <v>46484</v>
       </c>
       <c r="F11" s="16" t="n">
-        <f aca="false">IF(OR($L$6+10&lt;$L$4,$L$6+10&gt;$L$5),"",$L$6+10)</f>
+        <f aca="false">IF(OR($O$6+10&lt;$O$4,$O$6+10&gt;$O$5),"",$O$6+10)</f>
         <v>46485</v>
       </c>
       <c r="G11" s="16" t="n">
-        <f aca="false">IF(OR($L$6+11&lt;$L$4,$L$6+11&gt;$L$5),"",$L$6+11)</f>
+        <f aca="false">IF(OR($O$6+11&lt;$O$4,$O$6+11&gt;$O$5),"",$O$6+11)</f>
         <v>46486</v>
       </c>
       <c r="H11" s="16" t="n">
-        <f aca="false">IF(OR($L$6+12&lt;$L$4,$L$6+12&gt;$L$5),"",$L$6+12)</f>
+        <f aca="false">IF(OR($O$6+12&lt;$O$4,$O$6+12&gt;$O$5),"",$O$6+12)</f>
         <v>46487</v>
       </c>
       <c r="I11" s="16" t="n">
-        <f aca="false">IF(OR($L$6+13&lt;$L$4,$L$6+13&gt;$L$5),"",$L$6+13)</f>
+        <f aca="false">IF(OR($O$6+13&lt;$O$4,$O$6+13&gt;$O$5),"",$O$6+13)</f>
         <v>46488</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="C12" s="13" t="str">
-        <f aca="false">IF(C13="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),1)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(C13="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),1)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C13)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,C13)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C13)=1,IFERROR(INDEX($D$62:$D$101,MATCH(C13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C13)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(C13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C13)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="D12" s="13" t="str">
-        <f aca="false">IF(D13="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),2)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(D13="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),2)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D13)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,D13)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D13)=1,IFERROR(INDEX($D$62:$D$101,MATCH(D13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D13)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(D13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D13)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="E12" s="13" t="str">
-        <f aca="false">IF(E13="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),3)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(E13="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),3)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E13)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,E13)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E13)=1,IFERROR(INDEX($D$62:$D$101,MATCH(E13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E13)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(E13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E13)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="F12" s="13" t="str">
-        <f aca="false">IF(F13="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),4)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(F13="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),4)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F13)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,F13)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F13)=1,IFERROR(INDEX($D$62:$D$101,MATCH(F13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F13)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(F13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F13)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="G12" s="13" t="str">
-        <f aca="false">IF(G13="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),5)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(G13="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),5)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G13)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,G13)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G13)=1,IFERROR(INDEX($D$62:$D$101,MATCH(G13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G13)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(G13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G13)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="H12" s="13" t="str">
-        <f aca="false">IF(H13="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),6)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(H13="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),6)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H13)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,H13)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H13)=1,IFERROR(INDEX($D$62:$D$101,MATCH(H13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H13)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(H13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H13)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="I12" s="13" t="str">
-        <f aca="false">IF(I13="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),7)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(I13="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),7)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I13)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,I13)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I13)=1,IFERROR(INDEX($D$62:$D$101,MATCH(I13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I13)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(I13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I13)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
     </row>
@@ -1782,64 +1910,64 @@
         <v>du 12/04 au 18/04</v>
       </c>
       <c r="C13" s="16" t="n">
-        <f aca="false">IF(OR($L$6+14&lt;$L$4,$L$6+14&gt;$L$5),"",$L$6+14)</f>
+        <f aca="false">IF(OR($O$6+14&lt;$O$4,$O$6+14&gt;$O$5),"",$O$6+14)</f>
         <v>46489</v>
       </c>
       <c r="D13" s="16" t="n">
-        <f aca="false">IF(OR($L$6+15&lt;$L$4,$L$6+15&gt;$L$5),"",$L$6+15)</f>
+        <f aca="false">IF(OR($O$6+15&lt;$O$4,$O$6+15&gt;$O$5),"",$O$6+15)</f>
         <v>46490</v>
       </c>
       <c r="E13" s="16" t="n">
-        <f aca="false">IF(OR($L$6+16&lt;$L$4,$L$6+16&gt;$L$5),"",$L$6+16)</f>
+        <f aca="false">IF(OR($O$6+16&lt;$O$4,$O$6+16&gt;$O$5),"",$O$6+16)</f>
         <v>46491</v>
       </c>
       <c r="F13" s="16" t="n">
-        <f aca="false">IF(OR($L$6+17&lt;$L$4,$L$6+17&gt;$L$5),"",$L$6+17)</f>
+        <f aca="false">IF(OR($O$6+17&lt;$O$4,$O$6+17&gt;$O$5),"",$O$6+17)</f>
         <v>46492</v>
       </c>
       <c r="G13" s="16" t="n">
-        <f aca="false">IF(OR($L$6+18&lt;$L$4,$L$6+18&gt;$L$5),"",$L$6+18)</f>
+        <f aca="false">IF(OR($O$6+18&lt;$O$4,$O$6+18&gt;$O$5),"",$O$6+18)</f>
         <v>46493</v>
       </c>
       <c r="H13" s="16" t="n">
-        <f aca="false">IF(OR($L$6+19&lt;$L$4,$L$6+19&gt;$L$5),"",$L$6+19)</f>
+        <f aca="false">IF(OR($O$6+19&lt;$O$4,$O$6+19&gt;$O$5),"",$O$6+19)</f>
         <v>46494</v>
       </c>
       <c r="I13" s="16" t="n">
-        <f aca="false">IF(OR($L$6+20&lt;$L$4,$L$6+20&gt;$L$5),"",$L$6+20)</f>
+        <f aca="false">IF(OR($O$6+20&lt;$O$4,$O$6+20&gt;$O$5),"",$O$6+20)</f>
         <v>46495</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C14" s="13" t="str">
-        <f aca="false">IF(C15="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),1)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(C15="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),1)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C15)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,C15)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C15)=1,IFERROR(INDEX($D$62:$D$101,MATCH(C15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C15)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(C15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C15)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="D14" s="13" t="str">
-        <f aca="false">IF(D15="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),2)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(D15="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),2)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D15)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,D15)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D15)=1,IFERROR(INDEX($D$62:$D$101,MATCH(D15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D15)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(D15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D15)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="E14" s="13" t="str">
-        <f aca="false">IF(E15="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),3)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(E15="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),3)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E15)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,E15)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E15)=1,IFERROR(INDEX($D$62:$D$101,MATCH(E15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E15)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(E15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E15)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="F14" s="13" t="str">
-        <f aca="false">IF(F15="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),4)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(F15="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),4)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F15)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,F15)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F15)=1,IFERROR(INDEX($D$62:$D$101,MATCH(F15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F15)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(F15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F15)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="G14" s="13" t="str">
-        <f aca="false">IF(G15="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),5)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(G15="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),5)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G15)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,G15)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G15)=1,IFERROR(INDEX($D$62:$D$101,MATCH(G15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G15)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(G15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G15)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="H14" s="13" t="str">
-        <f aca="false">IF(H15="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),6)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(H15="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),6)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H15)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,H15)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H15)=1,IFERROR(INDEX($D$62:$D$101,MATCH(H15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H15)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(H15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H15)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="I14" s="13" t="str">
-        <f aca="false">IF(I15="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),7)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(I15="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),7)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I15)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,I15)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I15)=1,IFERROR(INDEX($D$62:$D$101,MATCH(I15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I15)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(I15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I15)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
     </row>
@@ -1849,64 +1977,64 @@
         <v>du 19/04 au 25/04</v>
       </c>
       <c r="C15" s="16" t="n">
-        <f aca="false">IF(OR($L$6+21&lt;$L$4,$L$6+21&gt;$L$5),"",$L$6+21)</f>
+        <f aca="false">IF(OR($O$6+21&lt;$O$4,$O$6+21&gt;$O$5),"",$O$6+21)</f>
         <v>46496</v>
       </c>
       <c r="D15" s="16" t="n">
-        <f aca="false">IF(OR($L$6+22&lt;$L$4,$L$6+22&gt;$L$5),"",$L$6+22)</f>
+        <f aca="false">IF(OR($O$6+22&lt;$O$4,$O$6+22&gt;$O$5),"",$O$6+22)</f>
         <v>46497</v>
       </c>
       <c r="E15" s="16" t="n">
-        <f aca="false">IF(OR($L$6+23&lt;$L$4,$L$6+23&gt;$L$5),"",$L$6+23)</f>
+        <f aca="false">IF(OR($O$6+23&lt;$O$4,$O$6+23&gt;$O$5),"",$O$6+23)</f>
         <v>46498</v>
       </c>
       <c r="F15" s="16" t="n">
-        <f aca="false">IF(OR($L$6+24&lt;$L$4,$L$6+24&gt;$L$5),"",$L$6+24)</f>
+        <f aca="false">IF(OR($O$6+24&lt;$O$4,$O$6+24&gt;$O$5),"",$O$6+24)</f>
         <v>46499</v>
       </c>
       <c r="G15" s="16" t="n">
-        <f aca="false">IF(OR($L$6+25&lt;$L$4,$L$6+25&gt;$L$5),"",$L$6+25)</f>
+        <f aca="false">IF(OR($O$6+25&lt;$O$4,$O$6+25&gt;$O$5),"",$O$6+25)</f>
         <v>46500</v>
       </c>
       <c r="H15" s="16" t="n">
-        <f aca="false">IF(OR($L$6+26&lt;$L$4,$L$6+26&gt;$L$5),"",$L$6+26)</f>
+        <f aca="false">IF(OR($O$6+26&lt;$O$4,$O$6+26&gt;$O$5),"",$O$6+26)</f>
         <v>46501</v>
       </c>
       <c r="I15" s="16" t="n">
-        <f aca="false">IF(OR($L$6+27&lt;$L$4,$L$6+27&gt;$L$5),"",$L$6+27)</f>
+        <f aca="false">IF(OR($O$6+27&lt;$O$4,$O$6+27&gt;$O$5),"",$O$6+27)</f>
         <v>46502</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="12" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="C16" s="13" t="str">
-        <f aca="false">IF(C17="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),1)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(C17="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),1)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C17)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,C17)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C17)=1,IFERROR(INDEX($D$62:$D$101,MATCH(C17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C17)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(C17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C17)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="D16" s="13" t="str">
-        <f aca="false">IF(D17="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),2)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(D17="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),2)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D17)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,D17)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D17)=1,IFERROR(INDEX($D$62:$D$101,MATCH(D17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D17)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(D17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D17)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="E16" s="13" t="str">
-        <f aca="false">IF(E17="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),3)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(E17="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),3)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E17)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,E17)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E17)=1,IFERROR(INDEX($D$62:$D$101,MATCH(E17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E17)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(E17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E17)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="F16" s="13" t="str">
-        <f aca="false">IF(F17="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),4)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(F17="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),4)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F17)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,F17)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F17)=1,IFERROR(INDEX($D$62:$D$101,MATCH(F17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F17)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(F17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F17)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="G16" s="13" t="str">
-        <f aca="false">IF(G17="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),5)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(G17="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),5)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G17)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,G17)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G17)=1,IFERROR(INDEX($D$62:$D$101,MATCH(G17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G17)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(G17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G17)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="H16" s="13" t="str">
-        <f aca="false">IF(H17="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),6)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(H17="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),6)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H17)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,H17)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H17)=1,IFERROR(INDEX($D$62:$D$101,MATCH(H17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H17)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(H17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H17)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="I16" s="13" t="str">
-        <f aca="false">IF(I17="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),7)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(I17="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),7)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I17)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,I17)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I17)=1,IFERROR(INDEX($D$62:$D$101,MATCH(I17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I17)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(I17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I17)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
     </row>
@@ -1916,64 +2044,64 @@
         <v>du 26/04 au 30/04</v>
       </c>
       <c r="C17" s="16" t="n">
-        <f aca="false">IF(OR($L$6+28&lt;$L$4,$L$6+28&gt;$L$5),"",$L$6+28)</f>
+        <f aca="false">IF(OR($O$6+28&lt;$O$4,$O$6+28&gt;$O$5),"",$O$6+28)</f>
         <v>46503</v>
       </c>
       <c r="D17" s="16" t="n">
-        <f aca="false">IF(OR($L$6+29&lt;$L$4,$L$6+29&gt;$L$5),"",$L$6+29)</f>
+        <f aca="false">IF(OR($O$6+29&lt;$O$4,$O$6+29&gt;$O$5),"",$O$6+29)</f>
         <v>46504</v>
       </c>
       <c r="E17" s="16" t="n">
-        <f aca="false">IF(OR($L$6+30&lt;$L$4,$L$6+30&gt;$L$5),"",$L$6+30)</f>
+        <f aca="false">IF(OR($O$6+30&lt;$O$4,$O$6+30&gt;$O$5),"",$O$6+30)</f>
         <v>46505</v>
       </c>
       <c r="F17" s="16" t="n">
-        <f aca="false">IF(OR($L$6+31&lt;$L$4,$L$6+31&gt;$L$5),"",$L$6+31)</f>
+        <f aca="false">IF(OR($O$6+31&lt;$O$4,$O$6+31&gt;$O$5),"",$O$6+31)</f>
         <v>46506</v>
       </c>
       <c r="G17" s="16" t="n">
-        <f aca="false">IF(OR($L$6+32&lt;$L$4,$L$6+32&gt;$L$5),"",$L$6+32)</f>
+        <f aca="false">IF(OR($O$6+32&lt;$O$4,$O$6+32&gt;$O$5),"",$O$6+32)</f>
         <v>46507</v>
       </c>
       <c r="H17" s="16" t="str">
-        <f aca="false">IF(OR($L$6+33&lt;$L$4,$L$6+33&gt;$L$5),"",$L$6+33)</f>
+        <f aca="false">IF(OR($O$6+33&lt;$O$4,$O$6+33&gt;$O$5),"",$O$6+33)</f>
         <v/>
       </c>
       <c r="I17" s="16" t="str">
-        <f aca="false">IF(OR($L$6+34&lt;$L$4,$L$6+34&gt;$L$5),"",$L$6+34)</f>
+        <f aca="false">IF(OR($O$6+34&lt;$O$4,$O$6+34&gt;$O$5),"",$O$6+34)</f>
         <v/>
       </c>
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="12" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C18" s="13" t="str">
-        <f aca="false">IF(C19="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),1)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(C19="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),1)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C19)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,C19)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C19)=1,IFERROR(INDEX($D$62:$D$101,MATCH(C19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C19)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(C19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="D18" s="13" t="str">
-        <f aca="false">IF(D19="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),2)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(D19="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),2)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D19)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,D19)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D19)=1,IFERROR(INDEX($D$62:$D$101,MATCH(D19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D19)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(D19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="E18" s="13" t="str">
-        <f aca="false">IF(E19="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),3)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(E19="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),3)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E19)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,E19)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E19)=1,IFERROR(INDEX($D$62:$D$101,MATCH(E19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E19)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(E19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="F18" s="13" t="str">
-        <f aca="false">IF(F19="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),4)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(F19="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),4)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F19)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,F19)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F19)=1,IFERROR(INDEX($D$62:$D$101,MATCH(F19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F19)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(F19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="G18" s="13" t="str">
-        <f aca="false">IF(G19="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),5)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(G19="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),5)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G19)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,G19)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G19)=1,IFERROR(INDEX($D$62:$D$101,MATCH(G19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G19)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(G19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="H18" s="13" t="str">
-        <f aca="false">IF(H19="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),6)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(H19="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),6)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H19)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,H19)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H19)=1,IFERROR(INDEX($D$62:$D$101,MATCH(H19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H19)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(H19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="I18" s="13" t="str">
-        <f aca="false">IF(I19="","",IFERROR(IF(INDEX($D$43:$J$54,MATCH($C$5,$B$43:$B$54,0),7)=1,INDEX($C$43:$C$54,MATCH($C$5,$B$43:$B$54,0)),""),""))</f>
+        <f aca="false">IF(I19="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),7)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I19)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,I19)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I19)=1,IFERROR(INDEX($D$62:$D$101,MATCH(I19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I19)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(I19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
     </row>
@@ -1983,1182 +2111,1946 @@
         <v/>
       </c>
       <c r="C19" s="16" t="str">
-        <f aca="false">IF(OR($L$6+35&lt;$L$4,$L$6+35&gt;$L$5),"",$L$6+35)</f>
+        <f aca="false">IF(OR($O$6+35&lt;$O$4,$O$6+35&gt;$O$5),"",$O$6+35)</f>
         <v/>
       </c>
       <c r="D19" s="16" t="str">
-        <f aca="false">IF(OR($L$6+36&lt;$L$4,$L$6+36&gt;$L$5),"",$L$6+36)</f>
+        <f aca="false">IF(OR($O$6+36&lt;$O$4,$O$6+36&gt;$O$5),"",$O$6+36)</f>
         <v/>
       </c>
       <c r="E19" s="16" t="str">
-        <f aca="false">IF(OR($L$6+37&lt;$L$4,$L$6+37&gt;$L$5),"",$L$6+37)</f>
+        <f aca="false">IF(OR($O$6+37&lt;$O$4,$O$6+37&gt;$O$5),"",$O$6+37)</f>
         <v/>
       </c>
       <c r="F19" s="16" t="str">
-        <f aca="false">IF(OR($L$6+38&lt;$L$4,$L$6+38&gt;$L$5),"",$L$6+38)</f>
+        <f aca="false">IF(OR($O$6+38&lt;$O$4,$O$6+38&gt;$O$5),"",$O$6+38)</f>
         <v/>
       </c>
       <c r="G19" s="16" t="str">
-        <f aca="false">IF(OR($L$6+39&lt;$L$4,$L$6+39&gt;$L$5),"",$L$6+39)</f>
+        <f aca="false">IF(OR($O$6+39&lt;$O$4,$O$6+39&gt;$O$5),"",$O$6+39)</f>
         <v/>
       </c>
       <c r="H19" s="16" t="str">
-        <f aca="false">IF(OR($L$6+40&lt;$L$4,$L$6+40&gt;$L$5),"",$L$6+40)</f>
+        <f aca="false">IF(OR($O$6+40&lt;$O$4,$O$6+40&gt;$O$5),"",$O$6+40)</f>
         <v/>
       </c>
       <c r="I19" s="16" t="str">
-        <f aca="false">IF(OR($L$6+41&lt;$L$4,$L$6+41&gt;$L$5),"",$L$6+41)</f>
+        <f aca="false">IF(OR($O$6+41&lt;$O$4,$O$6+41&gt;$O$5),"",$O$6+41)</f>
         <v/>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="17" t="s">
-        <v>29</v>
-      </c>
-      <c r="C20" s="18" t="n">
+      <c r="B20" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="C20" s="19" t="n">
         <f aca="false">COUNT(C9,C11,C13,C15,C17,C19)</f>
         <v>4</v>
       </c>
-      <c r="D20" s="18" t="n">
+      <c r="D20" s="19" t="n">
         <f aca="false">COUNT(D9,D11,D13,D15,D17,D19)</f>
         <v>4</v>
       </c>
-      <c r="E20" s="18" t="n">
+      <c r="E20" s="19" t="n">
         <f aca="false">COUNT(E9,E11,E13,E15,E17,E19)</f>
         <v>4</v>
       </c>
-      <c r="F20" s="18" t="n">
+      <c r="F20" s="19" t="n">
         <f aca="false">COUNT(F9,F11,F13,F15,F17,F19)</f>
         <v>5</v>
       </c>
-      <c r="G20" s="18" t="n">
+      <c r="G20" s="19" t="n">
         <f aca="false">COUNT(G9,G11,G13,G15,G17,G19)</f>
         <v>5</v>
       </c>
-      <c r="H20" s="18" t="n">
+      <c r="H20" s="19" t="n">
         <f aca="false">COUNT(H9,H11,H13,H15,H17,H19)</f>
         <v>4</v>
       </c>
-      <c r="I20" s="18" t="n">
+      <c r="I20" s="19" t="n">
         <f aca="false">COUNT(I9,I11,I13,I15,I17,I19)</f>
         <v>4</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="17" t="s">
-        <v>30</v>
-      </c>
-      <c r="C21" s="18" t="n">
+      <c r="B21" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="C21" s="19" t="n">
         <f aca="false">IF(COUNT(C9:I9)&gt;0,1,0)+IF(COUNT(C11:I11)&gt;0,1,0)+IF(COUNT(C13:I13)&gt;0,1,0)+IF(COUNT(C15:I15)&gt;0,1,0)+IF(COUNT(C17:I17)&gt;0,1,0)+IF(COUNT(C19:I19)&gt;0,1,0)</f>
         <v>5</v>
       </c>
-      <c r="D21" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="G21" s="19"/>
-      <c r="H21" s="19"/>
-      <c r="I21" s="19"/>
+      <c r="D21" s="20" t="s">
+        <v>33</v>
+      </c>
+      <c r="E21" s="20"/>
+      <c r="F21" s="20"/>
+      <c r="G21" s="20"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="20"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
       <c r="E23" s="9"/>
       <c r="F23" s="9"/>
       <c r="G23" s="9"/>
-    </row>
-    <row r="24" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="C24" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="D24" s="20" t="s">
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
+      <c r="K23" s="9"/>
+      <c r="L23" s="9"/>
+    </row>
+    <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="21" t="s">
         <v>35</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="C24" s="21" t="s">
+        <v>21</v>
+      </c>
+      <c r="D24" s="21" t="s">
         <v>36</v>
       </c>
-      <c r="F24" s="20" t="s">
+      <c r="E24" s="21" t="s">
         <v>37</v>
       </c>
-      <c r="G24" s="20" t="s">
+      <c r="F24" s="21" t="s">
         <v>38</v>
       </c>
+      <c r="G24" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="H24" s="21" t="s">
+        <v>40</v>
+      </c>
+      <c r="I24" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="J24" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="K24" s="21" t="s">
+        <v>43</v>
+      </c>
+      <c r="L24" s="21" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="21" t="str">
-        <f aca="false">$B$43</f>
+      <c r="B25" s="22" t="str">
+        <f aca="false">$B$45</f>
         <v>CDGRUN</v>
       </c>
-      <c r="C25" s="22" t="str">
-        <f aca="false">$C$43</f>
-        <v>77W</v>
-      </c>
-      <c r="D25" s="22" t="str">
-        <f aca="false">IF(SUM($D$43:$J$43)=0,"aucune operation",SUBSTITUTE(TRIM(IF($D$43=1,"J1 ","")&amp;IF($E$43=1,"J2 ","")&amp;IF($F$43=1,"J3 ","")&amp;IF($G$43=1,"J4 ","")&amp;IF($H$43=1,"J5 ","")&amp;IF($I$43=1,"J6 ","")&amp;IF($J$43=1,"J7 ",""))," ",", "))</f>
+      <c r="C25" s="23" t="str">
+        <f aca="false">$K$45</f>
+        <v>77W(4), 778(3)</v>
+      </c>
+      <c r="D25" s="23" t="str">
+        <f aca="false">IF(COUNTA($C$45:$I$45)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$45&lt;&gt;"","J1 ","")&amp;IF($D$45&lt;&gt;"","J2 ","")&amp;IF($E$45&lt;&gt;"","J3 ","")&amp;IF($F$45&lt;&gt;"","J4 ","")&amp;IF($G$45&lt;&gt;"","J5 ","")&amp;IF($H$45&lt;&gt;"","J6 ","")&amp;IF($I$45&lt;&gt;"","J7 ",""))," ",", "))</f>
         <v>J1, J2, J3, J4, J5, J6, J7</v>
       </c>
-      <c r="E25" s="23" t="n">
-        <f aca="false">SUM($D$43:$J$43)</f>
+      <c r="E25" s="24" t="n">
+        <f aca="false">$J$45</f>
         <v>7</v>
       </c>
-      <c r="F25" s="23" t="n">
+      <c r="F25" s="24" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G25" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,$D$43:$J$43)</f>
+      <c r="G25" s="25" t="n">
+        <f aca="false">H25+I25</f>
+        <v>32</v>
+      </c>
+      <c r="H25" s="24" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45&lt;&gt;""))</f>
         <v>30</v>
       </c>
+      <c r="I25" s="24" t="n">
+        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B25,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>2</v>
+      </c>
+      <c r="J25" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B25,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>17</v>
+      </c>
+      <c r="K25" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B25,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>15</v>
+      </c>
+      <c r="L25" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B25,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="21" t="str">
-        <f aca="false">$B$44</f>
+      <c r="B26" s="22" t="str">
+        <f aca="false">$B$46</f>
         <v>CDGDZA</v>
       </c>
-      <c r="C26" s="22" t="str">
-        <f aca="false">$C$44</f>
-        <v>778</v>
-      </c>
-      <c r="D26" s="22" t="str">
-        <f aca="false">IF(SUM($D$44:$J$44)=0,"aucune operation",SUBSTITUTE(TRIM(IF($D$44=1,"J1 ","")&amp;IF($E$44=1,"J2 ","")&amp;IF($F$44=1,"J3 ","")&amp;IF($G$44=1,"J4 ","")&amp;IF($H$44=1,"J5 ","")&amp;IF($I$44=1,"J6 ","")&amp;IF($J$44=1,"J7 ",""))," ",", "))</f>
+      <c r="C26" s="23" t="str">
+        <f aca="false">$K$46</f>
+        <v>77W(1), 778(2)</v>
+      </c>
+      <c r="D26" s="23" t="str">
+        <f aca="false">IF(COUNTA($C$46:$I$46)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$46&lt;&gt;"","J1 ","")&amp;IF($D$46&lt;&gt;"","J2 ","")&amp;IF($E$46&lt;&gt;"","J3 ","")&amp;IF($F$46&lt;&gt;"","J4 ","")&amp;IF($G$46&lt;&gt;"","J5 ","")&amp;IF($H$46&lt;&gt;"","J6 ","")&amp;IF($I$46&lt;&gt;"","J7 ",""))," ",", "))</f>
         <v>J2, J5, J7</v>
       </c>
-      <c r="E26" s="23" t="n">
-        <f aca="false">SUM($D$44:$J$44)</f>
+      <c r="E26" s="24" t="n">
+        <f aca="false">$J$46</f>
         <v>3</v>
       </c>
-      <c r="F26" s="23" t="n">
+      <c r="F26" s="24" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G26" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,$D$44:$J$44)</f>
+      <c r="G26" s="25" t="n">
+        <f aca="false">H26+I26</f>
         <v>13</v>
       </c>
+      <c r="H26" s="24" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$46:$I$46&lt;&gt;""))</f>
+        <v>13</v>
+      </c>
+      <c r="I26" s="24" t="n">
+        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B26,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="J26" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$46:$I$46="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B26,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>4</v>
+      </c>
+      <c r="K26" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$46:$I$46="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B26,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>9</v>
+      </c>
+      <c r="L26" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$46:$I$46="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B26,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="21" t="str">
-        <f aca="false">$B$45</f>
+      <c r="B27" s="22" t="str">
+        <f aca="false">$B$47</f>
         <v>BKKRUN</v>
       </c>
-      <c r="C27" s="22" t="str">
-        <f aca="false">$C$45</f>
-        <v>778</v>
-      </c>
-      <c r="D27" s="22" t="str">
-        <f aca="false">IF(SUM($D$45:$J$45)=0,"aucune operation",SUBSTITUTE(TRIM(IF($D$45=1,"J1 ","")&amp;IF($E$45=1,"J2 ","")&amp;IF($F$45=1,"J3 ","")&amp;IF($G$45=1,"J4 ","")&amp;IF($H$45=1,"J5 ","")&amp;IF($I$45=1,"J6 ","")&amp;IF($J$45=1,"J7 ",""))," ",", "))</f>
+      <c r="C27" s="23" t="str">
+        <f aca="false">$K$47</f>
+        <v>778(2)</v>
+      </c>
+      <c r="D27" s="23" t="str">
+        <f aca="false">IF(COUNTA($C$47:$I$47)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$47&lt;&gt;"","J1 ","")&amp;IF($D$47&lt;&gt;"","J2 ","")&amp;IF($E$47&lt;&gt;"","J3 ","")&amp;IF($F$47&lt;&gt;"","J4 ","")&amp;IF($G$47&lt;&gt;"","J5 ","")&amp;IF($H$47&lt;&gt;"","J6 ","")&amp;IF($I$47&lt;&gt;"","J7 ",""))," ",", "))</f>
         <v>J3, J6</v>
       </c>
-      <c r="E27" s="23" t="n">
-        <f aca="false">SUM($D$45:$J$45)</f>
+      <c r="E27" s="24" t="n">
+        <f aca="false">$J$47</f>
         <v>2</v>
       </c>
-      <c r="F27" s="23" t="n">
+      <c r="F27" s="24" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G27" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,$D$45:$J$45)</f>
+      <c r="G27" s="25" t="n">
+        <f aca="false">H27+I27</f>
         <v>8</v>
       </c>
+      <c r="H27" s="24" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$47:$I$47&lt;&gt;""))</f>
+        <v>8</v>
+      </c>
+      <c r="I27" s="24" t="n">
+        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B27,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="J27" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$47:$I$47="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B27,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="K27" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$47:$I$47="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B27,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>8</v>
+      </c>
+      <c r="L27" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$47:$I$47="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B27,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="21" t="str">
-        <f aca="false">$B$46</f>
+      <c r="B28" s="22" t="str">
+        <f aca="false">$B$48</f>
         <v>DZARUN</v>
       </c>
-      <c r="C28" s="22" t="str">
-        <f aca="false">$C$46</f>
-        <v>A320</v>
-      </c>
-      <c r="D28" s="22" t="str">
-        <f aca="false">IF(SUM($D$46:$J$46)=0,"aucune operation",SUBSTITUTE(TRIM(IF($D$46=1,"J1 ","")&amp;IF($E$46=1,"J2 ","")&amp;IF($F$46=1,"J3 ","")&amp;IF($G$46=1,"J4 ","")&amp;IF($H$46=1,"J5 ","")&amp;IF($I$46=1,"J6 ","")&amp;IF($J$46=1,"J7 ",""))," ",", "))</f>
+      <c r="C28" s="23" t="str">
+        <f aca="false">$K$48</f>
+        <v>A320(5)</v>
+      </c>
+      <c r="D28" s="23" t="str">
+        <f aca="false">IF(COUNTA($C$48:$I$48)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$48&lt;&gt;"","J1 ","")&amp;IF($D$48&lt;&gt;"","J2 ","")&amp;IF($E$48&lt;&gt;"","J3 ","")&amp;IF($F$48&lt;&gt;"","J4 ","")&amp;IF($G$48&lt;&gt;"","J5 ","")&amp;IF($H$48&lt;&gt;"","J6 ","")&amp;IF($I$48&lt;&gt;"","J7 ",""))," ",", "))</f>
         <v>J1, J2, J3, J4, J5</v>
       </c>
-      <c r="E28" s="23" t="n">
-        <f aca="false">SUM($D$46:$J$46)</f>
+      <c r="E28" s="24" t="n">
+        <f aca="false">$J$48</f>
         <v>5</v>
       </c>
-      <c r="F28" s="23" t="n">
+      <c r="F28" s="24" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G28" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,$D$46:$J$46)</f>
+      <c r="G28" s="25" t="n">
+        <f aca="false">H28+I28</f>
         <v>22</v>
       </c>
+      <c r="H28" s="24" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$48:$I$48&lt;&gt;""))</f>
+        <v>22</v>
+      </c>
+      <c r="I28" s="24" t="n">
+        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B28,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$48:$I$48="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B28,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$48:$I$48="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B28,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="L28" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$48:$I$48="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B28,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>22</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="21" t="str">
-        <f aca="false">$B$47</f>
+      <c r="B29" s="22" t="str">
+        <f aca="false">$B$49</f>
         <v>MRURUN</v>
       </c>
-      <c r="C29" s="22" t="str">
-        <f aca="false">$C$47</f>
-        <v>A320</v>
-      </c>
-      <c r="D29" s="22" t="str">
-        <f aca="false">IF(SUM($D$47:$J$47)=0,"aucune operation",SUBSTITUTE(TRIM(IF($D$47=1,"J1 ","")&amp;IF($E$47=1,"J2 ","")&amp;IF($F$47=1,"J3 ","")&amp;IF($G$47=1,"J4 ","")&amp;IF($H$47=1,"J5 ","")&amp;IF($I$47=1,"J6 ","")&amp;IF($J$47=1,"J7 ",""))," ",", "))</f>
+      <c r="C29" s="23" t="str">
+        <f aca="false">$K$49</f>
+        <v>A320(4)</v>
+      </c>
+      <c r="D29" s="23" t="str">
+        <f aca="false">IF(COUNTA($C$49:$I$49)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$49&lt;&gt;"","J1 ","")&amp;IF($D$49&lt;&gt;"","J2 ","")&amp;IF($E$49&lt;&gt;"","J3 ","")&amp;IF($F$49&lt;&gt;"","J4 ","")&amp;IF($G$49&lt;&gt;"","J5 ","")&amp;IF($H$49&lt;&gt;"","J6 ","")&amp;IF($I$49&lt;&gt;"","J7 ",""))," ",", "))</f>
         <v>J1, J3, J5, J7</v>
       </c>
-      <c r="E29" s="23" t="n">
-        <f aca="false">SUM($D$47:$J$47)</f>
+      <c r="E29" s="24" t="n">
+        <f aca="false">$J$49</f>
         <v>4</v>
       </c>
-      <c r="F29" s="23" t="n">
+      <c r="F29" s="24" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G29" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,$D$47:$J$47)</f>
+      <c r="G29" s="25" t="n">
+        <f aca="false">H29+I29</f>
         <v>17</v>
       </c>
+      <c r="H29" s="24" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$49:$I$49&lt;&gt;""))</f>
+        <v>17</v>
+      </c>
+      <c r="I29" s="24" t="n">
+        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B29,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="J29" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$49:$I$49="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B29,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="K29" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$49:$I$49="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B29,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="L29" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$49:$I$49="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B29,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>17</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="21" t="str">
-        <f aca="false">$B$48</f>
+      <c r="B30" s="22" t="str">
+        <f aca="false">$B$50</f>
         <v>NOSRUN</v>
       </c>
-      <c r="C30" s="22" t="str">
-        <f aca="false">$C$48</f>
-        <v>A320</v>
-      </c>
-      <c r="D30" s="22" t="str">
-        <f aca="false">IF(SUM($D$48:$J$48)=0,"aucune operation",SUBSTITUTE(TRIM(IF($D$48=1,"J1 ","")&amp;IF($E$48=1,"J2 ","")&amp;IF($F$48=1,"J3 ","")&amp;IF($G$48=1,"J4 ","")&amp;IF($H$48=1,"J5 ","")&amp;IF($I$48=1,"J6 ","")&amp;IF($J$48=1,"J7 ",""))," ",", "))</f>
+      <c r="C30" s="23" t="str">
+        <f aca="false">$K$50</f>
+        <v>A320(3)</v>
+      </c>
+      <c r="D30" s="23" t="str">
+        <f aca="false">IF(COUNTA($C$50:$I$50)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$50&lt;&gt;"","J1 ","")&amp;IF($D$50&lt;&gt;"","J2 ","")&amp;IF($E$50&lt;&gt;"","J3 ","")&amp;IF($F$50&lt;&gt;"","J4 ","")&amp;IF($G$50&lt;&gt;"","J5 ","")&amp;IF($H$50&lt;&gt;"","J6 ","")&amp;IF($I$50&lt;&gt;"","J7 ",""))," ",", "))</f>
         <v>J1, J4, J6</v>
       </c>
-      <c r="E30" s="23" t="n">
-        <f aca="false">SUM($D$48:$J$48)</f>
+      <c r="E30" s="24" t="n">
+        <f aca="false">$J$50</f>
         <v>3</v>
       </c>
-      <c r="F30" s="23" t="n">
+      <c r="F30" s="24" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G30" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,$D$48:$J$48)</f>
+      <c r="G30" s="25" t="n">
+        <f aca="false">H30+I30</f>
+        <v>15</v>
+      </c>
+      <c r="H30" s="24" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$50:$I$50&lt;&gt;""))</f>
         <v>13</v>
       </c>
+      <c r="I30" s="24" t="n">
+        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B30,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>2</v>
+      </c>
+      <c r="J30" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$50:$I$50="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B30,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="K30" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$50:$I$50="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B30,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="L30" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$50:$I$50="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B30,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>15</v>
+      </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="21" t="str">
-        <f aca="false">$B$49</f>
+      <c r="B31" s="22" t="str">
+        <f aca="false">$B$51</f>
         <v>RUNTNR</v>
       </c>
-      <c r="C31" s="22" t="str">
-        <f aca="false">$C$49</f>
-        <v>A320</v>
-      </c>
-      <c r="D31" s="22" t="str">
-        <f aca="false">IF(SUM($D$49:$J$49)=0,"aucune operation",SUBSTITUTE(TRIM(IF($D$49=1,"J1 ","")&amp;IF($E$49=1,"J2 ","")&amp;IF($F$49=1,"J3 ","")&amp;IF($G$49=1,"J4 ","")&amp;IF($H$49=1,"J5 ","")&amp;IF($I$49=1,"J6 ","")&amp;IF($J$49=1,"J7 ",""))," ",", "))</f>
+      <c r="C31" s="23" t="str">
+        <f aca="false">$K$51</f>
+        <v>A320(3)</v>
+      </c>
+      <c r="D31" s="23" t="str">
+        <f aca="false">IF(COUNTA($C$51:$I$51)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$51&lt;&gt;"","J1 ","")&amp;IF($D$51&lt;&gt;"","J2 ","")&amp;IF($E$51&lt;&gt;"","J3 ","")&amp;IF($F$51&lt;&gt;"","J4 ","")&amp;IF($G$51&lt;&gt;"","J5 ","")&amp;IF($H$51&lt;&gt;"","J6 ","")&amp;IF($I$51&lt;&gt;"","J7 ",""))," ",", "))</f>
         <v>J2, J4, J6</v>
       </c>
-      <c r="E31" s="23" t="n">
-        <f aca="false">SUM($D$49:$J$49)</f>
+      <c r="E31" s="24" t="n">
+        <f aca="false">$J$51</f>
         <v>3</v>
       </c>
-      <c r="F31" s="23" t="n">
+      <c r="F31" s="24" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G31" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,$D$49:$J$49)</f>
+      <c r="G31" s="25" t="n">
+        <f aca="false">H31+I31</f>
         <v>13</v>
       </c>
+      <c r="H31" s="24" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51&lt;&gt;""))</f>
+        <v>13</v>
+      </c>
+      <c r="I31" s="24" t="n">
+        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B31,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="J31" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B31,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="K31" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B31,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="L31" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B31,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>13</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="21" t="str">
-        <f aca="false">$B$50</f>
+      <c r="B32" s="22" t="str">
+        <f aca="false">$B$52</f>
         <v>JNBRUN</v>
       </c>
-      <c r="C32" s="22" t="str">
-        <f aca="false">$C$50</f>
-        <v>778</v>
-      </c>
-      <c r="D32" s="22" t="str">
-        <f aca="false">IF(SUM($D$50:$J$50)=0,"aucune operation",SUBSTITUTE(TRIM(IF($D$50=1,"J1 ","")&amp;IF($E$50=1,"J2 ","")&amp;IF($F$50=1,"J3 ","")&amp;IF($G$50=1,"J4 ","")&amp;IF($H$50=1,"J5 ","")&amp;IF($I$50=1,"J6 ","")&amp;IF($J$50=1,"J7 ",""))," ",", "))</f>
+      <c r="C32" s="23" t="str">
+        <f aca="false">$K$52</f>
+        <v>778(2)</v>
+      </c>
+      <c r="D32" s="23" t="str">
+        <f aca="false">IF(COUNTA($C$52:$I$52)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$52&lt;&gt;"","J1 ","")&amp;IF($D$52&lt;&gt;"","J2 ","")&amp;IF($E$52&lt;&gt;"","J3 ","")&amp;IF($F$52&lt;&gt;"","J4 ","")&amp;IF($G$52&lt;&gt;"","J5 ","")&amp;IF($H$52&lt;&gt;"","J6 ","")&amp;IF($I$52&lt;&gt;"","J7 ",""))," ",", "))</f>
         <v>J1, J5</v>
       </c>
-      <c r="E32" s="23" t="n">
-        <f aca="false">SUM($D$50:$J$50)</f>
+      <c r="E32" s="24" t="n">
+        <f aca="false">$J$52</f>
         <v>2</v>
       </c>
-      <c r="F32" s="23" t="n">
+      <c r="F32" s="24" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G32" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,$D$50:$J$50)</f>
+      <c r="G32" s="25" t="n">
+        <f aca="false">H32+I32</f>
         <v>9</v>
       </c>
+      <c r="H32" s="24" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$52:$I$52&lt;&gt;""))</f>
+        <v>9</v>
+      </c>
+      <c r="I32" s="24" t="n">
+        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B32,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="J32" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$52:$I$52="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B32,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="K32" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$52:$I$52="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B32,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>9</v>
+      </c>
+      <c r="L32" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$52:$I$52="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B32,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="21" t="str">
-        <f aca="false">$B$51</f>
+      <c r="B33" s="22" t="str">
+        <f aca="false">$B$53</f>
         <v>CPTRUN</v>
       </c>
-      <c r="C33" s="22" t="str">
-        <f aca="false">$C$51</f>
-        <v>778</v>
-      </c>
-      <c r="D33" s="22" t="str">
-        <f aca="false">IF(SUM($D$51:$J$51)=0,"aucune operation",SUBSTITUTE(TRIM(IF($D$51=1,"J1 ","")&amp;IF($E$51=1,"J2 ","")&amp;IF($F$51=1,"J3 ","")&amp;IF($G$51=1,"J4 ","")&amp;IF($H$51=1,"J5 ","")&amp;IF($I$51=1,"J6 ","")&amp;IF($J$51=1,"J7 ",""))," ",", "))</f>
+      <c r="C33" s="23" t="str">
+        <f aca="false">$K$53</f>
+        <v>778(1)</v>
+      </c>
+      <c r="D33" s="23" t="str">
+        <f aca="false">IF(COUNTA($C$53:$I$53)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$53&lt;&gt;"","J1 ","")&amp;IF($D$53&lt;&gt;"","J2 ","")&amp;IF($E$53&lt;&gt;"","J3 ","")&amp;IF($F$53&lt;&gt;"","J4 ","")&amp;IF($G$53&lt;&gt;"","J5 ","")&amp;IF($H$53&lt;&gt;"","J6 ","")&amp;IF($I$53&lt;&gt;"","J7 ",""))," ",", "))</f>
         <v>J4</v>
       </c>
-      <c r="E33" s="23" t="n">
-        <f aca="false">SUM($D$51:$J$51)</f>
+      <c r="E33" s="24" t="n">
+        <f aca="false">$J$53</f>
         <v>1</v>
       </c>
-      <c r="F33" s="23" t="n">
+      <c r="F33" s="24" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G33" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,$D$51:$J$51)</f>
+      <c r="G33" s="25" t="n">
+        <f aca="false">H33+I33</f>
         <v>5</v>
       </c>
+      <c r="H33" s="24" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$53:$I$53&lt;&gt;""))</f>
+        <v>5</v>
+      </c>
+      <c r="I33" s="24" t="n">
+        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B33,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="J33" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$53:$I$53="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B33,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="K33" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$53:$I$53="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B33,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>5</v>
+      </c>
+      <c r="L33" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$53:$I$53="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B33,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="21" t="str">
-        <f aca="false">$B$52</f>
+      <c r="B34" s="22" t="str">
+        <f aca="false">$B$54</f>
         <v>DIERUN</v>
       </c>
-      <c r="C34" s="22" t="str">
-        <f aca="false">$C$52</f>
-        <v>A320</v>
-      </c>
-      <c r="D34" s="22" t="str">
-        <f aca="false">IF(SUM($D$52:$J$52)=0,"aucune operation",SUBSTITUTE(TRIM(IF($D$52=1,"J1 ","")&amp;IF($E$52=1,"J2 ","")&amp;IF($F$52=1,"J3 ","")&amp;IF($G$52=1,"J4 ","")&amp;IF($H$52=1,"J5 ","")&amp;IF($I$52=1,"J6 ","")&amp;IF($J$52=1,"J7 ",""))," ",", "))</f>
+      <c r="C34" s="23" t="str">
+        <f aca="false">$K$54</f>
+        <v>A320(2)</v>
+      </c>
+      <c r="D34" s="23" t="str">
+        <f aca="false">IF(COUNTA($C$54:$I$54)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$54&lt;&gt;"","J1 ","")&amp;IF($D$54&lt;&gt;"","J2 ","")&amp;IF($E$54&lt;&gt;"","J3 ","")&amp;IF($F$54&lt;&gt;"","J4 ","")&amp;IF($G$54&lt;&gt;"","J5 ","")&amp;IF($H$54&lt;&gt;"","J6 ","")&amp;IF($I$54&lt;&gt;"","J7 ",""))," ",", "))</f>
         <v>J2, J6</v>
       </c>
-      <c r="E34" s="23" t="n">
-        <f aca="false">SUM($D$52:$J$52)</f>
+      <c r="E34" s="24" t="n">
+        <f aca="false">$J$54</f>
         <v>2</v>
       </c>
-      <c r="F34" s="23" t="n">
+      <c r="F34" s="24" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G34" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,$D$52:$J$52)</f>
+      <c r="G34" s="25" t="n">
+        <f aca="false">H34+I34</f>
         <v>8</v>
       </c>
+      <c r="H34" s="24" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$54:$I$54&lt;&gt;""))</f>
+        <v>8</v>
+      </c>
+      <c r="I34" s="24" t="n">
+        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B34,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="J34" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$54:$I$54="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B34,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="K34" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$54:$I$54="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B34,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="L34" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$54:$I$54="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B34,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="21" t="str">
-        <f aca="false">$B$53</f>
+      <c r="B35" s="22" t="str">
+        <f aca="false">$B$55</f>
         <v>RRGRUN</v>
       </c>
-      <c r="C35" s="22" t="str">
-        <f aca="false">$C$53</f>
-        <v>A320</v>
-      </c>
-      <c r="D35" s="22" t="str">
-        <f aca="false">IF(SUM($D$53:$J$53)=0,"aucune operation",SUBSTITUTE(TRIM(IF($D$53=1,"J1 ","")&amp;IF($E$53=1,"J2 ","")&amp;IF($F$53=1,"J3 ","")&amp;IF($G$53=1,"J4 ","")&amp;IF($H$53=1,"J5 ","")&amp;IF($I$53=1,"J6 ","")&amp;IF($J$53=1,"J7 ",""))," ",", "))</f>
+      <c r="C35" s="23" t="str">
+        <f aca="false">$K$55</f>
+        <v>A320(6)</v>
+      </c>
+      <c r="D35" s="23" t="str">
+        <f aca="false">IF(COUNTA($C$55:$I$55)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$55&lt;&gt;"","J1 ","")&amp;IF($D$55&lt;&gt;"","J2 ","")&amp;IF($E$55&lt;&gt;"","J3 ","")&amp;IF($F$55&lt;&gt;"","J4 ","")&amp;IF($G$55&lt;&gt;"","J5 ","")&amp;IF($H$55&lt;&gt;"","J6 ","")&amp;IF($I$55&lt;&gt;"","J7 ",""))," ",", "))</f>
         <v>J1, J2, J3, J4, J5, J6</v>
       </c>
-      <c r="E35" s="23" t="n">
-        <f aca="false">SUM($D$53:$J$53)</f>
+      <c r="E35" s="24" t="n">
+        <f aca="false">$J$55</f>
         <v>6</v>
       </c>
-      <c r="F35" s="23" t="n">
+      <c r="F35" s="24" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G35" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,$D$53:$J$53)</f>
+      <c r="G35" s="25" t="n">
+        <f aca="false">H35+I35</f>
         <v>26</v>
       </c>
+      <c r="H35" s="24" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$55:$I$55&lt;&gt;""))</f>
+        <v>26</v>
+      </c>
+      <c r="I35" s="24" t="n">
+        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B35,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="J35" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$55:$I$55="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B35,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="K35" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$55:$I$55="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B35,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="L35" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$55:$I$55="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B35,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>26</v>
+      </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="21" t="str">
-        <f aca="false">$B$54</f>
+      <c r="B36" s="22" t="str">
+        <f aca="false">$B$56</f>
         <v>TMMRUN</v>
       </c>
-      <c r="C36" s="22" t="str">
-        <f aca="false">$C$54</f>
-        <v>A320</v>
-      </c>
-      <c r="D36" s="22" t="str">
-        <f aca="false">IF(SUM($D$54:$J$54)=0,"aucune operation",SUBSTITUTE(TRIM(IF($D$54=1,"J1 ","")&amp;IF($E$54=1,"J2 ","")&amp;IF($F$54=1,"J3 ","")&amp;IF($G$54=1,"J4 ","")&amp;IF($H$54=1,"J5 ","")&amp;IF($I$54=1,"J6 ","")&amp;IF($J$54=1,"J7 ",""))," ",", "))</f>
+      <c r="C36" s="23" t="str">
+        <f aca="false">$K$56</f>
+        <v>A320(2)</v>
+      </c>
+      <c r="D36" s="23" t="str">
+        <f aca="false">IF(COUNTA($C$56:$I$56)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$56&lt;&gt;"","J1 ","")&amp;IF($D$56&lt;&gt;"","J2 ","")&amp;IF($E$56&lt;&gt;"","J3 ","")&amp;IF($F$56&lt;&gt;"","J4 ","")&amp;IF($G$56&lt;&gt;"","J5 ","")&amp;IF($H$56&lt;&gt;"","J6 ","")&amp;IF($I$56&lt;&gt;"","J7 ",""))," ",", "))</f>
         <v>J3, J7</v>
       </c>
-      <c r="E36" s="23" t="n">
-        <f aca="false">SUM($D$54:$J$54)</f>
+      <c r="E36" s="24" t="n">
+        <f aca="false">$J$56</f>
         <v>2</v>
       </c>
-      <c r="F36" s="23" t="n">
+      <c r="F36" s="24" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G36" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,$D$54:$J$54)</f>
+      <c r="G36" s="25" t="n">
+        <f aca="false">H36+I36</f>
         <v>8</v>
       </c>
+      <c r="H36" s="24" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$56:$I$56&lt;&gt;""))</f>
+        <v>8</v>
+      </c>
+      <c r="I36" s="24" t="n">
+        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B36,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="J36" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$56:$I$56="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B36,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="K36" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$56:$I$56="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B36,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="L36" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$56:$I$56="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B36,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>8</v>
+      </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="25" t="s">
-        <v>39</v>
-      </c>
-      <c r="C37" s="26"/>
-      <c r="D37" s="26"/>
-      <c r="E37" s="27" t="n">
+      <c r="B37" s="27" t="s">
+        <v>45</v>
+      </c>
+      <c r="C37" s="28"/>
+      <c r="D37" s="28"/>
+      <c r="E37" s="29" t="n">
         <f aca="false">SUM(E25:E36)</f>
         <v>40</v>
       </c>
-      <c r="F37" s="27" t="n">
+      <c r="F37" s="29" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G37" s="28" t="n">
+      <c r="G37" s="30" t="n">
         <f aca="false">SUM(G25:G36)</f>
+        <v>176</v>
+      </c>
+      <c r="H37" s="29" t="n">
+        <f aca="false">SUM(H25:H36)</f>
         <v>172</v>
       </c>
-    </row>
-    <row r="38" customFormat="false" ht="25.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="29" t="s">
-        <v>40</v>
-      </c>
-      <c r="C38" s="29"/>
-      <c r="D38" s="29"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B40" s="30" t="s">
-        <v>41</v>
-      </c>
-      <c r="C40" s="30"/>
-      <c r="D40" s="30"/>
-      <c r="E40" s="30"/>
-      <c r="F40" s="30"/>
-      <c r="G40" s="30"/>
-      <c r="H40" s="30"/>
-      <c r="I40" s="30"/>
-      <c r="J40" s="30"/>
-      <c r="K40" s="30"/>
-      <c r="L40" s="30"/>
-      <c r="M40" s="30"/>
-      <c r="N40" s="30"/>
-      <c r="O40" s="30"/>
-      <c r="P40" s="30"/>
-    </row>
-    <row r="41" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B41" s="31" t="s">
-        <v>42</v>
-      </c>
-      <c r="C41" s="31"/>
-      <c r="D41" s="31"/>
-      <c r="E41" s="31"/>
-      <c r="F41" s="31"/>
-      <c r="G41" s="31"/>
-      <c r="H41" s="31"/>
-      <c r="I41" s="31"/>
-      <c r="J41" s="31"/>
-      <c r="K41" s="31"/>
-      <c r="L41" s="31"/>
-      <c r="M41" s="31"/>
-      <c r="N41" s="31"/>
-      <c r="O41" s="31"/>
-      <c r="P41" s="31"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B42" s="32" t="s">
-        <v>33</v>
-      </c>
-      <c r="C42" s="32" t="s">
-        <v>34</v>
-      </c>
-      <c r="D42" s="32" t="s">
-        <v>43</v>
-      </c>
-      <c r="E42" s="32" t="s">
-        <v>44</v>
-      </c>
-      <c r="F42" s="32" t="s">
-        <v>45</v>
-      </c>
-      <c r="G42" s="32" t="s">
+      <c r="I37" s="29" t="n">
+        <f aca="false">SUM(I25:I36)</f>
+        <v>4</v>
+      </c>
+      <c r="J37" s="29" t="n">
+        <f aca="false">SUM(J25:J36)</f>
+        <v>21</v>
+      </c>
+      <c r="K37" s="29" t="n">
+        <f aca="false">SUM(K25:K36)</f>
         <v>46</v>
       </c>
-      <c r="H42" s="32" t="s">
+      <c r="L37" s="29" t="n">
+        <f aca="false">SUM(L25:L36)</f>
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B38" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C38" s="31"/>
+      <c r="D38" s="31"/>
+      <c r="E38" s="31"/>
+      <c r="F38" s="31"/>
+      <c r="G38" s="31"/>
+      <c r="H38" s="31"/>
+      <c r="I38" s="31"/>
+      <c r="J38" s="31"/>
+      <c r="K38" s="31"/>
+      <c r="L38" s="31"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B39" s="31"/>
+      <c r="C39" s="31"/>
+      <c r="D39" s="31"/>
+      <c r="E39" s="31"/>
+      <c r="F39" s="31"/>
+      <c r="G39" s="31"/>
+      <c r="H39" s="31"/>
+      <c r="I39" s="31"/>
+      <c r="J39" s="31"/>
+      <c r="K39" s="31"/>
+      <c r="L39" s="31"/>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B41" s="32" t="s">
         <v>47</v>
       </c>
-      <c r="I42" s="32" t="s">
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="32"/>
+      <c r="J41" s="32"/>
+      <c r="K41" s="32"/>
+      <c r="L41" s="32"/>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B42" s="33" t="s">
         <v>48</v>
       </c>
-      <c r="J42" s="32" t="s">
+      <c r="C42" s="33"/>
+      <c r="D42" s="33"/>
+      <c r="E42" s="33"/>
+      <c r="F42" s="33"/>
+      <c r="G42" s="33"/>
+      <c r="H42" s="33"/>
+      <c r="I42" s="33"/>
+      <c r="J42" s="33"/>
+      <c r="K42" s="33"/>
+      <c r="L42" s="33"/>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B43" s="33"/>
+      <c r="C43" s="33"/>
+      <c r="D43" s="33"/>
+      <c r="E43" s="33"/>
+      <c r="F43" s="33"/>
+      <c r="G43" s="33"/>
+      <c r="H43" s="33"/>
+      <c r="I43" s="33"/>
+      <c r="J43" s="33"/>
+      <c r="K43" s="33"/>
+      <c r="L43" s="33"/>
+    </row>
+    <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B44" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C44" s="34" t="s">
+        <v>14</v>
+      </c>
+      <c r="D44" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="E44" s="34" t="s">
+        <v>16</v>
+      </c>
+      <c r="F44" s="34" t="s">
+        <v>17</v>
+      </c>
+      <c r="G44" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="H44" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="I44" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="J44" s="34" t="s">
         <v>49</v>
       </c>
-      <c r="K42" s="32" t="s">
+      <c r="K44" s="34" t="s">
         <v>50</v>
       </c>
-      <c r="L42" s="32" t="s">
+      <c r="L44" s="34" t="s">
         <v>51</v>
       </c>
-      <c r="N42" s="33" t="s">
+      <c r="N44" s="35" t="s">
         <v>52</v>
       </c>
-      <c r="O42" s="33" t="s">
+      <c r="O44" s="35" t="s">
         <v>53</v>
       </c>
-      <c r="P42" s="33" t="s">
+      <c r="P44" s="35" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="34" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B45" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="C43" s="35" t="s">
+      <c r="C45" s="37" t="s">
         <v>56</v>
       </c>
-      <c r="D43" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E43" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="F43" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G43" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H43" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I43" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J43" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K43" s="21" t="str">
-        <f aca="false">SUM(D43:J43)&amp;"/7"</f>
-        <v>7/7</v>
-      </c>
-      <c r="L43" s="36"/>
-      <c r="N43" s="37" t="s">
+      <c r="D45" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="E45" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="F45" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="G45" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="H45" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="I45" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="J45" s="38" t="n">
+        <f aca="false">COUNTA(C45:I45)</f>
+        <v>7</v>
+      </c>
+      <c r="K45" s="23" t="str">
+        <f aca="false">IF(COUNTA(C45:I45)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C45:I45,"77W")&gt;0,"77W("&amp;COUNTIF(C45:I45,"77W")&amp;") ","")&amp;IF(COUNTIF(C45:I45,"778")&gt;0,"778("&amp;COUNTIF(C45:I45,"778")&amp;") ","")&amp;IF(COUNTIF(C45:I45,"A320")&gt;0,"A320("&amp;COUNTIF(C45:I45,"A320")&amp;") ",""))," ",", "))</f>
+        <v>77W(4), 778(3)</v>
+      </c>
+      <c r="L45" s="39"/>
+      <c r="N45" s="40" t="s">
         <v>4</v>
       </c>
-      <c r="O43" s="38" t="n">
+      <c r="O45" s="41" t="n">
         <f aca="false">DATE(2027,4,1)</f>
         <v>46478</v>
       </c>
-      <c r="P43" s="39" t="s">
+      <c r="P45" s="23" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B44" s="34" t="s">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B46" s="36" t="s">
+        <v>58</v>
+      </c>
+      <c r="C46" s="37"/>
+      <c r="D46" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="C44" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="D44" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E44" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="F44" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G44" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I44" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K44" s="21" t="str">
-        <f aca="false">SUM(D44:J44)&amp;"/7"</f>
-        <v>3/7</v>
-      </c>
-      <c r="L44" s="40"/>
-      <c r="N44" s="37" t="s">
+      <c r="E46" s="37"/>
+      <c r="F46" s="37"/>
+      <c r="G46" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="H46" s="37"/>
+      <c r="I46" s="37" t="s">
+        <v>56</v>
+      </c>
+      <c r="J46" s="38" t="n">
+        <f aca="false">COUNTA(C46:I46)</f>
+        <v>3</v>
+      </c>
+      <c r="K46" s="23" t="str">
+        <f aca="false">IF(COUNTA(C46:I46)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C46:I46,"77W")&gt;0,"77W("&amp;COUNTIF(C46:I46,"77W")&amp;") ","")&amp;IF(COUNTIF(C46:I46,"778")&gt;0,"778("&amp;COUNTIF(C46:I46,"778")&amp;") ","")&amp;IF(COUNTIF(C46:I46,"A320")&gt;0,"A320("&amp;COUNTIF(C46:I46,"A320")&amp;") ",""))," ",", "))</f>
+        <v>77W(1), 778(2)</v>
+      </c>
+      <c r="L46" s="42"/>
+      <c r="N46" s="40" t="s">
         <v>59</v>
       </c>
-      <c r="O44" s="38" t="n">
+      <c r="O46" s="41" t="n">
         <f aca="false">DATE(2027,5,1)</f>
         <v>46508</v>
       </c>
-      <c r="P44" s="39" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="34" t="s">
+      <c r="P46" s="23" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B47" s="36" t="s">
         <v>60</v>
       </c>
-      <c r="C45" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="D45" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F45" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G45" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J45" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="21" t="str">
-        <f aca="false">SUM(D45:J45)&amp;"/7"</f>
-        <v>2/7</v>
-      </c>
-      <c r="L45" s="41"/>
-      <c r="N45" s="37" t="s">
+      <c r="C47" s="37"/>
+      <c r="D47" s="37"/>
+      <c r="E47" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="F47" s="37"/>
+      <c r="G47" s="37"/>
+      <c r="H47" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="I47" s="37"/>
+      <c r="J47" s="38" t="n">
+        <f aca="false">COUNTA(C47:I47)</f>
+        <v>2</v>
+      </c>
+      <c r="K47" s="23" t="str">
+        <f aca="false">IF(COUNTA(C47:I47)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C47:I47,"77W")&gt;0,"77W("&amp;COUNTIF(C47:I47,"77W")&amp;") ","")&amp;IF(COUNTIF(C47:I47,"778")&gt;0,"778("&amp;COUNTIF(C47:I47,"778")&amp;") ","")&amp;IF(COUNTIF(C47:I47,"A320")&gt;0,"A320("&amp;COUNTIF(C47:I47,"A320")&amp;") ",""))," ",", "))</f>
+        <v>778(2)</v>
+      </c>
+      <c r="L47" s="43"/>
+      <c r="N47" s="40" t="s">
         <v>61</v>
       </c>
-      <c r="O45" s="38" t="n">
+      <c r="O47" s="41" t="n">
         <f aca="false">DATE(2027,6,1)</f>
         <v>46539</v>
       </c>
-      <c r="P45" s="39" t="s">
+      <c r="P47" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="34" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B48" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="C46" s="35" t="s">
+      <c r="C48" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="D46" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E46" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="F46" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G46" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H46" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I46" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="21" t="str">
-        <f aca="false">SUM(D46:J46)&amp;"/7"</f>
-        <v>5/7</v>
-      </c>
-      <c r="L46" s="42"/>
-      <c r="N46" s="37" t="s">
+      <c r="D48" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="F48" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="G48" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="H48" s="37"/>
+      <c r="I48" s="37"/>
+      <c r="J48" s="38" t="n">
+        <f aca="false">COUNTA(C48:I48)</f>
+        <v>5</v>
+      </c>
+      <c r="K48" s="23" t="str">
+        <f aca="false">IF(COUNTA(C48:I48)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C48:I48,"77W")&gt;0,"77W("&amp;COUNTIF(C48:I48,"77W")&amp;") ","")&amp;IF(COUNTIF(C48:I48,"778")&gt;0,"778("&amp;COUNTIF(C48:I48,"778")&amp;") ","")&amp;IF(COUNTIF(C48:I48,"A320")&gt;0,"A320("&amp;COUNTIF(C48:I48,"A320")&amp;") ",""))," ",", "))</f>
+        <v>A320(5)</v>
+      </c>
+      <c r="L48" s="44"/>
+      <c r="N48" s="40" t="s">
         <v>64</v>
       </c>
-      <c r="O46" s="38" t="n">
+      <c r="O48" s="41" t="n">
         <f aca="false">DATE(2027,7,1)</f>
         <v>46569</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="34" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B49" s="36" t="s">
         <v>65</v>
       </c>
-      <c r="C47" s="35" t="s">
+      <c r="C49" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="D47" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E47" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F47" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G47" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I47" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K47" s="21" t="str">
-        <f aca="false">SUM(D47:J47)&amp;"/7"</f>
-        <v>4/7</v>
-      </c>
-      <c r="L47" s="43"/>
-      <c r="N47" s="37" t="s">
+      <c r="D49" s="37"/>
+      <c r="E49" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="F49" s="37"/>
+      <c r="G49" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="H49" s="37"/>
+      <c r="I49" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="J49" s="38" t="n">
+        <f aca="false">COUNTA(C49:I49)</f>
+        <v>4</v>
+      </c>
+      <c r="K49" s="23" t="str">
+        <f aca="false">IF(COUNTA(C49:I49)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C49:I49,"77W")&gt;0,"77W("&amp;COUNTIF(C49:I49,"77W")&amp;") ","")&amp;IF(COUNTIF(C49:I49,"778")&gt;0,"778("&amp;COUNTIF(C49:I49,"778")&amp;") ","")&amp;IF(COUNTIF(C49:I49,"A320")&gt;0,"A320("&amp;COUNTIF(C49:I49,"A320")&amp;") ",""))," ",", "))</f>
+        <v>A320(4)</v>
+      </c>
+      <c r="L49" s="45"/>
+      <c r="N49" s="40" t="s">
         <v>66</v>
       </c>
-      <c r="O47" s="38" t="n">
+      <c r="O49" s="41" t="n">
         <f aca="false">DATE(2027,8,1)</f>
         <v>46600</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="34" t="s">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B50" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C48" s="35" t="s">
+      <c r="C50" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="D48" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E48" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H48" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J48" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="21" t="str">
-        <f aca="false">SUM(D48:J48)&amp;"/7"</f>
-        <v>3/7</v>
-      </c>
-      <c r="L48" s="44"/>
-      <c r="N48" s="37" t="s">
+      <c r="D50" s="37"/>
+      <c r="E50" s="37"/>
+      <c r="F50" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="G50" s="37"/>
+      <c r="H50" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="I50" s="37"/>
+      <c r="J50" s="38" t="n">
+        <f aca="false">COUNTA(C50:I50)</f>
+        <v>3</v>
+      </c>
+      <c r="K50" s="23" t="str">
+        <f aca="false">IF(COUNTA(C50:I50)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C50:I50,"77W")&gt;0,"77W("&amp;COUNTIF(C50:I50,"77W")&amp;") ","")&amp;IF(COUNTIF(C50:I50,"778")&gt;0,"778("&amp;COUNTIF(C50:I50,"778")&amp;") ","")&amp;IF(COUNTIF(C50:I50,"A320")&gt;0,"A320("&amp;COUNTIF(C50:I50,"A320")&amp;") ",""))," ",", "))</f>
+        <v>A320(3)</v>
+      </c>
+      <c r="L50" s="46"/>
+      <c r="N50" s="40" t="s">
         <v>67</v>
       </c>
-      <c r="O48" s="38" t="n">
+      <c r="O50" s="41" t="n">
         <f aca="false">DATE(2027,9,1)</f>
         <v>46631</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="34" t="s">
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B51" s="36" t="s">
         <v>68</v>
       </c>
-      <c r="C49" s="35" t="s">
+      <c r="C51" s="37"/>
+      <c r="D51" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="D49" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E49" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="F49" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H49" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J49" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="21" t="str">
-        <f aca="false">SUM(D49:J49)&amp;"/7"</f>
-        <v>3/7</v>
-      </c>
-      <c r="L49" s="45"/>
-      <c r="N49" s="37" t="s">
+      <c r="E51" s="37"/>
+      <c r="F51" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="G51" s="37"/>
+      <c r="H51" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="I51" s="37"/>
+      <c r="J51" s="38" t="n">
+        <f aca="false">COUNTA(C51:I51)</f>
+        <v>3</v>
+      </c>
+      <c r="K51" s="23" t="str">
+        <f aca="false">IF(COUNTA(C51:I51)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C51:I51,"77W")&gt;0,"77W("&amp;COUNTIF(C51:I51,"77W")&amp;") ","")&amp;IF(COUNTIF(C51:I51,"778")&gt;0,"778("&amp;COUNTIF(C51:I51,"778")&amp;") ","")&amp;IF(COUNTIF(C51:I51,"A320")&gt;0,"A320("&amp;COUNTIF(C51:I51,"A320")&amp;") ",""))," ",", "))</f>
+        <v>A320(3)</v>
+      </c>
+      <c r="L51" s="47"/>
+      <c r="N51" s="40" t="s">
         <v>69</v>
       </c>
-      <c r="O49" s="38" t="n">
+      <c r="O51" s="41" t="n">
         <f aca="false">DATE(2027,10,1)</f>
         <v>46661</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="34" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B52" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="C50" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="D50" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E50" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H50" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I50" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J50" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="21" t="str">
-        <f aca="false">SUM(D50:J50)&amp;"/7"</f>
-        <v>2/7</v>
-      </c>
-      <c r="L50" s="46"/>
-      <c r="N50" s="37" t="s">
+      <c r="C52" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="D52" s="37"/>
+      <c r="E52" s="37"/>
+      <c r="F52" s="37"/>
+      <c r="G52" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="H52" s="37"/>
+      <c r="I52" s="37"/>
+      <c r="J52" s="38" t="n">
+        <f aca="false">COUNTA(C52:I52)</f>
+        <v>2</v>
+      </c>
+      <c r="K52" s="23" t="str">
+        <f aca="false">IF(COUNTA(C52:I52)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C52:I52,"77W")&gt;0,"77W("&amp;COUNTIF(C52:I52,"77W")&amp;") ","")&amp;IF(COUNTIF(C52:I52,"778")&gt;0,"778("&amp;COUNTIF(C52:I52,"778")&amp;") ","")&amp;IF(COUNTIF(C52:I52,"A320")&gt;0,"A320("&amp;COUNTIF(C52:I52,"A320")&amp;") ",""))," ",", "))</f>
+        <v>778(2)</v>
+      </c>
+      <c r="L52" s="48"/>
+      <c r="N52" s="40" t="s">
         <v>71</v>
       </c>
-      <c r="O50" s="38" t="n">
+      <c r="O52" s="41" t="n">
         <f aca="false">DATE(2027,11,1)</f>
         <v>46692</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="34" t="s">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B53" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="C51" s="35" t="s">
-        <v>58</v>
-      </c>
-      <c r="D51" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="35" t="n">
+      <c r="C53" s="37"/>
+      <c r="D53" s="37"/>
+      <c r="E53" s="37"/>
+      <c r="F53" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="G53" s="37"/>
+      <c r="H53" s="37"/>
+      <c r="I53" s="37"/>
+      <c r="J53" s="38" t="n">
+        <f aca="false">COUNTA(C53:I53)</f>
         <v>1</v>
       </c>
-      <c r="H51" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J51" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="21" t="str">
-        <f aca="false">SUM(D51:J51)&amp;"/7"</f>
-        <v>1/7</v>
-      </c>
-      <c r="L51" s="47"/>
-      <c r="N51" s="37" t="s">
+      <c r="K53" s="23" t="str">
+        <f aca="false">IF(COUNTA(C53:I53)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C53:I53,"77W")&gt;0,"77W("&amp;COUNTIF(C53:I53,"77W")&amp;") ","")&amp;IF(COUNTIF(C53:I53,"778")&gt;0,"778("&amp;COUNTIF(C53:I53,"778")&amp;") ","")&amp;IF(COUNTIF(C53:I53,"A320")&gt;0,"A320("&amp;COUNTIF(C53:I53,"A320")&amp;") ",""))," ",", "))</f>
+        <v>778(1)</v>
+      </c>
+      <c r="L53" s="49"/>
+      <c r="N53" s="40" t="s">
         <v>73</v>
       </c>
-      <c r="O51" s="38" t="n">
+      <c r="O53" s="41" t="n">
         <f aca="false">DATE(2027,12,1)</f>
         <v>46722</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="34" t="s">
+    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B54" s="36" t="s">
         <v>74</v>
       </c>
-      <c r="C52" s="35" t="s">
+      <c r="C54" s="37"/>
+      <c r="D54" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="D52" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="F52" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G52" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J52" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="21" t="str">
-        <f aca="false">SUM(D52:J52)&amp;"/7"</f>
-        <v>2/7</v>
-      </c>
-      <c r="L52" s="48"/>
-      <c r="N52" s="37" t="s">
+      <c r="E54" s="37"/>
+      <c r="F54" s="37"/>
+      <c r="G54" s="37"/>
+      <c r="H54" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="I54" s="37"/>
+      <c r="J54" s="38" t="n">
+        <f aca="false">COUNTA(C54:I54)</f>
+        <v>2</v>
+      </c>
+      <c r="K54" s="23" t="str">
+        <f aca="false">IF(COUNTA(C54:I54)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C54:I54,"77W")&gt;0,"77W("&amp;COUNTIF(C54:I54,"77W")&amp;") ","")&amp;IF(COUNTIF(C54:I54,"778")&gt;0,"778("&amp;COUNTIF(C54:I54,"778")&amp;") ","")&amp;IF(COUNTIF(C54:I54,"A320")&gt;0,"A320("&amp;COUNTIF(C54:I54,"A320")&amp;") ",""))," ",", "))</f>
+        <v>A320(2)</v>
+      </c>
+      <c r="L54" s="50"/>
+      <c r="N54" s="40" t="s">
         <v>75</v>
       </c>
-      <c r="O52" s="38" t="n">
+      <c r="O54" s="41" t="n">
         <f aca="false">DATE(2028,1,1)</f>
         <v>46753</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="34" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B55" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="C53" s="35" t="s">
+      <c r="C55" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="D53" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="E53" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="F53" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G53" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="H53" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="I53" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="J53" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="21" t="str">
-        <f aca="false">SUM(D53:J53)&amp;"/7"</f>
-        <v>6/7</v>
-      </c>
-      <c r="L53" s="49"/>
-      <c r="N53" s="37" t="s">
+      <c r="D55" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="E55" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="F55" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="G55" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="H55" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="I55" s="37"/>
+      <c r="J55" s="38" t="n">
+        <f aca="false">COUNTA(C55:I55)</f>
+        <v>6</v>
+      </c>
+      <c r="K55" s="23" t="str">
+        <f aca="false">IF(COUNTA(C55:I55)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C55:I55,"77W")&gt;0,"77W("&amp;COUNTIF(C55:I55,"77W")&amp;") ","")&amp;IF(COUNTIF(C55:I55,"778")&gt;0,"778("&amp;COUNTIF(C55:I55,"778")&amp;") ","")&amp;IF(COUNTIF(C55:I55,"A320")&gt;0,"A320("&amp;COUNTIF(C55:I55,"A320")&amp;") ",""))," ",", "))</f>
+        <v>A320(6)</v>
+      </c>
+      <c r="L55" s="51"/>
+      <c r="N55" s="40" t="s">
         <v>77</v>
       </c>
-      <c r="O53" s="38" t="n">
+      <c r="O55" s="41" t="n">
         <f aca="false">DATE(2028,2,1)</f>
         <v>46784</v>
       </c>
     </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="34" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B56" s="36" t="s">
         <v>78</v>
       </c>
-      <c r="C54" s="35" t="s">
+      <c r="C56" s="37"/>
+      <c r="D56" s="37"/>
+      <c r="E56" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="D54" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="G54" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="H54" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="J54" s="35" t="n">
-        <v>1</v>
-      </c>
-      <c r="K54" s="21" t="str">
-        <f aca="false">SUM(D54:J54)&amp;"/7"</f>
-        <v>2/7</v>
-      </c>
-      <c r="L54" s="50"/>
-      <c r="N54" s="37" t="s">
+      <c r="F56" s="37"/>
+      <c r="G56" s="37"/>
+      <c r="H56" s="37"/>
+      <c r="I56" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="J56" s="38" t="n">
+        <f aca="false">COUNTA(C56:I56)</f>
+        <v>2</v>
+      </c>
+      <c r="K56" s="23" t="str">
+        <f aca="false">IF(COUNTA(C56:I56)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C56:I56,"77W")&gt;0,"77W("&amp;COUNTIF(C56:I56,"77W")&amp;") ","")&amp;IF(COUNTIF(C56:I56,"778")&gt;0,"778("&amp;COUNTIF(C56:I56,"778")&amp;") ","")&amp;IF(COUNTIF(C56:I56,"A320")&gt;0,"A320("&amp;COUNTIF(C56:I56,"A320")&amp;") ",""))," ",", "))</f>
+        <v>A320(2)</v>
+      </c>
+      <c r="L56" s="52"/>
+      <c r="N56" s="40" t="s">
         <v>79</v>
       </c>
-      <c r="O54" s="38" t="n">
+      <c r="O56" s="41" t="n">
         <f aca="false">DATE(2028,3,1)</f>
         <v>46813</v>
       </c>
     </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="32" t="s">
+        <v>80</v>
+      </c>
+      <c r="C59" s="32"/>
+      <c r="D59" s="32"/>
+      <c r="E59" s="32"/>
+      <c r="F59" s="32"/>
+      <c r="G59" s="32"/>
+      <c r="H59" s="32"/>
+      <c r="I59" s="32"/>
+      <c r="J59" s="32"/>
+      <c r="K59" s="32"/>
+      <c r="L59" s="32"/>
+    </row>
+    <row r="60" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B60" s="33" t="s">
+        <v>81</v>
+      </c>
+      <c r="C60" s="33"/>
+      <c r="D60" s="33"/>
+      <c r="E60" s="33"/>
+      <c r="F60" s="33"/>
+      <c r="G60" s="33"/>
+      <c r="H60" s="33"/>
+      <c r="I60" s="33"/>
+      <c r="J60" s="33"/>
+      <c r="K60" s="33"/>
+      <c r="L60" s="33"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="34" t="s">
+        <v>82</v>
+      </c>
+      <c r="C61" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="D61" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="E61" s="34" t="s">
+        <v>84</v>
+      </c>
+      <c r="F61" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="J61" s="53" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="54" t="n">
+        <v>46484</v>
+      </c>
+      <c r="C62" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D62" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="E62" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="56" t="s">
+        <v>87</v>
+      </c>
+      <c r="J62" s="57" t="str">
+        <f aca="false">IF(OR($B62="",$C62=""),"",$B62&amp;"|"&amp;$C62)</f>
+        <v>46484|NOSRUN</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="54" t="n">
+        <v>46487</v>
+      </c>
+      <c r="C63" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="D63" s="37" t="s">
+        <v>62</v>
+      </c>
+      <c r="E63" s="55" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="J63" s="57" t="str">
+        <f aca="false">IF(OR($B63="",$C63=""),"",$B63&amp;"|"&amp;$C63)</f>
+        <v>46487|NOSRUN</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="54" t="n">
+        <v>46497</v>
+      </c>
+      <c r="C64" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="D64" s="37" t="s">
+        <v>57</v>
+      </c>
+      <c r="E64" s="55" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" s="56" t="s">
+        <v>89</v>
+      </c>
+      <c r="J64" s="57" t="str">
+        <f aca="false">IF(OR($B64="",$C64=""),"",$B64&amp;"|"&amp;$C64)</f>
+        <v>46497|CDGRUN</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="54"/>
+      <c r="C65" s="37"/>
+      <c r="D65" s="37"/>
+      <c r="E65" s="55"/>
+      <c r="F65" s="56"/>
+      <c r="J65" s="57" t="str">
+        <f aca="false">IF(OR($B65="",$C65=""),"",$B65&amp;"|"&amp;$C65)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="54"/>
+      <c r="C66" s="37"/>
+      <c r="D66" s="37"/>
+      <c r="E66" s="55"/>
+      <c r="F66" s="56"/>
+      <c r="J66" s="57" t="str">
+        <f aca="false">IF(OR($B66="",$C66=""),"",$B66&amp;"|"&amp;$C66)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="54"/>
+      <c r="C67" s="37"/>
+      <c r="D67" s="37"/>
+      <c r="E67" s="55"/>
+      <c r="F67" s="56"/>
+      <c r="J67" s="57" t="str">
+        <f aca="false">IF(OR($B67="",$C67=""),"",$B67&amp;"|"&amp;$C67)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="54"/>
+      <c r="C68" s="37"/>
+      <c r="D68" s="37"/>
+      <c r="E68" s="55"/>
+      <c r="F68" s="56"/>
+      <c r="J68" s="57" t="str">
+        <f aca="false">IF(OR($B68="",$C68=""),"",$B68&amp;"|"&amp;$C68)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="54"/>
+      <c r="C69" s="37"/>
+      <c r="D69" s="37"/>
+      <c r="E69" s="55"/>
+      <c r="F69" s="56"/>
+      <c r="J69" s="57" t="str">
+        <f aca="false">IF(OR($B69="",$C69=""),"",$B69&amp;"|"&amp;$C69)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="54"/>
+      <c r="C70" s="37"/>
+      <c r="D70" s="37"/>
+      <c r="E70" s="55"/>
+      <c r="F70" s="56"/>
+      <c r="J70" s="57" t="str">
+        <f aca="false">IF(OR($B70="",$C70=""),"",$B70&amp;"|"&amp;$C70)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="54"/>
+      <c r="C71" s="37"/>
+      <c r="D71" s="37"/>
+      <c r="E71" s="55"/>
+      <c r="F71" s="56"/>
+      <c r="J71" s="57" t="str">
+        <f aca="false">IF(OR($B71="",$C71=""),"",$B71&amp;"|"&amp;$C71)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="54"/>
+      <c r="C72" s="37"/>
+      <c r="D72" s="37"/>
+      <c r="E72" s="55"/>
+      <c r="F72" s="56"/>
+      <c r="J72" s="57" t="str">
+        <f aca="false">IF(OR($B72="",$C72=""),"",$B72&amp;"|"&amp;$C72)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="54"/>
+      <c r="C73" s="37"/>
+      <c r="D73" s="37"/>
+      <c r="E73" s="55"/>
+      <c r="F73" s="56"/>
+      <c r="J73" s="57" t="str">
+        <f aca="false">IF(OR($B73="",$C73=""),"",$B73&amp;"|"&amp;$C73)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="54"/>
+      <c r="C74" s="37"/>
+      <c r="D74" s="37"/>
+      <c r="E74" s="55"/>
+      <c r="F74" s="56"/>
+      <c r="J74" s="57" t="str">
+        <f aca="false">IF(OR($B74="",$C74=""),"",$B74&amp;"|"&amp;$C74)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="54"/>
+      <c r="C75" s="37"/>
+      <c r="D75" s="37"/>
+      <c r="E75" s="55"/>
+      <c r="F75" s="56"/>
+      <c r="J75" s="57" t="str">
+        <f aca="false">IF(OR($B75="",$C75=""),"",$B75&amp;"|"&amp;$C75)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="54"/>
+      <c r="C76" s="37"/>
+      <c r="D76" s="37"/>
+      <c r="E76" s="55"/>
+      <c r="F76" s="56"/>
+      <c r="J76" s="57" t="str">
+        <f aca="false">IF(OR($B76="",$C76=""),"",$B76&amp;"|"&amp;$C76)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="54"/>
+      <c r="C77" s="37"/>
+      <c r="D77" s="37"/>
+      <c r="E77" s="55"/>
+      <c r="F77" s="56"/>
+      <c r="J77" s="57" t="str">
+        <f aca="false">IF(OR($B77="",$C77=""),"",$B77&amp;"|"&amp;$C77)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="54"/>
+      <c r="C78" s="37"/>
+      <c r="D78" s="37"/>
+      <c r="E78" s="55"/>
+      <c r="F78" s="56"/>
+      <c r="J78" s="57" t="str">
+        <f aca="false">IF(OR($B78="",$C78=""),"",$B78&amp;"|"&amp;$C78)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="54"/>
+      <c r="C79" s="37"/>
+      <c r="D79" s="37"/>
+      <c r="E79" s="55"/>
+      <c r="F79" s="56"/>
+      <c r="J79" s="57" t="str">
+        <f aca="false">IF(OR($B79="",$C79=""),"",$B79&amp;"|"&amp;$C79)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="54"/>
+      <c r="C80" s="37"/>
+      <c r="D80" s="37"/>
+      <c r="E80" s="55"/>
+      <c r="F80" s="56"/>
+      <c r="J80" s="57" t="str">
+        <f aca="false">IF(OR($B80="",$C80=""),"",$B80&amp;"|"&amp;$C80)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B81" s="54"/>
+      <c r="C81" s="37"/>
+      <c r="D81" s="37"/>
+      <c r="E81" s="55"/>
+      <c r="F81" s="56"/>
+      <c r="J81" s="57" t="str">
+        <f aca="false">IF(OR($B81="",$C81=""),"",$B81&amp;"|"&amp;$C81)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B82" s="54"/>
+      <c r="C82" s="37"/>
+      <c r="D82" s="37"/>
+      <c r="E82" s="55"/>
+      <c r="F82" s="56"/>
+      <c r="J82" s="57" t="str">
+        <f aca="false">IF(OR($B82="",$C82=""),"",$B82&amp;"|"&amp;$C82)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="54"/>
+      <c r="C83" s="37"/>
+      <c r="D83" s="37"/>
+      <c r="E83" s="55"/>
+      <c r="F83" s="56"/>
+      <c r="J83" s="57" t="str">
+        <f aca="false">IF(OR($B83="",$C83=""),"",$B83&amp;"|"&amp;$C83)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B84" s="54"/>
+      <c r="C84" s="37"/>
+      <c r="D84" s="37"/>
+      <c r="E84" s="55"/>
+      <c r="F84" s="56"/>
+      <c r="J84" s="57" t="str">
+        <f aca="false">IF(OR($B84="",$C84=""),"",$B84&amp;"|"&amp;$C84)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="54"/>
+      <c r="C85" s="37"/>
+      <c r="D85" s="37"/>
+      <c r="E85" s="55"/>
+      <c r="F85" s="56"/>
+      <c r="J85" s="57" t="str">
+        <f aca="false">IF(OR($B85="",$C85=""),"",$B85&amp;"|"&amp;$C85)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="54"/>
+      <c r="C86" s="37"/>
+      <c r="D86" s="37"/>
+      <c r="E86" s="55"/>
+      <c r="F86" s="56"/>
+      <c r="J86" s="57" t="str">
+        <f aca="false">IF(OR($B86="",$C86=""),"",$B86&amp;"|"&amp;$C86)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="54"/>
+      <c r="C87" s="37"/>
+      <c r="D87" s="37"/>
+      <c r="E87" s="55"/>
+      <c r="F87" s="56"/>
+      <c r="J87" s="57" t="str">
+        <f aca="false">IF(OR($B87="",$C87=""),"",$B87&amp;"|"&amp;$C87)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B88" s="54"/>
+      <c r="C88" s="37"/>
+      <c r="D88" s="37"/>
+      <c r="E88" s="55"/>
+      <c r="F88" s="56"/>
+      <c r="J88" s="57" t="str">
+        <f aca="false">IF(OR($B88="",$C88=""),"",$B88&amp;"|"&amp;$C88)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="54"/>
+      <c r="C89" s="37"/>
+      <c r="D89" s="37"/>
+      <c r="E89" s="55"/>
+      <c r="F89" s="56"/>
+      <c r="J89" s="57" t="str">
+        <f aca="false">IF(OR($B89="",$C89=""),"",$B89&amp;"|"&amp;$C89)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B90" s="54"/>
+      <c r="C90" s="37"/>
+      <c r="D90" s="37"/>
+      <c r="E90" s="55"/>
+      <c r="F90" s="56"/>
+      <c r="J90" s="57" t="str">
+        <f aca="false">IF(OR($B90="",$C90=""),"",$B90&amp;"|"&amp;$C90)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B91" s="54"/>
+      <c r="C91" s="37"/>
+      <c r="D91" s="37"/>
+      <c r="E91" s="55"/>
+      <c r="F91" s="56"/>
+      <c r="J91" s="57" t="str">
+        <f aca="false">IF(OR($B91="",$C91=""),"",$B91&amp;"|"&amp;$C91)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B92" s="54"/>
+      <c r="C92" s="37"/>
+      <c r="D92" s="37"/>
+      <c r="E92" s="55"/>
+      <c r="F92" s="56"/>
+      <c r="J92" s="57" t="str">
+        <f aca="false">IF(OR($B92="",$C92=""),"",$B92&amp;"|"&amp;$C92)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B93" s="54"/>
+      <c r="C93" s="37"/>
+      <c r="D93" s="37"/>
+      <c r="E93" s="55"/>
+      <c r="F93" s="56"/>
+      <c r="J93" s="57" t="str">
+        <f aca="false">IF(OR($B93="",$C93=""),"",$B93&amp;"|"&amp;$C93)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B94" s="54"/>
+      <c r="C94" s="37"/>
+      <c r="D94" s="37"/>
+      <c r="E94" s="55"/>
+      <c r="F94" s="56"/>
+      <c r="J94" s="57" t="str">
+        <f aca="false">IF(OR($B94="",$C94=""),"",$B94&amp;"|"&amp;$C94)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B95" s="54"/>
+      <c r="C95" s="37"/>
+      <c r="D95" s="37"/>
+      <c r="E95" s="55"/>
+      <c r="F95" s="56"/>
+      <c r="J95" s="57" t="str">
+        <f aca="false">IF(OR($B95="",$C95=""),"",$B95&amp;"|"&amp;$C95)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B96" s="54"/>
+      <c r="C96" s="37"/>
+      <c r="D96" s="37"/>
+      <c r="E96" s="55"/>
+      <c r="F96" s="56"/>
+      <c r="J96" s="57" t="str">
+        <f aca="false">IF(OR($B96="",$C96=""),"",$B96&amp;"|"&amp;$C96)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B97" s="54"/>
+      <c r="C97" s="37"/>
+      <c r="D97" s="37"/>
+      <c r="E97" s="55"/>
+      <c r="F97" s="56"/>
+      <c r="J97" s="57" t="str">
+        <f aca="false">IF(OR($B97="",$C97=""),"",$B97&amp;"|"&amp;$C97)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B98" s="54"/>
+      <c r="C98" s="37"/>
+      <c r="D98" s="37"/>
+      <c r="E98" s="55"/>
+      <c r="F98" s="56"/>
+      <c r="J98" s="57" t="str">
+        <f aca="false">IF(OR($B98="",$C98=""),"",$B98&amp;"|"&amp;$C98)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B99" s="54"/>
+      <c r="C99" s="37"/>
+      <c r="D99" s="37"/>
+      <c r="E99" s="55"/>
+      <c r="F99" s="56"/>
+      <c r="J99" s="57" t="str">
+        <f aca="false">IF(OR($B99="",$C99=""),"",$B99&amp;"|"&amp;$C99)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B100" s="54"/>
+      <c r="C100" s="37"/>
+      <c r="D100" s="37"/>
+      <c r="E100" s="55"/>
+      <c r="F100" s="56"/>
+      <c r="J100" s="57" t="str">
+        <f aca="false">IF(OR($B100="",$C100=""),"",$B100&amp;"|"&amp;$C100)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B101" s="54"/>
+      <c r="C101" s="37"/>
+      <c r="D101" s="37"/>
+      <c r="E101" s="55"/>
+      <c r="F101" s="56"/>
+      <c r="J101" s="57" t="str">
+        <f aca="false">IF(OR($B101="",$C101=""),"",$B101&amp;"|"&amp;$C101)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="11">
+  <mergeCells count="13">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="B2:I2"/>
-    <mergeCell ref="K3:L3"/>
+    <mergeCell ref="N3:O3"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="B6:I6"/>
     <mergeCell ref="D21:I21"/>
-    <mergeCell ref="B23:G23"/>
-    <mergeCell ref="B38:G38"/>
-    <mergeCell ref="B40:P40"/>
-    <mergeCell ref="B41:P41"/>
+    <mergeCell ref="B23:L23"/>
+    <mergeCell ref="B38:L39"/>
+    <mergeCell ref="B41:L41"/>
+    <mergeCell ref="B42:L43"/>
+    <mergeCell ref="B59:L59"/>
+    <mergeCell ref="B60:L60"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:I8 C10:I10 C12:I12 C14:I14 C16:I16 C18:I18">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
+      <formula>ISNUMBER(SEARCH("(+",C8))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>AND($C$5="CDGRUN",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND($C$5="CDGDZA",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>AND($C$5="BKKRUN",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>AND($C$5="DZARUN",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>AND($C$5="MRURUN",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>AND($C$5="NOSRUN",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>AND($C$5="RUNTNR",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>AND($C$5="JNBRUN",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>AND($C$5="CPTRUN",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>AND($C$5="DIERUN",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>AND($C$5="RRGRUN",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>AND($C$5="TMMRUN",C8&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25:B36">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>$B25="CDGRUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>$B25="CDGDZA"</formula>
     </cfRule>
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>$B25="BKKRUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>$B25="DZARUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>$B25="MRURUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
       <formula>$B25="NOSRUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
       <formula>$B25="RUNTNR"</formula>
     </cfRule>
-    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
       <formula>$B25="JNBRUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
+    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
       <formula>$B25="CPTRUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
       <formula>$B25="DIERUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
       <formula>$B25="RRGRUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
       <formula>$B25="TMMRUN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B43:B54">
-    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
-      <formula>$B43="CDGRUN"</formula>
-    </cfRule>
+  <conditionalFormatting sqref="B45:B56">
     <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
-      <formula>$B43="CDGDZA"</formula>
+      <formula>$B45="CDGRUN"</formula>
     </cfRule>
     <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
-      <formula>$B43="BKKRUN"</formula>
+      <formula>$B45="CDGDZA"</formula>
     </cfRule>
     <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
-      <formula>$B43="DZARUN"</formula>
+      <formula>$B45="BKKRUN"</formula>
     </cfRule>
     <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
-      <formula>$B43="MRURUN"</formula>
+      <formula>$B45="DZARUN"</formula>
     </cfRule>
     <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
-      <formula>$B43="NOSRUN"</formula>
+      <formula>$B45="MRURUN"</formula>
     </cfRule>
     <cfRule type="expression" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
-      <formula>$B43="RUNTNR"</formula>
+      <formula>$B45="NOSRUN"</formula>
     </cfRule>
     <cfRule type="expression" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
-      <formula>$B43="JNBRUN"</formula>
+      <formula>$B45="RUNTNR"</formula>
     </cfRule>
     <cfRule type="expression" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
-      <formula>$B43="CPTRUN"</formula>
+      <formula>$B45="JNBRUN"</formula>
     </cfRule>
     <cfRule type="expression" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
-      <formula>$B43="DIERUN"</formula>
+      <formula>$B45="CPTRUN"</formula>
     </cfRule>
     <cfRule type="expression" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
-      <formula>$B43="RRGRUN"</formula>
+      <formula>$B45="DIERUN"</formula>
     </cfRule>
     <cfRule type="expression" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
-      <formula>$B43="TMMRUN"</formula>
+      <formula>$B45="RRGRUN"</formula>
+    </cfRule>
+    <cfRule type="expression" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+      <formula>$B45="TMMRUN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <dataValidations count="4">
+  <dataValidations count="7">
     <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C4" type="list">
-      <formula1>$N$43:$N$54</formula1>
+      <formula1>$N$45:$N$56</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C5" type="list">
-      <formula1>$B$43:$B$54</formula1>
+      <formula1>$B$45:$B$56</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C43:C54" type="list">
-      <formula1>$P$43:$P$45</formula1>
+    <dataValidation allowBlank="true" error="Choisir un type avion dans la liste, ou laisser vide si la route n'opere pas ce jour-la." errorStyle="stop" errorTitle="Type avion invalide" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C45:I56" type="list">
+      <formula1>$P$45:$P$47</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="false" error="Saisir 1 (jour opere) ou 0 (pas d'operation)." errorStyle="stop" errorTitle="Valeur invalide" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D43:J54" type="list">
-      <formula1>"0,1"</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C62:C101" type="list">
+      <formula1>$B$45:$B$56</formula1>
       <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D62:D101" type="list">
+      <formula1>$P$45:$P$47</formula1>
+      <formula2>0</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="Nombre de rotations : entier entre 1 et 20." errorStyle="stop" errorTitle="Valeur invalide" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E62:E101" type="whole">
+      <formula1>1</formula1>
+      <formula2>20</formula2>
+    </dataValidation>
+    <dataValidation allowBlank="true" error="La date est hors de l'annee avril 2027 - mars 2028 : le vol ne sera visible dans aucun mois." errorStyle="warning" errorTitle="Date hors annee d'exploitation" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B62:B101" type="date">
+      <formula1>DATE(2027,4,1)</formula1>
+      <formula2>DATE(2028,3,31)</formula2>
     </dataValidation>
   </dataValidations>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/Programme_vols_mensuel_2027-2028.xlsx
+++ b/Programme_vols_mensuel_2027-2028.xlsx
@@ -28,7 +28,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="B62" authorId="0">
+    <comment ref="B75" authorId="0">
       <text>
         <r>
           <rPr>
@@ -71,12 +71,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="102">
   <si>
     <t xml:space="preserve">PROGRAMME DE VOLS MENSUEL - ANNEE D'EXPLOITATION AVRIL 2027 / MARS 2028</t>
   </si>
   <si>
-    <t xml:space="preserve">Feuille unique : les deux filtres ci-dessous (Mois et Route) pilotent la grille. Le recapitulatif ne suit que le filtre Mois. Chaque route a une semaine type pouvant melanger plusieurs types avion (un type par jour), a laquelle s'ajoutent les vols additionnels dates saisis en bas de feuille. Tout est calcule par formule.</t>
+    <t xml:space="preserve">Feuille unique : les deux filtres ci-dessous (Mois et Route) pilotent la grille, le recapitulatif ne suit que le filtre Mois. Chaque route a une semaine type de 2 vols possibles par jour, chacun avec son propre type avion (2 types differents le meme jour sont donc possibles), a laquelle s'ajoutent les vols additionnels dates saisis en bas de feuille. Tout est calcule par formule.</t>
   </si>
   <si>
     <t xml:space="preserve">REPERES CALCULES</t>
@@ -151,12 +151,42 @@
     <t xml:space="preserve">Semaine 2</t>
   </si>
   <si>
-    <t xml:space="preserve">(route filtree)</t>
+    <t xml:space="preserve">SEMAINE TYPE DE LA ROUTE FILTREE (auto - alimente la grille)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J6</t>
+  </si>
+  <si>
+    <t xml:space="preserve">J7</t>
   </si>
   <si>
     <t xml:space="preserve">Semaine 3</t>
   </si>
   <si>
+    <t xml:space="preserve">Vol 1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vol 2</t>
+  </si>
+  <si>
     <t xml:space="preserve">Semaine 4</t>
   </si>
   <si>
@@ -172,7 +202,7 @@
     <t xml:space="preserve">Nb de semaines calendaires du mois</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture d'une cellule : "778" = vol de la semaine type  |  "778 (+A320)" = semaine type + vol additionnel  |  "(+A320)" = vol additionnel seul (bordure rouge). Semaines partielles incluses.</t>
+    <t xml:space="preserve">Lecture : "778" = 1 vol de la semaine type  |  "77W/778" = 2 vols le meme jour  |  "778 (+A320)" = semaine type + vol additionnel (bordure rouge)  |  "(+A320)" = vol additionnel seul. Semaines partielles incluses.</t>
   </si>
   <si>
     <t xml:space="preserve">RECAPITULATIF MENSUEL - TOUTES ROUTES  (depend uniquement du filtre Mois)</t>
@@ -211,13 +241,16 @@
     <t xml:space="preserve">TOTAL GENERAL</t>
   </si>
   <si>
-    <t xml:space="preserve">Methode : pour chaque jour d'operation de la semaine type, le nombre d'occurrences de ce jour dans le mois est compte a partir des dates reelles de la grille (ligne "Occurrences du jour dans le mois", semaines partielles incluses). Total rotations du mois = semaine type + vols additionnels dates du mois. La colonne "Nb de semaines/occurrences" indique le nombre de semaines calendaires couvertes par le mois ; les colonnes Total 77W / 778 / A320 ventilent le total du mois par type avion (semaine type + vols additionnels).</t>
+    <t xml:space="preserve">Methode : pour chaque jour opere de la semaine type, le nombre d'occurrences de ce jour dans le mois est compte a partir des dates reelles de la grille (ligne "Occurrences du jour dans le mois", semaines partielles incluses), vol 1 et vol 2 comptes separement. Total rotations du mois = semaine type + vols additionnels dates du mois. La colonne "Nb de semaines/occurrences" indique le nombre de semaines calendaires couvertes par le mois ; les colonnes Total 77W / 778 / A320 ventilent le total du mois par type avion.</t>
   </si>
   <si>
     <t xml:space="preserve">1) SEMAINES TYPES PAR ROUTE (saisie unique, valable pour les 12 mois)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cellules en BLEU = saisie utilisateur. Pour chaque jour J1-J7, choisir dans la liste deroulante le TYPE AVION opere ce jour-la (77W / 778 / A320), ou laisser la cellule vide s'il n'y a pas d'operation. Une meme route peut donc utiliser plusieurs types avion dans la semaine (ex. CDGRUN : 77W les jours impairs, 778 les jours pairs). Toute modification recalcule immediatement la grille et le recapitulatif, pour les 12 mois. Valeurs livrees = exemples a ajuster (NOSRUN = 3/7 en A320 sur J1/J4/J6, conforme a l'exemple fourni).</t>
+    <t xml:space="preserve">Cellules en BLEU = saisie utilisateur. Chaque route occupe 2 lignes : le VOL 1 et le VOL 2 de la journee. Pour chaque jour J1-J7, choisir dans la liste deroulante le TYPE AVION opere (77W / 778 / A320), ou laisser vide s'il n'y a pas de vol. Renseigner les deux lignes pour un jour = 2 rotations ce jour-la, avec le meme type ou deux types differents (ex. CDGRUN le lundi : 77W + 778). Toute modification recalcule immediatement la grille et le recapitulatif, pour les 12 mois. Valeurs livrees = exemples a ajuster (NOSRUN = 3/7 en A320 sur J1/J4/J6, conforme a l'exemple fourni).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Route / vol du jour</t>
   </si>
   <si>
     <t xml:space="preserve">Rot./sem. (auto)</t>
@@ -244,73 +277,76 @@
     <t xml:space="preserve">77W</t>
   </si>
   <si>
+    <t xml:space="preserve">      + vol 2 du jour</t>
+  </si>
+  <si>
     <t xml:space="preserve">778</t>
   </si>
   <si>
+    <t xml:space="preserve">mai 2027</t>
+  </si>
+  <si>
     <t xml:space="preserve">CDGDZA</t>
   </si>
   <si>
-    <t xml:space="preserve">mai 2027</t>
+    <t xml:space="preserve">juin 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">juillet 2027</t>
   </si>
   <si>
     <t xml:space="preserve">BKKRUN</t>
   </si>
   <si>
-    <t xml:space="preserve">juin 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A320</t>
+    <t xml:space="preserve">aout 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">septembre 2027</t>
   </si>
   <si>
     <t xml:space="preserve">DZARUN</t>
   </si>
   <si>
-    <t xml:space="preserve">juillet 2027</t>
+    <t xml:space="preserve">octobre 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">novembre 2027</t>
   </si>
   <si>
     <t xml:space="preserve">MRURUN</t>
   </si>
   <si>
-    <t xml:space="preserve">aout 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">septembre 2027</t>
+    <t xml:space="preserve">decembre 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">janvier 2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fevrier 2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mars 2028</t>
   </si>
   <si>
     <t xml:space="preserve">RUNTNR</t>
   </si>
   <si>
-    <t xml:space="preserve">octobre 2027</t>
-  </si>
-  <si>
     <t xml:space="preserve">JNBRUN</t>
   </si>
   <si>
-    <t xml:space="preserve">novembre 2027</t>
-  </si>
-  <si>
     <t xml:space="preserve">CPTRUN</t>
   </si>
   <si>
-    <t xml:space="preserve">decembre 2027</t>
-  </si>
-  <si>
     <t xml:space="preserve">DIERUN</t>
   </si>
   <si>
-    <t xml:space="preserve">janvier 2028</t>
-  </si>
-  <si>
     <t xml:space="preserve">RRGRUN</t>
   </si>
   <si>
-    <t xml:space="preserve">fevrier 2028</t>
-  </si>
-  <si>
     <t xml:space="preserve">TMMRUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mars 2028</t>
   </si>
   <si>
     <t xml:space="preserve">2) VOLS ADDITIONNELS (en plus de la semaine type)</t>
@@ -449,25 +485,9 @@
       <charset val="1"/>
     </font>
     <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <i val="true"/>
       <sz val="8"/>
       <color rgb="FF595959"/>
-      <name val="Arial"/>
-      <family val="0"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <i val="true"/>
-      <sz val="8"/>
-      <color rgb="FF808080"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -481,7 +501,23 @@
       <charset val="1"/>
     </font>
     <font>
+      <b val="true"/>
+      <sz val="8"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
       <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Arial"/>
       <family val="0"/>
@@ -721,7 +757,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -774,7 +810,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -782,16 +818,28 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="4" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -802,19 +850,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -822,10 +866,6 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="166" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -834,7 +874,7 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="2" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -846,7 +886,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -858,11 +898,11 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="8" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -878,7 +918,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="9" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -890,47 +930,51 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="10" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="11" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="12" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="13" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="14" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="15" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="16" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="16" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="17" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="18" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="18" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="19" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="19" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="16" fillId="20" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -963,7 +1007,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="25">
+  <dxfs count="13">
     <dxf>
       <border diagonalUp="false" diagonalDown="false">
         <left style="medium">
@@ -980,186 +1024,6 @@
         </bottom>
         <diagonal/>
       </border>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF9DC3E6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FFFFFFFF"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF2E75B6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFE699"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFF4B183"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6E0B4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFD966"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD9D2E9"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFA9D08E"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF8FAADC"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFB7DEE8"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <name val="Arial"/>
-        <charset val="1"/>
-        <family val="0"/>
-        <b val="1"/>
-        <color rgb="FF000000"/>
-        <sz val="11"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFD5A6BD"/>
-        </patternFill>
-      </fill>
     </dxf>
     <dxf>
       <font>
@@ -1585,19 +1449,20 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:P101"/>
+  <dimension ref="B1:U114"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="15"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="0" width="3"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="0" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="0" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="21" min="17" style="0" width="9"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1725,31 +1590,31 @@
         <v>22</v>
       </c>
       <c r="C8" s="13" t="str">
-        <f aca="false">IF(C9="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),1)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C9)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,C9)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C9)=1,IFERROR(INDEX($D$62:$D$101,MATCH(C9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C9)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(C9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C9)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(C9="","",TRIM(O$12&amp;IF(AND(O$12&lt;&gt;"",O$13&lt;&gt;""),"/","")&amp;O$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C9)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,C9)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C9)=1,IFERROR(INDEX($D$75:$D$114,MATCH(C9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C9)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(C9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C9)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="D8" s="13" t="str">
-        <f aca="false">IF(D9="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),2)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D9)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,D9)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D9)=1,IFERROR(INDEX($D$62:$D$101,MATCH(D9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D9)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(D9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D9)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(D9="","",TRIM(P$12&amp;IF(AND(P$12&lt;&gt;"",P$13&lt;&gt;""),"/","")&amp;P$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D9)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,D9)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D9)=1,IFERROR(INDEX($D$75:$D$114,MATCH(D9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D9)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(D9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D9)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="E8" s="13" t="str">
-        <f aca="false">IF(E9="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),3)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E9)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,E9)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E9)=1,IFERROR(INDEX($D$62:$D$101,MATCH(E9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E9)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(E9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E9)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(E9="","",TRIM(Q$12&amp;IF(AND(Q$12&lt;&gt;"",Q$13&lt;&gt;""),"/","")&amp;Q$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E9)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,E9)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E9)=1,IFERROR(INDEX($D$75:$D$114,MATCH(E9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E9)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(E9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E9)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="F8" s="13" t="str">
-        <f aca="false">IF(F9="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),4)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F9)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,F9)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F9)=1,IFERROR(INDEX($D$62:$D$101,MATCH(F9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F9)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(F9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F9)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(F9="","",TRIM(R$12&amp;IF(AND(R$12&lt;&gt;"",R$13&lt;&gt;""),"/","")&amp;R$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F9)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,F9)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F9)=1,IFERROR(INDEX($D$75:$D$114,MATCH(F9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F9)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(F9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F9)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="G8" s="13" t="str">
-        <f aca="false">IF(G9="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),5)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G9)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,G9)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G9)=1,IFERROR(INDEX($D$62:$D$101,MATCH(G9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G9)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(G9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G9)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(G9="","",TRIM(S$12&amp;IF(AND(S$12&lt;&gt;"",S$13&lt;&gt;""),"/","")&amp;S$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G9)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,G9)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G9)=1,IFERROR(INDEX($D$75:$D$114,MATCH(G9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G9)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(G9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G9)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="H8" s="13" t="str">
-        <f aca="false">IF(H9="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),6)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H9)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,H9)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H9)=1,IFERROR(INDEX($D$62:$D$101,MATCH(H9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H9)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(H9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H9)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(H9="","",TRIM(T$12&amp;IF(AND(T$12&lt;&gt;"",T$13&lt;&gt;""),"/","")&amp;T$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H9)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,H9)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H9)=1,IFERROR(INDEX($D$75:$D$114,MATCH(H9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H9)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(H9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H9)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="I8" s="13" t="str">
-        <f aca="false">IF(I9="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),7)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I9)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,I9)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I9)=1,IFERROR(INDEX($D$62:$D$101,MATCH(I9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I9)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(I9&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I9)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(I9="","",TRIM(U$12&amp;IF(AND(U$12&lt;&gt;"",U$13&lt;&gt;""),"/","")&amp;U$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I9)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,I9)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I9)=1,IFERROR(INDEX($D$75:$D$114,MATCH(I9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I9)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(I9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I9)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="N8" s="7" t="s">
@@ -1806,36 +1671,43 @@
         <v>25</v>
       </c>
       <c r="C10" s="13" t="str">
-        <f aca="false">IF(C11="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),1)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C11)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,C11)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C11)=1,IFERROR(INDEX($D$62:$D$101,MATCH(C11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C11)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(C11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C11)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(C11="","",TRIM(O$12&amp;IF(AND(O$12&lt;&gt;"",O$13&lt;&gt;""),"/","")&amp;O$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C11)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,C11)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C11)=1,IFERROR(INDEX($D$75:$D$114,MATCH(C11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C11)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(C11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C11)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="D10" s="13" t="str">
-        <f aca="false">IF(D11="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),2)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D11)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,D11)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D11)=1,IFERROR(INDEX($D$62:$D$101,MATCH(D11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D11)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(D11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D11)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(D11="","",TRIM(P$12&amp;IF(AND(P$12&lt;&gt;"",P$13&lt;&gt;""),"/","")&amp;P$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D11)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,D11)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D11)=1,IFERROR(INDEX($D$75:$D$114,MATCH(D11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D11)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(D11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D11)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="E10" s="13" t="str">
-        <f aca="false">IF(E11="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),3)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E11)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,E11)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E11)=1,IFERROR(INDEX($D$62:$D$101,MATCH(E11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E11)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(E11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E11)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(E11="","",TRIM(Q$12&amp;IF(AND(Q$12&lt;&gt;"",Q$13&lt;&gt;""),"/","")&amp;Q$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E11)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,E11)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E11)=1,IFERROR(INDEX($D$75:$D$114,MATCH(E11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E11)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(E11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E11)&amp;" vols")&amp;")")))</f>
         <v>(+A320)</v>
       </c>
       <c r="F10" s="13" t="str">
-        <f aca="false">IF(F11="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),4)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F11)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,F11)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F11)=1,IFERROR(INDEX($D$62:$D$101,MATCH(F11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F11)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(F11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F11)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(F11="","",TRIM(R$12&amp;IF(AND(R$12&lt;&gt;"",R$13&lt;&gt;""),"/","")&amp;R$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F11)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,F11)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F11)=1,IFERROR(INDEX($D$75:$D$114,MATCH(F11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F11)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(F11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F11)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="G10" s="13" t="str">
-        <f aca="false">IF(G11="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),5)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G11)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,G11)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G11)=1,IFERROR(INDEX($D$62:$D$101,MATCH(G11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G11)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(G11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G11)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(G11="","",TRIM(S$12&amp;IF(AND(S$12&lt;&gt;"",S$13&lt;&gt;""),"/","")&amp;S$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G11)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,G11)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G11)=1,IFERROR(INDEX($D$75:$D$114,MATCH(G11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G11)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(G11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G11)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="H10" s="13" t="str">
-        <f aca="false">IF(H11="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),6)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H11)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,H11)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H11)=1,IFERROR(INDEX($D$62:$D$101,MATCH(H11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H11)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(H11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H11)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(H11="","",TRIM(T$12&amp;IF(AND(T$12&lt;&gt;"",T$13&lt;&gt;""),"/","")&amp;T$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H11)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,H11)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H11)=1,IFERROR(INDEX($D$75:$D$114,MATCH(H11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H11)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(H11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H11)&amp;" vols")&amp;")")))</f>
         <v>A320 (+A320)</v>
       </c>
       <c r="I10" s="13" t="str">
-        <f aca="false">IF(I11="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),7)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I11)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,I11)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I11)=1,IFERROR(INDEX($D$62:$D$101,MATCH(I11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I11)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(I11&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I11)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(I11="","",TRIM(U$12&amp;IF(AND(U$12&lt;&gt;"",U$13&lt;&gt;""),"/","")&amp;U$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I11)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,I11)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I11)=1,IFERROR(INDEX($D$75:$D$114,MATCH(I11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I11)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(I11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I11)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="N10" s="17" t="s">
         <v>26</v>
       </c>
+      <c r="O10" s="17"/>
+      <c r="P10" s="17"/>
+      <c r="Q10" s="17"/>
+      <c r="R10" s="17"/>
+      <c r="S10" s="17"/>
+      <c r="T10" s="17"/>
+      <c r="U10" s="17"/>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B11" s="15" t="str">
@@ -1870,37 +1742,92 @@
         <f aca="false">IF(OR($O$6+13&lt;$O$4,$O$6+13&gt;$O$5),"",$O$6+13)</f>
         <v>46488</v>
       </c>
+      <c r="N11" s="18" t="s">
+        <v>27</v>
+      </c>
+      <c r="O11" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="P11" s="18" t="s">
+        <v>29</v>
+      </c>
+      <c r="Q11" s="18" t="s">
+        <v>30</v>
+      </c>
+      <c r="R11" s="18" t="s">
+        <v>31</v>
+      </c>
+      <c r="S11" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="T11" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="U11" s="18" t="s">
+        <v>34</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B12" s="12" t="s">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="C12" s="13" t="str">
-        <f aca="false">IF(C13="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),1)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C13)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,C13)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C13)=1,IFERROR(INDEX($D$62:$D$101,MATCH(C13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C13)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(C13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C13)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(C13="","",TRIM(O$12&amp;IF(AND(O$12&lt;&gt;"",O$13&lt;&gt;""),"/","")&amp;O$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C13)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,C13)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C13)=1,IFERROR(INDEX($D$75:$D$114,MATCH(C13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C13)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(C13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C13)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="D12" s="13" t="str">
-        <f aca="false">IF(D13="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),2)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D13)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,D13)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D13)=1,IFERROR(INDEX($D$62:$D$101,MATCH(D13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D13)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(D13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D13)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(D13="","",TRIM(P$12&amp;IF(AND(P$12&lt;&gt;"",P$13&lt;&gt;""),"/","")&amp;P$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D13)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,D13)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D13)=1,IFERROR(INDEX($D$75:$D$114,MATCH(D13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D13)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(D13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D13)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="E12" s="13" t="str">
-        <f aca="false">IF(E13="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),3)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E13)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,E13)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E13)=1,IFERROR(INDEX($D$62:$D$101,MATCH(E13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E13)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(E13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E13)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(E13="","",TRIM(Q$12&amp;IF(AND(Q$12&lt;&gt;"",Q$13&lt;&gt;""),"/","")&amp;Q$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E13)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,E13)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E13)=1,IFERROR(INDEX($D$75:$D$114,MATCH(E13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E13)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(E13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E13)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="F12" s="13" t="str">
-        <f aca="false">IF(F13="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),4)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F13)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,F13)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F13)=1,IFERROR(INDEX($D$62:$D$101,MATCH(F13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F13)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(F13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F13)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(F13="","",TRIM(R$12&amp;IF(AND(R$12&lt;&gt;"",R$13&lt;&gt;""),"/","")&amp;R$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F13)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,F13)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F13)=1,IFERROR(INDEX($D$75:$D$114,MATCH(F13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F13)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(F13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F13)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="G12" s="13" t="str">
-        <f aca="false">IF(G13="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),5)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G13)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,G13)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G13)=1,IFERROR(INDEX($D$62:$D$101,MATCH(G13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G13)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(G13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G13)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(G13="","",TRIM(S$12&amp;IF(AND(S$12&lt;&gt;"",S$13&lt;&gt;""),"/","")&amp;S$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G13)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,G13)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G13)=1,IFERROR(INDEX($D$75:$D$114,MATCH(G13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G13)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(G13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G13)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="H12" s="13" t="str">
-        <f aca="false">IF(H13="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),6)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H13)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,H13)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H13)=1,IFERROR(INDEX($D$62:$D$101,MATCH(H13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H13)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(H13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H13)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(H13="","",TRIM(T$12&amp;IF(AND(T$12&lt;&gt;"",T$13&lt;&gt;""),"/","")&amp;T$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H13)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,H13)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H13)=1,IFERROR(INDEX($D$75:$D$114,MATCH(H13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H13)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(H13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H13)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="I12" s="13" t="str">
-        <f aca="false">IF(I13="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),7)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I13)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,I13)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I13)=1,IFERROR(INDEX($D$62:$D$101,MATCH(I13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I13)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(I13&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I13)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(I13="","",TRIM(U$12&amp;IF(AND(U$12&lt;&gt;"",U$13&lt;&gt;""),"/","")&amp;U$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I13)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,I13)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I13)=1,IFERROR(INDEX($D$75:$D$114,MATCH(I13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I13)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(I13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I13)&amp;" vols")&amp;")")))</f>
+        <v/>
+      </c>
+      <c r="N12" s="19" t="s">
+        <v>36</v>
+      </c>
+      <c r="O12" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+0,1)&amp;"","")</f>
+        <v>A320</v>
+      </c>
+      <c r="P12" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+0,2)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="Q12" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+0,3)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="R12" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+0,4)&amp;"","")</f>
+        <v>A320</v>
+      </c>
+      <c r="S12" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+0,5)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="T12" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+0,6)&amp;"","")</f>
+        <v>A320</v>
+      </c>
+      <c r="U12" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+0,7)&amp;"","")</f>
         <v/>
       </c>
     </row>
@@ -1937,37 +1864,68 @@
         <f aca="false">IF(OR($O$6+20&lt;$O$4,$O$6+20&gt;$O$5),"",$O$6+20)</f>
         <v>46495</v>
       </c>
+      <c r="N13" s="19" t="s">
+        <v>37</v>
+      </c>
+      <c r="O13" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+1,1)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="P13" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+1,2)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="Q13" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+1,3)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="R13" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+1,4)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="S13" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+1,5)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="T13" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+1,6)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="U13" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+1,7)&amp;"","")</f>
+        <v/>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B14" s="12" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="C14" s="13" t="str">
-        <f aca="false">IF(C15="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),1)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C15)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,C15)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C15)=1,IFERROR(INDEX($D$62:$D$101,MATCH(C15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C15)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(C15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C15)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(C15="","",TRIM(O$12&amp;IF(AND(O$12&lt;&gt;"",O$13&lt;&gt;""),"/","")&amp;O$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C15)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,C15)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C15)=1,IFERROR(INDEX($D$75:$D$114,MATCH(C15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C15)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(C15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C15)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="D14" s="13" t="str">
-        <f aca="false">IF(D15="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),2)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D15)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,D15)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D15)=1,IFERROR(INDEX($D$62:$D$101,MATCH(D15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D15)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(D15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D15)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(D15="","",TRIM(P$12&amp;IF(AND(P$12&lt;&gt;"",P$13&lt;&gt;""),"/","")&amp;P$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D15)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,D15)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D15)=1,IFERROR(INDEX($D$75:$D$114,MATCH(D15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D15)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(D15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D15)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="E14" s="13" t="str">
-        <f aca="false">IF(E15="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),3)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E15)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,E15)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E15)=1,IFERROR(INDEX($D$62:$D$101,MATCH(E15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E15)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(E15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E15)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(E15="","",TRIM(Q$12&amp;IF(AND(Q$12&lt;&gt;"",Q$13&lt;&gt;""),"/","")&amp;Q$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E15)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,E15)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E15)=1,IFERROR(INDEX($D$75:$D$114,MATCH(E15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E15)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(E15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E15)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="F14" s="13" t="str">
-        <f aca="false">IF(F15="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),4)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F15)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,F15)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F15)=1,IFERROR(INDEX($D$62:$D$101,MATCH(F15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F15)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(F15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F15)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(F15="","",TRIM(R$12&amp;IF(AND(R$12&lt;&gt;"",R$13&lt;&gt;""),"/","")&amp;R$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F15)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,F15)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F15)=1,IFERROR(INDEX($D$75:$D$114,MATCH(F15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F15)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(F15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F15)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="G14" s="13" t="str">
-        <f aca="false">IF(G15="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),5)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G15)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,G15)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G15)=1,IFERROR(INDEX($D$62:$D$101,MATCH(G15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G15)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(G15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G15)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(G15="","",TRIM(S$12&amp;IF(AND(S$12&lt;&gt;"",S$13&lt;&gt;""),"/","")&amp;S$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G15)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,G15)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G15)=1,IFERROR(INDEX($D$75:$D$114,MATCH(G15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G15)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(G15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G15)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="H14" s="13" t="str">
-        <f aca="false">IF(H15="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),6)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H15)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,H15)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H15)=1,IFERROR(INDEX($D$62:$D$101,MATCH(H15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H15)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(H15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H15)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(H15="","",TRIM(T$12&amp;IF(AND(T$12&lt;&gt;"",T$13&lt;&gt;""),"/","")&amp;T$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H15)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,H15)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H15)=1,IFERROR(INDEX($D$75:$D$114,MATCH(H15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H15)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(H15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H15)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="I14" s="13" t="str">
-        <f aca="false">IF(I15="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),7)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I15)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,I15)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I15)=1,IFERROR(INDEX($D$62:$D$101,MATCH(I15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I15)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(I15&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I15)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(I15="","",TRIM(U$12&amp;IF(AND(U$12&lt;&gt;"",U$13&lt;&gt;""),"/","")&amp;U$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I15)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,I15)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I15)=1,IFERROR(INDEX($D$75:$D$114,MATCH(I15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I15)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(I15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I15)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
     </row>
@@ -2007,34 +1965,34 @@
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="12" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="C16" s="13" t="str">
-        <f aca="false">IF(C17="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),1)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C17)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,C17)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C17)=1,IFERROR(INDEX($D$62:$D$101,MATCH(C17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C17)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(C17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C17)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(C17="","",TRIM(O$12&amp;IF(AND(O$12&lt;&gt;"",O$13&lt;&gt;""),"/","")&amp;O$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C17)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,C17)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C17)=1,IFERROR(INDEX($D$75:$D$114,MATCH(C17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C17)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(C17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C17)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="D16" s="13" t="str">
-        <f aca="false">IF(D17="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),2)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D17)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,D17)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D17)=1,IFERROR(INDEX($D$62:$D$101,MATCH(D17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D17)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(D17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D17)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(D17="","",TRIM(P$12&amp;IF(AND(P$12&lt;&gt;"",P$13&lt;&gt;""),"/","")&amp;P$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D17)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,D17)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D17)=1,IFERROR(INDEX($D$75:$D$114,MATCH(D17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D17)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(D17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D17)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="E16" s="13" t="str">
-        <f aca="false">IF(E17="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),3)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E17)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,E17)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E17)=1,IFERROR(INDEX($D$62:$D$101,MATCH(E17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E17)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(E17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E17)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(E17="","",TRIM(Q$12&amp;IF(AND(Q$12&lt;&gt;"",Q$13&lt;&gt;""),"/","")&amp;Q$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E17)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,E17)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E17)=1,IFERROR(INDEX($D$75:$D$114,MATCH(E17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E17)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(E17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E17)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="F16" s="13" t="str">
-        <f aca="false">IF(F17="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),4)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F17)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,F17)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F17)=1,IFERROR(INDEX($D$62:$D$101,MATCH(F17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F17)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(F17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F17)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(F17="","",TRIM(R$12&amp;IF(AND(R$12&lt;&gt;"",R$13&lt;&gt;""),"/","")&amp;R$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F17)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,F17)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F17)=1,IFERROR(INDEX($D$75:$D$114,MATCH(F17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F17)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(F17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F17)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="G16" s="13" t="str">
-        <f aca="false">IF(G17="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),5)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G17)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,G17)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G17)=1,IFERROR(INDEX($D$62:$D$101,MATCH(G17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G17)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(G17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G17)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(G17="","",TRIM(S$12&amp;IF(AND(S$12&lt;&gt;"",S$13&lt;&gt;""),"/","")&amp;S$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G17)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,G17)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G17)=1,IFERROR(INDEX($D$75:$D$114,MATCH(G17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G17)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(G17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G17)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="H16" s="13" t="str">
-        <f aca="false">IF(H17="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),6)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H17)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,H17)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H17)=1,IFERROR(INDEX($D$62:$D$101,MATCH(H17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H17)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(H17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H17)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(H17="","",TRIM(T$12&amp;IF(AND(T$12&lt;&gt;"",T$13&lt;&gt;""),"/","")&amp;T$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H17)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,H17)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H17)=1,IFERROR(INDEX($D$75:$D$114,MATCH(H17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H17)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(H17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H17)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="I16" s="13" t="str">
-        <f aca="false">IF(I17="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),7)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I17)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,I17)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I17)=1,IFERROR(INDEX($D$62:$D$101,MATCH(I17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I17)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(I17&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I17)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(I17="","",TRIM(U$12&amp;IF(AND(U$12&lt;&gt;"",U$13&lt;&gt;""),"/","")&amp;U$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I17)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,I17)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I17)=1,IFERROR(INDEX($D$75:$D$114,MATCH(I17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I17)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(I17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I17)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
     </row>
@@ -2074,34 +2032,34 @@
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="12" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="C18" s="13" t="str">
-        <f aca="false">IF(C19="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),1)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C19)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,C19)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C19)=1,IFERROR(INDEX($D$62:$D$101,MATCH(C19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C19)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(C19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,C19)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(C19="","",TRIM(O$12&amp;IF(AND(O$12&lt;&gt;"",O$13&lt;&gt;""),"/","")&amp;O$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C19)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,C19)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C19)=1,IFERROR(INDEX($D$75:$D$114,MATCH(C19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C19)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(C19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="D18" s="13" t="str">
-        <f aca="false">IF(D19="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),2)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D19)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,D19)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D19)=1,IFERROR(INDEX($D$62:$D$101,MATCH(D19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D19)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(D19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,D19)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(D19="","",TRIM(P$12&amp;IF(AND(P$12&lt;&gt;"",P$13&lt;&gt;""),"/","")&amp;P$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D19)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,D19)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D19)=1,IFERROR(INDEX($D$75:$D$114,MATCH(D19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D19)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(D19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="E18" s="13" t="str">
-        <f aca="false">IF(E19="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),3)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E19)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,E19)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E19)=1,IFERROR(INDEX($D$62:$D$101,MATCH(E19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E19)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(E19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,E19)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(E19="","",TRIM(Q$12&amp;IF(AND(Q$12&lt;&gt;"",Q$13&lt;&gt;""),"/","")&amp;Q$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E19)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,E19)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E19)=1,IFERROR(INDEX($D$75:$D$114,MATCH(E19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E19)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(E19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="F18" s="13" t="str">
-        <f aca="false">IF(F19="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),4)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F19)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,F19)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F19)=1,IFERROR(INDEX($D$62:$D$101,MATCH(F19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F19)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(F19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,F19)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(F19="","",TRIM(R$12&amp;IF(AND(R$12&lt;&gt;"",R$13&lt;&gt;""),"/","")&amp;R$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F19)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,F19)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F19)=1,IFERROR(INDEX($D$75:$D$114,MATCH(F19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F19)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(F19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="G18" s="13" t="str">
-        <f aca="false">IF(G19="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),5)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G19)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,G19)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G19)=1,IFERROR(INDEX($D$62:$D$101,MATCH(G19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G19)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(G19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,G19)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(G19="","",TRIM(S$12&amp;IF(AND(S$12&lt;&gt;"",S$13&lt;&gt;""),"/","")&amp;S$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G19)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,G19)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G19)=1,IFERROR(INDEX($D$75:$D$114,MATCH(G19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G19)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(G19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="H18" s="13" t="str">
-        <f aca="false">IF(H19="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),6)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H19)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,H19)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H19)=1,IFERROR(INDEX($D$62:$D$101,MATCH(H19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H19)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(H19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,H19)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(H19="","",TRIM(T$12&amp;IF(AND(T$12&lt;&gt;"",T$13&lt;&gt;""),"/","")&amp;T$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H19)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,H19)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H19)=1,IFERROR(INDEX($D$75:$D$114,MATCH(H19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H19)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(H19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="I18" s="13" t="str">
-        <f aca="false">IF(I19="","",TRIM(IFERROR(INDEX($C$45:$I$56,MATCH($C$5,$B$45:$B$56,0),7)&amp;"","")&amp;IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I19)=0,""," (+"&amp;IF(COUNTIFS($C$62:$C$101,$C$5,$B$62:$B$101,I19)=1,IF(SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I19)=1,IFERROR(INDEX($D$62:$D$101,MATCH(I19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),""),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I19)&amp;"x"&amp;IFERROR(INDEX($D$62:$D$101,MATCH(I19&amp;"|"&amp;$C$5,$J$62:$J$101,0)),"")),SUMIFS($E$62:$E$101,$C$62:$C$101,$C$5,$B$62:$B$101,I19)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(I19="","",TRIM(U$12&amp;IF(AND(U$12&lt;&gt;"",U$13&lt;&gt;""),"/","")&amp;U$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I19)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,I19)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I19)=1,IFERROR(INDEX($D$75:$D$114,MATCH(I19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I19)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(I19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
     </row>
@@ -2140,58 +2098,58 @@
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="C20" s="19" t="n">
+      <c r="B20" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="C20" s="22" t="n">
         <f aca="false">COUNT(C9,C11,C13,C15,C17,C19)</f>
         <v>4</v>
       </c>
-      <c r="D20" s="19" t="n">
+      <c r="D20" s="22" t="n">
         <f aca="false">COUNT(D9,D11,D13,D15,D17,D19)</f>
         <v>4</v>
       </c>
-      <c r="E20" s="19" t="n">
+      <c r="E20" s="22" t="n">
         <f aca="false">COUNT(E9,E11,E13,E15,E17,E19)</f>
         <v>4</v>
       </c>
-      <c r="F20" s="19" t="n">
+      <c r="F20" s="22" t="n">
         <f aca="false">COUNT(F9,F11,F13,F15,F17,F19)</f>
         <v>5</v>
       </c>
-      <c r="G20" s="19" t="n">
+      <c r="G20" s="22" t="n">
         <f aca="false">COUNT(G9,G11,G13,G15,G17,G19)</f>
         <v>5</v>
       </c>
-      <c r="H20" s="19" t="n">
+      <c r="H20" s="22" t="n">
         <f aca="false">COUNT(H9,H11,H13,H15,H17,H19)</f>
         <v>4</v>
       </c>
-      <c r="I20" s="19" t="n">
+      <c r="I20" s="22" t="n">
         <f aca="false">COUNT(I9,I11,I13,I15,I17,I19)</f>
         <v>4</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="C21" s="19" t="n">
+      <c r="B21" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="22" t="n">
         <f aca="false">IF(COUNT(C9:I9)&gt;0,1,0)+IF(COUNT(C11:I11)&gt;0,1,0)+IF(COUNT(C13:I13)&gt;0,1,0)+IF(COUNT(C15:I15)&gt;0,1,0)+IF(COUNT(C17:I17)&gt;0,1,0)+IF(COUNT(C19:I19)&gt;0,1,0)</f>
         <v>5</v>
       </c>
-      <c r="D21" s="20" t="s">
-        <v>33</v>
-      </c>
-      <c r="E21" s="20"/>
-      <c r="F21" s="20"/>
-      <c r="G21" s="20"/>
-      <c r="H21" s="20"/>
-      <c r="I21" s="20"/>
+      <c r="D21" s="23" t="s">
+        <v>43</v>
+      </c>
+      <c r="E21" s="23"/>
+      <c r="F21" s="23"/>
+      <c r="G21" s="23"/>
+      <c r="H21" s="23"/>
+      <c r="I21" s="23"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="9" t="s">
-        <v>34</v>
+        <v>44</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
@@ -2205,1706 +2163,1944 @@
       <c r="L23" s="9"/>
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B24" s="21" t="s">
-        <v>35</v>
-      </c>
-      <c r="C24" s="21" t="s">
+      <c r="B24" s="24" t="s">
+        <v>45</v>
+      </c>
+      <c r="C24" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="D24" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="E24" s="21" t="s">
-        <v>37</v>
-      </c>
-      <c r="F24" s="21" t="s">
-        <v>38</v>
-      </c>
-      <c r="G24" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="H24" s="21" t="s">
-        <v>40</v>
-      </c>
-      <c r="I24" s="21" t="s">
-        <v>41</v>
-      </c>
-      <c r="J24" s="21" t="s">
-        <v>42</v>
-      </c>
-      <c r="K24" s="21" t="s">
-        <v>43</v>
-      </c>
-      <c r="L24" s="21" t="s">
-        <v>44</v>
+      <c r="D24" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="E24" s="24" t="s">
+        <v>47</v>
+      </c>
+      <c r="F24" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="G24" s="24" t="s">
+        <v>49</v>
+      </c>
+      <c r="H24" s="24" t="s">
+        <v>50</v>
+      </c>
+      <c r="I24" s="24" t="s">
+        <v>51</v>
+      </c>
+      <c r="J24" s="24" t="s">
+        <v>52</v>
+      </c>
+      <c r="K24" s="24" t="s">
+        <v>53</v>
+      </c>
+      <c r="L24" s="24" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B25" s="22" t="str">
+      <c r="B25" s="13" t="str">
         <f aca="false">$B$45</f>
         <v>CDGRUN</v>
       </c>
-      <c r="C25" s="23" t="str">
+      <c r="C25" s="20" t="str">
         <f aca="false">$K$45</f>
-        <v>77W(4), 778(3)</v>
-      </c>
-      <c r="D25" s="23" t="str">
-        <f aca="false">IF(COUNTA($C$45:$I$45)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$45&lt;&gt;"","J1 ","")&amp;IF($D$45&lt;&gt;"","J2 ","")&amp;IF($E$45&lt;&gt;"","J3 ","")&amp;IF($F$45&lt;&gt;"","J4 ","")&amp;IF($G$45&lt;&gt;"","J5 ","")&amp;IF($H$45&lt;&gt;"","J6 ","")&amp;IF($I$45&lt;&gt;"","J7 ",""))," ",", "))</f>
+        <v>77W(7), 778(2)</v>
+      </c>
+      <c r="D25" s="20" t="str">
+        <f aca="false">IF(COUNTA($C$45:$I$46)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$45:$C$46)&gt;0,"J1 ","")&amp;IF(COUNTA($D$45:$D$46)&gt;0,"J2 ","")&amp;IF(COUNTA($E$45:$E$46)&gt;0,"J3 ","")&amp;IF(COUNTA($F$45:$F$46)&gt;0,"J4 ","")&amp;IF(COUNTA($G$45:$G$46)&gt;0,"J5 ","")&amp;IF(COUNTA($H$45:$H$46)&gt;0,"J6 ","")&amp;IF(COUNTA($I$45:$I$46)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J1, J2, J3, J4, J5, J6, J7</v>
       </c>
-      <c r="E25" s="24" t="n">
+      <c r="E25" s="25" t="n">
         <f aca="false">$J$45</f>
-        <v>7</v>
-      </c>
-      <c r="F25" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="F25" s="25" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G25" s="25" t="n">
+      <c r="G25" s="26" t="n">
         <f aca="false">H25+I25</f>
-        <v>32</v>
-      </c>
-      <c r="H25" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45&lt;&gt;""))</f>
+        <v>41</v>
+      </c>
+      <c r="H25" s="25" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$46:$I$46&lt;&gt;""))</f>
+        <v>39</v>
+      </c>
+      <c r="I25" s="25" t="n">
+        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B25,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+        <v>2</v>
+      </c>
+      <c r="J25" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45="77W"))+SUMPRODUCT($C$20:$I$20,--($C$46:$I$46="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B25,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>30</v>
       </c>
-      <c r="I25" s="24" t="n">
-        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B25,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
-        <v>2</v>
-      </c>
-      <c r="J25" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B25,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
-        <v>17</v>
-      </c>
-      <c r="K25" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B25,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
-        <v>15</v>
-      </c>
-      <c r="L25" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B25,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="K25" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45="778"))+SUMPRODUCT($C$20:$I$20,--($C$46:$I$46="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B25,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+        <v>11</v>
+      </c>
+      <c r="L25" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45="A320"))+SUMPRODUCT($C$20:$I$20,--($C$46:$I$46="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B25,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B26" s="22" t="str">
-        <f aca="false">$B$46</f>
+      <c r="B26" s="13" t="str">
+        <f aca="false">$B$47</f>
         <v>CDGDZA</v>
       </c>
-      <c r="C26" s="23" t="str">
-        <f aca="false">$K$46</f>
+      <c r="C26" s="20" t="str">
+        <f aca="false">$K$47</f>
         <v>77W(1), 778(2)</v>
       </c>
-      <c r="D26" s="23" t="str">
-        <f aca="false">IF(COUNTA($C$46:$I$46)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$46&lt;&gt;"","J1 ","")&amp;IF($D$46&lt;&gt;"","J2 ","")&amp;IF($E$46&lt;&gt;"","J3 ","")&amp;IF($F$46&lt;&gt;"","J4 ","")&amp;IF($G$46&lt;&gt;"","J5 ","")&amp;IF($H$46&lt;&gt;"","J6 ","")&amp;IF($I$46&lt;&gt;"","J7 ",""))," ",", "))</f>
+      <c r="D26" s="20" t="str">
+        <f aca="false">IF(COUNTA($C$47:$I$48)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$47:$C$48)&gt;0,"J1 ","")&amp;IF(COUNTA($D$47:$D$48)&gt;0,"J2 ","")&amp;IF(COUNTA($E$47:$E$48)&gt;0,"J3 ","")&amp;IF(COUNTA($F$47:$F$48)&gt;0,"J4 ","")&amp;IF(COUNTA($G$47:$G$48)&gt;0,"J5 ","")&amp;IF(COUNTA($H$47:$H$48)&gt;0,"J6 ","")&amp;IF(COUNTA($I$47:$I$48)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J2, J5, J7</v>
       </c>
-      <c r="E26" s="24" t="n">
-        <f aca="false">$J$46</f>
+      <c r="E26" s="25" t="n">
+        <f aca="false">$J$47</f>
         <v>3</v>
       </c>
-      <c r="F26" s="24" t="n">
+      <c r="F26" s="25" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G26" s="25" t="n">
+      <c r="G26" s="26" t="n">
         <f aca="false">H26+I26</f>
         <v>13</v>
       </c>
-      <c r="H26" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$46:$I$46&lt;&gt;""))</f>
+      <c r="H26" s="25" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$47:$I$47&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$48:$I$48&lt;&gt;""))</f>
         <v>13</v>
       </c>
-      <c r="I26" s="24" t="n">
-        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B26,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="I26" s="25" t="n">
+        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B26,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$46:$I$46="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B26,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="J26" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$47:$I$47="77W"))+SUMPRODUCT($C$20:$I$20,--($C$48:$I$48="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B26,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>4</v>
       </c>
-      <c r="K26" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$46:$I$46="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B26,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="K26" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$47:$I$47="778"))+SUMPRODUCT($C$20:$I$20,--($C$48:$I$48="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B26,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>9</v>
       </c>
-      <c r="L26" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$46:$I$46="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B26,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="L26" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$47:$I$47="A320"))+SUMPRODUCT($C$20:$I$20,--($C$48:$I$48="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B26,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B27" s="22" t="str">
-        <f aca="false">$B$47</f>
+      <c r="B27" s="13" t="str">
+        <f aca="false">$B$49</f>
         <v>BKKRUN</v>
       </c>
-      <c r="C27" s="23" t="str">
-        <f aca="false">$K$47</f>
+      <c r="C27" s="20" t="str">
+        <f aca="false">$K$49</f>
         <v>778(2)</v>
       </c>
-      <c r="D27" s="23" t="str">
-        <f aca="false">IF(COUNTA($C$47:$I$47)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$47&lt;&gt;"","J1 ","")&amp;IF($D$47&lt;&gt;"","J2 ","")&amp;IF($E$47&lt;&gt;"","J3 ","")&amp;IF($F$47&lt;&gt;"","J4 ","")&amp;IF($G$47&lt;&gt;"","J5 ","")&amp;IF($H$47&lt;&gt;"","J6 ","")&amp;IF($I$47&lt;&gt;"","J7 ",""))," ",", "))</f>
+      <c r="D27" s="20" t="str">
+        <f aca="false">IF(COUNTA($C$49:$I$50)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$49:$C$50)&gt;0,"J1 ","")&amp;IF(COUNTA($D$49:$D$50)&gt;0,"J2 ","")&amp;IF(COUNTA($E$49:$E$50)&gt;0,"J3 ","")&amp;IF(COUNTA($F$49:$F$50)&gt;0,"J4 ","")&amp;IF(COUNTA($G$49:$G$50)&gt;0,"J5 ","")&amp;IF(COUNTA($H$49:$H$50)&gt;0,"J6 ","")&amp;IF(COUNTA($I$49:$I$50)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J3, J6</v>
       </c>
-      <c r="E27" s="24" t="n">
-        <f aca="false">$J$47</f>
+      <c r="E27" s="25" t="n">
+        <f aca="false">$J$49</f>
         <v>2</v>
       </c>
-      <c r="F27" s="24" t="n">
+      <c r="F27" s="25" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G27" s="25" t="n">
+      <c r="G27" s="26" t="n">
         <f aca="false">H27+I27</f>
         <v>8</v>
       </c>
-      <c r="H27" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$47:$I$47&lt;&gt;""))</f>
+      <c r="H27" s="25" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$49:$I$49&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$50:$I$50&lt;&gt;""))</f>
         <v>8</v>
       </c>
-      <c r="I27" s="24" t="n">
-        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B27,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="I27" s="25" t="n">
+        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B27,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$47:$I$47="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B27,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="J27" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$49:$I$49="77W"))+SUMPRODUCT($C$20:$I$20,--($C$50:$I$50="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B27,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K27" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$47:$I$47="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B27,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="K27" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$49:$I$49="778"))+SUMPRODUCT($C$20:$I$20,--($C$50:$I$50="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B27,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>8</v>
       </c>
-      <c r="L27" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$47:$I$47="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B27,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="L27" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$49:$I$49="A320"))+SUMPRODUCT($C$20:$I$20,--($C$50:$I$50="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B27,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B28" s="22" t="str">
-        <f aca="false">$B$48</f>
+      <c r="B28" s="13" t="str">
+        <f aca="false">$B$51</f>
         <v>DZARUN</v>
       </c>
-      <c r="C28" s="23" t="str">
-        <f aca="false">$K$48</f>
-        <v>A320(5)</v>
-      </c>
-      <c r="D28" s="23" t="str">
-        <f aca="false">IF(COUNTA($C$48:$I$48)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$48&lt;&gt;"","J1 ","")&amp;IF($D$48&lt;&gt;"","J2 ","")&amp;IF($E$48&lt;&gt;"","J3 ","")&amp;IF($F$48&lt;&gt;"","J4 ","")&amp;IF($G$48&lt;&gt;"","J5 ","")&amp;IF($H$48&lt;&gt;"","J6 ","")&amp;IF($I$48&lt;&gt;"","J7 ",""))," ",", "))</f>
+      <c r="C28" s="20" t="str">
+        <f aca="false">$K$51</f>
+        <v>778(1), A320(5)</v>
+      </c>
+      <c r="D28" s="20" t="str">
+        <f aca="false">IF(COUNTA($C$51:$I$52)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$51:$C$52)&gt;0,"J1 ","")&amp;IF(COUNTA($D$51:$D$52)&gt;0,"J2 ","")&amp;IF(COUNTA($E$51:$E$52)&gt;0,"J3 ","")&amp;IF(COUNTA($F$51:$F$52)&gt;0,"J4 ","")&amp;IF(COUNTA($G$51:$G$52)&gt;0,"J5 ","")&amp;IF(COUNTA($H$51:$H$52)&gt;0,"J6 ","")&amp;IF(COUNTA($I$51:$I$52)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J1, J2, J3, J4, J5</v>
       </c>
-      <c r="E28" s="24" t="n">
-        <f aca="false">$J$48</f>
-        <v>5</v>
-      </c>
-      <c r="F28" s="24" t="n">
+      <c r="E28" s="25" t="n">
+        <f aca="false">$J$51</f>
+        <v>6</v>
+      </c>
+      <c r="F28" s="25" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G28" s="25" t="n">
+      <c r="G28" s="26" t="n">
         <f aca="false">H28+I28</f>
+        <v>26</v>
+      </c>
+      <c r="H28" s="25" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$52:$I$52&lt;&gt;""))</f>
+        <v>26</v>
+      </c>
+      <c r="I28" s="25" t="n">
+        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B28,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="J28" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51="77W"))+SUMPRODUCT($C$20:$I$20,--($C$52:$I$52="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B28,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+        <v>0</v>
+      </c>
+      <c r="K28" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51="778"))+SUMPRODUCT($C$20:$I$20,--($C$52:$I$52="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B28,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+        <v>4</v>
+      </c>
+      <c r="L28" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51="A320"))+SUMPRODUCT($C$20:$I$20,--($C$52:$I$52="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B28,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>22</v>
       </c>
-      <c r="H28" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$48:$I$48&lt;&gt;""))</f>
-        <v>22</v>
-      </c>
-      <c r="I28" s="24" t="n">
-        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B28,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
-        <v>0</v>
-      </c>
-      <c r="J28" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$48:$I$48="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B28,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
-        <v>0</v>
-      </c>
-      <c r="K28" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$48:$I$48="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B28,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
-        <v>0</v>
-      </c>
-      <c r="L28" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$48:$I$48="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B28,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
-        <v>22</v>
-      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B29" s="22" t="str">
-        <f aca="false">$B$49</f>
+      <c r="B29" s="13" t="str">
+        <f aca="false">$B$53</f>
         <v>MRURUN</v>
       </c>
-      <c r="C29" s="23" t="str">
-        <f aca="false">$K$49</f>
+      <c r="C29" s="20" t="str">
+        <f aca="false">$K$53</f>
         <v>A320(4)</v>
       </c>
-      <c r="D29" s="23" t="str">
-        <f aca="false">IF(COUNTA($C$49:$I$49)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$49&lt;&gt;"","J1 ","")&amp;IF($D$49&lt;&gt;"","J2 ","")&amp;IF($E$49&lt;&gt;"","J3 ","")&amp;IF($F$49&lt;&gt;"","J4 ","")&amp;IF($G$49&lt;&gt;"","J5 ","")&amp;IF($H$49&lt;&gt;"","J6 ","")&amp;IF($I$49&lt;&gt;"","J7 ",""))," ",", "))</f>
+      <c r="D29" s="20" t="str">
+        <f aca="false">IF(COUNTA($C$53:$I$54)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$53:$C$54)&gt;0,"J1 ","")&amp;IF(COUNTA($D$53:$D$54)&gt;0,"J2 ","")&amp;IF(COUNTA($E$53:$E$54)&gt;0,"J3 ","")&amp;IF(COUNTA($F$53:$F$54)&gt;0,"J4 ","")&amp;IF(COUNTA($G$53:$G$54)&gt;0,"J5 ","")&amp;IF(COUNTA($H$53:$H$54)&gt;0,"J6 ","")&amp;IF(COUNTA($I$53:$I$54)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J1, J3, J5, J7</v>
       </c>
-      <c r="E29" s="24" t="n">
-        <f aca="false">$J$49</f>
+      <c r="E29" s="25" t="n">
+        <f aca="false">$J$53</f>
         <v>4</v>
       </c>
-      <c r="F29" s="24" t="n">
+      <c r="F29" s="25" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G29" s="25" t="n">
+      <c r="G29" s="26" t="n">
         <f aca="false">H29+I29</f>
         <v>17</v>
       </c>
-      <c r="H29" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$49:$I$49&lt;&gt;""))</f>
+      <c r="H29" s="25" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$53:$I$53&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$54:$I$54&lt;&gt;""))</f>
         <v>17</v>
       </c>
-      <c r="I29" s="24" t="n">
-        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B29,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="I29" s="25" t="n">
+        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B29,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$49:$I$49="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B29,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="J29" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$53:$I$53="77W"))+SUMPRODUCT($C$20:$I$20,--($C$54:$I$54="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B29,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K29" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$49:$I$49="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B29,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="K29" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$53:$I$53="778"))+SUMPRODUCT($C$20:$I$20,--($C$54:$I$54="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B29,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="L29" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$49:$I$49="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B29,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="L29" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$53:$I$53="A320"))+SUMPRODUCT($C$20:$I$20,--($C$54:$I$54="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B29,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>17</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B30" s="22" t="str">
-        <f aca="false">$B$50</f>
+      <c r="B30" s="13" t="str">
+        <f aca="false">$B$55</f>
         <v>NOSRUN</v>
       </c>
-      <c r="C30" s="23" t="str">
-        <f aca="false">$K$50</f>
+      <c r="C30" s="20" t="str">
+        <f aca="false">$K$55</f>
         <v>A320(3)</v>
       </c>
-      <c r="D30" s="23" t="str">
-        <f aca="false">IF(COUNTA($C$50:$I$50)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$50&lt;&gt;"","J1 ","")&amp;IF($D$50&lt;&gt;"","J2 ","")&amp;IF($E$50&lt;&gt;"","J3 ","")&amp;IF($F$50&lt;&gt;"","J4 ","")&amp;IF($G$50&lt;&gt;"","J5 ","")&amp;IF($H$50&lt;&gt;"","J6 ","")&amp;IF($I$50&lt;&gt;"","J7 ",""))," ",", "))</f>
+      <c r="D30" s="20" t="str">
+        <f aca="false">IF(COUNTA($C$55:$I$56)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$55:$C$56)&gt;0,"J1 ","")&amp;IF(COUNTA($D$55:$D$56)&gt;0,"J2 ","")&amp;IF(COUNTA($E$55:$E$56)&gt;0,"J3 ","")&amp;IF(COUNTA($F$55:$F$56)&gt;0,"J4 ","")&amp;IF(COUNTA($G$55:$G$56)&gt;0,"J5 ","")&amp;IF(COUNTA($H$55:$H$56)&gt;0,"J6 ","")&amp;IF(COUNTA($I$55:$I$56)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J1, J4, J6</v>
       </c>
-      <c r="E30" s="24" t="n">
-        <f aca="false">$J$50</f>
+      <c r="E30" s="25" t="n">
+        <f aca="false">$J$55</f>
         <v>3</v>
       </c>
-      <c r="F30" s="24" t="n">
+      <c r="F30" s="25" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G30" s="25" t="n">
+      <c r="G30" s="26" t="n">
         <f aca="false">H30+I30</f>
         <v>15</v>
       </c>
-      <c r="H30" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$50:$I$50&lt;&gt;""))</f>
+      <c r="H30" s="25" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$55:$I$55&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$56:$I$56&lt;&gt;""))</f>
         <v>13</v>
       </c>
-      <c r="I30" s="24" t="n">
-        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B30,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="I30" s="25" t="n">
+        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B30,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>2</v>
       </c>
-      <c r="J30" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$50:$I$50="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B30,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="J30" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$55:$I$55="77W"))+SUMPRODUCT($C$20:$I$20,--($C$56:$I$56="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B30,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K30" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$50:$I$50="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B30,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="K30" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$55:$I$55="778"))+SUMPRODUCT($C$20:$I$20,--($C$56:$I$56="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B30,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="L30" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$50:$I$50="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B30,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="L30" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$55:$I$55="A320"))+SUMPRODUCT($C$20:$I$20,--($C$56:$I$56="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B30,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>15</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B31" s="22" t="str">
-        <f aca="false">$B$51</f>
+      <c r="B31" s="13" t="str">
+        <f aca="false">$B$57</f>
         <v>RUNTNR</v>
       </c>
-      <c r="C31" s="23" t="str">
-        <f aca="false">$K$51</f>
+      <c r="C31" s="20" t="str">
+        <f aca="false">$K$57</f>
         <v>A320(3)</v>
       </c>
-      <c r="D31" s="23" t="str">
-        <f aca="false">IF(COUNTA($C$51:$I$51)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$51&lt;&gt;"","J1 ","")&amp;IF($D$51&lt;&gt;"","J2 ","")&amp;IF($E$51&lt;&gt;"","J3 ","")&amp;IF($F$51&lt;&gt;"","J4 ","")&amp;IF($G$51&lt;&gt;"","J5 ","")&amp;IF($H$51&lt;&gt;"","J6 ","")&amp;IF($I$51&lt;&gt;"","J7 ",""))," ",", "))</f>
+      <c r="D31" s="20" t="str">
+        <f aca="false">IF(COUNTA($C$57:$I$58)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$57:$C$58)&gt;0,"J1 ","")&amp;IF(COUNTA($D$57:$D$58)&gt;0,"J2 ","")&amp;IF(COUNTA($E$57:$E$58)&gt;0,"J3 ","")&amp;IF(COUNTA($F$57:$F$58)&gt;0,"J4 ","")&amp;IF(COUNTA($G$57:$G$58)&gt;0,"J5 ","")&amp;IF(COUNTA($H$57:$H$58)&gt;0,"J6 ","")&amp;IF(COUNTA($I$57:$I$58)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J2, J4, J6</v>
       </c>
-      <c r="E31" s="24" t="n">
-        <f aca="false">$J$51</f>
+      <c r="E31" s="25" t="n">
+        <f aca="false">$J$57</f>
         <v>3</v>
       </c>
-      <c r="F31" s="24" t="n">
+      <c r="F31" s="25" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G31" s="25" t="n">
+      <c r="G31" s="26" t="n">
         <f aca="false">H31+I31</f>
         <v>13</v>
       </c>
-      <c r="H31" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51&lt;&gt;""))</f>
+      <c r="H31" s="25" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$57:$I$57&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$58:$I$58&lt;&gt;""))</f>
         <v>13</v>
       </c>
-      <c r="I31" s="24" t="n">
-        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B31,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="I31" s="25" t="n">
+        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B31,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J31" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B31,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="J31" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$57:$I$57="77W"))+SUMPRODUCT($C$20:$I$20,--($C$58:$I$58="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B31,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K31" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B31,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="K31" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$57:$I$57="778"))+SUMPRODUCT($C$20:$I$20,--($C$58:$I$58="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B31,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="L31" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B31,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="L31" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$57:$I$57="A320"))+SUMPRODUCT($C$20:$I$20,--($C$58:$I$58="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B31,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>13</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B32" s="22" t="str">
-        <f aca="false">$B$52</f>
+      <c r="B32" s="13" t="str">
+        <f aca="false">$B$59</f>
         <v>JNBRUN</v>
       </c>
-      <c r="C32" s="23" t="str">
-        <f aca="false">$K$52</f>
+      <c r="C32" s="20" t="str">
+        <f aca="false">$K$59</f>
         <v>778(2)</v>
       </c>
-      <c r="D32" s="23" t="str">
-        <f aca="false">IF(COUNTA($C$52:$I$52)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$52&lt;&gt;"","J1 ","")&amp;IF($D$52&lt;&gt;"","J2 ","")&amp;IF($E$52&lt;&gt;"","J3 ","")&amp;IF($F$52&lt;&gt;"","J4 ","")&amp;IF($G$52&lt;&gt;"","J5 ","")&amp;IF($H$52&lt;&gt;"","J6 ","")&amp;IF($I$52&lt;&gt;"","J7 ",""))," ",", "))</f>
+      <c r="D32" s="20" t="str">
+        <f aca="false">IF(COUNTA($C$59:$I$60)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$59:$C$60)&gt;0,"J1 ","")&amp;IF(COUNTA($D$59:$D$60)&gt;0,"J2 ","")&amp;IF(COUNTA($E$59:$E$60)&gt;0,"J3 ","")&amp;IF(COUNTA($F$59:$F$60)&gt;0,"J4 ","")&amp;IF(COUNTA($G$59:$G$60)&gt;0,"J5 ","")&amp;IF(COUNTA($H$59:$H$60)&gt;0,"J6 ","")&amp;IF(COUNTA($I$59:$I$60)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J1, J5</v>
       </c>
-      <c r="E32" s="24" t="n">
-        <f aca="false">$J$52</f>
+      <c r="E32" s="25" t="n">
+        <f aca="false">$J$59</f>
         <v>2</v>
       </c>
-      <c r="F32" s="24" t="n">
+      <c r="F32" s="25" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G32" s="25" t="n">
+      <c r="G32" s="26" t="n">
         <f aca="false">H32+I32</f>
         <v>9</v>
       </c>
-      <c r="H32" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$52:$I$52&lt;&gt;""))</f>
+      <c r="H32" s="25" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$59:$I$59&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$60:$I$60&lt;&gt;""))</f>
         <v>9</v>
       </c>
-      <c r="I32" s="24" t="n">
-        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B32,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="I32" s="25" t="n">
+        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B32,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J32" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$52:$I$52="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B32,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="J32" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$59:$I$59="77W"))+SUMPRODUCT($C$20:$I$20,--($C$60:$I$60="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B32,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K32" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$52:$I$52="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B32,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="K32" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$59:$I$59="778"))+SUMPRODUCT($C$20:$I$20,--($C$60:$I$60="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B32,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>9</v>
       </c>
-      <c r="L32" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$52:$I$52="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B32,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="L32" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$59:$I$59="A320"))+SUMPRODUCT($C$20:$I$20,--($C$60:$I$60="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B32,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B33" s="22" t="str">
-        <f aca="false">$B$53</f>
+      <c r="B33" s="13" t="str">
+        <f aca="false">$B$61</f>
         <v>CPTRUN</v>
       </c>
-      <c r="C33" s="23" t="str">
-        <f aca="false">$K$53</f>
+      <c r="C33" s="20" t="str">
+        <f aca="false">$K$61</f>
         <v>778(1)</v>
       </c>
-      <c r="D33" s="23" t="str">
-        <f aca="false">IF(COUNTA($C$53:$I$53)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$53&lt;&gt;"","J1 ","")&amp;IF($D$53&lt;&gt;"","J2 ","")&amp;IF($E$53&lt;&gt;"","J3 ","")&amp;IF($F$53&lt;&gt;"","J4 ","")&amp;IF($G$53&lt;&gt;"","J5 ","")&amp;IF($H$53&lt;&gt;"","J6 ","")&amp;IF($I$53&lt;&gt;"","J7 ",""))," ",", "))</f>
+      <c r="D33" s="20" t="str">
+        <f aca="false">IF(COUNTA($C$61:$I$62)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$61:$C$62)&gt;0,"J1 ","")&amp;IF(COUNTA($D$61:$D$62)&gt;0,"J2 ","")&amp;IF(COUNTA($E$61:$E$62)&gt;0,"J3 ","")&amp;IF(COUNTA($F$61:$F$62)&gt;0,"J4 ","")&amp;IF(COUNTA($G$61:$G$62)&gt;0,"J5 ","")&amp;IF(COUNTA($H$61:$H$62)&gt;0,"J6 ","")&amp;IF(COUNTA($I$61:$I$62)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J4</v>
       </c>
-      <c r="E33" s="24" t="n">
-        <f aca="false">$J$53</f>
+      <c r="E33" s="25" t="n">
+        <f aca="false">$J$61</f>
         <v>1</v>
       </c>
-      <c r="F33" s="24" t="n">
+      <c r="F33" s="25" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G33" s="25" t="n">
+      <c r="G33" s="26" t="n">
         <f aca="false">H33+I33</f>
         <v>5</v>
       </c>
-      <c r="H33" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$53:$I$53&lt;&gt;""))</f>
+      <c r="H33" s="25" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$61:$I$61&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$62:$I$62&lt;&gt;""))</f>
         <v>5</v>
       </c>
-      <c r="I33" s="24" t="n">
-        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B33,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="I33" s="25" t="n">
+        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B33,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J33" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$53:$I$53="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B33,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="J33" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$61:$I$61="77W"))+SUMPRODUCT($C$20:$I$20,--($C$62:$I$62="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B33,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K33" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$53:$I$53="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B33,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="K33" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$61:$I$61="778"))+SUMPRODUCT($C$20:$I$20,--($C$62:$I$62="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B33,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>5</v>
       </c>
-      <c r="L33" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$53:$I$53="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B33,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="L33" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$61:$I$61="A320"))+SUMPRODUCT($C$20:$I$20,--($C$62:$I$62="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B33,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B34" s="22" t="str">
-        <f aca="false">$B$54</f>
+      <c r="B34" s="13" t="str">
+        <f aca="false">$B$63</f>
         <v>DIERUN</v>
       </c>
-      <c r="C34" s="23" t="str">
-        <f aca="false">$K$54</f>
+      <c r="C34" s="20" t="str">
+        <f aca="false">$K$63</f>
         <v>A320(2)</v>
       </c>
-      <c r="D34" s="23" t="str">
-        <f aca="false">IF(COUNTA($C$54:$I$54)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$54&lt;&gt;"","J1 ","")&amp;IF($D$54&lt;&gt;"","J2 ","")&amp;IF($E$54&lt;&gt;"","J3 ","")&amp;IF($F$54&lt;&gt;"","J4 ","")&amp;IF($G$54&lt;&gt;"","J5 ","")&amp;IF($H$54&lt;&gt;"","J6 ","")&amp;IF($I$54&lt;&gt;"","J7 ",""))," ",", "))</f>
+      <c r="D34" s="20" t="str">
+        <f aca="false">IF(COUNTA($C$63:$I$64)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$63:$C$64)&gt;0,"J1 ","")&amp;IF(COUNTA($D$63:$D$64)&gt;0,"J2 ","")&amp;IF(COUNTA($E$63:$E$64)&gt;0,"J3 ","")&amp;IF(COUNTA($F$63:$F$64)&gt;0,"J4 ","")&amp;IF(COUNTA($G$63:$G$64)&gt;0,"J5 ","")&amp;IF(COUNTA($H$63:$H$64)&gt;0,"J6 ","")&amp;IF(COUNTA($I$63:$I$64)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J2, J6</v>
       </c>
-      <c r="E34" s="24" t="n">
-        <f aca="false">$J$54</f>
+      <c r="E34" s="25" t="n">
+        <f aca="false">$J$63</f>
         <v>2</v>
       </c>
-      <c r="F34" s="24" t="n">
+      <c r="F34" s="25" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G34" s="25" t="n">
+      <c r="G34" s="26" t="n">
         <f aca="false">H34+I34</f>
         <v>8</v>
       </c>
-      <c r="H34" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$54:$I$54&lt;&gt;""))</f>
+      <c r="H34" s="25" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$63:$I$63&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$64:$I$64&lt;&gt;""))</f>
         <v>8</v>
       </c>
-      <c r="I34" s="24" t="n">
-        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B34,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="I34" s="25" t="n">
+        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B34,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J34" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$54:$I$54="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B34,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="J34" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$63:$I$63="77W"))+SUMPRODUCT($C$20:$I$20,--($C$64:$I$64="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B34,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K34" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$54:$I$54="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B34,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="K34" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$63:$I$63="778"))+SUMPRODUCT($C$20:$I$20,--($C$64:$I$64="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B34,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="L34" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$54:$I$54="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B34,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="L34" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$63:$I$63="A320"))+SUMPRODUCT($C$20:$I$20,--($C$64:$I$64="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B34,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>8</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B35" s="22" t="str">
-        <f aca="false">$B$55</f>
+      <c r="B35" s="13" t="str">
+        <f aca="false">$B$65</f>
         <v>RRGRUN</v>
       </c>
-      <c r="C35" s="23" t="str">
-        <f aca="false">$K$55</f>
-        <v>A320(6)</v>
-      </c>
-      <c r="D35" s="23" t="str">
-        <f aca="false">IF(COUNTA($C$55:$I$55)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$55&lt;&gt;"","J1 ","")&amp;IF($D$55&lt;&gt;"","J2 ","")&amp;IF($E$55&lt;&gt;"","J3 ","")&amp;IF($F$55&lt;&gt;"","J4 ","")&amp;IF($G$55&lt;&gt;"","J5 ","")&amp;IF($H$55&lt;&gt;"","J6 ","")&amp;IF($I$55&lt;&gt;"","J7 ",""))," ",", "))</f>
+      <c r="C35" s="20" t="str">
+        <f aca="false">$K$65</f>
+        <v>A320(7)</v>
+      </c>
+      <c r="D35" s="20" t="str">
+        <f aca="false">IF(COUNTA($C$65:$I$66)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$65:$C$66)&gt;0,"J1 ","")&amp;IF(COUNTA($D$65:$D$66)&gt;0,"J2 ","")&amp;IF(COUNTA($E$65:$E$66)&gt;0,"J3 ","")&amp;IF(COUNTA($F$65:$F$66)&gt;0,"J4 ","")&amp;IF(COUNTA($G$65:$G$66)&gt;0,"J5 ","")&amp;IF(COUNTA($H$65:$H$66)&gt;0,"J6 ","")&amp;IF(COUNTA($I$65:$I$66)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J1, J2, J3, J4, J5, J6</v>
       </c>
-      <c r="E35" s="24" t="n">
-        <f aca="false">$J$55</f>
-        <v>6</v>
-      </c>
-      <c r="F35" s="24" t="n">
+      <c r="E35" s="25" t="n">
+        <f aca="false">$J$65</f>
+        <v>7</v>
+      </c>
+      <c r="F35" s="25" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G35" s="25" t="n">
+      <c r="G35" s="26" t="n">
         <f aca="false">H35+I35</f>
-        <v>26</v>
-      </c>
-      <c r="H35" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$55:$I$55&lt;&gt;""))</f>
-        <v>26</v>
-      </c>
-      <c r="I35" s="24" t="n">
-        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B35,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+        <v>31</v>
+      </c>
+      <c r="H35" s="25" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$65:$I$65&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$66:$I$66&lt;&gt;""))</f>
+        <v>31</v>
+      </c>
+      <c r="I35" s="25" t="n">
+        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B35,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J35" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$55:$I$55="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B35,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="J35" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$65:$I$65="77W"))+SUMPRODUCT($C$20:$I$20,--($C$66:$I$66="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B35,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K35" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$55:$I$55="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B35,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="K35" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$65:$I$65="778"))+SUMPRODUCT($C$20:$I$20,--($C$66:$I$66="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B35,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="L35" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$55:$I$55="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B35,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
-        <v>26</v>
+      <c r="L35" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$65:$I$65="A320"))+SUMPRODUCT($C$20:$I$20,--($C$66:$I$66="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B35,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+        <v>31</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B36" s="22" t="str">
-        <f aca="false">$B$56</f>
+      <c r="B36" s="13" t="str">
+        <f aca="false">$B$67</f>
         <v>TMMRUN</v>
       </c>
-      <c r="C36" s="23" t="str">
-        <f aca="false">$K$56</f>
+      <c r="C36" s="20" t="str">
+        <f aca="false">$K$67</f>
         <v>A320(2)</v>
       </c>
-      <c r="D36" s="23" t="str">
-        <f aca="false">IF(COUNTA($C$56:$I$56)=0,"aucune operation",SUBSTITUTE(TRIM(IF($C$56&lt;&gt;"","J1 ","")&amp;IF($D$56&lt;&gt;"","J2 ","")&amp;IF($E$56&lt;&gt;"","J3 ","")&amp;IF($F$56&lt;&gt;"","J4 ","")&amp;IF($G$56&lt;&gt;"","J5 ","")&amp;IF($H$56&lt;&gt;"","J6 ","")&amp;IF($I$56&lt;&gt;"","J7 ",""))," ",", "))</f>
+      <c r="D36" s="20" t="str">
+        <f aca="false">IF(COUNTA($C$67:$I$68)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$67:$C$68)&gt;0,"J1 ","")&amp;IF(COUNTA($D$67:$D$68)&gt;0,"J2 ","")&amp;IF(COUNTA($E$67:$E$68)&gt;0,"J3 ","")&amp;IF(COUNTA($F$67:$F$68)&gt;0,"J4 ","")&amp;IF(COUNTA($G$67:$G$68)&gt;0,"J5 ","")&amp;IF(COUNTA($H$67:$H$68)&gt;0,"J6 ","")&amp;IF(COUNTA($I$67:$I$68)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J3, J7</v>
       </c>
-      <c r="E36" s="24" t="n">
-        <f aca="false">$J$56</f>
+      <c r="E36" s="25" t="n">
+        <f aca="false">$J$67</f>
         <v>2</v>
       </c>
-      <c r="F36" s="24" t="n">
+      <c r="F36" s="25" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G36" s="25" t="n">
+      <c r="G36" s="26" t="n">
         <f aca="false">H36+I36</f>
         <v>8</v>
       </c>
-      <c r="H36" s="24" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$56:$I$56&lt;&gt;""))</f>
+      <c r="H36" s="25" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$67:$I$67&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$68:$I$68&lt;&gt;""))</f>
         <v>8</v>
       </c>
-      <c r="I36" s="24" t="n">
-        <f aca="false">SUMIFS($E$62:$E$101,$C$62:$C$101,$B36,$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="I36" s="25" t="n">
+        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B36,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J36" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$56:$I$56="77W"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B36,$D$62:$D$101,"77W",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="J36" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$67:$I$67="77W"))+SUMPRODUCT($C$20:$I$20,--($C$68:$I$68="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B36,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K36" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$56:$I$56="778"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B36,$D$62:$D$101,"778",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="K36" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$67:$I$67="778"))+SUMPRODUCT($C$20:$I$20,--($C$68:$I$68="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B36,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="L36" s="26" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$56:$I$56="A320"))+SUMIFS($E$62:$E$101,$C$62:$C$101,$B36,$D$62:$D$101,"A320",$B$62:$B$101,"&gt;="&amp;$O$4,$B$62:$B$101,"&lt;="&amp;$O$5)</f>
+      <c r="L36" s="27" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$67:$I$67="A320"))+SUMPRODUCT($C$20:$I$20,--($C$68:$I$68="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B36,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
         <v>8</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="27" t="s">
-        <v>45</v>
-      </c>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="29" t="n">
+      <c r="B37" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C37" s="29"/>
+      <c r="D37" s="29"/>
+      <c r="E37" s="30" t="n">
         <f aca="false">SUM(E25:E36)</f>
-        <v>40</v>
-      </c>
-      <c r="F37" s="29" t="n">
+        <v>44</v>
+      </c>
+      <c r="F37" s="30" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G37" s="30" t="n">
+      <c r="G37" s="31" t="n">
         <f aca="false">SUM(G25:G36)</f>
-        <v>176</v>
-      </c>
-      <c r="H37" s="29" t="n">
+        <v>194</v>
+      </c>
+      <c r="H37" s="30" t="n">
         <f aca="false">SUM(H25:H36)</f>
-        <v>172</v>
-      </c>
-      <c r="I37" s="29" t="n">
+        <v>190</v>
+      </c>
+      <c r="I37" s="30" t="n">
         <f aca="false">SUM(I25:I36)</f>
         <v>4</v>
       </c>
-      <c r="J37" s="29" t="n">
+      <c r="J37" s="30" t="n">
         <f aca="false">SUM(J25:J36)</f>
-        <v>21</v>
-      </c>
-      <c r="K37" s="29" t="n">
+        <v>34</v>
+      </c>
+      <c r="K37" s="30" t="n">
         <f aca="false">SUM(K25:K36)</f>
         <v>46</v>
       </c>
-      <c r="L37" s="29" t="n">
+      <c r="L37" s="30" t="n">
         <f aca="false">SUM(L25:L36)</f>
-        <v>109</v>
+        <v>114</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="31" t="s">
-        <v>46</v>
-      </c>
-      <c r="C38" s="31"/>
-      <c r="D38" s="31"/>
-      <c r="E38" s="31"/>
-      <c r="F38" s="31"/>
-      <c r="G38" s="31"/>
-      <c r="H38" s="31"/>
-      <c r="I38" s="31"/>
-      <c r="J38" s="31"/>
-      <c r="K38" s="31"/>
-      <c r="L38" s="31"/>
+      <c r="B38" s="32" t="s">
+        <v>56</v>
+      </c>
+      <c r="C38" s="32"/>
+      <c r="D38" s="32"/>
+      <c r="E38" s="32"/>
+      <c r="F38" s="32"/>
+      <c r="G38" s="32"/>
+      <c r="H38" s="32"/>
+      <c r="I38" s="32"/>
+      <c r="J38" s="32"/>
+      <c r="K38" s="32"/>
+      <c r="L38" s="32"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="31"/>
-      <c r="C39" s="31"/>
-      <c r="D39" s="31"/>
-      <c r="E39" s="31"/>
-      <c r="F39" s="31"/>
-      <c r="G39" s="31"/>
-      <c r="H39" s="31"/>
-      <c r="I39" s="31"/>
-      <c r="J39" s="31"/>
-      <c r="K39" s="31"/>
-      <c r="L39" s="31"/>
+      <c r="B39" s="32"/>
+      <c r="C39" s="32"/>
+      <c r="D39" s="32"/>
+      <c r="E39" s="32"/>
+      <c r="F39" s="32"/>
+      <c r="G39" s="32"/>
+      <c r="H39" s="32"/>
+      <c r="I39" s="32"/>
+      <c r="J39" s="32"/>
+      <c r="K39" s="32"/>
+      <c r="L39" s="32"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="32" t="s">
-        <v>47</v>
-      </c>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="32"/>
-      <c r="J41" s="32"/>
-      <c r="K41" s="32"/>
-      <c r="L41" s="32"/>
+      <c r="B41" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" s="33"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33"/>
+      <c r="I41" s="33"/>
+      <c r="J41" s="33"/>
+      <c r="K41" s="33"/>
+      <c r="L41" s="33"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="33" t="s">
-        <v>48</v>
-      </c>
-      <c r="C42" s="33"/>
-      <c r="D42" s="33"/>
-      <c r="E42" s="33"/>
-      <c r="F42" s="33"/>
-      <c r="G42" s="33"/>
-      <c r="H42" s="33"/>
-      <c r="I42" s="33"/>
-      <c r="J42" s="33"/>
-      <c r="K42" s="33"/>
-      <c r="L42" s="33"/>
+      <c r="B42" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="34"/>
+      <c r="F42" s="34"/>
+      <c r="G42" s="34"/>
+      <c r="H42" s="34"/>
+      <c r="I42" s="34"/>
+      <c r="J42" s="34"/>
+      <c r="K42" s="34"/>
+      <c r="L42" s="34"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="33"/>
-      <c r="C43" s="33"/>
-      <c r="D43" s="33"/>
-      <c r="E43" s="33"/>
-      <c r="F43" s="33"/>
-      <c r="G43" s="33"/>
-      <c r="H43" s="33"/>
-      <c r="I43" s="33"/>
-      <c r="J43" s="33"/>
-      <c r="K43" s="33"/>
-      <c r="L43" s="33"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="34"/>
+      <c r="F43" s="34"/>
+      <c r="G43" s="34"/>
+      <c r="H43" s="34"/>
+      <c r="I43" s="34"/>
+      <c r="J43" s="34"/>
+      <c r="K43" s="34"/>
+      <c r="L43" s="34"/>
     </row>
     <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="C44" s="34" t="s">
+      <c r="B44" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="C44" s="35" t="s">
         <v>14</v>
       </c>
-      <c r="D44" s="34" t="s">
+      <c r="D44" s="35" t="s">
         <v>15</v>
       </c>
-      <c r="E44" s="34" t="s">
+      <c r="E44" s="35" t="s">
         <v>16</v>
       </c>
-      <c r="F44" s="34" t="s">
+      <c r="F44" s="35" t="s">
         <v>17</v>
       </c>
-      <c r="G44" s="34" t="s">
+      <c r="G44" s="35" t="s">
         <v>18</v>
       </c>
-      <c r="H44" s="34" t="s">
+      <c r="H44" s="35" t="s">
         <v>19</v>
       </c>
-      <c r="I44" s="34" t="s">
+      <c r="I44" s="35" t="s">
         <v>20</v>
       </c>
-      <c r="J44" s="34" t="s">
-        <v>49</v>
-      </c>
-      <c r="K44" s="34" t="s">
-        <v>50</v>
-      </c>
-      <c r="L44" s="34" t="s">
-        <v>51</v>
-      </c>
-      <c r="N44" s="35" t="s">
-        <v>52</v>
-      </c>
-      <c r="O44" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="P44" s="35" t="s">
-        <v>54</v>
+      <c r="J44" s="35" t="s">
+        <v>60</v>
+      </c>
+      <c r="K44" s="35" t="s">
+        <v>61</v>
+      </c>
+      <c r="L44" s="35" t="s">
+        <v>62</v>
+      </c>
+      <c r="N44" s="36" t="s">
+        <v>63</v>
+      </c>
+      <c r="O44" s="36" t="s">
+        <v>64</v>
+      </c>
+      <c r="P44" s="36" t="s">
+        <v>65</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="36" t="s">
-        <v>55</v>
-      </c>
-      <c r="C45" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="D45" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E45" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="F45" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="G45" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="H45" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="I45" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="J45" s="38" t="n">
-        <f aca="false">COUNTA(C45:I45)</f>
-        <v>7</v>
-      </c>
-      <c r="K45" s="23" t="str">
-        <f aca="false">IF(COUNTA(C45:I45)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C45:I45,"77W")&gt;0,"77W("&amp;COUNTIF(C45:I45,"77W")&amp;") ","")&amp;IF(COUNTIF(C45:I45,"778")&gt;0,"778("&amp;COUNTIF(C45:I45,"778")&amp;") ","")&amp;IF(COUNTIF(C45:I45,"A320")&gt;0,"A320("&amp;COUNTIF(C45:I45,"A320")&amp;") ",""))," ",", "))</f>
-        <v>77W(4), 778(3)</v>
-      </c>
-      <c r="L45" s="39"/>
-      <c r="N45" s="40" t="s">
+      <c r="B45" s="37" t="s">
+        <v>66</v>
+      </c>
+      <c r="C45" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="D45" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="E45" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="F45" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="G45" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="H45" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="I45" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="J45" s="39" t="n">
+        <f aca="false">COUNTA(C45:I46)</f>
+        <v>9</v>
+      </c>
+      <c r="K45" s="20" t="str">
+        <f aca="false">IF(COUNTA(C45:I46)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C45:I46,"77W")&gt;0,"77W("&amp;COUNTIF(C45:I46,"77W")&amp;") ","")&amp;IF(COUNTIF(C45:I46,"778")&gt;0,"778("&amp;COUNTIF(C45:I46,"778")&amp;") ","")&amp;IF(COUNTIF(C45:I46,"A320")&gt;0,"A320("&amp;COUNTIF(C45:I46,"A320")&amp;") ",""))," ",", "))</f>
+        <v>77W(7), 778(2)</v>
+      </c>
+      <c r="L45" s="40"/>
+      <c r="N45" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="41" t="n">
+      <c r="O45" s="42" t="n">
         <f aca="false">DATE(2027,4,1)</f>
         <v>46478</v>
       </c>
-      <c r="P45" s="23" t="s">
-        <v>56</v>
+      <c r="P45" s="20" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="C46" s="37"/>
-      <c r="D46" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E46" s="37"/>
-      <c r="F46" s="37"/>
-      <c r="G46" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="H46" s="37"/>
-      <c r="I46" s="37" t="s">
-        <v>56</v>
-      </c>
-      <c r="J46" s="38" t="n">
-        <f aca="false">COUNTA(C46:I46)</f>
-        <v>3</v>
-      </c>
-      <c r="K46" s="23" t="str">
-        <f aca="false">IF(COUNTA(C46:I46)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C46:I46,"77W")&gt;0,"77W("&amp;COUNTIF(C46:I46,"77W")&amp;") ","")&amp;IF(COUNTIF(C46:I46,"778")&gt;0,"778("&amp;COUNTIF(C46:I46,"778")&amp;") ","")&amp;IF(COUNTIF(C46:I46,"A320")&gt;0,"A320("&amp;COUNTIF(C46:I46,"A320")&amp;") ",""))," ",", "))</f>
-        <v>77W(1), 778(2)</v>
-      </c>
-      <c r="L46" s="42"/>
-      <c r="N46" s="40" t="s">
-        <v>59</v>
-      </c>
-      <c r="O46" s="41" t="n">
+      <c r="B46" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C46" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="D46" s="38"/>
+      <c r="E46" s="38"/>
+      <c r="F46" s="38"/>
+      <c r="G46" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="H46" s="38"/>
+      <c r="I46" s="38"/>
+      <c r="J46" s="39"/>
+      <c r="K46" s="39"/>
+      <c r="L46" s="40"/>
+      <c r="N46" s="41" t="s">
+        <v>70</v>
+      </c>
+      <c r="O46" s="42" t="n">
         <f aca="false">DATE(2027,5,1)</f>
         <v>46508</v>
       </c>
-      <c r="P46" s="23" t="s">
-        <v>57</v>
+      <c r="P46" s="20" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="C47" s="37"/>
-      <c r="D47" s="37"/>
-      <c r="E47" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="F47" s="37"/>
-      <c r="G47" s="37"/>
-      <c r="H47" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="I47" s="37"/>
-      <c r="J47" s="38" t="n">
-        <f aca="false">COUNTA(C47:I47)</f>
-        <v>2</v>
-      </c>
-      <c r="K47" s="23" t="str">
-        <f aca="false">IF(COUNTA(C47:I47)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C47:I47,"77W")&gt;0,"77W("&amp;COUNTIF(C47:I47,"77W")&amp;") ","")&amp;IF(COUNTIF(C47:I47,"778")&gt;0,"778("&amp;COUNTIF(C47:I47,"778")&amp;") ","")&amp;IF(COUNTIF(C47:I47,"A320")&gt;0,"A320("&amp;COUNTIF(C47:I47,"A320")&amp;") ",""))," ",", "))</f>
-        <v>778(2)</v>
-      </c>
-      <c r="L47" s="43"/>
-      <c r="N47" s="40" t="s">
-        <v>61</v>
-      </c>
-      <c r="O47" s="41" t="n">
+      <c r="B47" s="37" t="s">
+        <v>71</v>
+      </c>
+      <c r="C47" s="38"/>
+      <c r="D47" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E47" s="38"/>
+      <c r="F47" s="38"/>
+      <c r="G47" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="H47" s="38"/>
+      <c r="I47" s="38" t="s">
+        <v>67</v>
+      </c>
+      <c r="J47" s="39" t="n">
+        <f aca="false">COUNTA(C47:I48)</f>
+        <v>3</v>
+      </c>
+      <c r="K47" s="20" t="str">
+        <f aca="false">IF(COUNTA(C47:I48)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C47:I48,"77W")&gt;0,"77W("&amp;COUNTIF(C47:I48,"77W")&amp;") ","")&amp;IF(COUNTIF(C47:I48,"778")&gt;0,"778("&amp;COUNTIF(C47:I48,"778")&amp;") ","")&amp;IF(COUNTIF(C47:I48,"A320")&gt;0,"A320("&amp;COUNTIF(C47:I48,"A320")&amp;") ",""))," ",", "))</f>
+        <v>77W(1), 778(2)</v>
+      </c>
+      <c r="L47" s="44"/>
+      <c r="N47" s="41" t="s">
+        <v>72</v>
+      </c>
+      <c r="O47" s="42" t="n">
         <f aca="false">DATE(2027,6,1)</f>
         <v>46539</v>
       </c>
-      <c r="P47" s="23" t="s">
-        <v>62</v>
+      <c r="P47" s="20" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="36" t="s">
-        <v>63</v>
-      </c>
-      <c r="C48" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="D48" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="E48" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="F48" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="G48" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="H48" s="37"/>
-      <c r="I48" s="37"/>
-      <c r="J48" s="38" t="n">
-        <f aca="false">COUNTA(C48:I48)</f>
-        <v>5</v>
-      </c>
-      <c r="K48" s="23" t="str">
-        <f aca="false">IF(COUNTA(C48:I48)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C48:I48,"77W")&gt;0,"77W("&amp;COUNTIF(C48:I48,"77W")&amp;") ","")&amp;IF(COUNTIF(C48:I48,"778")&gt;0,"778("&amp;COUNTIF(C48:I48,"778")&amp;") ","")&amp;IF(COUNTIF(C48:I48,"A320")&gt;0,"A320("&amp;COUNTIF(C48:I48,"A320")&amp;") ",""))," ",", "))</f>
-        <v>A320(5)</v>
-      </c>
+      <c r="B48" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C48" s="38"/>
+      <c r="D48" s="38"/>
+      <c r="E48" s="38"/>
+      <c r="F48" s="38"/>
+      <c r="G48" s="38"/>
+      <c r="H48" s="38"/>
+      <c r="I48" s="38"/>
+      <c r="J48" s="39"/>
+      <c r="K48" s="39"/>
       <c r="L48" s="44"/>
-      <c r="N48" s="40" t="s">
-        <v>64</v>
-      </c>
-      <c r="O48" s="41" t="n">
+      <c r="N48" s="41" t="s">
+        <v>74</v>
+      </c>
+      <c r="O48" s="42" t="n">
         <f aca="false">DATE(2027,7,1)</f>
         <v>46569</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="C49" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="D49" s="37"/>
-      <c r="E49" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="F49" s="37"/>
-      <c r="G49" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="H49" s="37"/>
-      <c r="I49" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="J49" s="38" t="n">
-        <f aca="false">COUNTA(C49:I49)</f>
-        <v>4</v>
-      </c>
-      <c r="K49" s="23" t="str">
-        <f aca="false">IF(COUNTA(C49:I49)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C49:I49,"77W")&gt;0,"77W("&amp;COUNTIF(C49:I49,"77W")&amp;") ","")&amp;IF(COUNTIF(C49:I49,"778")&gt;0,"778("&amp;COUNTIF(C49:I49,"778")&amp;") ","")&amp;IF(COUNTIF(C49:I49,"A320")&gt;0,"A320("&amp;COUNTIF(C49:I49,"A320")&amp;") ",""))," ",", "))</f>
-        <v>A320(4)</v>
+      <c r="B49" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="C49" s="38"/>
+      <c r="D49" s="38"/>
+      <c r="E49" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="F49" s="38"/>
+      <c r="G49" s="38"/>
+      <c r="H49" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="I49" s="38"/>
+      <c r="J49" s="39" t="n">
+        <f aca="false">COUNTA(C49:I50)</f>
+        <v>2</v>
+      </c>
+      <c r="K49" s="20" t="str">
+        <f aca="false">IF(COUNTA(C49:I50)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C49:I50,"77W")&gt;0,"77W("&amp;COUNTIF(C49:I50,"77W")&amp;") ","")&amp;IF(COUNTIF(C49:I50,"778")&gt;0,"778("&amp;COUNTIF(C49:I50,"778")&amp;") ","")&amp;IF(COUNTIF(C49:I50,"A320")&gt;0,"A320("&amp;COUNTIF(C49:I50,"A320")&amp;") ",""))," ",", "))</f>
+        <v>778(2)</v>
       </c>
       <c r="L49" s="45"/>
-      <c r="N49" s="40" t="s">
-        <v>66</v>
-      </c>
-      <c r="O49" s="41" t="n">
+      <c r="N49" s="41" t="s">
+        <v>76</v>
+      </c>
+      <c r="O49" s="42" t="n">
         <f aca="false">DATE(2027,8,1)</f>
         <v>46600</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="36" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="D50" s="37"/>
-      <c r="E50" s="37"/>
-      <c r="F50" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="G50" s="37"/>
-      <c r="H50" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="I50" s="37"/>
-      <c r="J50" s="38" t="n">
-        <f aca="false">COUNTA(C50:I50)</f>
-        <v>3</v>
-      </c>
-      <c r="K50" s="23" t="str">
-        <f aca="false">IF(COUNTA(C50:I50)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C50:I50,"77W")&gt;0,"77W("&amp;COUNTIF(C50:I50,"77W")&amp;") ","")&amp;IF(COUNTIF(C50:I50,"778")&gt;0,"778("&amp;COUNTIF(C50:I50,"778")&amp;") ","")&amp;IF(COUNTIF(C50:I50,"A320")&gt;0,"A320("&amp;COUNTIF(C50:I50,"A320")&amp;") ",""))," ",", "))</f>
-        <v>A320(3)</v>
-      </c>
-      <c r="L50" s="46"/>
-      <c r="N50" s="40" t="s">
-        <v>67</v>
-      </c>
-      <c r="O50" s="41" t="n">
+      <c r="B50" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C50" s="38"/>
+      <c r="D50" s="38"/>
+      <c r="E50" s="38"/>
+      <c r="F50" s="38"/>
+      <c r="G50" s="38"/>
+      <c r="H50" s="38"/>
+      <c r="I50" s="38"/>
+      <c r="J50" s="39"/>
+      <c r="K50" s="39"/>
+      <c r="L50" s="45"/>
+      <c r="N50" s="41" t="s">
+        <v>77</v>
+      </c>
+      <c r="O50" s="42" t="n">
         <f aca="false">DATE(2027,9,1)</f>
         <v>46631</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="C51" s="37"/>
-      <c r="D51" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="E51" s="37"/>
-      <c r="F51" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="G51" s="37"/>
-      <c r="H51" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="I51" s="37"/>
-      <c r="J51" s="38" t="n">
-        <f aca="false">COUNTA(C51:I51)</f>
-        <v>3</v>
-      </c>
-      <c r="K51" s="23" t="str">
-        <f aca="false">IF(COUNTA(C51:I51)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C51:I51,"77W")&gt;0,"77W("&amp;COUNTIF(C51:I51,"77W")&amp;") ","")&amp;IF(COUNTIF(C51:I51,"778")&gt;0,"778("&amp;COUNTIF(C51:I51,"778")&amp;") ","")&amp;IF(COUNTIF(C51:I51,"A320")&gt;0,"A320("&amp;COUNTIF(C51:I51,"A320")&amp;") ",""))," ",", "))</f>
-        <v>A320(3)</v>
-      </c>
-      <c r="L51" s="47"/>
-      <c r="N51" s="40" t="s">
-        <v>69</v>
-      </c>
-      <c r="O51" s="41" t="n">
+      <c r="B51" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="C51" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="D51" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="E51" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="F51" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="G51" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H51" s="38"/>
+      <c r="I51" s="38"/>
+      <c r="J51" s="39" t="n">
+        <f aca="false">COUNTA(C51:I52)</f>
+        <v>6</v>
+      </c>
+      <c r="K51" s="20" t="str">
+        <f aca="false">IF(COUNTA(C51:I52)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C51:I52,"77W")&gt;0,"77W("&amp;COUNTIF(C51:I52,"77W")&amp;") ","")&amp;IF(COUNTIF(C51:I52,"778")&gt;0,"778("&amp;COUNTIF(C51:I52,"778")&amp;") ","")&amp;IF(COUNTIF(C51:I52,"A320")&gt;0,"A320("&amp;COUNTIF(C51:I52,"A320")&amp;") ",""))," ",", "))</f>
+        <v>778(1), A320(5)</v>
+      </c>
+      <c r="L51" s="46"/>
+      <c r="N51" s="41" t="s">
+        <v>79</v>
+      </c>
+      <c r="O51" s="42" t="n">
         <f aca="false">DATE(2027,10,1)</f>
         <v>46661</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="C52" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="D52" s="37"/>
-      <c r="E52" s="37"/>
-      <c r="F52" s="37"/>
-      <c r="G52" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="H52" s="37"/>
-      <c r="I52" s="37"/>
-      <c r="J52" s="38" t="n">
-        <f aca="false">COUNTA(C52:I52)</f>
-        <v>2</v>
-      </c>
-      <c r="K52" s="23" t="str">
-        <f aca="false">IF(COUNTA(C52:I52)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C52:I52,"77W")&gt;0,"77W("&amp;COUNTIF(C52:I52,"77W")&amp;") ","")&amp;IF(COUNTIF(C52:I52,"778")&gt;0,"778("&amp;COUNTIF(C52:I52,"778")&amp;") ","")&amp;IF(COUNTIF(C52:I52,"A320")&gt;0,"A320("&amp;COUNTIF(C52:I52,"A320")&amp;") ",""))," ",", "))</f>
-        <v>778(2)</v>
-      </c>
-      <c r="L52" s="48"/>
-      <c r="N52" s="40" t="s">
-        <v>71</v>
-      </c>
-      <c r="O52" s="41" t="n">
+      <c r="B52" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52" s="38"/>
+      <c r="D52" s="38"/>
+      <c r="E52" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="F52" s="38"/>
+      <c r="G52" s="38"/>
+      <c r="H52" s="38"/>
+      <c r="I52" s="38"/>
+      <c r="J52" s="39"/>
+      <c r="K52" s="39"/>
+      <c r="L52" s="46"/>
+      <c r="N52" s="41" t="s">
+        <v>80</v>
+      </c>
+      <c r="O52" s="42" t="n">
         <f aca="false">DATE(2027,11,1)</f>
         <v>46692</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="36" t="s">
-        <v>72</v>
-      </c>
-      <c r="C53" s="37"/>
-      <c r="D53" s="37"/>
-      <c r="E53" s="37"/>
-      <c r="F53" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="G53" s="37"/>
-      <c r="H53" s="37"/>
-      <c r="I53" s="37"/>
-      <c r="J53" s="38" t="n">
-        <f aca="false">COUNTA(C53:I53)</f>
-        <v>1</v>
-      </c>
-      <c r="K53" s="23" t="str">
-        <f aca="false">IF(COUNTA(C53:I53)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C53:I53,"77W")&gt;0,"77W("&amp;COUNTIF(C53:I53,"77W")&amp;") ","")&amp;IF(COUNTIF(C53:I53,"778")&gt;0,"778("&amp;COUNTIF(C53:I53,"778")&amp;") ","")&amp;IF(COUNTIF(C53:I53,"A320")&gt;0,"A320("&amp;COUNTIF(C53:I53,"A320")&amp;") ",""))," ",", "))</f>
-        <v>778(1)</v>
-      </c>
-      <c r="L53" s="49"/>
-      <c r="N53" s="40" t="s">
+      <c r="B53" s="37" t="s">
+        <v>81</v>
+      </c>
+      <c r="C53" s="38" t="s">
         <v>73</v>
       </c>
-      <c r="O53" s="41" t="n">
+      <c r="D53" s="38"/>
+      <c r="E53" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="F53" s="38"/>
+      <c r="G53" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H53" s="38"/>
+      <c r="I53" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="J53" s="39" t="n">
+        <f aca="false">COUNTA(C53:I54)</f>
+        <v>4</v>
+      </c>
+      <c r="K53" s="20" t="str">
+        <f aca="false">IF(COUNTA(C53:I54)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C53:I54,"77W")&gt;0,"77W("&amp;COUNTIF(C53:I54,"77W")&amp;") ","")&amp;IF(COUNTIF(C53:I54,"778")&gt;0,"778("&amp;COUNTIF(C53:I54,"778")&amp;") ","")&amp;IF(COUNTIF(C53:I54,"A320")&gt;0,"A320("&amp;COUNTIF(C53:I54,"A320")&amp;") ",""))," ",", "))</f>
+        <v>A320(4)</v>
+      </c>
+      <c r="L53" s="47"/>
+      <c r="N53" s="41" t="s">
+        <v>82</v>
+      </c>
+      <c r="O53" s="42" t="n">
         <f aca="false">DATE(2027,12,1)</f>
         <v>46722</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="C54" s="37"/>
-      <c r="D54" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="E54" s="37"/>
-      <c r="F54" s="37"/>
-      <c r="G54" s="37"/>
-      <c r="H54" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="I54" s="37"/>
-      <c r="J54" s="38" t="n">
-        <f aca="false">COUNTA(C54:I54)</f>
-        <v>2</v>
-      </c>
-      <c r="K54" s="23" t="str">
-        <f aca="false">IF(COUNTA(C54:I54)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C54:I54,"77W")&gt;0,"77W("&amp;COUNTIF(C54:I54,"77W")&amp;") ","")&amp;IF(COUNTIF(C54:I54,"778")&gt;0,"778("&amp;COUNTIF(C54:I54,"778")&amp;") ","")&amp;IF(COUNTIF(C54:I54,"A320")&gt;0,"A320("&amp;COUNTIF(C54:I54,"A320")&amp;") ",""))," ",", "))</f>
-        <v>A320(2)</v>
-      </c>
-      <c r="L54" s="50"/>
-      <c r="N54" s="40" t="s">
-        <v>75</v>
-      </c>
-      <c r="O54" s="41" t="n">
+      <c r="B54" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C54" s="38"/>
+      <c r="D54" s="38"/>
+      <c r="E54" s="38"/>
+      <c r="F54" s="38"/>
+      <c r="G54" s="38"/>
+      <c r="H54" s="38"/>
+      <c r="I54" s="38"/>
+      <c r="J54" s="39"/>
+      <c r="K54" s="39"/>
+      <c r="L54" s="47"/>
+      <c r="N54" s="41" t="s">
+        <v>83</v>
+      </c>
+      <c r="O54" s="42" t="n">
         <f aca="false">DATE(2028,1,1)</f>
         <v>46753</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="36" t="s">
-        <v>76</v>
-      </c>
-      <c r="C55" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="D55" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="E55" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="F55" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="G55" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="H55" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="I55" s="37"/>
-      <c r="J55" s="38" t="n">
-        <f aca="false">COUNTA(C55:I55)</f>
-        <v>6</v>
-      </c>
-      <c r="K55" s="23" t="str">
-        <f aca="false">IF(COUNTA(C55:I55)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C55:I55,"77W")&gt;0,"77W("&amp;COUNTIF(C55:I55,"77W")&amp;") ","")&amp;IF(COUNTIF(C55:I55,"778")&gt;0,"778("&amp;COUNTIF(C55:I55,"778")&amp;") ","")&amp;IF(COUNTIF(C55:I55,"A320")&gt;0,"A320("&amp;COUNTIF(C55:I55,"A320")&amp;") ",""))," ",", "))</f>
-        <v>A320(6)</v>
-      </c>
-      <c r="L55" s="51"/>
-      <c r="N55" s="40" t="s">
-        <v>77</v>
-      </c>
-      <c r="O55" s="41" t="n">
+      <c r="B55" s="37" t="s">
+        <v>8</v>
+      </c>
+      <c r="C55" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="D55" s="38"/>
+      <c r="E55" s="38"/>
+      <c r="F55" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="G55" s="38"/>
+      <c r="H55" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="I55" s="38"/>
+      <c r="J55" s="39" t="n">
+        <f aca="false">COUNTA(C55:I56)</f>
+        <v>3</v>
+      </c>
+      <c r="K55" s="20" t="str">
+        <f aca="false">IF(COUNTA(C55:I56)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C55:I56,"77W")&gt;0,"77W("&amp;COUNTIF(C55:I56,"77W")&amp;") ","")&amp;IF(COUNTIF(C55:I56,"778")&gt;0,"778("&amp;COUNTIF(C55:I56,"778")&amp;") ","")&amp;IF(COUNTIF(C55:I56,"A320")&gt;0,"A320("&amp;COUNTIF(C55:I56,"A320")&amp;") ",""))," ",", "))</f>
+        <v>A320(3)</v>
+      </c>
+      <c r="L55" s="48"/>
+      <c r="N55" s="41" t="s">
+        <v>84</v>
+      </c>
+      <c r="O55" s="42" t="n">
         <f aca="false">DATE(2028,2,1)</f>
         <v>46784</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="36" t="s">
-        <v>78</v>
-      </c>
-      <c r="C56" s="37"/>
-      <c r="D56" s="37"/>
-      <c r="E56" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="F56" s="37"/>
-      <c r="G56" s="37"/>
-      <c r="H56" s="37"/>
-      <c r="I56" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="J56" s="38" t="n">
-        <f aca="false">COUNTA(C56:I56)</f>
-        <v>2</v>
-      </c>
-      <c r="K56" s="23" t="str">
-        <f aca="false">IF(COUNTA(C56:I56)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C56:I56,"77W")&gt;0,"77W("&amp;COUNTIF(C56:I56,"77W")&amp;") ","")&amp;IF(COUNTIF(C56:I56,"778")&gt;0,"778("&amp;COUNTIF(C56:I56,"778")&amp;") ","")&amp;IF(COUNTIF(C56:I56,"A320")&gt;0,"A320("&amp;COUNTIF(C56:I56,"A320")&amp;") ",""))," ",", "))</f>
-        <v>A320(2)</v>
-      </c>
-      <c r="L56" s="52"/>
-      <c r="N56" s="40" t="s">
-        <v>79</v>
-      </c>
-      <c r="O56" s="41" t="n">
+      <c r="B56" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C56" s="38"/>
+      <c r="D56" s="38"/>
+      <c r="E56" s="38"/>
+      <c r="F56" s="38"/>
+      <c r="G56" s="38"/>
+      <c r="H56" s="38"/>
+      <c r="I56" s="38"/>
+      <c r="J56" s="39"/>
+      <c r="K56" s="39"/>
+      <c r="L56" s="48"/>
+      <c r="N56" s="41" t="s">
+        <v>85</v>
+      </c>
+      <c r="O56" s="42" t="n">
         <f aca="false">DATE(2028,3,1)</f>
         <v>46813</v>
       </c>
     </row>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B57" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="C57" s="38"/>
+      <c r="D57" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="E57" s="38"/>
+      <c r="F57" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="G57" s="38"/>
+      <c r="H57" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="I57" s="38"/>
+      <c r="J57" s="39" t="n">
+        <f aca="false">COUNTA(C57:I58)</f>
+        <v>3</v>
+      </c>
+      <c r="K57" s="20" t="str">
+        <f aca="false">IF(COUNTA(C57:I58)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C57:I58,"77W")&gt;0,"77W("&amp;COUNTIF(C57:I58,"77W")&amp;") ","")&amp;IF(COUNTIF(C57:I58,"778")&gt;0,"778("&amp;COUNTIF(C57:I58,"778")&amp;") ","")&amp;IF(COUNTIF(C57:I58,"A320")&gt;0,"A320("&amp;COUNTIF(C57:I58,"A320")&amp;") ",""))," ",", "))</f>
+        <v>A320(3)</v>
+      </c>
+      <c r="L57" s="49"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C58" s="38"/>
+      <c r="D58" s="38"/>
+      <c r="E58" s="38"/>
+      <c r="F58" s="38"/>
+      <c r="G58" s="38"/>
+      <c r="H58" s="38"/>
+      <c r="I58" s="38"/>
+      <c r="J58" s="39"/>
+      <c r="K58" s="39"/>
+      <c r="L58" s="49"/>
+    </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="32" t="s">
-        <v>80</v>
-      </c>
-      <c r="C59" s="32"/>
-      <c r="D59" s="32"/>
-      <c r="E59" s="32"/>
-      <c r="F59" s="32"/>
-      <c r="G59" s="32"/>
-      <c r="H59" s="32"/>
-      <c r="I59" s="32"/>
-      <c r="J59" s="32"/>
-      <c r="K59" s="32"/>
-      <c r="L59" s="32"/>
-    </row>
-    <row r="60" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B60" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="C60" s="33"/>
-      <c r="D60" s="33"/>
-      <c r="E60" s="33"/>
-      <c r="F60" s="33"/>
-      <c r="G60" s="33"/>
-      <c r="H60" s="33"/>
-      <c r="I60" s="33"/>
-      <c r="J60" s="33"/>
-      <c r="K60" s="33"/>
-      <c r="L60" s="33"/>
+      <c r="B59" s="37" t="s">
+        <v>87</v>
+      </c>
+      <c r="C59" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="D59" s="38"/>
+      <c r="E59" s="38"/>
+      <c r="F59" s="38"/>
+      <c r="G59" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="H59" s="38"/>
+      <c r="I59" s="38"/>
+      <c r="J59" s="39" t="n">
+        <f aca="false">COUNTA(C59:I60)</f>
+        <v>2</v>
+      </c>
+      <c r="K59" s="20" t="str">
+        <f aca="false">IF(COUNTA(C59:I60)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C59:I60,"77W")&gt;0,"77W("&amp;COUNTIF(C59:I60,"77W")&amp;") ","")&amp;IF(COUNTIF(C59:I60,"778")&gt;0,"778("&amp;COUNTIF(C59:I60,"778")&amp;") ","")&amp;IF(COUNTIF(C59:I60,"A320")&gt;0,"A320("&amp;COUNTIF(C59:I60,"A320")&amp;") ",""))," ",", "))</f>
+        <v>778(2)</v>
+      </c>
+      <c r="L59" s="50"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C60" s="38"/>
+      <c r="D60" s="38"/>
+      <c r="E60" s="38"/>
+      <c r="F60" s="38"/>
+      <c r="G60" s="38"/>
+      <c r="H60" s="38"/>
+      <c r="I60" s="38"/>
+      <c r="J60" s="39"/>
+      <c r="K60" s="39"/>
+      <c r="L60" s="50"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="34" t="s">
-        <v>82</v>
-      </c>
-      <c r="C61" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="D61" s="34" t="s">
-        <v>83</v>
-      </c>
-      <c r="E61" s="34" t="s">
-        <v>84</v>
-      </c>
-      <c r="F61" s="34" t="s">
-        <v>85</v>
-      </c>
-      <c r="J61" s="53" t="s">
-        <v>86</v>
-      </c>
+      <c r="B61" s="37" t="s">
+        <v>88</v>
+      </c>
+      <c r="C61" s="38"/>
+      <c r="D61" s="38"/>
+      <c r="E61" s="38"/>
+      <c r="F61" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="G61" s="38"/>
+      <c r="H61" s="38"/>
+      <c r="I61" s="38"/>
+      <c r="J61" s="39" t="n">
+        <f aca="false">COUNTA(C61:I62)</f>
+        <v>1</v>
+      </c>
+      <c r="K61" s="20" t="str">
+        <f aca="false">IF(COUNTA(C61:I62)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C61:I62,"77W")&gt;0,"77W("&amp;COUNTIF(C61:I62,"77W")&amp;") ","")&amp;IF(COUNTIF(C61:I62,"778")&gt;0,"778("&amp;COUNTIF(C61:I62,"778")&amp;") ","")&amp;IF(COUNTIF(C61:I62,"A320")&gt;0,"A320("&amp;COUNTIF(C61:I62,"A320")&amp;") ",""))," ",", "))</f>
+        <v>778(1)</v>
+      </c>
+      <c r="L61" s="51"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="54" t="n">
+      <c r="B62" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C62" s="38"/>
+      <c r="D62" s="38"/>
+      <c r="E62" s="38"/>
+      <c r="F62" s="38"/>
+      <c r="G62" s="38"/>
+      <c r="H62" s="38"/>
+      <c r="I62" s="38"/>
+      <c r="J62" s="39"/>
+      <c r="K62" s="39"/>
+      <c r="L62" s="51"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="C63" s="38"/>
+      <c r="D63" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="E63" s="38"/>
+      <c r="F63" s="38"/>
+      <c r="G63" s="38"/>
+      <c r="H63" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="I63" s="38"/>
+      <c r="J63" s="39" t="n">
+        <f aca="false">COUNTA(C63:I64)</f>
+        <v>2</v>
+      </c>
+      <c r="K63" s="20" t="str">
+        <f aca="false">IF(COUNTA(C63:I64)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C63:I64,"77W")&gt;0,"77W("&amp;COUNTIF(C63:I64,"77W")&amp;") ","")&amp;IF(COUNTIF(C63:I64,"778")&gt;0,"778("&amp;COUNTIF(C63:I64,"778")&amp;") ","")&amp;IF(COUNTIF(C63:I64,"A320")&gt;0,"A320("&amp;COUNTIF(C63:I64,"A320")&amp;") ",""))," ",", "))</f>
+        <v>A320(2)</v>
+      </c>
+      <c r="L63" s="52"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C64" s="38"/>
+      <c r="D64" s="38"/>
+      <c r="E64" s="38"/>
+      <c r="F64" s="38"/>
+      <c r="G64" s="38"/>
+      <c r="H64" s="38"/>
+      <c r="I64" s="38"/>
+      <c r="J64" s="39"/>
+      <c r="K64" s="39"/>
+      <c r="L64" s="52"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="37" t="s">
+        <v>90</v>
+      </c>
+      <c r="C65" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="D65" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="E65" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="F65" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="G65" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H65" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="I65" s="38"/>
+      <c r="J65" s="39" t="n">
+        <f aca="false">COUNTA(C65:I66)</f>
+        <v>7</v>
+      </c>
+      <c r="K65" s="20" t="str">
+        <f aca="false">IF(COUNTA(C65:I66)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C65:I66,"77W")&gt;0,"77W("&amp;COUNTIF(C65:I66,"77W")&amp;") ","")&amp;IF(COUNTIF(C65:I66,"778")&gt;0,"778("&amp;COUNTIF(C65:I66,"778")&amp;") ","")&amp;IF(COUNTIF(C65:I66,"A320")&gt;0,"A320("&amp;COUNTIF(C65:I66,"A320")&amp;") ",""))," ",", "))</f>
+        <v>A320(7)</v>
+      </c>
+      <c r="L65" s="53"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C66" s="38"/>
+      <c r="D66" s="38"/>
+      <c r="E66" s="38"/>
+      <c r="F66" s="38"/>
+      <c r="G66" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="H66" s="38"/>
+      <c r="I66" s="38"/>
+      <c r="J66" s="39"/>
+      <c r="K66" s="39"/>
+      <c r="L66" s="53"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="37" t="s">
+        <v>91</v>
+      </c>
+      <c r="C67" s="38"/>
+      <c r="D67" s="38"/>
+      <c r="E67" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="F67" s="38"/>
+      <c r="G67" s="38"/>
+      <c r="H67" s="38"/>
+      <c r="I67" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="J67" s="39" t="n">
+        <f aca="false">COUNTA(C67:I68)</f>
+        <v>2</v>
+      </c>
+      <c r="K67" s="20" t="str">
+        <f aca="false">IF(COUNTA(C67:I68)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C67:I68,"77W")&gt;0,"77W("&amp;COUNTIF(C67:I68,"77W")&amp;") ","")&amp;IF(COUNTIF(C67:I68,"778")&gt;0,"778("&amp;COUNTIF(C67:I68,"778")&amp;") ","")&amp;IF(COUNTIF(C67:I68,"A320")&gt;0,"A320("&amp;COUNTIF(C67:I68,"A320")&amp;") ",""))," ",", "))</f>
+        <v>A320(2)</v>
+      </c>
+      <c r="L67" s="54"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="43" t="s">
+        <v>68</v>
+      </c>
+      <c r="C68" s="38"/>
+      <c r="D68" s="38"/>
+      <c r="E68" s="38"/>
+      <c r="F68" s="38"/>
+      <c r="G68" s="38"/>
+      <c r="H68" s="38"/>
+      <c r="I68" s="38"/>
+      <c r="J68" s="39"/>
+      <c r="K68" s="39"/>
+      <c r="L68" s="54"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="33" t="s">
+        <v>92</v>
+      </c>
+      <c r="C71" s="33"/>
+      <c r="D71" s="33"/>
+      <c r="E71" s="33"/>
+      <c r="F71" s="33"/>
+      <c r="G71" s="33"/>
+      <c r="H71" s="33"/>
+      <c r="I71" s="33"/>
+      <c r="J71" s="33"/>
+      <c r="K71" s="33"/>
+      <c r="L71" s="33"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B72" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="C72" s="34"/>
+      <c r="D72" s="34"/>
+      <c r="E72" s="34"/>
+      <c r="F72" s="34"/>
+      <c r="G72" s="34"/>
+      <c r="H72" s="34"/>
+      <c r="I72" s="34"/>
+      <c r="J72" s="34"/>
+      <c r="K72" s="34"/>
+      <c r="L72" s="34"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="34"/>
+      <c r="C73" s="34"/>
+      <c r="D73" s="34"/>
+      <c r="E73" s="34"/>
+      <c r="F73" s="34"/>
+      <c r="G73" s="34"/>
+      <c r="H73" s="34"/>
+      <c r="I73" s="34"/>
+      <c r="J73" s="34"/>
+      <c r="K73" s="34"/>
+      <c r="L73" s="34"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="35" t="s">
+        <v>94</v>
+      </c>
+      <c r="C74" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="D74" s="35" t="s">
+        <v>95</v>
+      </c>
+      <c r="E74" s="35" t="s">
+        <v>96</v>
+      </c>
+      <c r="F74" s="35" t="s">
+        <v>97</v>
+      </c>
+      <c r="J74" s="55" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="56" t="n">
         <v>46484</v>
       </c>
-      <c r="C62" s="37" t="s">
+      <c r="C75" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="D62" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="E62" s="55" t="n">
+      <c r="D75" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="E75" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="F62" s="56" t="s">
-        <v>87</v>
-      </c>
-      <c r="J62" s="57" t="str">
-        <f aca="false">IF(OR($B62="",$C62=""),"",$B62&amp;"|"&amp;$C62)</f>
+      <c r="F75" s="58" t="s">
+        <v>99</v>
+      </c>
+      <c r="J75" s="59" t="str">
+        <f aca="false">IF(OR($B75="",$C75=""),"",$B75&amp;"|"&amp;$C75)</f>
         <v>46484|NOSRUN</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="54" t="n">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="56" t="n">
         <v>46487</v>
       </c>
-      <c r="C63" s="37" t="s">
+      <c r="C76" s="38" t="s">
         <v>8</v>
       </c>
-      <c r="D63" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="E63" s="55" t="n">
+      <c r="D76" s="38" t="s">
+        <v>73</v>
+      </c>
+      <c r="E76" s="57" t="n">
         <v>1</v>
       </c>
-      <c r="F63" s="56" t="s">
-        <v>88</v>
-      </c>
-      <c r="J63" s="57" t="str">
-        <f aca="false">IF(OR($B63="",$C63=""),"",$B63&amp;"|"&amp;$C63)</f>
+      <c r="F76" s="58" t="s">
+        <v>100</v>
+      </c>
+      <c r="J76" s="59" t="str">
+        <f aca="false">IF(OR($B76="",$C76=""),"",$B76&amp;"|"&amp;$C76)</f>
         <v>46487|NOSRUN</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="54" t="n">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="56" t="n">
         <v>46497</v>
       </c>
-      <c r="C64" s="37" t="s">
-        <v>55</v>
-      </c>
-      <c r="D64" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="E64" s="55" t="n">
+      <c r="C77" s="38" t="s">
+        <v>66</v>
+      </c>
+      <c r="D77" s="38" t="s">
+        <v>69</v>
+      </c>
+      <c r="E77" s="57" t="n">
         <v>2</v>
       </c>
-      <c r="F64" s="56" t="s">
-        <v>89</v>
-      </c>
-      <c r="J64" s="57" t="str">
-        <f aca="false">IF(OR($B64="",$C64=""),"",$B64&amp;"|"&amp;$C64)</f>
+      <c r="F77" s="58" t="s">
+        <v>101</v>
+      </c>
+      <c r="J77" s="59" t="str">
+        <f aca="false">IF(OR($B77="",$C77=""),"",$B77&amp;"|"&amp;$C77)</f>
         <v>46497|CDGRUN</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="54"/>
-      <c r="C65" s="37"/>
-      <c r="D65" s="37"/>
-      <c r="E65" s="55"/>
-      <c r="F65" s="56"/>
-      <c r="J65" s="57" t="str">
-        <f aca="false">IF(OR($B65="",$C65=""),"",$B65&amp;"|"&amp;$C65)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="54"/>
-      <c r="C66" s="37"/>
-      <c r="D66" s="37"/>
-      <c r="E66" s="55"/>
-      <c r="F66" s="56"/>
-      <c r="J66" s="57" t="str">
-        <f aca="false">IF(OR($B66="",$C66=""),"",$B66&amp;"|"&amp;$C66)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="54"/>
-      <c r="C67" s="37"/>
-      <c r="D67" s="37"/>
-      <c r="E67" s="55"/>
-      <c r="F67" s="56"/>
-      <c r="J67" s="57" t="str">
-        <f aca="false">IF(OR($B67="",$C67=""),"",$B67&amp;"|"&amp;$C67)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="54"/>
-      <c r="C68" s="37"/>
-      <c r="D68" s="37"/>
-      <c r="E68" s="55"/>
-      <c r="F68" s="56"/>
-      <c r="J68" s="57" t="str">
-        <f aca="false">IF(OR($B68="",$C68=""),"",$B68&amp;"|"&amp;$C68)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B69" s="54"/>
-      <c r="C69" s="37"/>
-      <c r="D69" s="37"/>
-      <c r="E69" s="55"/>
-      <c r="F69" s="56"/>
-      <c r="J69" s="57" t="str">
-        <f aca="false">IF(OR($B69="",$C69=""),"",$B69&amp;"|"&amp;$C69)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B70" s="54"/>
-      <c r="C70" s="37"/>
-      <c r="D70" s="37"/>
-      <c r="E70" s="55"/>
-      <c r="F70" s="56"/>
-      <c r="J70" s="57" t="str">
-        <f aca="false">IF(OR($B70="",$C70=""),"",$B70&amp;"|"&amp;$C70)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="54"/>
-      <c r="C71" s="37"/>
-      <c r="D71" s="37"/>
-      <c r="E71" s="55"/>
-      <c r="F71" s="56"/>
-      <c r="J71" s="57" t="str">
-        <f aca="false">IF(OR($B71="",$C71=""),"",$B71&amp;"|"&amp;$C71)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B72" s="54"/>
-      <c r="C72" s="37"/>
-      <c r="D72" s="37"/>
-      <c r="E72" s="55"/>
-      <c r="F72" s="56"/>
-      <c r="J72" s="57" t="str">
-        <f aca="false">IF(OR($B72="",$C72=""),"",$B72&amp;"|"&amp;$C72)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="54"/>
-      <c r="C73" s="37"/>
-      <c r="D73" s="37"/>
-      <c r="E73" s="55"/>
-      <c r="F73" s="56"/>
-      <c r="J73" s="57" t="str">
-        <f aca="false">IF(OR($B73="",$C73=""),"",$B73&amp;"|"&amp;$C73)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="54"/>
-      <c r="C74" s="37"/>
-      <c r="D74" s="37"/>
-      <c r="E74" s="55"/>
-      <c r="F74" s="56"/>
-      <c r="J74" s="57" t="str">
-        <f aca="false">IF(OR($B74="",$C74=""),"",$B74&amp;"|"&amp;$C74)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="54"/>
-      <c r="C75" s="37"/>
-      <c r="D75" s="37"/>
-      <c r="E75" s="55"/>
-      <c r="F75" s="56"/>
-      <c r="J75" s="57" t="str">
-        <f aca="false">IF(OR($B75="",$C75=""),"",$B75&amp;"|"&amp;$C75)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="54"/>
-      <c r="C76" s="37"/>
-      <c r="D76" s="37"/>
-      <c r="E76" s="55"/>
-      <c r="F76" s="56"/>
-      <c r="J76" s="57" t="str">
-        <f aca="false">IF(OR($B76="",$C76=""),"",$B76&amp;"|"&amp;$C76)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="54"/>
-      <c r="C77" s="37"/>
-      <c r="D77" s="37"/>
-      <c r="E77" s="55"/>
-      <c r="F77" s="56"/>
-      <c r="J77" s="57" t="str">
-        <f aca="false">IF(OR($B77="",$C77=""),"",$B77&amp;"|"&amp;$C77)</f>
-        <v/>
-      </c>
-    </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="54"/>
-      <c r="C78" s="37"/>
-      <c r="D78" s="37"/>
-      <c r="E78" s="55"/>
-      <c r="F78" s="56"/>
-      <c r="J78" s="57" t="str">
+      <c r="B78" s="56"/>
+      <c r="C78" s="38"/>
+      <c r="D78" s="38"/>
+      <c r="E78" s="57"/>
+      <c r="F78" s="58"/>
+      <c r="J78" s="59" t="str">
         <f aca="false">IF(OR($B78="",$C78=""),"",$B78&amp;"|"&amp;$C78)</f>
         <v/>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="54"/>
-      <c r="C79" s="37"/>
-      <c r="D79" s="37"/>
-      <c r="E79" s="55"/>
-      <c r="F79" s="56"/>
-      <c r="J79" s="57" t="str">
+      <c r="B79" s="56"/>
+      <c r="C79" s="38"/>
+      <c r="D79" s="38"/>
+      <c r="E79" s="57"/>
+      <c r="F79" s="58"/>
+      <c r="J79" s="59" t="str">
         <f aca="false">IF(OR($B79="",$C79=""),"",$B79&amp;"|"&amp;$C79)</f>
         <v/>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="54"/>
-      <c r="C80" s="37"/>
-      <c r="D80" s="37"/>
-      <c r="E80" s="55"/>
-      <c r="F80" s="56"/>
-      <c r="J80" s="57" t="str">
+      <c r="B80" s="56"/>
+      <c r="C80" s="38"/>
+      <c r="D80" s="38"/>
+      <c r="E80" s="57"/>
+      <c r="F80" s="58"/>
+      <c r="J80" s="59" t="str">
         <f aca="false">IF(OR($B80="",$C80=""),"",$B80&amp;"|"&amp;$C80)</f>
         <v/>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="54"/>
-      <c r="C81" s="37"/>
-      <c r="D81" s="37"/>
-      <c r="E81" s="55"/>
-      <c r="F81" s="56"/>
-      <c r="J81" s="57" t="str">
+      <c r="B81" s="56"/>
+      <c r="C81" s="38"/>
+      <c r="D81" s="38"/>
+      <c r="E81" s="57"/>
+      <c r="F81" s="58"/>
+      <c r="J81" s="59" t="str">
         <f aca="false">IF(OR($B81="",$C81=""),"",$B81&amp;"|"&amp;$C81)</f>
         <v/>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="54"/>
-      <c r="C82" s="37"/>
-      <c r="D82" s="37"/>
-      <c r="E82" s="55"/>
-      <c r="F82" s="56"/>
-      <c r="J82" s="57" t="str">
+      <c r="B82" s="56"/>
+      <c r="C82" s="38"/>
+      <c r="D82" s="38"/>
+      <c r="E82" s="57"/>
+      <c r="F82" s="58"/>
+      <c r="J82" s="59" t="str">
         <f aca="false">IF(OR($B82="",$C82=""),"",$B82&amp;"|"&amp;$C82)</f>
         <v/>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="54"/>
-      <c r="C83" s="37"/>
-      <c r="D83" s="37"/>
-      <c r="E83" s="55"/>
-      <c r="F83" s="56"/>
-      <c r="J83" s="57" t="str">
+      <c r="B83" s="56"/>
+      <c r="C83" s="38"/>
+      <c r="D83" s="38"/>
+      <c r="E83" s="57"/>
+      <c r="F83" s="58"/>
+      <c r="J83" s="59" t="str">
         <f aca="false">IF(OR($B83="",$C83=""),"",$B83&amp;"|"&amp;$C83)</f>
         <v/>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="54"/>
-      <c r="C84" s="37"/>
-      <c r="D84" s="37"/>
-      <c r="E84" s="55"/>
-      <c r="F84" s="56"/>
-      <c r="J84" s="57" t="str">
+      <c r="B84" s="56"/>
+      <c r="C84" s="38"/>
+      <c r="D84" s="38"/>
+      <c r="E84" s="57"/>
+      <c r="F84" s="58"/>
+      <c r="J84" s="59" t="str">
         <f aca="false">IF(OR($B84="",$C84=""),"",$B84&amp;"|"&amp;$C84)</f>
         <v/>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="54"/>
-      <c r="C85" s="37"/>
-      <c r="D85" s="37"/>
-      <c r="E85" s="55"/>
-      <c r="F85" s="56"/>
-      <c r="J85" s="57" t="str">
+      <c r="B85" s="56"/>
+      <c r="C85" s="38"/>
+      <c r="D85" s="38"/>
+      <c r="E85" s="57"/>
+      <c r="F85" s="58"/>
+      <c r="J85" s="59" t="str">
         <f aca="false">IF(OR($B85="",$C85=""),"",$B85&amp;"|"&amp;$C85)</f>
         <v/>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="54"/>
-      <c r="C86" s="37"/>
-      <c r="D86" s="37"/>
-      <c r="E86" s="55"/>
-      <c r="F86" s="56"/>
-      <c r="J86" s="57" t="str">
+      <c r="B86" s="56"/>
+      <c r="C86" s="38"/>
+      <c r="D86" s="38"/>
+      <c r="E86" s="57"/>
+      <c r="F86" s="58"/>
+      <c r="J86" s="59" t="str">
         <f aca="false">IF(OR($B86="",$C86=""),"",$B86&amp;"|"&amp;$C86)</f>
         <v/>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="54"/>
-      <c r="C87" s="37"/>
-      <c r="D87" s="37"/>
-      <c r="E87" s="55"/>
-      <c r="F87" s="56"/>
-      <c r="J87" s="57" t="str">
+      <c r="B87" s="56"/>
+      <c r="C87" s="38"/>
+      <c r="D87" s="38"/>
+      <c r="E87" s="57"/>
+      <c r="F87" s="58"/>
+      <c r="J87" s="59" t="str">
         <f aca="false">IF(OR($B87="",$C87=""),"",$B87&amp;"|"&amp;$C87)</f>
         <v/>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="54"/>
-      <c r="C88" s="37"/>
-      <c r="D88" s="37"/>
-      <c r="E88" s="55"/>
-      <c r="F88" s="56"/>
-      <c r="J88" s="57" t="str">
+      <c r="B88" s="56"/>
+      <c r="C88" s="38"/>
+      <c r="D88" s="38"/>
+      <c r="E88" s="57"/>
+      <c r="F88" s="58"/>
+      <c r="J88" s="59" t="str">
         <f aca="false">IF(OR($B88="",$C88=""),"",$B88&amp;"|"&amp;$C88)</f>
         <v/>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="54"/>
-      <c r="C89" s="37"/>
-      <c r="D89" s="37"/>
-      <c r="E89" s="55"/>
-      <c r="F89" s="56"/>
-      <c r="J89" s="57" t="str">
+      <c r="B89" s="56"/>
+      <c r="C89" s="38"/>
+      <c r="D89" s="38"/>
+      <c r="E89" s="57"/>
+      <c r="F89" s="58"/>
+      <c r="J89" s="59" t="str">
         <f aca="false">IF(OR($B89="",$C89=""),"",$B89&amp;"|"&amp;$C89)</f>
         <v/>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="54"/>
-      <c r="C90" s="37"/>
-      <c r="D90" s="37"/>
-      <c r="E90" s="55"/>
-      <c r="F90" s="56"/>
-      <c r="J90" s="57" t="str">
+      <c r="B90" s="56"/>
+      <c r="C90" s="38"/>
+      <c r="D90" s="38"/>
+      <c r="E90" s="57"/>
+      <c r="F90" s="58"/>
+      <c r="J90" s="59" t="str">
         <f aca="false">IF(OR($B90="",$C90=""),"",$B90&amp;"|"&amp;$C90)</f>
         <v/>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="54"/>
-      <c r="C91" s="37"/>
-      <c r="D91" s="37"/>
-      <c r="E91" s="55"/>
-      <c r="F91" s="56"/>
-      <c r="J91" s="57" t="str">
+      <c r="B91" s="56"/>
+      <c r="C91" s="38"/>
+      <c r="D91" s="38"/>
+      <c r="E91" s="57"/>
+      <c r="F91" s="58"/>
+      <c r="J91" s="59" t="str">
         <f aca="false">IF(OR($B91="",$C91=""),"",$B91&amp;"|"&amp;$C91)</f>
         <v/>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="54"/>
-      <c r="C92" s="37"/>
-      <c r="D92" s="37"/>
-      <c r="E92" s="55"/>
-      <c r="F92" s="56"/>
-      <c r="J92" s="57" t="str">
+      <c r="B92" s="56"/>
+      <c r="C92" s="38"/>
+      <c r="D92" s="38"/>
+      <c r="E92" s="57"/>
+      <c r="F92" s="58"/>
+      <c r="J92" s="59" t="str">
         <f aca="false">IF(OR($B92="",$C92=""),"",$B92&amp;"|"&amp;$C92)</f>
         <v/>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="54"/>
-      <c r="C93" s="37"/>
-      <c r="D93" s="37"/>
-      <c r="E93" s="55"/>
-      <c r="F93" s="56"/>
-      <c r="J93" s="57" t="str">
+      <c r="B93" s="56"/>
+      <c r="C93" s="38"/>
+      <c r="D93" s="38"/>
+      <c r="E93" s="57"/>
+      <c r="F93" s="58"/>
+      <c r="J93" s="59" t="str">
         <f aca="false">IF(OR($B93="",$C93=""),"",$B93&amp;"|"&amp;$C93)</f>
         <v/>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="54"/>
-      <c r="C94" s="37"/>
-      <c r="D94" s="37"/>
-      <c r="E94" s="55"/>
-      <c r="F94" s="56"/>
-      <c r="J94" s="57" t="str">
+      <c r="B94" s="56"/>
+      <c r="C94" s="38"/>
+      <c r="D94" s="38"/>
+      <c r="E94" s="57"/>
+      <c r="F94" s="58"/>
+      <c r="J94" s="59" t="str">
         <f aca="false">IF(OR($B94="",$C94=""),"",$B94&amp;"|"&amp;$C94)</f>
         <v/>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="54"/>
-      <c r="C95" s="37"/>
-      <c r="D95" s="37"/>
-      <c r="E95" s="55"/>
-      <c r="F95" s="56"/>
-      <c r="J95" s="57" t="str">
+      <c r="B95" s="56"/>
+      <c r="C95" s="38"/>
+      <c r="D95" s="38"/>
+      <c r="E95" s="57"/>
+      <c r="F95" s="58"/>
+      <c r="J95" s="59" t="str">
         <f aca="false">IF(OR($B95="",$C95=""),"",$B95&amp;"|"&amp;$C95)</f>
         <v/>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B96" s="54"/>
-      <c r="C96" s="37"/>
-      <c r="D96" s="37"/>
-      <c r="E96" s="55"/>
-      <c r="F96" s="56"/>
-      <c r="J96" s="57" t="str">
+      <c r="B96" s="56"/>
+      <c r="C96" s="38"/>
+      <c r="D96" s="38"/>
+      <c r="E96" s="57"/>
+      <c r="F96" s="58"/>
+      <c r="J96" s="59" t="str">
         <f aca="false">IF(OR($B96="",$C96=""),"",$B96&amp;"|"&amp;$C96)</f>
         <v/>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B97" s="54"/>
-      <c r="C97" s="37"/>
-      <c r="D97" s="37"/>
-      <c r="E97" s="55"/>
-      <c r="F97" s="56"/>
-      <c r="J97" s="57" t="str">
+      <c r="B97" s="56"/>
+      <c r="C97" s="38"/>
+      <c r="D97" s="38"/>
+      <c r="E97" s="57"/>
+      <c r="F97" s="58"/>
+      <c r="J97" s="59" t="str">
         <f aca="false">IF(OR($B97="",$C97=""),"",$B97&amp;"|"&amp;$C97)</f>
         <v/>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B98" s="54"/>
-      <c r="C98" s="37"/>
-      <c r="D98" s="37"/>
-      <c r="E98" s="55"/>
-      <c r="F98" s="56"/>
-      <c r="J98" s="57" t="str">
+      <c r="B98" s="56"/>
+      <c r="C98" s="38"/>
+      <c r="D98" s="38"/>
+      <c r="E98" s="57"/>
+      <c r="F98" s="58"/>
+      <c r="J98" s="59" t="str">
         <f aca="false">IF(OR($B98="",$C98=""),"",$B98&amp;"|"&amp;$C98)</f>
         <v/>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="54"/>
-      <c r="C99" s="37"/>
-      <c r="D99" s="37"/>
-      <c r="E99" s="55"/>
-      <c r="F99" s="56"/>
-      <c r="J99" s="57" t="str">
+      <c r="B99" s="56"/>
+      <c r="C99" s="38"/>
+      <c r="D99" s="38"/>
+      <c r="E99" s="57"/>
+      <c r="F99" s="58"/>
+      <c r="J99" s="59" t="str">
         <f aca="false">IF(OR($B99="",$C99=""),"",$B99&amp;"|"&amp;$C99)</f>
         <v/>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B100" s="54"/>
-      <c r="C100" s="37"/>
-      <c r="D100" s="37"/>
-      <c r="E100" s="55"/>
-      <c r="F100" s="56"/>
-      <c r="J100" s="57" t="str">
+      <c r="B100" s="56"/>
+      <c r="C100" s="38"/>
+      <c r="D100" s="38"/>
+      <c r="E100" s="57"/>
+      <c r="F100" s="58"/>
+      <c r="J100" s="59" t="str">
         <f aca="false">IF(OR($B100="",$C100=""),"",$B100&amp;"|"&amp;$C100)</f>
         <v/>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B101" s="54"/>
-      <c r="C101" s="37"/>
-      <c r="D101" s="37"/>
-      <c r="E101" s="55"/>
-      <c r="F101" s="56"/>
-      <c r="J101" s="57" t="str">
+      <c r="B101" s="56"/>
+      <c r="C101" s="38"/>
+      <c r="D101" s="38"/>
+      <c r="E101" s="57"/>
+      <c r="F101" s="58"/>
+      <c r="J101" s="59" t="str">
         <f aca="false">IF(OR($B101="",$C101=""),"",$B101&amp;"|"&amp;$C101)</f>
         <v/>
       </c>
     </row>
+    <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B102" s="56"/>
+      <c r="C102" s="38"/>
+      <c r="D102" s="38"/>
+      <c r="E102" s="57"/>
+      <c r="F102" s="58"/>
+      <c r="J102" s="59" t="str">
+        <f aca="false">IF(OR($B102="",$C102=""),"",$B102&amp;"|"&amp;$C102)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B103" s="56"/>
+      <c r="C103" s="38"/>
+      <c r="D103" s="38"/>
+      <c r="E103" s="57"/>
+      <c r="F103" s="58"/>
+      <c r="J103" s="59" t="str">
+        <f aca="false">IF(OR($B103="",$C103=""),"",$B103&amp;"|"&amp;$C103)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B104" s="56"/>
+      <c r="C104" s="38"/>
+      <c r="D104" s="38"/>
+      <c r="E104" s="57"/>
+      <c r="F104" s="58"/>
+      <c r="J104" s="59" t="str">
+        <f aca="false">IF(OR($B104="",$C104=""),"",$B104&amp;"|"&amp;$C104)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B105" s="56"/>
+      <c r="C105" s="38"/>
+      <c r="D105" s="38"/>
+      <c r="E105" s="57"/>
+      <c r="F105" s="58"/>
+      <c r="J105" s="59" t="str">
+        <f aca="false">IF(OR($B105="",$C105=""),"",$B105&amp;"|"&amp;$C105)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B106" s="56"/>
+      <c r="C106" s="38"/>
+      <c r="D106" s="38"/>
+      <c r="E106" s="57"/>
+      <c r="F106" s="58"/>
+      <c r="J106" s="59" t="str">
+        <f aca="false">IF(OR($B106="",$C106=""),"",$B106&amp;"|"&amp;$C106)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B107" s="56"/>
+      <c r="C107" s="38"/>
+      <c r="D107" s="38"/>
+      <c r="E107" s="57"/>
+      <c r="F107" s="58"/>
+      <c r="J107" s="59" t="str">
+        <f aca="false">IF(OR($B107="",$C107=""),"",$B107&amp;"|"&amp;$C107)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B108" s="56"/>
+      <c r="C108" s="38"/>
+      <c r="D108" s="38"/>
+      <c r="E108" s="57"/>
+      <c r="F108" s="58"/>
+      <c r="J108" s="59" t="str">
+        <f aca="false">IF(OR($B108="",$C108=""),"",$B108&amp;"|"&amp;$C108)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B109" s="56"/>
+      <c r="C109" s="38"/>
+      <c r="D109" s="38"/>
+      <c r="E109" s="57"/>
+      <c r="F109" s="58"/>
+      <c r="J109" s="59" t="str">
+        <f aca="false">IF(OR($B109="",$C109=""),"",$B109&amp;"|"&amp;$C109)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B110" s="56"/>
+      <c r="C110" s="38"/>
+      <c r="D110" s="38"/>
+      <c r="E110" s="57"/>
+      <c r="F110" s="58"/>
+      <c r="J110" s="59" t="str">
+        <f aca="false">IF(OR($B110="",$C110=""),"",$B110&amp;"|"&amp;$C110)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B111" s="56"/>
+      <c r="C111" s="38"/>
+      <c r="D111" s="38"/>
+      <c r="E111" s="57"/>
+      <c r="F111" s="58"/>
+      <c r="J111" s="59" t="str">
+        <f aca="false">IF(OR($B111="",$C111=""),"",$B111&amp;"|"&amp;$C111)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B112" s="56"/>
+      <c r="C112" s="38"/>
+      <c r="D112" s="38"/>
+      <c r="E112" s="57"/>
+      <c r="F112" s="58"/>
+      <c r="J112" s="59" t="str">
+        <f aca="false">IF(OR($B112="",$C112=""),"",$B112&amp;"|"&amp;$C112)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B113" s="56"/>
+      <c r="C113" s="38"/>
+      <c r="D113" s="38"/>
+      <c r="E113" s="57"/>
+      <c r="F113" s="58"/>
+      <c r="J113" s="59" t="str">
+        <f aca="false">IF(OR($B113="",$C113=""),"",$B113&amp;"|"&amp;$C113)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B114" s="56"/>
+      <c r="C114" s="38"/>
+      <c r="D114" s="38"/>
+      <c r="E114" s="57"/>
+      <c r="F114" s="58"/>
+      <c r="J114" s="59" t="str">
+        <f aca="false">IF(OR($B114="",$C114=""),"",$B114&amp;"|"&amp;$C114)</f>
+        <v/>
+      </c>
+    </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="50">
     <mergeCell ref="B1:I1"/>
     <mergeCell ref="B2:I2"/>
     <mergeCell ref="N3:O3"/>
     <mergeCell ref="C4:D4"/>
     <mergeCell ref="C5:D5"/>
     <mergeCell ref="B6:I6"/>
+    <mergeCell ref="N10:U10"/>
     <mergeCell ref="D21:I21"/>
     <mergeCell ref="B23:L23"/>
     <mergeCell ref="B38:L39"/>
     <mergeCell ref="B41:L41"/>
     <mergeCell ref="B42:L43"/>
-    <mergeCell ref="B59:L59"/>
-    <mergeCell ref="B60:L60"/>
+    <mergeCell ref="J45:J46"/>
+    <mergeCell ref="K45:K46"/>
+    <mergeCell ref="L45:L46"/>
+    <mergeCell ref="J47:J48"/>
+    <mergeCell ref="K47:K48"/>
+    <mergeCell ref="L47:L48"/>
+    <mergeCell ref="J49:J50"/>
+    <mergeCell ref="K49:K50"/>
+    <mergeCell ref="L49:L50"/>
+    <mergeCell ref="J51:J52"/>
+    <mergeCell ref="K51:K52"/>
+    <mergeCell ref="L51:L52"/>
+    <mergeCell ref="J53:J54"/>
+    <mergeCell ref="K53:K54"/>
+    <mergeCell ref="L53:L54"/>
+    <mergeCell ref="J55:J56"/>
+    <mergeCell ref="K55:K56"/>
+    <mergeCell ref="L55:L56"/>
+    <mergeCell ref="J57:J58"/>
+    <mergeCell ref="K57:K58"/>
+    <mergeCell ref="L57:L58"/>
+    <mergeCell ref="J59:J60"/>
+    <mergeCell ref="K59:K60"/>
+    <mergeCell ref="L59:L60"/>
+    <mergeCell ref="J61:J62"/>
+    <mergeCell ref="K61:K62"/>
+    <mergeCell ref="L61:L62"/>
+    <mergeCell ref="J63:J64"/>
+    <mergeCell ref="K63:K64"/>
+    <mergeCell ref="L63:L64"/>
+    <mergeCell ref="J65:J66"/>
+    <mergeCell ref="K65:K66"/>
+    <mergeCell ref="L65:L66"/>
+    <mergeCell ref="J67:J68"/>
+    <mergeCell ref="K67:K68"/>
+    <mergeCell ref="L67:L68"/>
+    <mergeCell ref="B71:L71"/>
+    <mergeCell ref="B72:L73"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:I8 C10:I10 C12:I12 C14:I14 C16:I16 C18:I18">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -3948,79 +4144,79 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25:B36">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
       <formula>$B25="CDGRUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>$B25="CDGDZA"</formula>
     </cfRule>
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>$B25="BKKRUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>$B25="DZARUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>$B25="MRURUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>$B25="NOSRUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
+    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$B25="RUNTNR"</formula>
     </cfRule>
-    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
+    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>$B25="JNBRUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
+    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$B25="CPTRUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
+    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$B25="DIERUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
+    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$B25="RRGRUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
+    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$B25="TMMRUN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B45:B56">
-    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
-      <formula>$B45="CDGRUN"</formula>
+  <conditionalFormatting sqref="B45:B68">
+    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>OR($B45="CDGRUN",$B44="CDGRUN")</formula>
     </cfRule>
-    <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
-      <formula>$B45="CDGDZA"</formula>
+    <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+      <formula>OR($B45="CDGDZA",$B44="CDGDZA")</formula>
     </cfRule>
-    <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
-      <formula>$B45="BKKRUN"</formula>
+    <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+      <formula>OR($B45="BKKRUN",$B44="BKKRUN")</formula>
     </cfRule>
-    <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
-      <formula>$B45="DZARUN"</formula>
+    <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+      <formula>OR($B45="DZARUN",$B44="DZARUN")</formula>
     </cfRule>
-    <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
-      <formula>$B45="MRURUN"</formula>
+    <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+      <formula>OR($B45="MRURUN",$B44="MRURUN")</formula>
     </cfRule>
-    <cfRule type="expression" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
-      <formula>$B45="NOSRUN"</formula>
+    <cfRule type="expression" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+      <formula>OR($B45="NOSRUN",$B44="NOSRUN")</formula>
     </cfRule>
-    <cfRule type="expression" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="19">
-      <formula>$B45="RUNTNR"</formula>
+    <cfRule type="expression" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+      <formula>OR($B45="RUNTNR",$B44="RUNTNR")</formula>
     </cfRule>
-    <cfRule type="expression" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="20">
-      <formula>$B45="JNBRUN"</formula>
+    <cfRule type="expression" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+      <formula>OR($B45="JNBRUN",$B44="JNBRUN")</formula>
     </cfRule>
-    <cfRule type="expression" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="21">
-      <formula>$B45="CPTRUN"</formula>
+    <cfRule type="expression" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+      <formula>OR($B45="CPTRUN",$B44="CPTRUN")</formula>
     </cfRule>
-    <cfRule type="expression" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="22">
-      <formula>$B45="DIERUN"</formula>
+    <cfRule type="expression" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+      <formula>OR($B45="DIERUN",$B44="DIERUN")</formula>
     </cfRule>
-    <cfRule type="expression" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="23">
-      <formula>$B45="RRGRUN"</formula>
+    <cfRule type="expression" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+      <formula>OR($B45="RRGRUN",$B44="RRGRUN")</formula>
     </cfRule>
-    <cfRule type="expression" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="24">
-      <formula>$B45="TMMRUN"</formula>
+    <cfRule type="expression" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+      <formula>OR($B45="TMMRUN",$B44="TMMRUN")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
@@ -4029,26 +4225,26 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C5" type="list">
-      <formula1>$B$45:$B$56</formula1>
+      <formula1>$B$45:$B$68</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Choisir un type avion dans la liste, ou laisser vide si la route n'opere pas ce jour-la." errorStyle="stop" errorTitle="Type avion invalide" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C45:I56" type="list">
+    <dataValidation allowBlank="true" error="Choisir un type avion dans la liste, ou laisser vide s'il n'y a pas de vol ce jour-la." errorStyle="stop" errorTitle="Type avion invalide" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C45:I68" type="list">
       <formula1>$P$45:$P$47</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C62:C101" type="list">
-      <formula1>$B$45:$B$56</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C75:C114" type="list">
+      <formula1>$B$45:$B$68</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D62:D101" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D75:D114" type="list">
       <formula1>$P$45:$P$47</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Nombre de rotations : entier entre 1 et 20." errorStyle="stop" errorTitle="Valeur invalide" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E62:E101" type="whole">
+    <dataValidation allowBlank="true" error="Nombre de rotations : entier entre 1 et 20." errorStyle="stop" errorTitle="Valeur invalide" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E75:E114" type="whole">
       <formula1>1</formula1>
       <formula2>20</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="La date est hors de l'annee avril 2027 - mars 2028 : le vol ne sera visible dans aucun mois." errorStyle="warning" errorTitle="Date hors annee d'exploitation" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B62:B101" type="date">
+    <dataValidation allowBlank="true" error="La date est hors de l'annee avril 2027 - mars 2028 : le vol ne sera visible dans aucun mois." errorStyle="warning" errorTitle="Date hors annee d'exploitation" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B75:B114" type="date">
       <formula1>DATE(2027,4,1)</formula1>
       <formula2>DATE(2028,3,31)</formula2>
     </dataValidation>

--- a/Programme_vols_mensuel_2027-2028.xlsx
+++ b/Programme_vols_mensuel_2027-2028.xlsx
@@ -28,7 +28,7 @@
     <author>Unknown Author</author>
   </authors>
   <commentList>
-    <comment ref="B75" authorId="0">
+    <comment ref="B87" authorId="0">
       <text>
         <r>
           <rPr>
@@ -71,12 +71,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="102">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="104">
   <si>
     <t xml:space="preserve">PROGRAMME DE VOLS MENSUEL - ANNEE D'EXPLOITATION AVRIL 2027 / MARS 2028</t>
   </si>
   <si>
-    <t xml:space="preserve">Feuille unique : les deux filtres ci-dessous (Mois et Route) pilotent la grille, le recapitulatif ne suit que le filtre Mois. Chaque route a une semaine type de 2 vols possibles par jour, chacun avec son propre type avion (2 types differents le meme jour sont donc possibles), a laquelle s'ajoutent les vols additionnels dates saisis en bas de feuille. Tout est calcule par formule.</t>
+    <t xml:space="preserve">Feuille unique : les deux filtres ci-dessous (Mois et Route) pilotent la grille, le recapitulatif ne suit que le filtre Mois. Chaque route a une semaine type de 3 vols possibles par jour, chacun avec son propre type avion (2 voire 3 types differents le meme jour sont donc possibles), a laquelle s'ajoutent les vols additionnels dates saisis en bas de feuille. Tout est calcule par formule.</t>
   </si>
   <si>
     <t xml:space="preserve">REPERES CALCULES</t>
@@ -190,6 +190,9 @@
     <t xml:space="preserve">Semaine 4</t>
   </si>
   <si>
+    <t xml:space="preserve">Vol 3</t>
+  </si>
+  <si>
     <t xml:space="preserve">Semaine 5</t>
   </si>
   <si>
@@ -202,7 +205,7 @@
     <t xml:space="preserve">Nb de semaines calendaires du mois</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture : "778" = 1 vol de la semaine type  |  "77W/778" = 2 vols le meme jour  |  "778 (+A320)" = semaine type + vol additionnel (bordure rouge)  |  "(+A320)" = vol additionnel seul. Semaines partielles incluses.</t>
+    <t xml:space="preserve">Lecture : "778" = 1 vol de la semaine type  |  "77W/778/A320" = 2 ou 3 vols le meme jour  |  "778 (+A320)" = semaine type + vol additionnel (bordure rouge)  |  "(+A320)" = vol additionnel seul. Semaines partielles incluses.</t>
   </si>
   <si>
     <t xml:space="preserve">RECAPITULATIF MENSUEL - TOUTES ROUTES  (depend uniquement du filtre Mois)</t>
@@ -241,13 +244,13 @@
     <t xml:space="preserve">TOTAL GENERAL</t>
   </si>
   <si>
-    <t xml:space="preserve">Methode : pour chaque jour opere de la semaine type, le nombre d'occurrences de ce jour dans le mois est compte a partir des dates reelles de la grille (ligne "Occurrences du jour dans le mois", semaines partielles incluses), vol 1 et vol 2 comptes separement. Total rotations du mois = semaine type + vols additionnels dates du mois. La colonne "Nb de semaines/occurrences" indique le nombre de semaines calendaires couvertes par le mois ; les colonnes Total 77W / 778 / A320 ventilent le total du mois par type avion.</t>
+    <t xml:space="preserve">Methode : pour chaque jour opere de la semaine type, le nombre d'occurrences de ce jour dans le mois est compte a partir des dates reelles de la grille (ligne "Occurrences du jour dans le mois", semaines partielles incluses), les vols 1, 2 et 3 etant comptes separement. Total rotations du mois = semaine type + vols additionnels dates du mois. La colonne "Nb de semaines/occurrences" indique le nombre de semaines calendaires couvertes par le mois ; les colonnes Total 77W / 778 / A320 ventilent le total du mois par type avion.</t>
   </si>
   <si>
     <t xml:space="preserve">1) SEMAINES TYPES PAR ROUTE (saisie unique, valable pour les 12 mois)</t>
   </si>
   <si>
-    <t xml:space="preserve">Cellules en BLEU = saisie utilisateur. Chaque route occupe 2 lignes : le VOL 1 et le VOL 2 de la journee. Pour chaque jour J1-J7, choisir dans la liste deroulante le TYPE AVION opere (77W / 778 / A320), ou laisser vide s'il n'y a pas de vol. Renseigner les deux lignes pour un jour = 2 rotations ce jour-la, avec le meme type ou deux types differents (ex. CDGRUN le lundi : 77W + 778). Toute modification recalcule immediatement la grille et le recapitulatif, pour les 12 mois. Valeurs livrees = exemples a ajuster (NOSRUN = 3/7 en A320 sur J1/J4/J6, conforme a l'exemple fourni).</t>
+    <t xml:space="preserve">Cellules en BLEU = saisie utilisateur. Chaque route occupe 3 lignes : les VOLS 1, 2 et 3 de la journee. Pour chaque jour J1-J7, choisir dans la liste deroulante le TYPE AVION opere (77W / 778 / A320), ou laisser vide s'il n'y a pas de vol. Renseigner plusieurs lignes pour un jour = 2 voire 3 rotations ce jour-la, avec le meme type ou des types differents (ex. CDGRUN le lundi : 77W + 778 + A320). Toute modification recalcule la grille et le recapitulatif, pour les 12 mois. Valeurs livrees = exemples a ajuster (NOSRUN = 3/7 en A320 sur J1/J4/J6, conforme a l'exemple fourni).</t>
   </si>
   <si>
     <t xml:space="preserve">Route / vol du jour</t>
@@ -286,49 +289,52 @@
     <t xml:space="preserve">mai 2027</t>
   </si>
   <si>
+    <t xml:space="preserve">      + vol 3 du jour</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A320</t>
+  </si>
+  <si>
+    <t xml:space="preserve">juin 2027</t>
+  </si>
+  <si>
     <t xml:space="preserve">CDGDZA</t>
   </si>
   <si>
-    <t xml:space="preserve">juin 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">A320</t>
-  </si>
-  <si>
     <t xml:space="preserve">juillet 2027</t>
   </si>
   <si>
+    <t xml:space="preserve">aout 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">septembre 2027</t>
+  </si>
+  <si>
     <t xml:space="preserve">BKKRUN</t>
   </si>
   <si>
-    <t xml:space="preserve">aout 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">septembre 2027</t>
+    <t xml:space="preserve">octobre 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">novembre 2027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">decembre 2027</t>
   </si>
   <si>
     <t xml:space="preserve">DZARUN</t>
   </si>
   <si>
-    <t xml:space="preserve">octobre 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">novembre 2027</t>
+    <t xml:space="preserve">janvier 2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fevrier 2028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mars 2028</t>
   </si>
   <si>
     <t xml:space="preserve">MRURUN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">decembre 2027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">janvier 2028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">fevrier 2028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mars 2028</t>
   </si>
   <si>
     <t xml:space="preserve">RUNTNR</t>
@@ -757,7 +763,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -855,6 +861,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1449,12 +1459,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="B1:U114"/>
+  <dimension ref="B1:U126"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="2"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="3" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="11" style="0" width="18"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="12"/>
@@ -1590,31 +1600,31 @@
         <v>22</v>
       </c>
       <c r="C8" s="13" t="str">
-        <f aca="false">IF(C9="","",TRIM(O$12&amp;IF(AND(O$12&lt;&gt;"",O$13&lt;&gt;""),"/","")&amp;O$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C9)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,C9)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C9)=1,IFERROR(INDEX($D$75:$D$114,MATCH(C9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C9)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(C9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C9)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(C9="","",TRIM(O$12&amp;IF(O$13="","",IF(O$12="","","/")&amp;O$13)&amp;IF(O$14="","",IF(AND(O$12="",O$13=""),"","/")&amp;O$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C9)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,C9)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C9)=1,IFERROR(INDEX($D$87:$D$126,MATCH(C9&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C9)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(C9&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C9)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="D8" s="13" t="str">
-        <f aca="false">IF(D9="","",TRIM(P$12&amp;IF(AND(P$12&lt;&gt;"",P$13&lt;&gt;""),"/","")&amp;P$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D9)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,D9)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D9)=1,IFERROR(INDEX($D$75:$D$114,MATCH(D9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D9)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(D9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D9)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(D9="","",TRIM(P$12&amp;IF(P$13="","",IF(P$12="","","/")&amp;P$13)&amp;IF(P$14="","",IF(AND(P$12="",P$13=""),"","/")&amp;P$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D9)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,D9)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D9)=1,IFERROR(INDEX($D$87:$D$126,MATCH(D9&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D9)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(D9&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D9)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="E8" s="13" t="str">
-        <f aca="false">IF(E9="","",TRIM(Q$12&amp;IF(AND(Q$12&lt;&gt;"",Q$13&lt;&gt;""),"/","")&amp;Q$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E9)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,E9)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E9)=1,IFERROR(INDEX($D$75:$D$114,MATCH(E9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E9)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(E9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E9)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(E9="","",TRIM(Q$12&amp;IF(Q$13="","",IF(Q$12="","","/")&amp;Q$13)&amp;IF(Q$14="","",IF(AND(Q$12="",Q$13=""),"","/")&amp;Q$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E9)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,E9)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E9)=1,IFERROR(INDEX($D$87:$D$126,MATCH(E9&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E9)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(E9&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E9)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="F8" s="13" t="str">
-        <f aca="false">IF(F9="","",TRIM(R$12&amp;IF(AND(R$12&lt;&gt;"",R$13&lt;&gt;""),"/","")&amp;R$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F9)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,F9)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F9)=1,IFERROR(INDEX($D$75:$D$114,MATCH(F9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F9)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(F9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F9)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(F9="","",TRIM(R$12&amp;IF(R$13="","",IF(R$12="","","/")&amp;R$13)&amp;IF(R$14="","",IF(AND(R$12="",R$13=""),"","/")&amp;R$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F9)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,F9)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F9)=1,IFERROR(INDEX($D$87:$D$126,MATCH(F9&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F9)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(F9&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F9)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="G8" s="13" t="str">
-        <f aca="false">IF(G9="","",TRIM(S$12&amp;IF(AND(S$12&lt;&gt;"",S$13&lt;&gt;""),"/","")&amp;S$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G9)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,G9)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G9)=1,IFERROR(INDEX($D$75:$D$114,MATCH(G9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G9)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(G9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G9)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(G9="","",TRIM(S$12&amp;IF(S$13="","",IF(S$12="","","/")&amp;S$13)&amp;IF(S$14="","",IF(AND(S$12="",S$13=""),"","/")&amp;S$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G9)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,G9)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G9)=1,IFERROR(INDEX($D$87:$D$126,MATCH(G9&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G9)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(G9&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G9)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="H8" s="13" t="str">
-        <f aca="false">IF(H9="","",TRIM(T$12&amp;IF(AND(T$12&lt;&gt;"",T$13&lt;&gt;""),"/","")&amp;T$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H9)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,H9)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H9)=1,IFERROR(INDEX($D$75:$D$114,MATCH(H9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H9)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(H9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H9)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(H9="","",TRIM(T$12&amp;IF(T$13="","",IF(T$12="","","/")&amp;T$13)&amp;IF(T$14="","",IF(AND(T$12="",T$13=""),"","/")&amp;T$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H9)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,H9)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H9)=1,IFERROR(INDEX($D$87:$D$126,MATCH(H9&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H9)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(H9&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H9)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="I8" s="13" t="str">
-        <f aca="false">IF(I9="","",TRIM(U$12&amp;IF(AND(U$12&lt;&gt;"",U$13&lt;&gt;""),"/","")&amp;U$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I9)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,I9)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I9)=1,IFERROR(INDEX($D$75:$D$114,MATCH(I9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I9)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(I9&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I9)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(I9="","",TRIM(U$12&amp;IF(U$13="","",IF(U$12="","","/")&amp;U$13)&amp;IF(U$14="","",IF(AND(U$12="",U$13=""),"","/")&amp;U$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I9)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,I9)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I9)=1,IFERROR(INDEX($D$87:$D$126,MATCH(I9&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I9)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(I9&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I9)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="N8" s="7" t="s">
@@ -1671,31 +1681,31 @@
         <v>25</v>
       </c>
       <c r="C10" s="13" t="str">
-        <f aca="false">IF(C11="","",TRIM(O$12&amp;IF(AND(O$12&lt;&gt;"",O$13&lt;&gt;""),"/","")&amp;O$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C11)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,C11)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C11)=1,IFERROR(INDEX($D$75:$D$114,MATCH(C11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C11)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(C11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C11)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(C11="","",TRIM(O$12&amp;IF(O$13="","",IF(O$12="","","/")&amp;O$13)&amp;IF(O$14="","",IF(AND(O$12="",O$13=""),"","/")&amp;O$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C11)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,C11)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C11)=1,IFERROR(INDEX($D$87:$D$126,MATCH(C11&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C11)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(C11&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C11)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="D10" s="13" t="str">
-        <f aca="false">IF(D11="","",TRIM(P$12&amp;IF(AND(P$12&lt;&gt;"",P$13&lt;&gt;""),"/","")&amp;P$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D11)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,D11)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D11)=1,IFERROR(INDEX($D$75:$D$114,MATCH(D11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D11)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(D11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D11)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(D11="","",TRIM(P$12&amp;IF(P$13="","",IF(P$12="","","/")&amp;P$13)&amp;IF(P$14="","",IF(AND(P$12="",P$13=""),"","/")&amp;P$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D11)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,D11)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D11)=1,IFERROR(INDEX($D$87:$D$126,MATCH(D11&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D11)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(D11&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D11)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="E10" s="13" t="str">
-        <f aca="false">IF(E11="","",TRIM(Q$12&amp;IF(AND(Q$12&lt;&gt;"",Q$13&lt;&gt;""),"/","")&amp;Q$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E11)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,E11)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E11)=1,IFERROR(INDEX($D$75:$D$114,MATCH(E11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E11)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(E11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E11)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(E11="","",TRIM(Q$12&amp;IF(Q$13="","",IF(Q$12="","","/")&amp;Q$13)&amp;IF(Q$14="","",IF(AND(Q$12="",Q$13=""),"","/")&amp;Q$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E11)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,E11)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E11)=1,IFERROR(INDEX($D$87:$D$126,MATCH(E11&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E11)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(E11&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E11)&amp;" vols")&amp;")")))</f>
         <v>(+A320)</v>
       </c>
       <c r="F10" s="13" t="str">
-        <f aca="false">IF(F11="","",TRIM(R$12&amp;IF(AND(R$12&lt;&gt;"",R$13&lt;&gt;""),"/","")&amp;R$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F11)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,F11)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F11)=1,IFERROR(INDEX($D$75:$D$114,MATCH(F11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F11)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(F11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F11)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(F11="","",TRIM(R$12&amp;IF(R$13="","",IF(R$12="","","/")&amp;R$13)&amp;IF(R$14="","",IF(AND(R$12="",R$13=""),"","/")&amp;R$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F11)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,F11)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F11)=1,IFERROR(INDEX($D$87:$D$126,MATCH(F11&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F11)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(F11&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F11)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="G10" s="13" t="str">
-        <f aca="false">IF(G11="","",TRIM(S$12&amp;IF(AND(S$12&lt;&gt;"",S$13&lt;&gt;""),"/","")&amp;S$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G11)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,G11)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G11)=1,IFERROR(INDEX($D$75:$D$114,MATCH(G11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G11)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(G11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G11)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(G11="","",TRIM(S$12&amp;IF(S$13="","",IF(S$12="","","/")&amp;S$13)&amp;IF(S$14="","",IF(AND(S$12="",S$13=""),"","/")&amp;S$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G11)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,G11)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G11)=1,IFERROR(INDEX($D$87:$D$126,MATCH(G11&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G11)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(G11&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G11)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="H10" s="13" t="str">
-        <f aca="false">IF(H11="","",TRIM(T$12&amp;IF(AND(T$12&lt;&gt;"",T$13&lt;&gt;""),"/","")&amp;T$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H11)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,H11)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H11)=1,IFERROR(INDEX($D$75:$D$114,MATCH(H11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H11)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(H11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H11)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(H11="","",TRIM(T$12&amp;IF(T$13="","",IF(T$12="","","/")&amp;T$13)&amp;IF(T$14="","",IF(AND(T$12="",T$13=""),"","/")&amp;T$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H11)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,H11)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H11)=1,IFERROR(INDEX($D$87:$D$126,MATCH(H11&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H11)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(H11&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H11)&amp;" vols")&amp;")")))</f>
         <v>A320 (+A320)</v>
       </c>
       <c r="I10" s="13" t="str">
-        <f aca="false">IF(I11="","",TRIM(U$12&amp;IF(AND(U$12&lt;&gt;"",U$13&lt;&gt;""),"/","")&amp;U$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I11)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,I11)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I11)=1,IFERROR(INDEX($D$75:$D$114,MATCH(I11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I11)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(I11&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I11)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(I11="","",TRIM(U$12&amp;IF(U$13="","",IF(U$12="","","/")&amp;U$13)&amp;IF(U$14="","",IF(AND(U$12="",U$13=""),"","/")&amp;U$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I11)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,I11)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I11)=1,IFERROR(INDEX($D$87:$D$126,MATCH(I11&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I11)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(I11&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I11)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="N10" s="17" t="s">
@@ -1772,62 +1782,62 @@
         <v>35</v>
       </c>
       <c r="C12" s="13" t="str">
-        <f aca="false">IF(C13="","",TRIM(O$12&amp;IF(AND(O$12&lt;&gt;"",O$13&lt;&gt;""),"/","")&amp;O$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C13)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,C13)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C13)=1,IFERROR(INDEX($D$75:$D$114,MATCH(C13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C13)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(C13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C13)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(C13="","",TRIM(O$12&amp;IF(O$13="","",IF(O$12="","","/")&amp;O$13)&amp;IF(O$14="","",IF(AND(O$12="",O$13=""),"","/")&amp;O$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C13)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,C13)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C13)=1,IFERROR(INDEX($D$87:$D$126,MATCH(C13&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C13)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(C13&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C13)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="D12" s="13" t="str">
-        <f aca="false">IF(D13="","",TRIM(P$12&amp;IF(AND(P$12&lt;&gt;"",P$13&lt;&gt;""),"/","")&amp;P$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D13)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,D13)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D13)=1,IFERROR(INDEX($D$75:$D$114,MATCH(D13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D13)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(D13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D13)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(D13="","",TRIM(P$12&amp;IF(P$13="","",IF(P$12="","","/")&amp;P$13)&amp;IF(P$14="","",IF(AND(P$12="",P$13=""),"","/")&amp;P$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D13)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,D13)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D13)=1,IFERROR(INDEX($D$87:$D$126,MATCH(D13&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D13)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(D13&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D13)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="E12" s="13" t="str">
-        <f aca="false">IF(E13="","",TRIM(Q$12&amp;IF(AND(Q$12&lt;&gt;"",Q$13&lt;&gt;""),"/","")&amp;Q$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E13)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,E13)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E13)=1,IFERROR(INDEX($D$75:$D$114,MATCH(E13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E13)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(E13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E13)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(E13="","",TRIM(Q$12&amp;IF(Q$13="","",IF(Q$12="","","/")&amp;Q$13)&amp;IF(Q$14="","",IF(AND(Q$12="",Q$13=""),"","/")&amp;Q$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E13)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,E13)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E13)=1,IFERROR(INDEX($D$87:$D$126,MATCH(E13&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E13)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(E13&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E13)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="F12" s="13" t="str">
-        <f aca="false">IF(F13="","",TRIM(R$12&amp;IF(AND(R$12&lt;&gt;"",R$13&lt;&gt;""),"/","")&amp;R$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F13)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,F13)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F13)=1,IFERROR(INDEX($D$75:$D$114,MATCH(F13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F13)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(F13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F13)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(F13="","",TRIM(R$12&amp;IF(R$13="","",IF(R$12="","","/")&amp;R$13)&amp;IF(R$14="","",IF(AND(R$12="",R$13=""),"","/")&amp;R$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F13)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,F13)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F13)=1,IFERROR(INDEX($D$87:$D$126,MATCH(F13&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F13)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(F13&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F13)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="G12" s="13" t="str">
-        <f aca="false">IF(G13="","",TRIM(S$12&amp;IF(AND(S$12&lt;&gt;"",S$13&lt;&gt;""),"/","")&amp;S$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G13)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,G13)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G13)=1,IFERROR(INDEX($D$75:$D$114,MATCH(G13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G13)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(G13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G13)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(G13="","",TRIM(S$12&amp;IF(S$13="","",IF(S$12="","","/")&amp;S$13)&amp;IF(S$14="","",IF(AND(S$12="",S$13=""),"","/")&amp;S$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G13)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,G13)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G13)=1,IFERROR(INDEX($D$87:$D$126,MATCH(G13&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G13)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(G13&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G13)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="H12" s="13" t="str">
-        <f aca="false">IF(H13="","",TRIM(T$12&amp;IF(AND(T$12&lt;&gt;"",T$13&lt;&gt;""),"/","")&amp;T$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H13)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,H13)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H13)=1,IFERROR(INDEX($D$75:$D$114,MATCH(H13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H13)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(H13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H13)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(H13="","",TRIM(T$12&amp;IF(T$13="","",IF(T$12="","","/")&amp;T$13)&amp;IF(T$14="","",IF(AND(T$12="",T$13=""),"","/")&amp;T$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H13)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,H13)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H13)=1,IFERROR(INDEX($D$87:$D$126,MATCH(H13&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H13)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(H13&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H13)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="I12" s="13" t="str">
-        <f aca="false">IF(I13="","",TRIM(U$12&amp;IF(AND(U$12&lt;&gt;"",U$13&lt;&gt;""),"/","")&amp;U$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I13)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,I13)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I13)=1,IFERROR(INDEX($D$75:$D$114,MATCH(I13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I13)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(I13&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I13)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(I13="","",TRIM(U$12&amp;IF(U$13="","",IF(U$12="","","/")&amp;U$13)&amp;IF(U$14="","",IF(AND(U$12="",U$13=""),"","/")&amp;U$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I13)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,I13)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I13)=1,IFERROR(INDEX($D$87:$D$126,MATCH(I13&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I13)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(I13&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I13)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="N12" s="19" t="s">
         <v>36</v>
       </c>
       <c r="O12" s="20" t="str">
-        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+0,1)&amp;"","")</f>
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+0,1)&amp;"","")</f>
         <v>A320</v>
       </c>
       <c r="P12" s="20" t="str">
-        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+0,2)&amp;"","")</f>
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+0,2)&amp;"","")</f>
         <v/>
       </c>
       <c r="Q12" s="20" t="str">
-        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+0,3)&amp;"","")</f>
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+0,3)&amp;"","")</f>
         <v/>
       </c>
       <c r="R12" s="20" t="str">
-        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+0,4)&amp;"","")</f>
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+0,4)&amp;"","")</f>
         <v>A320</v>
       </c>
       <c r="S12" s="20" t="str">
-        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+0,5)&amp;"","")</f>
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+0,5)&amp;"","")</f>
         <v/>
       </c>
       <c r="T12" s="20" t="str">
-        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+0,6)&amp;"","")</f>
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+0,6)&amp;"","")</f>
         <v>A320</v>
       </c>
       <c r="U12" s="20" t="str">
-        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+0,7)&amp;"","")</f>
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+0,7)&amp;"","")</f>
         <v/>
       </c>
     </row>
@@ -1868,31 +1878,31 @@
         <v>37</v>
       </c>
       <c r="O13" s="20" t="str">
-        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+1,1)&amp;"","")</f>
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+1,1)&amp;"","")</f>
         <v/>
       </c>
       <c r="P13" s="20" t="str">
-        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+1,2)&amp;"","")</f>
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+1,2)&amp;"","")</f>
         <v/>
       </c>
       <c r="Q13" s="20" t="str">
-        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+1,3)&amp;"","")</f>
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+1,3)&amp;"","")</f>
         <v/>
       </c>
       <c r="R13" s="20" t="str">
-        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+1,4)&amp;"","")</f>
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+1,4)&amp;"","")</f>
         <v/>
       </c>
       <c r="S13" s="20" t="str">
-        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+1,5)&amp;"","")</f>
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+1,5)&amp;"","")</f>
         <v/>
       </c>
       <c r="T13" s="20" t="str">
-        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+1,6)&amp;"","")</f>
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+1,6)&amp;"","")</f>
         <v/>
       </c>
       <c r="U13" s="20" t="str">
-        <f aca="false">IFERROR(INDEX($C$45:$I$68,MATCH($C$5,$B$45:$B$68,0)+1,7)&amp;"","")</f>
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+1,7)&amp;"","")</f>
         <v/>
       </c>
     </row>
@@ -1901,31 +1911,62 @@
         <v>38</v>
       </c>
       <c r="C14" s="13" t="str">
-        <f aca="false">IF(C15="","",TRIM(O$12&amp;IF(AND(O$12&lt;&gt;"",O$13&lt;&gt;""),"/","")&amp;O$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C15)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,C15)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C15)=1,IFERROR(INDEX($D$75:$D$114,MATCH(C15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C15)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(C15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C15)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(C15="","",TRIM(O$12&amp;IF(O$13="","",IF(O$12="","","/")&amp;O$13)&amp;IF(O$14="","",IF(AND(O$12="",O$13=""),"","/")&amp;O$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C15)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,C15)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C15)=1,IFERROR(INDEX($D$87:$D$126,MATCH(C15&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C15)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(C15&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C15)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="D14" s="13" t="str">
-        <f aca="false">IF(D15="","",TRIM(P$12&amp;IF(AND(P$12&lt;&gt;"",P$13&lt;&gt;""),"/","")&amp;P$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D15)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,D15)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D15)=1,IFERROR(INDEX($D$75:$D$114,MATCH(D15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D15)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(D15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D15)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(D15="","",TRIM(P$12&amp;IF(P$13="","",IF(P$12="","","/")&amp;P$13)&amp;IF(P$14="","",IF(AND(P$12="",P$13=""),"","/")&amp;P$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D15)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,D15)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D15)=1,IFERROR(INDEX($D$87:$D$126,MATCH(D15&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D15)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(D15&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D15)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="E14" s="13" t="str">
-        <f aca="false">IF(E15="","",TRIM(Q$12&amp;IF(AND(Q$12&lt;&gt;"",Q$13&lt;&gt;""),"/","")&amp;Q$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E15)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,E15)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E15)=1,IFERROR(INDEX($D$75:$D$114,MATCH(E15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E15)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(E15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E15)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(E15="","",TRIM(Q$12&amp;IF(Q$13="","",IF(Q$12="","","/")&amp;Q$13)&amp;IF(Q$14="","",IF(AND(Q$12="",Q$13=""),"","/")&amp;Q$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E15)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,E15)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E15)=1,IFERROR(INDEX($D$87:$D$126,MATCH(E15&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E15)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(E15&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E15)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="F14" s="13" t="str">
-        <f aca="false">IF(F15="","",TRIM(R$12&amp;IF(AND(R$12&lt;&gt;"",R$13&lt;&gt;""),"/","")&amp;R$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F15)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,F15)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F15)=1,IFERROR(INDEX($D$75:$D$114,MATCH(F15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F15)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(F15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F15)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(F15="","",TRIM(R$12&amp;IF(R$13="","",IF(R$12="","","/")&amp;R$13)&amp;IF(R$14="","",IF(AND(R$12="",R$13=""),"","/")&amp;R$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F15)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,F15)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F15)=1,IFERROR(INDEX($D$87:$D$126,MATCH(F15&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F15)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(F15&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F15)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="G14" s="13" t="str">
-        <f aca="false">IF(G15="","",TRIM(S$12&amp;IF(AND(S$12&lt;&gt;"",S$13&lt;&gt;""),"/","")&amp;S$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G15)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,G15)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G15)=1,IFERROR(INDEX($D$75:$D$114,MATCH(G15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G15)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(G15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G15)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(G15="","",TRIM(S$12&amp;IF(S$13="","",IF(S$12="","","/")&amp;S$13)&amp;IF(S$14="","",IF(AND(S$12="",S$13=""),"","/")&amp;S$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G15)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,G15)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G15)=1,IFERROR(INDEX($D$87:$D$126,MATCH(G15&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G15)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(G15&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G15)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="H14" s="13" t="str">
-        <f aca="false">IF(H15="","",TRIM(T$12&amp;IF(AND(T$12&lt;&gt;"",T$13&lt;&gt;""),"/","")&amp;T$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H15)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,H15)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H15)=1,IFERROR(INDEX($D$75:$D$114,MATCH(H15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H15)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(H15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H15)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(H15="","",TRIM(T$12&amp;IF(T$13="","",IF(T$12="","","/")&amp;T$13)&amp;IF(T$14="","",IF(AND(T$12="",T$13=""),"","/")&amp;T$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H15)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,H15)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H15)=1,IFERROR(INDEX($D$87:$D$126,MATCH(H15&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H15)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(H15&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H15)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="I14" s="13" t="str">
-        <f aca="false">IF(I15="","",TRIM(U$12&amp;IF(AND(U$12&lt;&gt;"",U$13&lt;&gt;""),"/","")&amp;U$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I15)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,I15)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I15)=1,IFERROR(INDEX($D$75:$D$114,MATCH(I15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I15)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(I15&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I15)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(I15="","",TRIM(U$12&amp;IF(U$13="","",IF(U$12="","","/")&amp;U$13)&amp;IF(U$14="","",IF(AND(U$12="",U$13=""),"","/")&amp;U$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I15)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,I15)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I15)=1,IFERROR(INDEX($D$87:$D$126,MATCH(I15&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I15)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(I15&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I15)&amp;" vols")&amp;")")))</f>
+        <v/>
+      </c>
+      <c r="N14" s="19" t="s">
+        <v>39</v>
+      </c>
+      <c r="O14" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+2,1)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="P14" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+2,2)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="Q14" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+2,3)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="R14" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+2,4)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="S14" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+2,5)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="T14" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+2,6)&amp;"","")</f>
+        <v/>
+      </c>
+      <c r="U14" s="20" t="str">
+        <f aca="false">IFERROR(INDEX($C$45:$I$80,MATCH($C$5,$B$45:$B$80,0)+2,7)&amp;"","")</f>
         <v/>
       </c>
     </row>
@@ -1965,34 +2006,34 @@
     </row>
     <row r="16" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B16" s="12" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C16" s="13" t="str">
-        <f aca="false">IF(C17="","",TRIM(O$12&amp;IF(AND(O$12&lt;&gt;"",O$13&lt;&gt;""),"/","")&amp;O$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C17)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,C17)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C17)=1,IFERROR(INDEX($D$75:$D$114,MATCH(C17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C17)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(C17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C17)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(C17="","",TRIM(O$12&amp;IF(O$13="","",IF(O$12="","","/")&amp;O$13)&amp;IF(O$14="","",IF(AND(O$12="",O$13=""),"","/")&amp;O$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C17)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,C17)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C17)=1,IFERROR(INDEX($D$87:$D$126,MATCH(C17&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C17)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(C17&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C17)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="D16" s="13" t="str">
-        <f aca="false">IF(D17="","",TRIM(P$12&amp;IF(AND(P$12&lt;&gt;"",P$13&lt;&gt;""),"/","")&amp;P$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D17)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,D17)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D17)=1,IFERROR(INDEX($D$75:$D$114,MATCH(D17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D17)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(D17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D17)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(D17="","",TRIM(P$12&amp;IF(P$13="","",IF(P$12="","","/")&amp;P$13)&amp;IF(P$14="","",IF(AND(P$12="",P$13=""),"","/")&amp;P$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D17)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,D17)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D17)=1,IFERROR(INDEX($D$87:$D$126,MATCH(D17&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D17)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(D17&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D17)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="E16" s="13" t="str">
-        <f aca="false">IF(E17="","",TRIM(Q$12&amp;IF(AND(Q$12&lt;&gt;"",Q$13&lt;&gt;""),"/","")&amp;Q$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E17)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,E17)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E17)=1,IFERROR(INDEX($D$75:$D$114,MATCH(E17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E17)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(E17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E17)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(E17="","",TRIM(Q$12&amp;IF(Q$13="","",IF(Q$12="","","/")&amp;Q$13)&amp;IF(Q$14="","",IF(AND(Q$12="",Q$13=""),"","/")&amp;Q$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E17)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,E17)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E17)=1,IFERROR(INDEX($D$87:$D$126,MATCH(E17&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E17)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(E17&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E17)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="F16" s="13" t="str">
-        <f aca="false">IF(F17="","",TRIM(R$12&amp;IF(AND(R$12&lt;&gt;"",R$13&lt;&gt;""),"/","")&amp;R$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F17)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,F17)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F17)=1,IFERROR(INDEX($D$75:$D$114,MATCH(F17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F17)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(F17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F17)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(F17="","",TRIM(R$12&amp;IF(R$13="","",IF(R$12="","","/")&amp;R$13)&amp;IF(R$14="","",IF(AND(R$12="",R$13=""),"","/")&amp;R$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F17)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,F17)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F17)=1,IFERROR(INDEX($D$87:$D$126,MATCH(F17&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F17)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(F17&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F17)&amp;" vols")&amp;")")))</f>
         <v>A320</v>
       </c>
       <c r="G16" s="13" t="str">
-        <f aca="false">IF(G17="","",TRIM(S$12&amp;IF(AND(S$12&lt;&gt;"",S$13&lt;&gt;""),"/","")&amp;S$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G17)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,G17)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G17)=1,IFERROR(INDEX($D$75:$D$114,MATCH(G17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G17)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(G17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G17)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(G17="","",TRIM(S$12&amp;IF(S$13="","",IF(S$12="","","/")&amp;S$13)&amp;IF(S$14="","",IF(AND(S$12="",S$13=""),"","/")&amp;S$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G17)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,G17)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G17)=1,IFERROR(INDEX($D$87:$D$126,MATCH(G17&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G17)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(G17&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G17)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="H16" s="13" t="str">
-        <f aca="false">IF(H17="","",TRIM(T$12&amp;IF(AND(T$12&lt;&gt;"",T$13&lt;&gt;""),"/","")&amp;T$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H17)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,H17)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H17)=1,IFERROR(INDEX($D$75:$D$114,MATCH(H17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H17)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(H17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H17)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(H17="","",TRIM(T$12&amp;IF(T$13="","",IF(T$12="","","/")&amp;T$13)&amp;IF(T$14="","",IF(AND(T$12="",T$13=""),"","/")&amp;T$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H17)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,H17)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H17)=1,IFERROR(INDEX($D$87:$D$126,MATCH(H17&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H17)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(H17&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H17)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="I16" s="13" t="str">
-        <f aca="false">IF(I17="","",TRIM(U$12&amp;IF(AND(U$12&lt;&gt;"",U$13&lt;&gt;""),"/","")&amp;U$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I17)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,I17)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I17)=1,IFERROR(INDEX($D$75:$D$114,MATCH(I17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I17)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(I17&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I17)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(I17="","",TRIM(U$12&amp;IF(U$13="","",IF(U$12="","","/")&amp;U$13)&amp;IF(U$14="","",IF(AND(U$12="",U$13=""),"","/")&amp;U$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I17)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,I17)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I17)=1,IFERROR(INDEX($D$87:$D$126,MATCH(I17&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I17)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(I17&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I17)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
     </row>
@@ -2032,34 +2073,34 @@
     </row>
     <row r="18" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B18" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C18" s="13" t="str">
-        <f aca="false">IF(C19="","",TRIM(O$12&amp;IF(AND(O$12&lt;&gt;"",O$13&lt;&gt;""),"/","")&amp;O$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C19)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,C19)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C19)=1,IFERROR(INDEX($D$75:$D$114,MATCH(C19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C19)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(C19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,C19)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(C19="","",TRIM(O$12&amp;IF(O$13="","",IF(O$12="","","/")&amp;O$13)&amp;IF(O$14="","",IF(AND(O$12="",O$13=""),"","/")&amp;O$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C19)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,C19)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C19)=1,IFERROR(INDEX($D$87:$D$126,MATCH(C19&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C19)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(C19&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,C19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="D18" s="13" t="str">
-        <f aca="false">IF(D19="","",TRIM(P$12&amp;IF(AND(P$12&lt;&gt;"",P$13&lt;&gt;""),"/","")&amp;P$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D19)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,D19)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D19)=1,IFERROR(INDEX($D$75:$D$114,MATCH(D19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D19)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(D19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,D19)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(D19="","",TRIM(P$12&amp;IF(P$13="","",IF(P$12="","","/")&amp;P$13)&amp;IF(P$14="","",IF(AND(P$12="",P$13=""),"","/")&amp;P$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D19)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,D19)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D19)=1,IFERROR(INDEX($D$87:$D$126,MATCH(D19&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D19)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(D19&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,D19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="E18" s="13" t="str">
-        <f aca="false">IF(E19="","",TRIM(Q$12&amp;IF(AND(Q$12&lt;&gt;"",Q$13&lt;&gt;""),"/","")&amp;Q$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E19)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,E19)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E19)=1,IFERROR(INDEX($D$75:$D$114,MATCH(E19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E19)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(E19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,E19)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(E19="","",TRIM(Q$12&amp;IF(Q$13="","",IF(Q$12="","","/")&amp;Q$13)&amp;IF(Q$14="","",IF(AND(Q$12="",Q$13=""),"","/")&amp;Q$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E19)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,E19)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E19)=1,IFERROR(INDEX($D$87:$D$126,MATCH(E19&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E19)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(E19&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,E19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="F18" s="13" t="str">
-        <f aca="false">IF(F19="","",TRIM(R$12&amp;IF(AND(R$12&lt;&gt;"",R$13&lt;&gt;""),"/","")&amp;R$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F19)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,F19)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F19)=1,IFERROR(INDEX($D$75:$D$114,MATCH(F19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F19)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(F19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,F19)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(F19="","",TRIM(R$12&amp;IF(R$13="","",IF(R$12="","","/")&amp;R$13)&amp;IF(R$14="","",IF(AND(R$12="",R$13=""),"","/")&amp;R$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F19)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,F19)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F19)=1,IFERROR(INDEX($D$87:$D$126,MATCH(F19&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F19)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(F19&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,F19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="G18" s="13" t="str">
-        <f aca="false">IF(G19="","",TRIM(S$12&amp;IF(AND(S$12&lt;&gt;"",S$13&lt;&gt;""),"/","")&amp;S$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G19)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,G19)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G19)=1,IFERROR(INDEX($D$75:$D$114,MATCH(G19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G19)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(G19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,G19)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(G19="","",TRIM(S$12&amp;IF(S$13="","",IF(S$12="","","/")&amp;S$13)&amp;IF(S$14="","",IF(AND(S$12="",S$13=""),"","/")&amp;S$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G19)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,G19)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G19)=1,IFERROR(INDEX($D$87:$D$126,MATCH(G19&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G19)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(G19&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,G19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="H18" s="13" t="str">
-        <f aca="false">IF(H19="","",TRIM(T$12&amp;IF(AND(T$12&lt;&gt;"",T$13&lt;&gt;""),"/","")&amp;T$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H19)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,H19)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H19)=1,IFERROR(INDEX($D$75:$D$114,MATCH(H19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H19)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(H19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,H19)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(H19="","",TRIM(T$12&amp;IF(T$13="","",IF(T$12="","","/")&amp;T$13)&amp;IF(T$14="","",IF(AND(T$12="",T$13=""),"","/")&amp;T$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H19)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,H19)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H19)=1,IFERROR(INDEX($D$87:$D$126,MATCH(H19&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H19)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(H19&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,H19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
       <c r="I18" s="13" t="str">
-        <f aca="false">IF(I19="","",TRIM(U$12&amp;IF(AND(U$12&lt;&gt;"",U$13&lt;&gt;""),"/","")&amp;U$13&amp;IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I19)=0,""," (+"&amp;IF(COUNTIFS($C$75:$C$114,$C$5,$B$75:$B$114,I19)=1,IF(SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I19)=1,IFERROR(INDEX($D$75:$D$114,MATCH(I19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),""),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I19)&amp;"x"&amp;IFERROR(INDEX($D$75:$D$114,MATCH(I19&amp;"|"&amp;$C$5,$J$75:$J$114,0)),"")),SUMIFS($E$75:$E$114,$C$75:$C$114,$C$5,$B$75:$B$114,I19)&amp;" vols")&amp;")")))</f>
+        <f aca="false">IF(I19="","",TRIM(U$12&amp;IF(U$13="","",IF(U$12="","","/")&amp;U$13)&amp;IF(U$14="","",IF(AND(U$12="",U$13=""),"","/")&amp;U$14)&amp;IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I19)=0,""," (+"&amp;IF(COUNTIFS($C$87:$C$126,$C$5,$B$87:$B$126,I19)=1,IF(SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I19)=1,IFERROR(INDEX($D$87:$D$126,MATCH(I19&amp;"|"&amp;$C$5,$J$87:$J$126,0)),""),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I19)&amp;"x"&amp;IFERROR(INDEX($D$87:$D$126,MATCH(I19&amp;"|"&amp;$C$5,$J$87:$J$126,0)),"")),SUMIFS($E$87:$E$126,$C$87:$C$126,$C$5,$B$87:$B$126,I19)&amp;" vols")&amp;")")))</f>
         <v/>
       </c>
     </row>
@@ -2099,7 +2140,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B20" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C20" s="22" t="n">
         <f aca="false">COUNT(C9,C11,C13,C15,C17,C19)</f>
@@ -2132,14 +2173,14 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B21" s="21" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C21" s="22" t="n">
         <f aca="false">IF(COUNT(C9:I9)&gt;0,1,0)+IF(COUNT(C11:I11)&gt;0,1,0)+IF(COUNT(C13:I13)&gt;0,1,0)+IF(COUNT(C15:I15)&gt;0,1,0)+IF(COUNT(C17:I17)&gt;0,1,0)+IF(COUNT(C19:I19)&gt;0,1,0)</f>
         <v>5</v>
       </c>
       <c r="D21" s="23" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E21" s="23"/>
       <c r="F21" s="23"/>
@@ -2149,7 +2190,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="9" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9"/>
@@ -2164,849 +2205,839 @@
     </row>
     <row r="24" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B24" s="24" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C24" s="24" t="s">
         <v>21</v>
       </c>
       <c r="D24" s="24" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E24" s="24" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F24" s="24" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="G24" s="24" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="H24" s="24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="I24" s="24" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J24" s="24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="K24" s="24" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="L24" s="24" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B25" s="13" t="str">
         <f aca="false">$B$45</f>
         <v>CDGRUN</v>
       </c>
-      <c r="C25" s="20" t="str">
+      <c r="C25" s="25" t="str">
         <f aca="false">$K$45</f>
-        <v>77W(7), 778(2)</v>
-      </c>
-      <c r="D25" s="20" t="str">
-        <f aca="false">IF(COUNTA($C$45:$I$46)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$45:$C$46)&gt;0,"J1 ","")&amp;IF(COUNTA($D$45:$D$46)&gt;0,"J2 ","")&amp;IF(COUNTA($E$45:$E$46)&gt;0,"J3 ","")&amp;IF(COUNTA($F$45:$F$46)&gt;0,"J4 ","")&amp;IF(COUNTA($G$45:$G$46)&gt;0,"J5 ","")&amp;IF(COUNTA($H$45:$H$46)&gt;0,"J6 ","")&amp;IF(COUNTA($I$45:$I$46)&gt;0,"J7 ",""))," ",", "))</f>
+        <v>77W(7), 778(2), A320(1)</v>
+      </c>
+      <c r="D25" s="25" t="str">
+        <f aca="false">IF(COUNTA($C$45:$I$47)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$45:$C$47)&gt;0,"J1 ","")&amp;IF(COUNTA($D$45:$D$47)&gt;0,"J2 ","")&amp;IF(COUNTA($E$45:$E$47)&gt;0,"J3 ","")&amp;IF(COUNTA($F$45:$F$47)&gt;0,"J4 ","")&amp;IF(COUNTA($G$45:$G$47)&gt;0,"J5 ","")&amp;IF(COUNTA($H$45:$H$47)&gt;0,"J6 ","")&amp;IF(COUNTA($I$45:$I$47)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J1, J2, J3, J4, J5, J6, J7</v>
       </c>
-      <c r="E25" s="25" t="n">
+      <c r="E25" s="26" t="n">
         <f aca="false">$J$45</f>
-        <v>9</v>
-      </c>
-      <c r="F25" s="25" t="n">
+        <v>10</v>
+      </c>
+      <c r="F25" s="26" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G25" s="26" t="n">
+      <c r="G25" s="27" t="n">
         <f aca="false">H25+I25</f>
-        <v>41</v>
-      </c>
-      <c r="H25" s="25" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$46:$I$46&lt;&gt;""))</f>
-        <v>39</v>
-      </c>
-      <c r="I25" s="25" t="n">
-        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B25,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+        <v>45</v>
+      </c>
+      <c r="H25" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$46:$I$46&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$47:$I$47&lt;&gt;""))</f>
+        <v>43</v>
+      </c>
+      <c r="I25" s="26" t="n">
+        <f aca="false">SUMIFS($E$87:$E$126,$C$87:$C$126,$B25,$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>2</v>
       </c>
-      <c r="J25" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45="77W"))+SUMPRODUCT($C$20:$I$20,--($C$46:$I$46="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B25,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="J25" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45="77W"))+SUMPRODUCT($C$20:$I$20,--($C$46:$I$46="77W"))+SUMPRODUCT($C$20:$I$20,--($C$47:$I$47="77W"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B25,$D$87:$D$126,"77W",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>30</v>
       </c>
-      <c r="K25" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45="778"))+SUMPRODUCT($C$20:$I$20,--($C$46:$I$46="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B25,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="K25" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45="778"))+SUMPRODUCT($C$20:$I$20,--($C$46:$I$46="778"))+SUMPRODUCT($C$20:$I$20,--($C$47:$I$47="778"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B25,$D$87:$D$126,"778",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>11</v>
       </c>
-      <c r="L25" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45="A320"))+SUMPRODUCT($C$20:$I$20,--($C$46:$I$46="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B25,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L25" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$45:$I$45="A320"))+SUMPRODUCT($C$20:$I$20,--($C$46:$I$46="A320"))+SUMPRODUCT($C$20:$I$20,--($C$47:$I$47="A320"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B25,$D$87:$D$126,"A320",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B26" s="13" t="str">
-        <f aca="false">$B$47</f>
+        <f aca="false">$B$48</f>
         <v>CDGDZA</v>
       </c>
-      <c r="C26" s="20" t="str">
-        <f aca="false">$K$47</f>
+      <c r="C26" s="25" t="str">
+        <f aca="false">$K$48</f>
         <v>77W(1), 778(2)</v>
       </c>
-      <c r="D26" s="20" t="str">
-        <f aca="false">IF(COUNTA($C$47:$I$48)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$47:$C$48)&gt;0,"J1 ","")&amp;IF(COUNTA($D$47:$D$48)&gt;0,"J2 ","")&amp;IF(COUNTA($E$47:$E$48)&gt;0,"J3 ","")&amp;IF(COUNTA($F$47:$F$48)&gt;0,"J4 ","")&amp;IF(COUNTA($G$47:$G$48)&gt;0,"J5 ","")&amp;IF(COUNTA($H$47:$H$48)&gt;0,"J6 ","")&amp;IF(COUNTA($I$47:$I$48)&gt;0,"J7 ",""))," ",", "))</f>
+      <c r="D26" s="25" t="str">
+        <f aca="false">IF(COUNTA($C$48:$I$50)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$48:$C$50)&gt;0,"J1 ","")&amp;IF(COUNTA($D$48:$D$50)&gt;0,"J2 ","")&amp;IF(COUNTA($E$48:$E$50)&gt;0,"J3 ","")&amp;IF(COUNTA($F$48:$F$50)&gt;0,"J4 ","")&amp;IF(COUNTA($G$48:$G$50)&gt;0,"J5 ","")&amp;IF(COUNTA($H$48:$H$50)&gt;0,"J6 ","")&amp;IF(COUNTA($I$48:$I$50)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J2, J5, J7</v>
       </c>
-      <c r="E26" s="25" t="n">
-        <f aca="false">$J$47</f>
+      <c r="E26" s="26" t="n">
+        <f aca="false">$J$48</f>
         <v>3</v>
       </c>
-      <c r="F26" s="25" t="n">
+      <c r="F26" s="26" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G26" s="26" t="n">
+      <c r="G26" s="27" t="n">
         <f aca="false">H26+I26</f>
         <v>13</v>
       </c>
-      <c r="H26" s="25" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$47:$I$47&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$48:$I$48&lt;&gt;""))</f>
+      <c r="H26" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$48:$I$48&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$49:$I$49&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$50:$I$50&lt;&gt;""))</f>
         <v>13</v>
       </c>
-      <c r="I26" s="25" t="n">
-        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B26,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="I26" s="26" t="n">
+        <f aca="false">SUMIFS($E$87:$E$126,$C$87:$C$126,$B26,$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J26" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$47:$I$47="77W"))+SUMPRODUCT($C$20:$I$20,--($C$48:$I$48="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B26,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="J26" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$48:$I$48="77W"))+SUMPRODUCT($C$20:$I$20,--($C$49:$I$49="77W"))+SUMPRODUCT($C$20:$I$20,--($C$50:$I$50="77W"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B26,$D$87:$D$126,"77W",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>4</v>
       </c>
-      <c r="K26" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$47:$I$47="778"))+SUMPRODUCT($C$20:$I$20,--($C$48:$I$48="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B26,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="K26" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$48:$I$48="778"))+SUMPRODUCT($C$20:$I$20,--($C$49:$I$49="778"))+SUMPRODUCT($C$20:$I$20,--($C$50:$I$50="778"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B26,$D$87:$D$126,"778",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>9</v>
       </c>
-      <c r="L26" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$47:$I$47="A320"))+SUMPRODUCT($C$20:$I$20,--($C$48:$I$48="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B26,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="L26" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$48:$I$48="A320"))+SUMPRODUCT($C$20:$I$20,--($C$49:$I$49="A320"))+SUMPRODUCT($C$20:$I$20,--($C$50:$I$50="A320"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B26,$D$87:$D$126,"A320",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="27" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B27" s="13" t="str">
-        <f aca="false">$B$49</f>
+        <f aca="false">$B$51</f>
         <v>BKKRUN</v>
       </c>
-      <c r="C27" s="20" t="str">
-        <f aca="false">$K$49</f>
+      <c r="C27" s="25" t="str">
+        <f aca="false">$K$51</f>
         <v>778(2)</v>
       </c>
-      <c r="D27" s="20" t="str">
-        <f aca="false">IF(COUNTA($C$49:$I$50)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$49:$C$50)&gt;0,"J1 ","")&amp;IF(COUNTA($D$49:$D$50)&gt;0,"J2 ","")&amp;IF(COUNTA($E$49:$E$50)&gt;0,"J3 ","")&amp;IF(COUNTA($F$49:$F$50)&gt;0,"J4 ","")&amp;IF(COUNTA($G$49:$G$50)&gt;0,"J5 ","")&amp;IF(COUNTA($H$49:$H$50)&gt;0,"J6 ","")&amp;IF(COUNTA($I$49:$I$50)&gt;0,"J7 ",""))," ",", "))</f>
+      <c r="D27" s="25" t="str">
+        <f aca="false">IF(COUNTA($C$51:$I$53)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$51:$C$53)&gt;0,"J1 ","")&amp;IF(COUNTA($D$51:$D$53)&gt;0,"J2 ","")&amp;IF(COUNTA($E$51:$E$53)&gt;0,"J3 ","")&amp;IF(COUNTA($F$51:$F$53)&gt;0,"J4 ","")&amp;IF(COUNTA($G$51:$G$53)&gt;0,"J5 ","")&amp;IF(COUNTA($H$51:$H$53)&gt;0,"J6 ","")&amp;IF(COUNTA($I$51:$I$53)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J3, J6</v>
       </c>
-      <c r="E27" s="25" t="n">
-        <f aca="false">$J$49</f>
+      <c r="E27" s="26" t="n">
+        <f aca="false">$J$51</f>
         <v>2</v>
       </c>
-      <c r="F27" s="25" t="n">
+      <c r="F27" s="26" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G27" s="26" t="n">
+      <c r="G27" s="27" t="n">
         <f aca="false">H27+I27</f>
         <v>8</v>
       </c>
-      <c r="H27" s="25" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$49:$I$49&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$50:$I$50&lt;&gt;""))</f>
+      <c r="H27" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$52:$I$52&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$53:$I$53&lt;&gt;""))</f>
         <v>8</v>
       </c>
-      <c r="I27" s="25" t="n">
-        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B27,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="I27" s="26" t="n">
+        <f aca="false">SUMIFS($E$87:$E$126,$C$87:$C$126,$B27,$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J27" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$49:$I$49="77W"))+SUMPRODUCT($C$20:$I$20,--($C$50:$I$50="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B27,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="J27" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51="77W"))+SUMPRODUCT($C$20:$I$20,--($C$52:$I$52="77W"))+SUMPRODUCT($C$20:$I$20,--($C$53:$I$53="77W"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B27,$D$87:$D$126,"77W",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K27" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$49:$I$49="778"))+SUMPRODUCT($C$20:$I$20,--($C$50:$I$50="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B27,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="K27" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51="778"))+SUMPRODUCT($C$20:$I$20,--($C$52:$I$52="778"))+SUMPRODUCT($C$20:$I$20,--($C$53:$I$53="778"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B27,$D$87:$D$126,"778",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>8</v>
       </c>
-      <c r="L27" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$49:$I$49="A320"))+SUMPRODUCT($C$20:$I$20,--($C$50:$I$50="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B27,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="L27" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51="A320"))+SUMPRODUCT($C$20:$I$20,--($C$52:$I$52="A320"))+SUMPRODUCT($C$20:$I$20,--($C$53:$I$53="A320"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B27,$D$87:$D$126,"A320",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="28" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B28" s="13" t="str">
-        <f aca="false">$B$51</f>
+        <f aca="false">$B$54</f>
         <v>DZARUN</v>
       </c>
-      <c r="C28" s="20" t="str">
-        <f aca="false">$K$51</f>
+      <c r="C28" s="25" t="str">
+        <f aca="false">$K$54</f>
         <v>778(1), A320(5)</v>
       </c>
-      <c r="D28" s="20" t="str">
-        <f aca="false">IF(COUNTA($C$51:$I$52)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$51:$C$52)&gt;0,"J1 ","")&amp;IF(COUNTA($D$51:$D$52)&gt;0,"J2 ","")&amp;IF(COUNTA($E$51:$E$52)&gt;0,"J3 ","")&amp;IF(COUNTA($F$51:$F$52)&gt;0,"J4 ","")&amp;IF(COUNTA($G$51:$G$52)&gt;0,"J5 ","")&amp;IF(COUNTA($H$51:$H$52)&gt;0,"J6 ","")&amp;IF(COUNTA($I$51:$I$52)&gt;0,"J7 ",""))," ",", "))</f>
+      <c r="D28" s="25" t="str">
+        <f aca="false">IF(COUNTA($C$54:$I$56)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$54:$C$56)&gt;0,"J1 ","")&amp;IF(COUNTA($D$54:$D$56)&gt;0,"J2 ","")&amp;IF(COUNTA($E$54:$E$56)&gt;0,"J3 ","")&amp;IF(COUNTA($F$54:$F$56)&gt;0,"J4 ","")&amp;IF(COUNTA($G$54:$G$56)&gt;0,"J5 ","")&amp;IF(COUNTA($H$54:$H$56)&gt;0,"J6 ","")&amp;IF(COUNTA($I$54:$I$56)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J1, J2, J3, J4, J5</v>
       </c>
-      <c r="E28" s="25" t="n">
-        <f aca="false">$J$51</f>
+      <c r="E28" s="26" t="n">
+        <f aca="false">$J$54</f>
         <v>6</v>
       </c>
-      <c r="F28" s="25" t="n">
+      <c r="F28" s="26" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G28" s="26" t="n">
+      <c r="G28" s="27" t="n">
         <f aca="false">H28+I28</f>
         <v>26</v>
       </c>
-      <c r="H28" s="25" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$52:$I$52&lt;&gt;""))</f>
+      <c r="H28" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$54:$I$54&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$55:$I$55&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$56:$I$56&lt;&gt;""))</f>
         <v>26</v>
       </c>
-      <c r="I28" s="25" t="n">
-        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B28,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="I28" s="26" t="n">
+        <f aca="false">SUMIFS($E$87:$E$126,$C$87:$C$126,$B28,$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J28" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51="77W"))+SUMPRODUCT($C$20:$I$20,--($C$52:$I$52="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B28,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="J28" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$54:$I$54="77W"))+SUMPRODUCT($C$20:$I$20,--($C$55:$I$55="77W"))+SUMPRODUCT($C$20:$I$20,--($C$56:$I$56="77W"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B28,$D$87:$D$126,"77W",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K28" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51="778"))+SUMPRODUCT($C$20:$I$20,--($C$52:$I$52="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B28,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="K28" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$54:$I$54="778"))+SUMPRODUCT($C$20:$I$20,--($C$55:$I$55="778"))+SUMPRODUCT($C$20:$I$20,--($C$56:$I$56="778"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B28,$D$87:$D$126,"778",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>4</v>
       </c>
-      <c r="L28" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$51:$I$51="A320"))+SUMPRODUCT($C$20:$I$20,--($C$52:$I$52="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B28,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="L28" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$54:$I$54="A320"))+SUMPRODUCT($C$20:$I$20,--($C$55:$I$55="A320"))+SUMPRODUCT($C$20:$I$20,--($C$56:$I$56="A320"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B28,$D$87:$D$126,"A320",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>22</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="29" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B29" s="13" t="str">
-        <f aca="false">$B$53</f>
+        <f aca="false">$B$57</f>
         <v>MRURUN</v>
       </c>
-      <c r="C29" s="20" t="str">
-        <f aca="false">$K$53</f>
+      <c r="C29" s="25" t="str">
+        <f aca="false">$K$57</f>
         <v>A320(4)</v>
       </c>
-      <c r="D29" s="20" t="str">
-        <f aca="false">IF(COUNTA($C$53:$I$54)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$53:$C$54)&gt;0,"J1 ","")&amp;IF(COUNTA($D$53:$D$54)&gt;0,"J2 ","")&amp;IF(COUNTA($E$53:$E$54)&gt;0,"J3 ","")&amp;IF(COUNTA($F$53:$F$54)&gt;0,"J4 ","")&amp;IF(COUNTA($G$53:$G$54)&gt;0,"J5 ","")&amp;IF(COUNTA($H$53:$H$54)&gt;0,"J6 ","")&amp;IF(COUNTA($I$53:$I$54)&gt;0,"J7 ",""))," ",", "))</f>
+      <c r="D29" s="25" t="str">
+        <f aca="false">IF(COUNTA($C$57:$I$59)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$57:$C$59)&gt;0,"J1 ","")&amp;IF(COUNTA($D$57:$D$59)&gt;0,"J2 ","")&amp;IF(COUNTA($E$57:$E$59)&gt;0,"J3 ","")&amp;IF(COUNTA($F$57:$F$59)&gt;0,"J4 ","")&amp;IF(COUNTA($G$57:$G$59)&gt;0,"J5 ","")&amp;IF(COUNTA($H$57:$H$59)&gt;0,"J6 ","")&amp;IF(COUNTA($I$57:$I$59)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J1, J3, J5, J7</v>
       </c>
-      <c r="E29" s="25" t="n">
-        <f aca="false">$J$53</f>
+      <c r="E29" s="26" t="n">
+        <f aca="false">$J$57</f>
         <v>4</v>
       </c>
-      <c r="F29" s="25" t="n">
+      <c r="F29" s="26" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G29" s="26" t="n">
+      <c r="G29" s="27" t="n">
         <f aca="false">H29+I29</f>
         <v>17</v>
       </c>
-      <c r="H29" s="25" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$53:$I$53&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$54:$I$54&lt;&gt;""))</f>
+      <c r="H29" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$57:$I$57&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$58:$I$58&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$59:$I$59&lt;&gt;""))</f>
         <v>17</v>
       </c>
-      <c r="I29" s="25" t="n">
-        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B29,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="I29" s="26" t="n">
+        <f aca="false">SUMIFS($E$87:$E$126,$C$87:$C$126,$B29,$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J29" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$53:$I$53="77W"))+SUMPRODUCT($C$20:$I$20,--($C$54:$I$54="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B29,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="J29" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$57:$I$57="77W"))+SUMPRODUCT($C$20:$I$20,--($C$58:$I$58="77W"))+SUMPRODUCT($C$20:$I$20,--($C$59:$I$59="77W"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B29,$D$87:$D$126,"77W",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K29" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$53:$I$53="778"))+SUMPRODUCT($C$20:$I$20,--($C$54:$I$54="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B29,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="K29" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$57:$I$57="778"))+SUMPRODUCT($C$20:$I$20,--($C$58:$I$58="778"))+SUMPRODUCT($C$20:$I$20,--($C$59:$I$59="778"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B29,$D$87:$D$126,"778",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="L29" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$53:$I$53="A320"))+SUMPRODUCT($C$20:$I$20,--($C$54:$I$54="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B29,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="L29" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$57:$I$57="A320"))+SUMPRODUCT($C$20:$I$20,--($C$58:$I$58="A320"))+SUMPRODUCT($C$20:$I$20,--($C$59:$I$59="A320"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B29,$D$87:$D$126,"A320",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>17</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="30" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B30" s="13" t="str">
-        <f aca="false">$B$55</f>
+        <f aca="false">$B$60</f>
         <v>NOSRUN</v>
       </c>
-      <c r="C30" s="20" t="str">
-        <f aca="false">$K$55</f>
+      <c r="C30" s="25" t="str">
+        <f aca="false">$K$60</f>
         <v>A320(3)</v>
       </c>
-      <c r="D30" s="20" t="str">
-        <f aca="false">IF(COUNTA($C$55:$I$56)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$55:$C$56)&gt;0,"J1 ","")&amp;IF(COUNTA($D$55:$D$56)&gt;0,"J2 ","")&amp;IF(COUNTA($E$55:$E$56)&gt;0,"J3 ","")&amp;IF(COUNTA($F$55:$F$56)&gt;0,"J4 ","")&amp;IF(COUNTA($G$55:$G$56)&gt;0,"J5 ","")&amp;IF(COUNTA($H$55:$H$56)&gt;0,"J6 ","")&amp;IF(COUNTA($I$55:$I$56)&gt;0,"J7 ",""))," ",", "))</f>
+      <c r="D30" s="25" t="str">
+        <f aca="false">IF(COUNTA($C$60:$I$62)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$60:$C$62)&gt;0,"J1 ","")&amp;IF(COUNTA($D$60:$D$62)&gt;0,"J2 ","")&amp;IF(COUNTA($E$60:$E$62)&gt;0,"J3 ","")&amp;IF(COUNTA($F$60:$F$62)&gt;0,"J4 ","")&amp;IF(COUNTA($G$60:$G$62)&gt;0,"J5 ","")&amp;IF(COUNTA($H$60:$H$62)&gt;0,"J6 ","")&amp;IF(COUNTA($I$60:$I$62)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J1, J4, J6</v>
       </c>
-      <c r="E30" s="25" t="n">
-        <f aca="false">$J$55</f>
+      <c r="E30" s="26" t="n">
+        <f aca="false">$J$60</f>
         <v>3</v>
       </c>
-      <c r="F30" s="25" t="n">
+      <c r="F30" s="26" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G30" s="26" t="n">
+      <c r="G30" s="27" t="n">
         <f aca="false">H30+I30</f>
         <v>15</v>
       </c>
-      <c r="H30" s="25" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$55:$I$55&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$56:$I$56&lt;&gt;""))</f>
+      <c r="H30" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$60:$I$60&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$61:$I$61&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$62:$I$62&lt;&gt;""))</f>
         <v>13</v>
       </c>
-      <c r="I30" s="25" t="n">
-        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B30,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="I30" s="26" t="n">
+        <f aca="false">SUMIFS($E$87:$E$126,$C$87:$C$126,$B30,$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>2</v>
       </c>
-      <c r="J30" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$55:$I$55="77W"))+SUMPRODUCT($C$20:$I$20,--($C$56:$I$56="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B30,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="J30" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$60:$I$60="77W"))+SUMPRODUCT($C$20:$I$20,--($C$61:$I$61="77W"))+SUMPRODUCT($C$20:$I$20,--($C$62:$I$62="77W"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B30,$D$87:$D$126,"77W",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K30" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$55:$I$55="778"))+SUMPRODUCT($C$20:$I$20,--($C$56:$I$56="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B30,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="K30" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$60:$I$60="778"))+SUMPRODUCT($C$20:$I$20,--($C$61:$I$61="778"))+SUMPRODUCT($C$20:$I$20,--($C$62:$I$62="778"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B30,$D$87:$D$126,"778",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="L30" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$55:$I$55="A320"))+SUMPRODUCT($C$20:$I$20,--($C$56:$I$56="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B30,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="L30" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$60:$I$60="A320"))+SUMPRODUCT($C$20:$I$20,--($C$61:$I$61="A320"))+SUMPRODUCT($C$20:$I$20,--($C$62:$I$62="A320"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B30,$D$87:$D$126,"A320",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>15</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="31" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B31" s="13" t="str">
-        <f aca="false">$B$57</f>
+        <f aca="false">$B$63</f>
         <v>RUNTNR</v>
       </c>
-      <c r="C31" s="20" t="str">
-        <f aca="false">$K$57</f>
+      <c r="C31" s="25" t="str">
+        <f aca="false">$K$63</f>
         <v>A320(3)</v>
       </c>
-      <c r="D31" s="20" t="str">
-        <f aca="false">IF(COUNTA($C$57:$I$58)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$57:$C$58)&gt;0,"J1 ","")&amp;IF(COUNTA($D$57:$D$58)&gt;0,"J2 ","")&amp;IF(COUNTA($E$57:$E$58)&gt;0,"J3 ","")&amp;IF(COUNTA($F$57:$F$58)&gt;0,"J4 ","")&amp;IF(COUNTA($G$57:$G$58)&gt;0,"J5 ","")&amp;IF(COUNTA($H$57:$H$58)&gt;0,"J6 ","")&amp;IF(COUNTA($I$57:$I$58)&gt;0,"J7 ",""))," ",", "))</f>
+      <c r="D31" s="25" t="str">
+        <f aca="false">IF(COUNTA($C$63:$I$65)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$63:$C$65)&gt;0,"J1 ","")&amp;IF(COUNTA($D$63:$D$65)&gt;0,"J2 ","")&amp;IF(COUNTA($E$63:$E$65)&gt;0,"J3 ","")&amp;IF(COUNTA($F$63:$F$65)&gt;0,"J4 ","")&amp;IF(COUNTA($G$63:$G$65)&gt;0,"J5 ","")&amp;IF(COUNTA($H$63:$H$65)&gt;0,"J6 ","")&amp;IF(COUNTA($I$63:$I$65)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J2, J4, J6</v>
       </c>
-      <c r="E31" s="25" t="n">
-        <f aca="false">$J$57</f>
+      <c r="E31" s="26" t="n">
+        <f aca="false">$J$63</f>
         <v>3</v>
       </c>
-      <c r="F31" s="25" t="n">
+      <c r="F31" s="26" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G31" s="26" t="n">
+      <c r="G31" s="27" t="n">
         <f aca="false">H31+I31</f>
         <v>13</v>
       </c>
-      <c r="H31" s="25" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$57:$I$57&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$58:$I$58&lt;&gt;""))</f>
+      <c r="H31" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$63:$I$63&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$64:$I$64&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$65:$I$65&lt;&gt;""))</f>
         <v>13</v>
       </c>
-      <c r="I31" s="25" t="n">
-        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B31,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="I31" s="26" t="n">
+        <f aca="false">SUMIFS($E$87:$E$126,$C$87:$C$126,$B31,$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J31" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$57:$I$57="77W"))+SUMPRODUCT($C$20:$I$20,--($C$58:$I$58="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B31,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="J31" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$63:$I$63="77W"))+SUMPRODUCT($C$20:$I$20,--($C$64:$I$64="77W"))+SUMPRODUCT($C$20:$I$20,--($C$65:$I$65="77W"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B31,$D$87:$D$126,"77W",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K31" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$57:$I$57="778"))+SUMPRODUCT($C$20:$I$20,--($C$58:$I$58="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B31,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="K31" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$63:$I$63="778"))+SUMPRODUCT($C$20:$I$20,--($C$64:$I$64="778"))+SUMPRODUCT($C$20:$I$20,--($C$65:$I$65="778"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B31,$D$87:$D$126,"778",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="L31" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$57:$I$57="A320"))+SUMPRODUCT($C$20:$I$20,--($C$58:$I$58="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B31,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="L31" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$63:$I$63="A320"))+SUMPRODUCT($C$20:$I$20,--($C$64:$I$64="A320"))+SUMPRODUCT($C$20:$I$20,--($C$65:$I$65="A320"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B31,$D$87:$D$126,"A320",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>13</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="32" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B32" s="13" t="str">
-        <f aca="false">$B$59</f>
+        <f aca="false">$B$66</f>
         <v>JNBRUN</v>
       </c>
-      <c r="C32" s="20" t="str">
-        <f aca="false">$K$59</f>
+      <c r="C32" s="25" t="str">
+        <f aca="false">$K$66</f>
         <v>778(2)</v>
       </c>
-      <c r="D32" s="20" t="str">
-        <f aca="false">IF(COUNTA($C$59:$I$60)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$59:$C$60)&gt;0,"J1 ","")&amp;IF(COUNTA($D$59:$D$60)&gt;0,"J2 ","")&amp;IF(COUNTA($E$59:$E$60)&gt;0,"J3 ","")&amp;IF(COUNTA($F$59:$F$60)&gt;0,"J4 ","")&amp;IF(COUNTA($G$59:$G$60)&gt;0,"J5 ","")&amp;IF(COUNTA($H$59:$H$60)&gt;0,"J6 ","")&amp;IF(COUNTA($I$59:$I$60)&gt;0,"J7 ",""))," ",", "))</f>
+      <c r="D32" s="25" t="str">
+        <f aca="false">IF(COUNTA($C$66:$I$68)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$66:$C$68)&gt;0,"J1 ","")&amp;IF(COUNTA($D$66:$D$68)&gt;0,"J2 ","")&amp;IF(COUNTA($E$66:$E$68)&gt;0,"J3 ","")&amp;IF(COUNTA($F$66:$F$68)&gt;0,"J4 ","")&amp;IF(COUNTA($G$66:$G$68)&gt;0,"J5 ","")&amp;IF(COUNTA($H$66:$H$68)&gt;0,"J6 ","")&amp;IF(COUNTA($I$66:$I$68)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J1, J5</v>
       </c>
-      <c r="E32" s="25" t="n">
-        <f aca="false">$J$59</f>
+      <c r="E32" s="26" t="n">
+        <f aca="false">$J$66</f>
         <v>2</v>
       </c>
-      <c r="F32" s="25" t="n">
+      <c r="F32" s="26" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G32" s="26" t="n">
+      <c r="G32" s="27" t="n">
         <f aca="false">H32+I32</f>
         <v>9</v>
       </c>
-      <c r="H32" s="25" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$59:$I$59&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$60:$I$60&lt;&gt;""))</f>
+      <c r="H32" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$66:$I$66&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$67:$I$67&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$68:$I$68&lt;&gt;""))</f>
         <v>9</v>
       </c>
-      <c r="I32" s="25" t="n">
-        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B32,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="I32" s="26" t="n">
+        <f aca="false">SUMIFS($E$87:$E$126,$C$87:$C$126,$B32,$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J32" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$59:$I$59="77W"))+SUMPRODUCT($C$20:$I$20,--($C$60:$I$60="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B32,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="J32" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$66:$I$66="77W"))+SUMPRODUCT($C$20:$I$20,--($C$67:$I$67="77W"))+SUMPRODUCT($C$20:$I$20,--($C$68:$I$68="77W"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B32,$D$87:$D$126,"77W",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K32" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$59:$I$59="778"))+SUMPRODUCT($C$20:$I$20,--($C$60:$I$60="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B32,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="K32" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$66:$I$66="778"))+SUMPRODUCT($C$20:$I$20,--($C$67:$I$67="778"))+SUMPRODUCT($C$20:$I$20,--($C$68:$I$68="778"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B32,$D$87:$D$126,"778",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>9</v>
       </c>
-      <c r="L32" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$59:$I$59="A320"))+SUMPRODUCT($C$20:$I$20,--($C$60:$I$60="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B32,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="L32" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$66:$I$66="A320"))+SUMPRODUCT($C$20:$I$20,--($C$67:$I$67="A320"))+SUMPRODUCT($C$20:$I$20,--($C$68:$I$68="A320"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B32,$D$87:$D$126,"A320",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="33" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B33" s="13" t="str">
-        <f aca="false">$B$61</f>
+        <f aca="false">$B$69</f>
         <v>CPTRUN</v>
       </c>
-      <c r="C33" s="20" t="str">
-        <f aca="false">$K$61</f>
+      <c r="C33" s="25" t="str">
+        <f aca="false">$K$69</f>
         <v>778(1)</v>
       </c>
-      <c r="D33" s="20" t="str">
-        <f aca="false">IF(COUNTA($C$61:$I$62)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$61:$C$62)&gt;0,"J1 ","")&amp;IF(COUNTA($D$61:$D$62)&gt;0,"J2 ","")&amp;IF(COUNTA($E$61:$E$62)&gt;0,"J3 ","")&amp;IF(COUNTA($F$61:$F$62)&gt;0,"J4 ","")&amp;IF(COUNTA($G$61:$G$62)&gt;0,"J5 ","")&amp;IF(COUNTA($H$61:$H$62)&gt;0,"J6 ","")&amp;IF(COUNTA($I$61:$I$62)&gt;0,"J7 ",""))," ",", "))</f>
+      <c r="D33" s="25" t="str">
+        <f aca="false">IF(COUNTA($C$69:$I$71)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$69:$C$71)&gt;0,"J1 ","")&amp;IF(COUNTA($D$69:$D$71)&gt;0,"J2 ","")&amp;IF(COUNTA($E$69:$E$71)&gt;0,"J3 ","")&amp;IF(COUNTA($F$69:$F$71)&gt;0,"J4 ","")&amp;IF(COUNTA($G$69:$G$71)&gt;0,"J5 ","")&amp;IF(COUNTA($H$69:$H$71)&gt;0,"J6 ","")&amp;IF(COUNTA($I$69:$I$71)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J4</v>
       </c>
-      <c r="E33" s="25" t="n">
-        <f aca="false">$J$61</f>
+      <c r="E33" s="26" t="n">
+        <f aca="false">$J$69</f>
         <v>1</v>
       </c>
-      <c r="F33" s="25" t="n">
+      <c r="F33" s="26" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G33" s="26" t="n">
+      <c r="G33" s="27" t="n">
         <f aca="false">H33+I33</f>
         <v>5</v>
       </c>
-      <c r="H33" s="25" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$61:$I$61&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$62:$I$62&lt;&gt;""))</f>
+      <c r="H33" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$69:$I$69&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$70:$I$70&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$71:$I$71&lt;&gt;""))</f>
         <v>5</v>
       </c>
-      <c r="I33" s="25" t="n">
-        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B33,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="I33" s="26" t="n">
+        <f aca="false">SUMIFS($E$87:$E$126,$C$87:$C$126,$B33,$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J33" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$61:$I$61="77W"))+SUMPRODUCT($C$20:$I$20,--($C$62:$I$62="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B33,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="J33" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$69:$I$69="77W"))+SUMPRODUCT($C$20:$I$20,--($C$70:$I$70="77W"))+SUMPRODUCT($C$20:$I$20,--($C$71:$I$71="77W"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B33,$D$87:$D$126,"77W",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K33" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$61:$I$61="778"))+SUMPRODUCT($C$20:$I$20,--($C$62:$I$62="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B33,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="K33" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$69:$I$69="778"))+SUMPRODUCT($C$20:$I$20,--($C$70:$I$70="778"))+SUMPRODUCT($C$20:$I$20,--($C$71:$I$71="778"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B33,$D$87:$D$126,"778",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>5</v>
       </c>
-      <c r="L33" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$61:$I$61="A320"))+SUMPRODUCT($C$20:$I$20,--($C$62:$I$62="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B33,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="L33" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$69:$I$69="A320"))+SUMPRODUCT($C$20:$I$20,--($C$70:$I$70="A320"))+SUMPRODUCT($C$20:$I$20,--($C$71:$I$71="A320"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B33,$D$87:$D$126,"A320",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="34" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B34" s="13" t="str">
-        <f aca="false">$B$63</f>
+        <f aca="false">$B$72</f>
         <v>DIERUN</v>
       </c>
-      <c r="C34" s="20" t="str">
-        <f aca="false">$K$63</f>
+      <c r="C34" s="25" t="str">
+        <f aca="false">$K$72</f>
         <v>A320(2)</v>
       </c>
-      <c r="D34" s="20" t="str">
-        <f aca="false">IF(COUNTA($C$63:$I$64)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$63:$C$64)&gt;0,"J1 ","")&amp;IF(COUNTA($D$63:$D$64)&gt;0,"J2 ","")&amp;IF(COUNTA($E$63:$E$64)&gt;0,"J3 ","")&amp;IF(COUNTA($F$63:$F$64)&gt;0,"J4 ","")&amp;IF(COUNTA($G$63:$G$64)&gt;0,"J5 ","")&amp;IF(COUNTA($H$63:$H$64)&gt;0,"J6 ","")&amp;IF(COUNTA($I$63:$I$64)&gt;0,"J7 ",""))," ",", "))</f>
+      <c r="D34" s="25" t="str">
+        <f aca="false">IF(COUNTA($C$72:$I$74)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$72:$C$74)&gt;0,"J1 ","")&amp;IF(COUNTA($D$72:$D$74)&gt;0,"J2 ","")&amp;IF(COUNTA($E$72:$E$74)&gt;0,"J3 ","")&amp;IF(COUNTA($F$72:$F$74)&gt;0,"J4 ","")&amp;IF(COUNTA($G$72:$G$74)&gt;0,"J5 ","")&amp;IF(COUNTA($H$72:$H$74)&gt;0,"J6 ","")&amp;IF(COUNTA($I$72:$I$74)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J2, J6</v>
       </c>
-      <c r="E34" s="25" t="n">
-        <f aca="false">$J$63</f>
+      <c r="E34" s="26" t="n">
+        <f aca="false">$J$72</f>
         <v>2</v>
       </c>
-      <c r="F34" s="25" t="n">
+      <c r="F34" s="26" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G34" s="26" t="n">
+      <c r="G34" s="27" t="n">
         <f aca="false">H34+I34</f>
         <v>8</v>
       </c>
-      <c r="H34" s="25" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$63:$I$63&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$64:$I$64&lt;&gt;""))</f>
+      <c r="H34" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$72:$I$72&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$73:$I$73&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$74:$I$74&lt;&gt;""))</f>
         <v>8</v>
       </c>
-      <c r="I34" s="25" t="n">
-        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B34,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="I34" s="26" t="n">
+        <f aca="false">SUMIFS($E$87:$E$126,$C$87:$C$126,$B34,$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J34" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$63:$I$63="77W"))+SUMPRODUCT($C$20:$I$20,--($C$64:$I$64="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B34,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="J34" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$72:$I$72="77W"))+SUMPRODUCT($C$20:$I$20,--($C$73:$I$73="77W"))+SUMPRODUCT($C$20:$I$20,--($C$74:$I$74="77W"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B34,$D$87:$D$126,"77W",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K34" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$63:$I$63="778"))+SUMPRODUCT($C$20:$I$20,--($C$64:$I$64="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B34,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="K34" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$72:$I$72="778"))+SUMPRODUCT($C$20:$I$20,--($C$73:$I$73="778"))+SUMPRODUCT($C$20:$I$20,--($C$74:$I$74="778"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B34,$D$87:$D$126,"778",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="L34" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$63:$I$63="A320"))+SUMPRODUCT($C$20:$I$20,--($C$64:$I$64="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B34,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="L34" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$72:$I$72="A320"))+SUMPRODUCT($C$20:$I$20,--($C$73:$I$73="A320"))+SUMPRODUCT($C$20:$I$20,--($C$74:$I$74="A320"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B34,$D$87:$D$126,"A320",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>8</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="35" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B35" s="13" t="str">
-        <f aca="false">$B$65</f>
+        <f aca="false">$B$75</f>
         <v>RRGRUN</v>
       </c>
-      <c r="C35" s="20" t="str">
-        <f aca="false">$K$65</f>
-        <v>A320(7)</v>
-      </c>
-      <c r="D35" s="20" t="str">
-        <f aca="false">IF(COUNTA($C$65:$I$66)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$65:$C$66)&gt;0,"J1 ","")&amp;IF(COUNTA($D$65:$D$66)&gt;0,"J2 ","")&amp;IF(COUNTA($E$65:$E$66)&gt;0,"J3 ","")&amp;IF(COUNTA($F$65:$F$66)&gt;0,"J4 ","")&amp;IF(COUNTA($G$65:$G$66)&gt;0,"J5 ","")&amp;IF(COUNTA($H$65:$H$66)&gt;0,"J6 ","")&amp;IF(COUNTA($I$65:$I$66)&gt;0,"J7 ",""))," ",", "))</f>
+      <c r="C35" s="25" t="str">
+        <f aca="false">$K$75</f>
+        <v>A320(8)</v>
+      </c>
+      <c r="D35" s="25" t="str">
+        <f aca="false">IF(COUNTA($C$75:$I$77)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$75:$C$77)&gt;0,"J1 ","")&amp;IF(COUNTA($D$75:$D$77)&gt;0,"J2 ","")&amp;IF(COUNTA($E$75:$E$77)&gt;0,"J3 ","")&amp;IF(COUNTA($F$75:$F$77)&gt;0,"J4 ","")&amp;IF(COUNTA($G$75:$G$77)&gt;0,"J5 ","")&amp;IF(COUNTA($H$75:$H$77)&gt;0,"J6 ","")&amp;IF(COUNTA($I$75:$I$77)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J1, J2, J3, J4, J5, J6</v>
       </c>
-      <c r="E35" s="25" t="n">
-        <f aca="false">$J$65</f>
-        <v>7</v>
-      </c>
-      <c r="F35" s="25" t="n">
+      <c r="E35" s="26" t="n">
+        <f aca="false">$J$75</f>
+        <v>8</v>
+      </c>
+      <c r="F35" s="26" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G35" s="26" t="n">
+      <c r="G35" s="27" t="n">
         <f aca="false">H35+I35</f>
-        <v>31</v>
-      </c>
-      <c r="H35" s="25" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$65:$I$65&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$66:$I$66&lt;&gt;""))</f>
-        <v>31</v>
-      </c>
-      <c r="I35" s="25" t="n">
-        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B35,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+        <v>36</v>
+      </c>
+      <c r="H35" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$75:$I$75&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$76:$I$76&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$77:$I$77&lt;&gt;""))</f>
+        <v>36</v>
+      </c>
+      <c r="I35" s="26" t="n">
+        <f aca="false">SUMIFS($E$87:$E$126,$C$87:$C$126,$B35,$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J35" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$65:$I$65="77W"))+SUMPRODUCT($C$20:$I$20,--($C$66:$I$66="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B35,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="J35" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$75:$I$75="77W"))+SUMPRODUCT($C$20:$I$20,--($C$76:$I$76="77W"))+SUMPRODUCT($C$20:$I$20,--($C$77:$I$77="77W"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B35,$D$87:$D$126,"77W",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K35" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$65:$I$65="778"))+SUMPRODUCT($C$20:$I$20,--($C$66:$I$66="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B35,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="K35" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$75:$I$75="778"))+SUMPRODUCT($C$20:$I$20,--($C$76:$I$76="778"))+SUMPRODUCT($C$20:$I$20,--($C$77:$I$77="778"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B35,$D$87:$D$126,"778",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="L35" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$65:$I$65="A320"))+SUMPRODUCT($C$20:$I$20,--($C$66:$I$66="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B35,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
-        <v>31</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="L35" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$75:$I$75="A320"))+SUMPRODUCT($C$20:$I$20,--($C$76:$I$76="A320"))+SUMPRODUCT($C$20:$I$20,--($C$77:$I$77="A320"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B35,$D$87:$D$126,"A320",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
+        <v>36</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B36" s="13" t="str">
-        <f aca="false">$B$67</f>
+        <f aca="false">$B$78</f>
         <v>TMMRUN</v>
       </c>
-      <c r="C36" s="20" t="str">
-        <f aca="false">$K$67</f>
+      <c r="C36" s="25" t="str">
+        <f aca="false">$K$78</f>
         <v>A320(2)</v>
       </c>
-      <c r="D36" s="20" t="str">
-        <f aca="false">IF(COUNTA($C$67:$I$68)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$67:$C$68)&gt;0,"J1 ","")&amp;IF(COUNTA($D$67:$D$68)&gt;0,"J2 ","")&amp;IF(COUNTA($E$67:$E$68)&gt;0,"J3 ","")&amp;IF(COUNTA($F$67:$F$68)&gt;0,"J4 ","")&amp;IF(COUNTA($G$67:$G$68)&gt;0,"J5 ","")&amp;IF(COUNTA($H$67:$H$68)&gt;0,"J6 ","")&amp;IF(COUNTA($I$67:$I$68)&gt;0,"J7 ",""))," ",", "))</f>
+      <c r="D36" s="25" t="str">
+        <f aca="false">IF(COUNTA($C$78:$I$80)=0,"aucune operation",SUBSTITUTE(TRIM(IF(COUNTA($C$78:$C$80)&gt;0,"J1 ","")&amp;IF(COUNTA($D$78:$D$80)&gt;0,"J2 ","")&amp;IF(COUNTA($E$78:$E$80)&gt;0,"J3 ","")&amp;IF(COUNTA($F$78:$F$80)&gt;0,"J4 ","")&amp;IF(COUNTA($G$78:$G$80)&gt;0,"J5 ","")&amp;IF(COUNTA($H$78:$H$80)&gt;0,"J6 ","")&amp;IF(COUNTA($I$78:$I$80)&gt;0,"J7 ",""))," ",", "))</f>
         <v>J3, J7</v>
       </c>
-      <c r="E36" s="25" t="n">
-        <f aca="false">$J$67</f>
+      <c r="E36" s="26" t="n">
+        <f aca="false">$J$78</f>
         <v>2</v>
       </c>
-      <c r="F36" s="25" t="n">
+      <c r="F36" s="26" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G36" s="26" t="n">
+      <c r="G36" s="27" t="n">
         <f aca="false">H36+I36</f>
         <v>8</v>
       </c>
-      <c r="H36" s="25" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$67:$I$67&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$68:$I$68&lt;&gt;""))</f>
+      <c r="H36" s="26" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$78:$I$78&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$79:$I$79&lt;&gt;""))+SUMPRODUCT($C$20:$I$20,--($C$80:$I$80&lt;&gt;""))</f>
         <v>8</v>
       </c>
-      <c r="I36" s="25" t="n">
-        <f aca="false">SUMIFS($E$75:$E$114,$C$75:$C$114,$B36,$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="I36" s="26" t="n">
+        <f aca="false">SUMIFS($E$87:$E$126,$C$87:$C$126,$B36,$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="J36" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$67:$I$67="77W"))+SUMPRODUCT($C$20:$I$20,--($C$68:$I$68="77W"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B36,$D$75:$D$114,"77W",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="J36" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$78:$I$78="77W"))+SUMPRODUCT($C$20:$I$20,--($C$79:$I$79="77W"))+SUMPRODUCT($C$20:$I$20,--($C$80:$I$80="77W"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B36,$D$87:$D$126,"77W",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="K36" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$67:$I$67="778"))+SUMPRODUCT($C$20:$I$20,--($C$68:$I$68="778"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B36,$D$75:$D$114,"778",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="K36" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$78:$I$78="778"))+SUMPRODUCT($C$20:$I$20,--($C$79:$I$79="778"))+SUMPRODUCT($C$20:$I$20,--($C$80:$I$80="778"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B36,$D$87:$D$126,"778",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>0</v>
       </c>
-      <c r="L36" s="27" t="n">
-        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$67:$I$67="A320"))+SUMPRODUCT($C$20:$I$20,--($C$68:$I$68="A320"))+SUMIFS($E$75:$E$114,$C$75:$C$114,$B36,$D$75:$D$114,"A320",$B$75:$B$114,"&gt;="&amp;$O$4,$B$75:$B$114,"&lt;="&amp;$O$5)</f>
+      <c r="L36" s="28" t="n">
+        <f aca="false">SUMPRODUCT($C$20:$I$20,--($C$78:$I$78="A320"))+SUMPRODUCT($C$20:$I$20,--($C$79:$I$79="A320"))+SUMPRODUCT($C$20:$I$20,--($C$80:$I$80="A320"))+SUMIFS($E$87:$E$126,$C$87:$C$126,$B36,$D$87:$D$126,"A320",$B$87:$B$126,"&gt;="&amp;$O$4,$B$87:$B$126,"&lt;="&amp;$O$5)</f>
         <v>8</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B37" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" s="29"/>
-      <c r="D37" s="29"/>
-      <c r="E37" s="30" t="n">
+      <c r="B37" s="29" t="s">
+        <v>56</v>
+      </c>
+      <c r="C37" s="30"/>
+      <c r="D37" s="30"/>
+      <c r="E37" s="31" t="n">
         <f aca="false">SUM(E25:E36)</f>
-        <v>44</v>
-      </c>
-      <c r="F37" s="30" t="n">
+        <v>46</v>
+      </c>
+      <c r="F37" s="31" t="n">
         <f aca="false">$C$21</f>
         <v>5</v>
       </c>
-      <c r="G37" s="31" t="n">
+      <c r="G37" s="32" t="n">
         <f aca="false">SUM(G25:G36)</f>
-        <v>194</v>
-      </c>
-      <c r="H37" s="30" t="n">
+        <v>203</v>
+      </c>
+      <c r="H37" s="31" t="n">
         <f aca="false">SUM(H25:H36)</f>
-        <v>190</v>
-      </c>
-      <c r="I37" s="30" t="n">
+        <v>199</v>
+      </c>
+      <c r="I37" s="31" t="n">
         <f aca="false">SUM(I25:I36)</f>
         <v>4</v>
       </c>
-      <c r="J37" s="30" t="n">
+      <c r="J37" s="31" t="n">
         <f aca="false">SUM(J25:J36)</f>
         <v>34</v>
       </c>
-      <c r="K37" s="30" t="n">
+      <c r="K37" s="31" t="n">
         <f aca="false">SUM(K25:K36)</f>
         <v>46</v>
       </c>
-      <c r="L37" s="30" t="n">
+      <c r="L37" s="31" t="n">
         <f aca="false">SUM(L25:L36)</f>
-        <v>114</v>
+        <v>123</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B38" s="32" t="s">
-        <v>56</v>
-      </c>
-      <c r="C38" s="32"/>
-      <c r="D38" s="32"/>
-      <c r="E38" s="32"/>
-      <c r="F38" s="32"/>
-      <c r="G38" s="32"/>
-      <c r="H38" s="32"/>
-      <c r="I38" s="32"/>
-      <c r="J38" s="32"/>
-      <c r="K38" s="32"/>
-      <c r="L38" s="32"/>
+      <c r="B38" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="C38" s="33"/>
+      <c r="D38" s="33"/>
+      <c r="E38" s="33"/>
+      <c r="F38" s="33"/>
+      <c r="G38" s="33"/>
+      <c r="H38" s="33"/>
+      <c r="I38" s="33"/>
+      <c r="J38" s="33"/>
+      <c r="K38" s="33"/>
+      <c r="L38" s="33"/>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B39" s="32"/>
-      <c r="C39" s="32"/>
-      <c r="D39" s="32"/>
-      <c r="E39" s="32"/>
-      <c r="F39" s="32"/>
-      <c r="G39" s="32"/>
-      <c r="H39" s="32"/>
-      <c r="I39" s="32"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="32"/>
-      <c r="L39" s="32"/>
+      <c r="B39" s="33"/>
+      <c r="C39" s="33"/>
+      <c r="D39" s="33"/>
+      <c r="E39" s="33"/>
+      <c r="F39" s="33"/>
+      <c r="G39" s="33"/>
+      <c r="H39" s="33"/>
+      <c r="I39" s="33"/>
+      <c r="J39" s="33"/>
+      <c r="K39" s="33"/>
+      <c r="L39" s="33"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B41" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="C41" s="33"/>
-      <c r="D41" s="33"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="33"/>
-      <c r="G41" s="33"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="33"/>
-      <c r="J41" s="33"/>
-      <c r="K41" s="33"/>
-      <c r="L41" s="33"/>
+      <c r="B41" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C41" s="34"/>
+      <c r="D41" s="34"/>
+      <c r="E41" s="34"/>
+      <c r="F41" s="34"/>
+      <c r="G41" s="34"/>
+      <c r="H41" s="34"/>
+      <c r="I41" s="34"/>
+      <c r="J41" s="34"/>
+      <c r="K41" s="34"/>
+      <c r="L41" s="34"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B42" s="34" t="s">
-        <v>58</v>
-      </c>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="34"/>
-      <c r="F42" s="34"/>
-      <c r="G42" s="34"/>
-      <c r="H42" s="34"/>
-      <c r="I42" s="34"/>
-      <c r="J42" s="34"/>
-      <c r="K42" s="34"/>
-      <c r="L42" s="34"/>
+      <c r="B42" s="35" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" s="35"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="35"/>
+      <c r="F42" s="35"/>
+      <c r="G42" s="35"/>
+      <c r="H42" s="35"/>
+      <c r="I42" s="35"/>
+      <c r="J42" s="35"/>
+      <c r="K42" s="35"/>
+      <c r="L42" s="35"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B43" s="34"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="34"/>
-      <c r="H43" s="34"/>
-      <c r="I43" s="34"/>
-      <c r="J43" s="34"/>
-      <c r="K43" s="34"/>
-      <c r="L43" s="34"/>
+      <c r="B43" s="35"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="35"/>
+      <c r="F43" s="35"/>
+      <c r="G43" s="35"/>
+      <c r="H43" s="35"/>
+      <c r="I43" s="35"/>
+      <c r="J43" s="35"/>
+      <c r="K43" s="35"/>
+      <c r="L43" s="35"/>
     </row>
     <row r="44" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B44" s="35" t="s">
-        <v>59</v>
-      </c>
-      <c r="C44" s="35" t="s">
+      <c r="B44" s="36" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="36" t="s">
         <v>14</v>
       </c>
-      <c r="D44" s="35" t="s">
+      <c r="D44" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="E44" s="35" t="s">
+      <c r="E44" s="36" t="s">
         <v>16</v>
       </c>
-      <c r="F44" s="35" t="s">
+      <c r="F44" s="36" t="s">
         <v>17</v>
       </c>
-      <c r="G44" s="35" t="s">
+      <c r="G44" s="36" t="s">
         <v>18</v>
       </c>
-      <c r="H44" s="35" t="s">
+      <c r="H44" s="36" t="s">
         <v>19</v>
       </c>
-      <c r="I44" s="35" t="s">
+      <c r="I44" s="36" t="s">
         <v>20</v>
       </c>
-      <c r="J44" s="35" t="s">
-        <v>60</v>
-      </c>
-      <c r="K44" s="35" t="s">
+      <c r="J44" s="36" t="s">
         <v>61</v>
       </c>
-      <c r="L44" s="35" t="s">
+      <c r="K44" s="36" t="s">
         <v>62</v>
       </c>
-      <c r="N44" s="36" t="s">
+      <c r="L44" s="36" t="s">
         <v>63</v>
       </c>
-      <c r="O44" s="36" t="s">
+      <c r="N44" s="37" t="s">
         <v>64</v>
       </c>
-      <c r="P44" s="36" t="s">
+      <c r="O44" s="37" t="s">
         <v>65</v>
       </c>
+      <c r="P44" s="37" t="s">
+        <v>66</v>
+      </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B45" s="37" t="s">
-        <v>66</v>
-      </c>
-      <c r="C45" s="38" t="s">
+      <c r="B45" s="38" t="s">
         <v>67</v>
       </c>
-      <c r="D45" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="E45" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="F45" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="G45" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="H45" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="I45" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="J45" s="39" t="n">
-        <f aca="false">COUNTA(C45:I46)</f>
-        <v>9</v>
+      <c r="C45" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="D45" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="E45" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="F45" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="G45" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="H45" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="I45" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="J45" s="40" t="n">
+        <f aca="false">COUNTA(C45:I47)</f>
+        <v>10</v>
       </c>
       <c r="K45" s="20" t="str">
-        <f aca="false">IF(COUNTA(C45:I46)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C45:I46,"77W")&gt;0,"77W("&amp;COUNTIF(C45:I46,"77W")&amp;") ","")&amp;IF(COUNTIF(C45:I46,"778")&gt;0,"778("&amp;COUNTIF(C45:I46,"778")&amp;") ","")&amp;IF(COUNTIF(C45:I46,"A320")&gt;0,"A320("&amp;COUNTIF(C45:I46,"A320")&amp;") ",""))," ",", "))</f>
-        <v>77W(7), 778(2)</v>
-      </c>
-      <c r="L45" s="40"/>
-      <c r="N45" s="41" t="s">
+        <f aca="false">IF(COUNTA(C45:I47)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C45:I47,"77W")&gt;0,"77W("&amp;COUNTIF(C45:I47,"77W")&amp;") ","")&amp;IF(COUNTIF(C45:I47,"778")&gt;0,"778("&amp;COUNTIF(C45:I47,"778")&amp;") ","")&amp;IF(COUNTIF(C45:I47,"A320")&gt;0,"A320("&amp;COUNTIF(C45:I47,"A320")&amp;") ",""))," ",", "))</f>
+        <v>77W(7), 778(2), A320(1)</v>
+      </c>
+      <c r="L45" s="41"/>
+      <c r="N45" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="O45" s="42" t="n">
+      <c r="O45" s="43" t="n">
         <f aca="false">DATE(2027,4,1)</f>
         <v>46478</v>
       </c>
       <c r="P45" s="20" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B46" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="C46" s="38" t="s">
+      <c r="B46" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="D46" s="38"/>
-      <c r="E46" s="38"/>
-      <c r="F46" s="38"/>
-      <c r="G46" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="H46" s="38"/>
-      <c r="I46" s="38"/>
-      <c r="J46" s="39"/>
-      <c r="K46" s="39"/>
-      <c r="L46" s="40"/>
-      <c r="N46" s="41" t="s">
+      <c r="C46" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="O46" s="42" t="n">
+      <c r="D46" s="39"/>
+      <c r="E46" s="39"/>
+      <c r="F46" s="39"/>
+      <c r="G46" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="H46" s="39"/>
+      <c r="I46" s="39"/>
+      <c r="J46" s="40"/>
+      <c r="K46" s="40"/>
+      <c r="L46" s="41"/>
+      <c r="N46" s="42" t="s">
+        <v>71</v>
+      </c>
+      <c r="O46" s="43" t="n">
         <f aca="false">DATE(2027,5,1)</f>
         <v>46508</v>
       </c>
       <c r="P46" s="20" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B47" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="C47" s="38"/>
-      <c r="D47" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="E47" s="38"/>
-      <c r="F47" s="38"/>
-      <c r="G47" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="H47" s="38"/>
-      <c r="I47" s="38" t="s">
-        <v>67</v>
-      </c>
-      <c r="J47" s="39" t="n">
-        <f aca="false">COUNTA(C47:I48)</f>
-        <v>3</v>
-      </c>
-      <c r="K47" s="20" t="str">
-        <f aca="false">IF(COUNTA(C47:I48)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C47:I48,"77W")&gt;0,"77W("&amp;COUNTIF(C47:I48,"77W")&amp;") ","")&amp;IF(COUNTIF(C47:I48,"778")&gt;0,"778("&amp;COUNTIF(C47:I48,"778")&amp;") ","")&amp;IF(COUNTIF(C47:I48,"A320")&gt;0,"A320("&amp;COUNTIF(C47:I48,"A320")&amp;") ",""))," ",", "))</f>
-        <v>77W(1), 778(2)</v>
-      </c>
-      <c r="L47" s="44"/>
-      <c r="N47" s="41" t="s">
+      <c r="B47" s="44" t="s">
         <v>72</v>
       </c>
-      <c r="O47" s="42" t="n">
+      <c r="C47" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="D47" s="39"/>
+      <c r="E47" s="39"/>
+      <c r="F47" s="39"/>
+      <c r="G47" s="39"/>
+      <c r="H47" s="39"/>
+      <c r="I47" s="39"/>
+      <c r="J47" s="40"/>
+      <c r="K47" s="40"/>
+      <c r="L47" s="41"/>
+      <c r="N47" s="42" t="s">
+        <v>74</v>
+      </c>
+      <c r="O47" s="43" t="n">
         <f aca="false">DATE(2027,6,1)</f>
         <v>46539</v>
       </c>
@@ -3015,1037 +3046,1231 @@
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B48" s="43" t="s">
+      <c r="B48" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="C48" s="39"/>
+      <c r="D48" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="E48" s="39"/>
+      <c r="F48" s="39"/>
+      <c r="G48" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="H48" s="39"/>
+      <c r="I48" s="39" t="s">
         <v>68</v>
       </c>
-      <c r="C48" s="38"/>
-      <c r="D48" s="38"/>
-      <c r="E48" s="38"/>
-      <c r="F48" s="38"/>
-      <c r="G48" s="38"/>
-      <c r="H48" s="38"/>
-      <c r="I48" s="38"/>
-      <c r="J48" s="39"/>
-      <c r="K48" s="39"/>
-      <c r="L48" s="44"/>
-      <c r="N48" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="O48" s="42" t="n">
+      <c r="J48" s="40" t="n">
+        <f aca="false">COUNTA(C48:I50)</f>
+        <v>3</v>
+      </c>
+      <c r="K48" s="20" t="str">
+        <f aca="false">IF(COUNTA(C48:I50)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C48:I50,"77W")&gt;0,"77W("&amp;COUNTIF(C48:I50,"77W")&amp;") ","")&amp;IF(COUNTIF(C48:I50,"778")&gt;0,"778("&amp;COUNTIF(C48:I50,"778")&amp;") ","")&amp;IF(COUNTIF(C48:I50,"A320")&gt;0,"A320("&amp;COUNTIF(C48:I50,"A320")&amp;") ",""))," ",", "))</f>
+        <v>77W(1), 778(2)</v>
+      </c>
+      <c r="L48" s="45"/>
+      <c r="N48" s="42" t="s">
+        <v>76</v>
+      </c>
+      <c r="O48" s="43" t="n">
         <f aca="false">DATE(2027,7,1)</f>
         <v>46569</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B49" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="C49" s="38"/>
-      <c r="D49" s="38"/>
-      <c r="E49" s="38" t="s">
+      <c r="B49" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="F49" s="38"/>
-      <c r="G49" s="38"/>
-      <c r="H49" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="I49" s="38"/>
-      <c r="J49" s="39" t="n">
-        <f aca="false">COUNTA(C49:I50)</f>
-        <v>2</v>
-      </c>
-      <c r="K49" s="20" t="str">
-        <f aca="false">IF(COUNTA(C49:I50)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C49:I50,"77W")&gt;0,"77W("&amp;COUNTIF(C49:I50,"77W")&amp;") ","")&amp;IF(COUNTIF(C49:I50,"778")&gt;0,"778("&amp;COUNTIF(C49:I50,"778")&amp;") ","")&amp;IF(COUNTIF(C49:I50,"A320")&gt;0,"A320("&amp;COUNTIF(C49:I50,"A320")&amp;") ",""))," ",", "))</f>
-        <v>778(2)</v>
-      </c>
+      <c r="C49" s="39"/>
+      <c r="D49" s="39"/>
+      <c r="E49" s="39"/>
+      <c r="F49" s="39"/>
+      <c r="G49" s="39"/>
+      <c r="H49" s="39"/>
+      <c r="I49" s="39"/>
+      <c r="J49" s="40"/>
+      <c r="K49" s="40"/>
       <c r="L49" s="45"/>
-      <c r="N49" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="O49" s="42" t="n">
+      <c r="N49" s="42" t="s">
+        <v>77</v>
+      </c>
+      <c r="O49" s="43" t="n">
         <f aca="false">DATE(2027,8,1)</f>
         <v>46600</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B50" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="C50" s="38"/>
-      <c r="D50" s="38"/>
-      <c r="E50" s="38"/>
-      <c r="F50" s="38"/>
-      <c r="G50" s="38"/>
-      <c r="H50" s="38"/>
-      <c r="I50" s="38"/>
-      <c r="J50" s="39"/>
-      <c r="K50" s="39"/>
+      <c r="B50" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="C50" s="39"/>
+      <c r="D50" s="39"/>
+      <c r="E50" s="39"/>
+      <c r="F50" s="39"/>
+      <c r="G50" s="39"/>
+      <c r="H50" s="39"/>
+      <c r="I50" s="39"/>
+      <c r="J50" s="40"/>
+      <c r="K50" s="40"/>
       <c r="L50" s="45"/>
-      <c r="N50" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="O50" s="42" t="n">
+      <c r="N50" s="42" t="s">
+        <v>78</v>
+      </c>
+      <c r="O50" s="43" t="n">
         <f aca="false">DATE(2027,9,1)</f>
         <v>46631</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B51" s="37" t="s">
-        <v>78</v>
-      </c>
-      <c r="C51" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="D51" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="E51" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="F51" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="G51" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="H51" s="38"/>
-      <c r="I51" s="38"/>
-      <c r="J51" s="39" t="n">
-        <f aca="false">COUNTA(C51:I52)</f>
-        <v>6</v>
+      <c r="B51" s="38" t="s">
+        <v>79</v>
+      </c>
+      <c r="C51" s="39"/>
+      <c r="D51" s="39"/>
+      <c r="E51" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="F51" s="39"/>
+      <c r="G51" s="39"/>
+      <c r="H51" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="I51" s="39"/>
+      <c r="J51" s="40" t="n">
+        <f aca="false">COUNTA(C51:I53)</f>
+        <v>2</v>
       </c>
       <c r="K51" s="20" t="str">
-        <f aca="false">IF(COUNTA(C51:I52)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C51:I52,"77W")&gt;0,"77W("&amp;COUNTIF(C51:I52,"77W")&amp;") ","")&amp;IF(COUNTIF(C51:I52,"778")&gt;0,"778("&amp;COUNTIF(C51:I52,"778")&amp;") ","")&amp;IF(COUNTIF(C51:I52,"A320")&gt;0,"A320("&amp;COUNTIF(C51:I52,"A320")&amp;") ",""))," ",", "))</f>
-        <v>778(1), A320(5)</v>
+        <f aca="false">IF(COUNTA(C51:I53)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C51:I53,"77W")&gt;0,"77W("&amp;COUNTIF(C51:I53,"77W")&amp;") ","")&amp;IF(COUNTIF(C51:I53,"778")&gt;0,"778("&amp;COUNTIF(C51:I53,"778")&amp;") ","")&amp;IF(COUNTIF(C51:I53,"A320")&gt;0,"A320("&amp;COUNTIF(C51:I53,"A320")&amp;") ",""))," ",", "))</f>
+        <v>778(2)</v>
       </c>
       <c r="L51" s="46"/>
-      <c r="N51" s="41" t="s">
-        <v>79</v>
-      </c>
-      <c r="O51" s="42" t="n">
+      <c r="N51" s="42" t="s">
+        <v>80</v>
+      </c>
+      <c r="O51" s="43" t="n">
         <f aca="false">DATE(2027,10,1)</f>
         <v>46661</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B52" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="C52" s="38"/>
-      <c r="D52" s="38"/>
-      <c r="E52" s="38" t="s">
+      <c r="B52" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="F52" s="38"/>
-      <c r="G52" s="38"/>
-      <c r="H52" s="38"/>
-      <c r="I52" s="38"/>
-      <c r="J52" s="39"/>
-      <c r="K52" s="39"/>
+      <c r="C52" s="39"/>
+      <c r="D52" s="39"/>
+      <c r="E52" s="39"/>
+      <c r="F52" s="39"/>
+      <c r="G52" s="39"/>
+      <c r="H52" s="39"/>
+      <c r="I52" s="39"/>
+      <c r="J52" s="40"/>
+      <c r="K52" s="40"/>
       <c r="L52" s="46"/>
-      <c r="N52" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="O52" s="42" t="n">
+      <c r="N52" s="42" t="s">
+        <v>81</v>
+      </c>
+      <c r="O52" s="43" t="n">
         <f aca="false">DATE(2027,11,1)</f>
         <v>46692</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B53" s="37" t="s">
-        <v>81</v>
-      </c>
-      <c r="C53" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="D53" s="38"/>
-      <c r="E53" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="F53" s="38"/>
-      <c r="G53" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="H53" s="38"/>
-      <c r="I53" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="J53" s="39" t="n">
-        <f aca="false">COUNTA(C53:I54)</f>
-        <v>4</v>
-      </c>
-      <c r="K53" s="20" t="str">
-        <f aca="false">IF(COUNTA(C53:I54)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C53:I54,"77W")&gt;0,"77W("&amp;COUNTIF(C53:I54,"77W")&amp;") ","")&amp;IF(COUNTIF(C53:I54,"778")&gt;0,"778("&amp;COUNTIF(C53:I54,"778")&amp;") ","")&amp;IF(COUNTIF(C53:I54,"A320")&gt;0,"A320("&amp;COUNTIF(C53:I54,"A320")&amp;") ",""))," ",", "))</f>
-        <v>A320(4)</v>
-      </c>
-      <c r="L53" s="47"/>
-      <c r="N53" s="41" t="s">
+      <c r="B53" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="C53" s="39"/>
+      <c r="D53" s="39"/>
+      <c r="E53" s="39"/>
+      <c r="F53" s="39"/>
+      <c r="G53" s="39"/>
+      <c r="H53" s="39"/>
+      <c r="I53" s="39"/>
+      <c r="J53" s="40"/>
+      <c r="K53" s="40"/>
+      <c r="L53" s="46"/>
+      <c r="N53" s="42" t="s">
         <v>82</v>
       </c>
-      <c r="O53" s="42" t="n">
+      <c r="O53" s="43" t="n">
         <f aca="false">DATE(2027,12,1)</f>
         <v>46722</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B54" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="C54" s="38"/>
-      <c r="D54" s="38"/>
-      <c r="E54" s="38"/>
-      <c r="F54" s="38"/>
-      <c r="G54" s="38"/>
-      <c r="H54" s="38"/>
-      <c r="I54" s="38"/>
-      <c r="J54" s="39"/>
-      <c r="K54" s="39"/>
+      <c r="B54" s="38" t="s">
+        <v>83</v>
+      </c>
+      <c r="C54" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="D54" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="E54" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="F54" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="G54" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="H54" s="39"/>
+      <c r="I54" s="39"/>
+      <c r="J54" s="40" t="n">
+        <f aca="false">COUNTA(C54:I56)</f>
+        <v>6</v>
+      </c>
+      <c r="K54" s="20" t="str">
+        <f aca="false">IF(COUNTA(C54:I56)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C54:I56,"77W")&gt;0,"77W("&amp;COUNTIF(C54:I56,"77W")&amp;") ","")&amp;IF(COUNTIF(C54:I56,"778")&gt;0,"778("&amp;COUNTIF(C54:I56,"778")&amp;") ","")&amp;IF(COUNTIF(C54:I56,"A320")&gt;0,"A320("&amp;COUNTIF(C54:I56,"A320")&amp;") ",""))," ",", "))</f>
+        <v>778(1), A320(5)</v>
+      </c>
       <c r="L54" s="47"/>
-      <c r="N54" s="41" t="s">
-        <v>83</v>
-      </c>
-      <c r="O54" s="42" t="n">
+      <c r="N54" s="42" t="s">
+        <v>84</v>
+      </c>
+      <c r="O54" s="43" t="n">
         <f aca="false">DATE(2028,1,1)</f>
         <v>46753</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B55" s="37" t="s">
-        <v>8</v>
-      </c>
-      <c r="C55" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="D55" s="38"/>
-      <c r="E55" s="38"/>
-      <c r="F55" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="G55" s="38"/>
-      <c r="H55" s="38" t="s">
-        <v>73</v>
-      </c>
-      <c r="I55" s="38"/>
-      <c r="J55" s="39" t="n">
-        <f aca="false">COUNTA(C55:I56)</f>
-        <v>3</v>
-      </c>
-      <c r="K55" s="20" t="str">
-        <f aca="false">IF(COUNTA(C55:I56)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C55:I56,"77W")&gt;0,"77W("&amp;COUNTIF(C55:I56,"77W")&amp;") ","")&amp;IF(COUNTIF(C55:I56,"778")&gt;0,"778("&amp;COUNTIF(C55:I56,"778")&amp;") ","")&amp;IF(COUNTIF(C55:I56,"A320")&gt;0,"A320("&amp;COUNTIF(C55:I56,"A320")&amp;") ",""))," ",", "))</f>
-        <v>A320(3)</v>
-      </c>
-      <c r="L55" s="48"/>
-      <c r="N55" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="O55" s="42" t="n">
+      <c r="B55" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="C55" s="39"/>
+      <c r="D55" s="39"/>
+      <c r="E55" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="F55" s="39"/>
+      <c r="G55" s="39"/>
+      <c r="H55" s="39"/>
+      <c r="I55" s="39"/>
+      <c r="J55" s="40"/>
+      <c r="K55" s="40"/>
+      <c r="L55" s="47"/>
+      <c r="N55" s="42" t="s">
+        <v>85</v>
+      </c>
+      <c r="O55" s="43" t="n">
         <f aca="false">DATE(2028,2,1)</f>
         <v>46784</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B56" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="C56" s="38"/>
-      <c r="D56" s="38"/>
-      <c r="E56" s="38"/>
-      <c r="F56" s="38"/>
-      <c r="G56" s="38"/>
-      <c r="H56" s="38"/>
-      <c r="I56" s="38"/>
-      <c r="J56" s="39"/>
-      <c r="K56" s="39"/>
-      <c r="L56" s="48"/>
-      <c r="N56" s="41" t="s">
-        <v>85</v>
-      </c>
-      <c r="O56" s="42" t="n">
+      <c r="B56" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="C56" s="39"/>
+      <c r="D56" s="39"/>
+      <c r="E56" s="39"/>
+      <c r="F56" s="39"/>
+      <c r="G56" s="39"/>
+      <c r="H56" s="39"/>
+      <c r="I56" s="39"/>
+      <c r="J56" s="40"/>
+      <c r="K56" s="40"/>
+      <c r="L56" s="47"/>
+      <c r="N56" s="42" t="s">
+        <v>86</v>
+      </c>
+      <c r="O56" s="43" t="n">
         <f aca="false">DATE(2028,3,1)</f>
         <v>46813</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B57" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="C57" s="38"/>
-      <c r="D57" s="38" t="s">
+      <c r="B57" s="38" t="s">
+        <v>87</v>
+      </c>
+      <c r="C57" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="E57" s="38"/>
-      <c r="F57" s="38" t="s">
+      <c r="D57" s="39"/>
+      <c r="E57" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="G57" s="38"/>
-      <c r="H57" s="38" t="s">
+      <c r="F57" s="39"/>
+      <c r="G57" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="I57" s="38"/>
-      <c r="J57" s="39" t="n">
-        <f aca="false">COUNTA(C57:I58)</f>
+      <c r="H57" s="39"/>
+      <c r="I57" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="J57" s="40" t="n">
+        <f aca="false">COUNTA(C57:I59)</f>
+        <v>4</v>
+      </c>
+      <c r="K57" s="20" t="str">
+        <f aca="false">IF(COUNTA(C57:I59)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C57:I59,"77W")&gt;0,"77W("&amp;COUNTIF(C57:I59,"77W")&amp;") ","")&amp;IF(COUNTIF(C57:I59,"778")&gt;0,"778("&amp;COUNTIF(C57:I59,"778")&amp;") ","")&amp;IF(COUNTIF(C57:I59,"A320")&gt;0,"A320("&amp;COUNTIF(C57:I59,"A320")&amp;") ",""))," ",", "))</f>
+        <v>A320(4)</v>
+      </c>
+      <c r="L57" s="48"/>
+    </row>
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B58" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="C58" s="39"/>
+      <c r="D58" s="39"/>
+      <c r="E58" s="39"/>
+      <c r="F58" s="39"/>
+      <c r="G58" s="39"/>
+      <c r="H58" s="39"/>
+      <c r="I58" s="39"/>
+      <c r="J58" s="40"/>
+      <c r="K58" s="40"/>
+      <c r="L58" s="48"/>
+    </row>
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B59" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="C59" s="39"/>
+      <c r="D59" s="39"/>
+      <c r="E59" s="39"/>
+      <c r="F59" s="39"/>
+      <c r="G59" s="39"/>
+      <c r="H59" s="39"/>
+      <c r="I59" s="39"/>
+      <c r="J59" s="40"/>
+      <c r="K59" s="40"/>
+      <c r="L59" s="48"/>
+    </row>
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B60" s="38" t="s">
+        <v>8</v>
+      </c>
+      <c r="C60" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="D60" s="39"/>
+      <c r="E60" s="39"/>
+      <c r="F60" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="G60" s="39"/>
+      <c r="H60" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="I60" s="39"/>
+      <c r="J60" s="40" t="n">
+        <f aca="false">COUNTA(C60:I62)</f>
         <v>3</v>
       </c>
-      <c r="K57" s="20" t="str">
-        <f aca="false">IF(COUNTA(C57:I58)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C57:I58,"77W")&gt;0,"77W("&amp;COUNTIF(C57:I58,"77W")&amp;") ","")&amp;IF(COUNTIF(C57:I58,"778")&gt;0,"778("&amp;COUNTIF(C57:I58,"778")&amp;") ","")&amp;IF(COUNTIF(C57:I58,"A320")&gt;0,"A320("&amp;COUNTIF(C57:I58,"A320")&amp;") ",""))," ",", "))</f>
+      <c r="K60" s="20" t="str">
+        <f aca="false">IF(COUNTA(C60:I62)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C60:I62,"77W")&gt;0,"77W("&amp;COUNTIF(C60:I62,"77W")&amp;") ","")&amp;IF(COUNTIF(C60:I62,"778")&gt;0,"778("&amp;COUNTIF(C60:I62,"778")&amp;") ","")&amp;IF(COUNTIF(C60:I62,"A320")&gt;0,"A320("&amp;COUNTIF(C60:I62,"A320")&amp;") ",""))," ",", "))</f>
         <v>A320(3)</v>
       </c>
-      <c r="L57" s="49"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B58" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="C58" s="38"/>
-      <c r="D58" s="38"/>
-      <c r="E58" s="38"/>
-      <c r="F58" s="38"/>
-      <c r="G58" s="38"/>
-      <c r="H58" s="38"/>
-      <c r="I58" s="38"/>
-      <c r="J58" s="39"/>
-      <c r="K58" s="39"/>
-      <c r="L58" s="49"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B59" s="37" t="s">
-        <v>87</v>
-      </c>
-      <c r="C59" s="38" t="s">
+      <c r="L60" s="49"/>
+    </row>
+    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B61" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="D59" s="38"/>
-      <c r="E59" s="38"/>
-      <c r="F59" s="38"/>
-      <c r="G59" s="38" t="s">
+      <c r="C61" s="39"/>
+      <c r="D61" s="39"/>
+      <c r="E61" s="39"/>
+      <c r="F61" s="39"/>
+      <c r="G61" s="39"/>
+      <c r="H61" s="39"/>
+      <c r="I61" s="39"/>
+      <c r="J61" s="40"/>
+      <c r="K61" s="40"/>
+      <c r="L61" s="49"/>
+    </row>
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B62" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="C62" s="39"/>
+      <c r="D62" s="39"/>
+      <c r="E62" s="39"/>
+      <c r="F62" s="39"/>
+      <c r="G62" s="39"/>
+      <c r="H62" s="39"/>
+      <c r="I62" s="39"/>
+      <c r="J62" s="40"/>
+      <c r="K62" s="40"/>
+      <c r="L62" s="49"/>
+    </row>
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B63" s="38" t="s">
+        <v>88</v>
+      </c>
+      <c r="C63" s="39"/>
+      <c r="D63" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="E63" s="39"/>
+      <c r="F63" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="G63" s="39"/>
+      <c r="H63" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="I63" s="39"/>
+      <c r="J63" s="40" t="n">
+        <f aca="false">COUNTA(C63:I65)</f>
+        <v>3</v>
+      </c>
+      <c r="K63" s="20" t="str">
+        <f aca="false">IF(COUNTA(C63:I65)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C63:I65,"77W")&gt;0,"77W("&amp;COUNTIF(C63:I65,"77W")&amp;") ","")&amp;IF(COUNTIF(C63:I65,"778")&gt;0,"778("&amp;COUNTIF(C63:I65,"778")&amp;") ","")&amp;IF(COUNTIF(C63:I65,"A320")&gt;0,"A320("&amp;COUNTIF(C63:I65,"A320")&amp;") ",""))," ",", "))</f>
+        <v>A320(3)</v>
+      </c>
+      <c r="L63" s="50"/>
+    </row>
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B64" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="H59" s="38"/>
-      <c r="I59" s="38"/>
-      <c r="J59" s="39" t="n">
-        <f aca="false">COUNTA(C59:I60)</f>
+      <c r="C64" s="39"/>
+      <c r="D64" s="39"/>
+      <c r="E64" s="39"/>
+      <c r="F64" s="39"/>
+      <c r="G64" s="39"/>
+      <c r="H64" s="39"/>
+      <c r="I64" s="39"/>
+      <c r="J64" s="40"/>
+      <c r="K64" s="40"/>
+      <c r="L64" s="50"/>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B65" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="C65" s="39"/>
+      <c r="D65" s="39"/>
+      <c r="E65" s="39"/>
+      <c r="F65" s="39"/>
+      <c r="G65" s="39"/>
+      <c r="H65" s="39"/>
+      <c r="I65" s="39"/>
+      <c r="J65" s="40"/>
+      <c r="K65" s="40"/>
+      <c r="L65" s="50"/>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B66" s="38" t="s">
+        <v>89</v>
+      </c>
+      <c r="C66" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="D66" s="39"/>
+      <c r="E66" s="39"/>
+      <c r="F66" s="39"/>
+      <c r="G66" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="H66" s="39"/>
+      <c r="I66" s="39"/>
+      <c r="J66" s="40" t="n">
+        <f aca="false">COUNTA(C66:I68)</f>
         <v>2</v>
       </c>
-      <c r="K59" s="20" t="str">
-        <f aca="false">IF(COUNTA(C59:I60)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C59:I60,"77W")&gt;0,"77W("&amp;COUNTIF(C59:I60,"77W")&amp;") ","")&amp;IF(COUNTIF(C59:I60,"778")&gt;0,"778("&amp;COUNTIF(C59:I60,"778")&amp;") ","")&amp;IF(COUNTIF(C59:I60,"A320")&gt;0,"A320("&amp;COUNTIF(C59:I60,"A320")&amp;") ",""))," ",", "))</f>
+      <c r="K66" s="20" t="str">
+        <f aca="false">IF(COUNTA(C66:I68)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C66:I68,"77W")&gt;0,"77W("&amp;COUNTIF(C66:I68,"77W")&amp;") ","")&amp;IF(COUNTIF(C66:I68,"778")&gt;0,"778("&amp;COUNTIF(C66:I68,"778")&amp;") ","")&amp;IF(COUNTIF(C66:I68,"A320")&gt;0,"A320("&amp;COUNTIF(C66:I68,"A320")&amp;") ",""))," ",", "))</f>
         <v>778(2)</v>
       </c>
-      <c r="L59" s="50"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B60" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="C60" s="38"/>
-      <c r="D60" s="38"/>
-      <c r="E60" s="38"/>
-      <c r="F60" s="38"/>
-      <c r="G60" s="38"/>
-      <c r="H60" s="38"/>
-      <c r="I60" s="38"/>
-      <c r="J60" s="39"/>
-      <c r="K60" s="39"/>
-      <c r="L60" s="50"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B61" s="37" t="s">
-        <v>88</v>
-      </c>
-      <c r="C61" s="38"/>
-      <c r="D61" s="38"/>
-      <c r="E61" s="38"/>
-      <c r="F61" s="38" t="s">
+      <c r="L66" s="51"/>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B67" s="44" t="s">
         <v>69</v>
       </c>
-      <c r="G61" s="38"/>
-      <c r="H61" s="38"/>
-      <c r="I61" s="38"/>
-      <c r="J61" s="39" t="n">
-        <f aca="false">COUNTA(C61:I62)</f>
+      <c r="C67" s="39"/>
+      <c r="D67" s="39"/>
+      <c r="E67" s="39"/>
+      <c r="F67" s="39"/>
+      <c r="G67" s="39"/>
+      <c r="H67" s="39"/>
+      <c r="I67" s="39"/>
+      <c r="J67" s="40"/>
+      <c r="K67" s="40"/>
+      <c r="L67" s="51"/>
+    </row>
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B68" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="C68" s="39"/>
+      <c r="D68" s="39"/>
+      <c r="E68" s="39"/>
+      <c r="F68" s="39"/>
+      <c r="G68" s="39"/>
+      <c r="H68" s="39"/>
+      <c r="I68" s="39"/>
+      <c r="J68" s="40"/>
+      <c r="K68" s="40"/>
+      <c r="L68" s="51"/>
+    </row>
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B69" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="C69" s="39"/>
+      <c r="D69" s="39"/>
+      <c r="E69" s="39"/>
+      <c r="F69" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="G69" s="39"/>
+      <c r="H69" s="39"/>
+      <c r="I69" s="39"/>
+      <c r="J69" s="40" t="n">
+        <f aca="false">COUNTA(C69:I71)</f>
         <v>1</v>
       </c>
-      <c r="K61" s="20" t="str">
-        <f aca="false">IF(COUNTA(C61:I62)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C61:I62,"77W")&gt;0,"77W("&amp;COUNTIF(C61:I62,"77W")&amp;") ","")&amp;IF(COUNTIF(C61:I62,"778")&gt;0,"778("&amp;COUNTIF(C61:I62,"778")&amp;") ","")&amp;IF(COUNTIF(C61:I62,"A320")&gt;0,"A320("&amp;COUNTIF(C61:I62,"A320")&amp;") ",""))," ",", "))</f>
+      <c r="K69" s="20" t="str">
+        <f aca="false">IF(COUNTA(C69:I71)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C69:I71,"77W")&gt;0,"77W("&amp;COUNTIF(C69:I71,"77W")&amp;") ","")&amp;IF(COUNTIF(C69:I71,"778")&gt;0,"778("&amp;COUNTIF(C69:I71,"778")&amp;") ","")&amp;IF(COUNTIF(C69:I71,"A320")&gt;0,"A320("&amp;COUNTIF(C69:I71,"A320")&amp;") ",""))," ",", "))</f>
         <v>778(1)</v>
       </c>
-      <c r="L61" s="51"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B62" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="C62" s="38"/>
-      <c r="D62" s="38"/>
-      <c r="E62" s="38"/>
-      <c r="F62" s="38"/>
-      <c r="G62" s="38"/>
-      <c r="H62" s="38"/>
-      <c r="I62" s="38"/>
-      <c r="J62" s="39"/>
-      <c r="K62" s="39"/>
-      <c r="L62" s="51"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B63" s="37" t="s">
-        <v>89</v>
-      </c>
-      <c r="C63" s="38"/>
-      <c r="D63" s="38" t="s">
+      <c r="L69" s="52"/>
+    </row>
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B70" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="C70" s="39"/>
+      <c r="D70" s="39"/>
+      <c r="E70" s="39"/>
+      <c r="F70" s="39"/>
+      <c r="G70" s="39"/>
+      <c r="H70" s="39"/>
+      <c r="I70" s="39"/>
+      <c r="J70" s="40"/>
+      <c r="K70" s="40"/>
+      <c r="L70" s="52"/>
+    </row>
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B71" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="C71" s="39"/>
+      <c r="D71" s="39"/>
+      <c r="E71" s="39"/>
+      <c r="F71" s="39"/>
+      <c r="G71" s="39"/>
+      <c r="H71" s="39"/>
+      <c r="I71" s="39"/>
+      <c r="J71" s="40"/>
+      <c r="K71" s="40"/>
+      <c r="L71" s="52"/>
+    </row>
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B72" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="C72" s="39"/>
+      <c r="D72" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="E63" s="38"/>
-      <c r="F63" s="38"/>
-      <c r="G63" s="38"/>
-      <c r="H63" s="38" t="s">
+      <c r="E72" s="39"/>
+      <c r="F72" s="39"/>
+      <c r="G72" s="39"/>
+      <c r="H72" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="I63" s="38"/>
-      <c r="J63" s="39" t="n">
-        <f aca="false">COUNTA(C63:I64)</f>
+      <c r="I72" s="39"/>
+      <c r="J72" s="40" t="n">
+        <f aca="false">COUNTA(C72:I74)</f>
         <v>2</v>
       </c>
-      <c r="K63" s="20" t="str">
-        <f aca="false">IF(COUNTA(C63:I64)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C63:I64,"77W")&gt;0,"77W("&amp;COUNTIF(C63:I64,"77W")&amp;") ","")&amp;IF(COUNTIF(C63:I64,"778")&gt;0,"778("&amp;COUNTIF(C63:I64,"778")&amp;") ","")&amp;IF(COUNTIF(C63:I64,"A320")&gt;0,"A320("&amp;COUNTIF(C63:I64,"A320")&amp;") ",""))," ",", "))</f>
+      <c r="K72" s="20" t="str">
+        <f aca="false">IF(COUNTA(C72:I74)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C72:I74,"77W")&gt;0,"77W("&amp;COUNTIF(C72:I74,"77W")&amp;") ","")&amp;IF(COUNTIF(C72:I74,"778")&gt;0,"778("&amp;COUNTIF(C72:I74,"778")&amp;") ","")&amp;IF(COUNTIF(C72:I74,"A320")&gt;0,"A320("&amp;COUNTIF(C72:I74,"A320")&amp;") ",""))," ",", "))</f>
         <v>A320(2)</v>
       </c>
-      <c r="L63" s="52"/>
-    </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B64" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="C64" s="38"/>
-      <c r="D64" s="38"/>
-      <c r="E64" s="38"/>
-      <c r="F64" s="38"/>
-      <c r="G64" s="38"/>
-      <c r="H64" s="38"/>
-      <c r="I64" s="38"/>
-      <c r="J64" s="39"/>
-      <c r="K64" s="39"/>
-      <c r="L64" s="52"/>
-    </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B65" s="37" t="s">
-        <v>90</v>
-      </c>
-      <c r="C65" s="38" t="s">
+      <c r="L72" s="53"/>
+    </row>
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B73" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="C73" s="39"/>
+      <c r="D73" s="39"/>
+      <c r="E73" s="39"/>
+      <c r="F73" s="39"/>
+      <c r="G73" s="39"/>
+      <c r="H73" s="39"/>
+      <c r="I73" s="39"/>
+      <c r="J73" s="40"/>
+      <c r="K73" s="40"/>
+      <c r="L73" s="53"/>
+    </row>
+    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B74" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="C74" s="39"/>
+      <c r="D74" s="39"/>
+      <c r="E74" s="39"/>
+      <c r="F74" s="39"/>
+      <c r="G74" s="39"/>
+      <c r="H74" s="39"/>
+      <c r="I74" s="39"/>
+      <c r="J74" s="40"/>
+      <c r="K74" s="40"/>
+      <c r="L74" s="53"/>
+    </row>
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B75" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="C75" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="D65" s="38" t="s">
+      <c r="D75" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="E65" s="38" t="s">
+      <c r="E75" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="F65" s="38" t="s">
+      <c r="F75" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="G65" s="38" t="s">
+      <c r="G75" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="H65" s="38" t="s">
+      <c r="H75" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="I65" s="38"/>
-      <c r="J65" s="39" t="n">
-        <f aca="false">COUNTA(C65:I66)</f>
-        <v>7</v>
-      </c>
-      <c r="K65" s="20" t="str">
-        <f aca="false">IF(COUNTA(C65:I66)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C65:I66,"77W")&gt;0,"77W("&amp;COUNTIF(C65:I66,"77W")&amp;") ","")&amp;IF(COUNTIF(C65:I66,"778")&gt;0,"778("&amp;COUNTIF(C65:I66,"778")&amp;") ","")&amp;IF(COUNTIF(C65:I66,"A320")&gt;0,"A320("&amp;COUNTIF(C65:I66,"A320")&amp;") ",""))," ",", "))</f>
-        <v>A320(7)</v>
-      </c>
-      <c r="L65" s="53"/>
-    </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B66" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="C66" s="38"/>
-      <c r="D66" s="38"/>
-      <c r="E66" s="38"/>
-      <c r="F66" s="38"/>
-      <c r="G66" s="38" t="s">
+      <c r="I75" s="39"/>
+      <c r="J75" s="40" t="n">
+        <f aca="false">COUNTA(C75:I77)</f>
+        <v>8</v>
+      </c>
+      <c r="K75" s="20" t="str">
+        <f aca="false">IF(COUNTA(C75:I77)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C75:I77,"77W")&gt;0,"77W("&amp;COUNTIF(C75:I77,"77W")&amp;") ","")&amp;IF(COUNTIF(C75:I77,"778")&gt;0,"778("&amp;COUNTIF(C75:I77,"778")&amp;") ","")&amp;IF(COUNTIF(C75:I77,"A320")&gt;0,"A320("&amp;COUNTIF(C75:I77,"A320")&amp;") ",""))," ",", "))</f>
+        <v>A320(8)</v>
+      </c>
+      <c r="L75" s="54"/>
+    </row>
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B76" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="C76" s="39"/>
+      <c r="D76" s="39"/>
+      <c r="E76" s="39"/>
+      <c r="F76" s="39"/>
+      <c r="G76" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="H66" s="38"/>
-      <c r="I66" s="38"/>
-      <c r="J66" s="39"/>
-      <c r="K66" s="39"/>
-      <c r="L66" s="53"/>
-    </row>
-    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B67" s="37" t="s">
-        <v>91</v>
-      </c>
-      <c r="C67" s="38"/>
-      <c r="D67" s="38"/>
-      <c r="E67" s="38" t="s">
+      <c r="H76" s="39"/>
+      <c r="I76" s="39"/>
+      <c r="J76" s="40"/>
+      <c r="K76" s="40"/>
+      <c r="L76" s="54"/>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B77" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="C77" s="39"/>
+      <c r="D77" s="39"/>
+      <c r="E77" s="39"/>
+      <c r="F77" s="39"/>
+      <c r="G77" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="F67" s="38"/>
-      <c r="G67" s="38"/>
-      <c r="H67" s="38"/>
-      <c r="I67" s="38" t="s">
+      <c r="H77" s="39"/>
+      <c r="I77" s="39"/>
+      <c r="J77" s="40"/>
+      <c r="K77" s="40"/>
+      <c r="L77" s="54"/>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B78" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="C78" s="39"/>
+      <c r="D78" s="39"/>
+      <c r="E78" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="J67" s="39" t="n">
-        <f aca="false">COUNTA(C67:I68)</f>
+      <c r="F78" s="39"/>
+      <c r="G78" s="39"/>
+      <c r="H78" s="39"/>
+      <c r="I78" s="39" t="s">
+        <v>73</v>
+      </c>
+      <c r="J78" s="40" t="n">
+        <f aca="false">COUNTA(C78:I80)</f>
         <v>2</v>
       </c>
-      <c r="K67" s="20" t="str">
-        <f aca="false">IF(COUNTA(C67:I68)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C67:I68,"77W")&gt;0,"77W("&amp;COUNTIF(C67:I68,"77W")&amp;") ","")&amp;IF(COUNTIF(C67:I68,"778")&gt;0,"778("&amp;COUNTIF(C67:I68,"778")&amp;") ","")&amp;IF(COUNTIF(C67:I68,"A320")&gt;0,"A320("&amp;COUNTIF(C67:I68,"A320")&amp;") ",""))," ",", "))</f>
+      <c r="K78" s="20" t="str">
+        <f aca="false">IF(COUNTA(C78:I80)=0,"-",SUBSTITUTE(TRIM(IF(COUNTIF(C78:I80,"77W")&gt;0,"77W("&amp;COUNTIF(C78:I80,"77W")&amp;") ","")&amp;IF(COUNTIF(C78:I80,"778")&gt;0,"778("&amp;COUNTIF(C78:I80,"778")&amp;") ","")&amp;IF(COUNTIF(C78:I80,"A320")&gt;0,"A320("&amp;COUNTIF(C78:I80,"A320")&amp;") ",""))," ",", "))</f>
         <v>A320(2)</v>
       </c>
-      <c r="L67" s="54"/>
-    </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B68" s="43" t="s">
-        <v>68</v>
-      </c>
-      <c r="C68" s="38"/>
-      <c r="D68" s="38"/>
-      <c r="E68" s="38"/>
-      <c r="F68" s="38"/>
-      <c r="G68" s="38"/>
-      <c r="H68" s="38"/>
-      <c r="I68" s="38"/>
-      <c r="J68" s="39"/>
-      <c r="K68" s="39"/>
-      <c r="L68" s="54"/>
-    </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B71" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="C71" s="33"/>
-      <c r="D71" s="33"/>
-      <c r="E71" s="33"/>
-      <c r="F71" s="33"/>
-      <c r="G71" s="33"/>
-      <c r="H71" s="33"/>
-      <c r="I71" s="33"/>
-      <c r="J71" s="33"/>
-      <c r="K71" s="33"/>
-      <c r="L71" s="33"/>
-    </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B72" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="C72" s="34"/>
-      <c r="D72" s="34"/>
-      <c r="E72" s="34"/>
-      <c r="F72" s="34"/>
-      <c r="G72" s="34"/>
-      <c r="H72" s="34"/>
-      <c r="I72" s="34"/>
-      <c r="J72" s="34"/>
-      <c r="K72" s="34"/>
-      <c r="L72" s="34"/>
-    </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B73" s="34"/>
-      <c r="C73" s="34"/>
-      <c r="D73" s="34"/>
-      <c r="E73" s="34"/>
-      <c r="F73" s="34"/>
-      <c r="G73" s="34"/>
-      <c r="H73" s="34"/>
-      <c r="I73" s="34"/>
-      <c r="J73" s="34"/>
-      <c r="K73" s="34"/>
-      <c r="L73" s="34"/>
-    </row>
-    <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B74" s="35" t="s">
+      <c r="L78" s="55"/>
+    </row>
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B79" s="44" t="s">
+        <v>69</v>
+      </c>
+      <c r="C79" s="39"/>
+      <c r="D79" s="39"/>
+      <c r="E79" s="39"/>
+      <c r="F79" s="39"/>
+      <c r="G79" s="39"/>
+      <c r="H79" s="39"/>
+      <c r="I79" s="39"/>
+      <c r="J79" s="40"/>
+      <c r="K79" s="40"/>
+      <c r="L79" s="55"/>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B80" s="44" t="s">
+        <v>72</v>
+      </c>
+      <c r="C80" s="39"/>
+      <c r="D80" s="39"/>
+      <c r="E80" s="39"/>
+      <c r="F80" s="39"/>
+      <c r="G80" s="39"/>
+      <c r="H80" s="39"/>
+      <c r="I80" s="39"/>
+      <c r="J80" s="40"/>
+      <c r="K80" s="40"/>
+      <c r="L80" s="55"/>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B83" s="34" t="s">
         <v>94</v>
       </c>
-      <c r="C74" s="35" t="s">
-        <v>45</v>
-      </c>
-      <c r="D74" s="35" t="s">
+      <c r="C83" s="34"/>
+      <c r="D83" s="34"/>
+      <c r="E83" s="34"/>
+      <c r="F83" s="34"/>
+      <c r="G83" s="34"/>
+      <c r="H83" s="34"/>
+      <c r="I83" s="34"/>
+      <c r="J83" s="34"/>
+      <c r="K83" s="34"/>
+      <c r="L83" s="34"/>
+    </row>
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B84" s="35" t="s">
         <v>95</v>
       </c>
-      <c r="E74" s="35" t="s">
+      <c r="C84" s="35"/>
+      <c r="D84" s="35"/>
+      <c r="E84" s="35"/>
+      <c r="F84" s="35"/>
+      <c r="G84" s="35"/>
+      <c r="H84" s="35"/>
+      <c r="I84" s="35"/>
+      <c r="J84" s="35"/>
+      <c r="K84" s="35"/>
+      <c r="L84" s="35"/>
+    </row>
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B85" s="35"/>
+      <c r="C85" s="35"/>
+      <c r="D85" s="35"/>
+      <c r="E85" s="35"/>
+      <c r="F85" s="35"/>
+      <c r="G85" s="35"/>
+      <c r="H85" s="35"/>
+      <c r="I85" s="35"/>
+      <c r="J85" s="35"/>
+      <c r="K85" s="35"/>
+      <c r="L85" s="35"/>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B86" s="36" t="s">
         <v>96</v>
       </c>
-      <c r="F74" s="35" t="s">
+      <c r="C86" s="36" t="s">
+        <v>46</v>
+      </c>
+      <c r="D86" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="J74" s="55" t="s">
+      <c r="E86" s="36" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B75" s="56" t="n">
+      <c r="F86" s="36" t="s">
+        <v>99</v>
+      </c>
+      <c r="J86" s="56" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B87" s="57" t="n">
         <v>46484</v>
       </c>
-      <c r="C75" s="38" t="s">
+      <c r="C87" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="D75" s="38" t="s">
+      <c r="D87" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="E75" s="57" t="n">
+      <c r="E87" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="F75" s="58" t="s">
-        <v>99</v>
-      </c>
-      <c r="J75" s="59" t="str">
-        <f aca="false">IF(OR($B75="",$C75=""),"",$B75&amp;"|"&amp;$C75)</f>
+      <c r="F87" s="59" t="s">
+        <v>101</v>
+      </c>
+      <c r="J87" s="60" t="str">
+        <f aca="false">IF(OR($B87="",$C87=""),"",$B87&amp;"|"&amp;$C87)</f>
         <v>46484|NOSRUN</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B76" s="56" t="n">
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B88" s="57" t="n">
         <v>46487</v>
       </c>
-      <c r="C76" s="38" t="s">
+      <c r="C88" s="39" t="s">
         <v>8</v>
       </c>
-      <c r="D76" s="38" t="s">
+      <c r="D88" s="39" t="s">
         <v>73</v>
       </c>
-      <c r="E76" s="57" t="n">
+      <c r="E88" s="58" t="n">
         <v>1</v>
       </c>
-      <c r="F76" s="58" t="s">
-        <v>100</v>
-      </c>
-      <c r="J76" s="59" t="str">
-        <f aca="false">IF(OR($B76="",$C76=""),"",$B76&amp;"|"&amp;$C76)</f>
+      <c r="F88" s="59" t="s">
+        <v>102</v>
+      </c>
+      <c r="J88" s="60" t="str">
+        <f aca="false">IF(OR($B88="",$C88=""),"",$B88&amp;"|"&amp;$C88)</f>
         <v>46487|NOSRUN</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B77" s="56" t="n">
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B89" s="57" t="n">
         <v>46497</v>
       </c>
-      <c r="C77" s="38" t="s">
-        <v>66</v>
-      </c>
-      <c r="D77" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="E77" s="57" t="n">
+      <c r="C89" s="39" t="s">
+        <v>67</v>
+      </c>
+      <c r="D89" s="39" t="s">
+        <v>70</v>
+      </c>
+      <c r="E89" s="58" t="n">
         <v>2</v>
       </c>
-      <c r="F77" s="58" t="s">
-        <v>101</v>
-      </c>
-      <c r="J77" s="59" t="str">
-        <f aca="false">IF(OR($B77="",$C77=""),"",$B77&amp;"|"&amp;$C77)</f>
+      <c r="F89" s="59" t="s">
+        <v>103</v>
+      </c>
+      <c r="J89" s="60" t="str">
+        <f aca="false">IF(OR($B89="",$C89=""),"",$B89&amp;"|"&amp;$C89)</f>
         <v>46497|CDGRUN</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B78" s="56"/>
-      <c r="C78" s="38"/>
-      <c r="D78" s="38"/>
-      <c r="E78" s="57"/>
-      <c r="F78" s="58"/>
-      <c r="J78" s="59" t="str">
-        <f aca="false">IF(OR($B78="",$C78=""),"",$B78&amp;"|"&amp;$C78)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B79" s="56"/>
-      <c r="C79" s="38"/>
-      <c r="D79" s="38"/>
-      <c r="E79" s="57"/>
-      <c r="F79" s="58"/>
-      <c r="J79" s="59" t="str">
-        <f aca="false">IF(OR($B79="",$C79=""),"",$B79&amp;"|"&amp;$C79)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B80" s="56"/>
-      <c r="C80" s="38"/>
-      <c r="D80" s="38"/>
-      <c r="E80" s="57"/>
-      <c r="F80" s="58"/>
-      <c r="J80" s="59" t="str">
-        <f aca="false">IF(OR($B80="",$C80=""),"",$B80&amp;"|"&amp;$C80)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B81" s="56"/>
-      <c r="C81" s="38"/>
-      <c r="D81" s="38"/>
-      <c r="E81" s="57"/>
-      <c r="F81" s="58"/>
-      <c r="J81" s="59" t="str">
-        <f aca="false">IF(OR($B81="",$C81=""),"",$B81&amp;"|"&amp;$C81)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B82" s="56"/>
-      <c r="C82" s="38"/>
-      <c r="D82" s="38"/>
-      <c r="E82" s="57"/>
-      <c r="F82" s="58"/>
-      <c r="J82" s="59" t="str">
-        <f aca="false">IF(OR($B82="",$C82=""),"",$B82&amp;"|"&amp;$C82)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B83" s="56"/>
-      <c r="C83" s="38"/>
-      <c r="D83" s="38"/>
-      <c r="E83" s="57"/>
-      <c r="F83" s="58"/>
-      <c r="J83" s="59" t="str">
-        <f aca="false">IF(OR($B83="",$C83=""),"",$B83&amp;"|"&amp;$C83)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B84" s="56"/>
-      <c r="C84" s="38"/>
-      <c r="D84" s="38"/>
-      <c r="E84" s="57"/>
-      <c r="F84" s="58"/>
-      <c r="J84" s="59" t="str">
-        <f aca="false">IF(OR($B84="",$C84=""),"",$B84&amp;"|"&amp;$C84)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B85" s="56"/>
-      <c r="C85" s="38"/>
-      <c r="D85" s="38"/>
-      <c r="E85" s="57"/>
-      <c r="F85" s="58"/>
-      <c r="J85" s="59" t="str">
-        <f aca="false">IF(OR($B85="",$C85=""),"",$B85&amp;"|"&amp;$C85)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B86" s="56"/>
-      <c r="C86" s="38"/>
-      <c r="D86" s="38"/>
-      <c r="E86" s="57"/>
-      <c r="F86" s="58"/>
-      <c r="J86" s="59" t="str">
-        <f aca="false">IF(OR($B86="",$C86=""),"",$B86&amp;"|"&amp;$C86)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B87" s="56"/>
-      <c r="C87" s="38"/>
-      <c r="D87" s="38"/>
-      <c r="E87" s="57"/>
-      <c r="F87" s="58"/>
-      <c r="J87" s="59" t="str">
-        <f aca="false">IF(OR($B87="",$C87=""),"",$B87&amp;"|"&amp;$C87)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B88" s="56"/>
-      <c r="C88" s="38"/>
-      <c r="D88" s="38"/>
-      <c r="E88" s="57"/>
-      <c r="F88" s="58"/>
-      <c r="J88" s="59" t="str">
-        <f aca="false">IF(OR($B88="",$C88=""),"",$B88&amp;"|"&amp;$C88)</f>
-        <v/>
-      </c>
-    </row>
-    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B89" s="56"/>
-      <c r="C89" s="38"/>
-      <c r="D89" s="38"/>
-      <c r="E89" s="57"/>
-      <c r="F89" s="58"/>
-      <c r="J89" s="59" t="str">
-        <f aca="false">IF(OR($B89="",$C89=""),"",$B89&amp;"|"&amp;$C89)</f>
-        <v/>
-      </c>
-    </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B90" s="56"/>
-      <c r="C90" s="38"/>
-      <c r="D90" s="38"/>
-      <c r="E90" s="57"/>
-      <c r="F90" s="58"/>
-      <c r="J90" s="59" t="str">
+      <c r="B90" s="57"/>
+      <c r="C90" s="39"/>
+      <c r="D90" s="39"/>
+      <c r="E90" s="58"/>
+      <c r="F90" s="59"/>
+      <c r="J90" s="60" t="str">
         <f aca="false">IF(OR($B90="",$C90=""),"",$B90&amp;"|"&amp;$C90)</f>
         <v/>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B91" s="56"/>
-      <c r="C91" s="38"/>
-      <c r="D91" s="38"/>
-      <c r="E91" s="57"/>
-      <c r="F91" s="58"/>
-      <c r="J91" s="59" t="str">
+      <c r="B91" s="57"/>
+      <c r="C91" s="39"/>
+      <c r="D91" s="39"/>
+      <c r="E91" s="58"/>
+      <c r="F91" s="59"/>
+      <c r="J91" s="60" t="str">
         <f aca="false">IF(OR($B91="",$C91=""),"",$B91&amp;"|"&amp;$C91)</f>
         <v/>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B92" s="56"/>
-      <c r="C92" s="38"/>
-      <c r="D92" s="38"/>
-      <c r="E92" s="57"/>
-      <c r="F92" s="58"/>
-      <c r="J92" s="59" t="str">
+      <c r="B92" s="57"/>
+      <c r="C92" s="39"/>
+      <c r="D92" s="39"/>
+      <c r="E92" s="58"/>
+      <c r="F92" s="59"/>
+      <c r="J92" s="60" t="str">
         <f aca="false">IF(OR($B92="",$C92=""),"",$B92&amp;"|"&amp;$C92)</f>
         <v/>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B93" s="56"/>
-      <c r="C93" s="38"/>
-      <c r="D93" s="38"/>
-      <c r="E93" s="57"/>
-      <c r="F93" s="58"/>
-      <c r="J93" s="59" t="str">
+      <c r="B93" s="57"/>
+      <c r="C93" s="39"/>
+      <c r="D93" s="39"/>
+      <c r="E93" s="58"/>
+      <c r="F93" s="59"/>
+      <c r="J93" s="60" t="str">
         <f aca="false">IF(OR($B93="",$C93=""),"",$B93&amp;"|"&amp;$C93)</f>
         <v/>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B94" s="56"/>
-      <c r="C94" s="38"/>
-      <c r="D94" s="38"/>
-      <c r="E94" s="57"/>
-      <c r="F94" s="58"/>
-      <c r="J94" s="59" t="str">
+      <c r="B94" s="57"/>
+      <c r="C94" s="39"/>
+      <c r="D94" s="39"/>
+      <c r="E94" s="58"/>
+      <c r="F94" s="59"/>
+      <c r="J94" s="60" t="str">
         <f aca="false">IF(OR($B94="",$C94=""),"",$B94&amp;"|"&amp;$C94)</f>
         <v/>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B95" s="56"/>
-      <c r="C95" s="38"/>
-      <c r="D95" s="38"/>
-      <c r="E95" s="57"/>
-      <c r="F95" s="58"/>
-      <c r="J95" s="59" t="str">
+      <c r="B95" s="57"/>
+      <c r="C95" s="39"/>
+      <c r="D95" s="39"/>
+      <c r="E95" s="58"/>
+      <c r="F95" s="59"/>
+      <c r="J95" s="60" t="str">
         <f aca="false">IF(OR($B95="",$C95=""),"",$B95&amp;"|"&amp;$C95)</f>
         <v/>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B96" s="56"/>
-      <c r="C96" s="38"/>
-      <c r="D96" s="38"/>
-      <c r="E96" s="57"/>
-      <c r="F96" s="58"/>
-      <c r="J96" s="59" t="str">
+      <c r="B96" s="57"/>
+      <c r="C96" s="39"/>
+      <c r="D96" s="39"/>
+      <c r="E96" s="58"/>
+      <c r="F96" s="59"/>
+      <c r="J96" s="60" t="str">
         <f aca="false">IF(OR($B96="",$C96=""),"",$B96&amp;"|"&amp;$C96)</f>
         <v/>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B97" s="56"/>
-      <c r="C97" s="38"/>
-      <c r="D97" s="38"/>
-      <c r="E97" s="57"/>
-      <c r="F97" s="58"/>
-      <c r="J97" s="59" t="str">
+      <c r="B97" s="57"/>
+      <c r="C97" s="39"/>
+      <c r="D97" s="39"/>
+      <c r="E97" s="58"/>
+      <c r="F97" s="59"/>
+      <c r="J97" s="60" t="str">
         <f aca="false">IF(OR($B97="",$C97=""),"",$B97&amp;"|"&amp;$C97)</f>
         <v/>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B98" s="56"/>
-      <c r="C98" s="38"/>
-      <c r="D98" s="38"/>
-      <c r="E98" s="57"/>
-      <c r="F98" s="58"/>
-      <c r="J98" s="59" t="str">
+      <c r="B98" s="57"/>
+      <c r="C98" s="39"/>
+      <c r="D98" s="39"/>
+      <c r="E98" s="58"/>
+      <c r="F98" s="59"/>
+      <c r="J98" s="60" t="str">
         <f aca="false">IF(OR($B98="",$C98=""),"",$B98&amp;"|"&amp;$C98)</f>
         <v/>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B99" s="56"/>
-      <c r="C99" s="38"/>
-      <c r="D99" s="38"/>
-      <c r="E99" s="57"/>
-      <c r="F99" s="58"/>
-      <c r="J99" s="59" t="str">
+      <c r="B99" s="57"/>
+      <c r="C99" s="39"/>
+      <c r="D99" s="39"/>
+      <c r="E99" s="58"/>
+      <c r="F99" s="59"/>
+      <c r="J99" s="60" t="str">
         <f aca="false">IF(OR($B99="",$C99=""),"",$B99&amp;"|"&amp;$C99)</f>
         <v/>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B100" s="56"/>
-      <c r="C100" s="38"/>
-      <c r="D100" s="38"/>
-      <c r="E100" s="57"/>
-      <c r="F100" s="58"/>
-      <c r="J100" s="59" t="str">
+      <c r="B100" s="57"/>
+      <c r="C100" s="39"/>
+      <c r="D100" s="39"/>
+      <c r="E100" s="58"/>
+      <c r="F100" s="59"/>
+      <c r="J100" s="60" t="str">
         <f aca="false">IF(OR($B100="",$C100=""),"",$B100&amp;"|"&amp;$C100)</f>
         <v/>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B101" s="56"/>
-      <c r="C101" s="38"/>
-      <c r="D101" s="38"/>
-      <c r="E101" s="57"/>
-      <c r="F101" s="58"/>
-      <c r="J101" s="59" t="str">
+      <c r="B101" s="57"/>
+      <c r="C101" s="39"/>
+      <c r="D101" s="39"/>
+      <c r="E101" s="58"/>
+      <c r="F101" s="59"/>
+      <c r="J101" s="60" t="str">
         <f aca="false">IF(OR($B101="",$C101=""),"",$B101&amp;"|"&amp;$C101)</f>
         <v/>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B102" s="56"/>
-      <c r="C102" s="38"/>
-      <c r="D102" s="38"/>
-      <c r="E102" s="57"/>
-      <c r="F102" s="58"/>
-      <c r="J102" s="59" t="str">
+      <c r="B102" s="57"/>
+      <c r="C102" s="39"/>
+      <c r="D102" s="39"/>
+      <c r="E102" s="58"/>
+      <c r="F102" s="59"/>
+      <c r="J102" s="60" t="str">
         <f aca="false">IF(OR($B102="",$C102=""),"",$B102&amp;"|"&amp;$C102)</f>
         <v/>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B103" s="56"/>
-      <c r="C103" s="38"/>
-      <c r="D103" s="38"/>
-      <c r="E103" s="57"/>
-      <c r="F103" s="58"/>
-      <c r="J103" s="59" t="str">
+      <c r="B103" s="57"/>
+      <c r="C103" s="39"/>
+      <c r="D103" s="39"/>
+      <c r="E103" s="58"/>
+      <c r="F103" s="59"/>
+      <c r="J103" s="60" t="str">
         <f aca="false">IF(OR($B103="",$C103=""),"",$B103&amp;"|"&amp;$C103)</f>
         <v/>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B104" s="56"/>
-      <c r="C104" s="38"/>
-      <c r="D104" s="38"/>
-      <c r="E104" s="57"/>
-      <c r="F104" s="58"/>
-      <c r="J104" s="59" t="str">
+      <c r="B104" s="57"/>
+      <c r="C104" s="39"/>
+      <c r="D104" s="39"/>
+      <c r="E104" s="58"/>
+      <c r="F104" s="59"/>
+      <c r="J104" s="60" t="str">
         <f aca="false">IF(OR($B104="",$C104=""),"",$B104&amp;"|"&amp;$C104)</f>
         <v/>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B105" s="56"/>
-      <c r="C105" s="38"/>
-      <c r="D105" s="38"/>
-      <c r="E105" s="57"/>
-      <c r="F105" s="58"/>
-      <c r="J105" s="59" t="str">
+      <c r="B105" s="57"/>
+      <c r="C105" s="39"/>
+      <c r="D105" s="39"/>
+      <c r="E105" s="58"/>
+      <c r="F105" s="59"/>
+      <c r="J105" s="60" t="str">
         <f aca="false">IF(OR($B105="",$C105=""),"",$B105&amp;"|"&amp;$C105)</f>
         <v/>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B106" s="56"/>
-      <c r="C106" s="38"/>
-      <c r="D106" s="38"/>
-      <c r="E106" s="57"/>
-      <c r="F106" s="58"/>
-      <c r="J106" s="59" t="str">
+      <c r="B106" s="57"/>
+      <c r="C106" s="39"/>
+      <c r="D106" s="39"/>
+      <c r="E106" s="58"/>
+      <c r="F106" s="59"/>
+      <c r="J106" s="60" t="str">
         <f aca="false">IF(OR($B106="",$C106=""),"",$B106&amp;"|"&amp;$C106)</f>
         <v/>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B107" s="56"/>
-      <c r="C107" s="38"/>
-      <c r="D107" s="38"/>
-      <c r="E107" s="57"/>
-      <c r="F107" s="58"/>
-      <c r="J107" s="59" t="str">
+      <c r="B107" s="57"/>
+      <c r="C107" s="39"/>
+      <c r="D107" s="39"/>
+      <c r="E107" s="58"/>
+      <c r="F107" s="59"/>
+      <c r="J107" s="60" t="str">
         <f aca="false">IF(OR($B107="",$C107=""),"",$B107&amp;"|"&amp;$C107)</f>
         <v/>
       </c>
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B108" s="56"/>
-      <c r="C108" s="38"/>
-      <c r="D108" s="38"/>
-      <c r="E108" s="57"/>
-      <c r="F108" s="58"/>
-      <c r="J108" s="59" t="str">
+      <c r="B108" s="57"/>
+      <c r="C108" s="39"/>
+      <c r="D108" s="39"/>
+      <c r="E108" s="58"/>
+      <c r="F108" s="59"/>
+      <c r="J108" s="60" t="str">
         <f aca="false">IF(OR($B108="",$C108=""),"",$B108&amp;"|"&amp;$C108)</f>
         <v/>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B109" s="56"/>
-      <c r="C109" s="38"/>
-      <c r="D109" s="38"/>
-      <c r="E109" s="57"/>
-      <c r="F109" s="58"/>
-      <c r="J109" s="59" t="str">
+      <c r="B109" s="57"/>
+      <c r="C109" s="39"/>
+      <c r="D109" s="39"/>
+      <c r="E109" s="58"/>
+      <c r="F109" s="59"/>
+      <c r="J109" s="60" t="str">
         <f aca="false">IF(OR($B109="",$C109=""),"",$B109&amp;"|"&amp;$C109)</f>
         <v/>
       </c>
     </row>
     <row r="110" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B110" s="56"/>
-      <c r="C110" s="38"/>
-      <c r="D110" s="38"/>
-      <c r="E110" s="57"/>
-      <c r="F110" s="58"/>
-      <c r="J110" s="59" t="str">
+      <c r="B110" s="57"/>
+      <c r="C110" s="39"/>
+      <c r="D110" s="39"/>
+      <c r="E110" s="58"/>
+      <c r="F110" s="59"/>
+      <c r="J110" s="60" t="str">
         <f aca="false">IF(OR($B110="",$C110=""),"",$B110&amp;"|"&amp;$C110)</f>
         <v/>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B111" s="56"/>
-      <c r="C111" s="38"/>
-      <c r="D111" s="38"/>
-      <c r="E111" s="57"/>
-      <c r="F111" s="58"/>
-      <c r="J111" s="59" t="str">
+      <c r="B111" s="57"/>
+      <c r="C111" s="39"/>
+      <c r="D111" s="39"/>
+      <c r="E111" s="58"/>
+      <c r="F111" s="59"/>
+      <c r="J111" s="60" t="str">
         <f aca="false">IF(OR($B111="",$C111=""),"",$B111&amp;"|"&amp;$C111)</f>
         <v/>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B112" s="56"/>
-      <c r="C112" s="38"/>
-      <c r="D112" s="38"/>
-      <c r="E112" s="57"/>
-      <c r="F112" s="58"/>
-      <c r="J112" s="59" t="str">
+      <c r="B112" s="57"/>
+      <c r="C112" s="39"/>
+      <c r="D112" s="39"/>
+      <c r="E112" s="58"/>
+      <c r="F112" s="59"/>
+      <c r="J112" s="60" t="str">
         <f aca="false">IF(OR($B112="",$C112=""),"",$B112&amp;"|"&amp;$C112)</f>
         <v/>
       </c>
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B113" s="56"/>
-      <c r="C113" s="38"/>
-      <c r="D113" s="38"/>
-      <c r="E113" s="57"/>
-      <c r="F113" s="58"/>
-      <c r="J113" s="59" t="str">
+      <c r="B113" s="57"/>
+      <c r="C113" s="39"/>
+      <c r="D113" s="39"/>
+      <c r="E113" s="58"/>
+      <c r="F113" s="59"/>
+      <c r="J113" s="60" t="str">
         <f aca="false">IF(OR($B113="",$C113=""),"",$B113&amp;"|"&amp;$C113)</f>
         <v/>
       </c>
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B114" s="56"/>
-      <c r="C114" s="38"/>
-      <c r="D114" s="38"/>
-      <c r="E114" s="57"/>
-      <c r="F114" s="58"/>
-      <c r="J114" s="59" t="str">
+      <c r="B114" s="57"/>
+      <c r="C114" s="39"/>
+      <c r="D114" s="39"/>
+      <c r="E114" s="58"/>
+      <c r="F114" s="59"/>
+      <c r="J114" s="60" t="str">
         <f aca="false">IF(OR($B114="",$C114=""),"",$B114&amp;"|"&amp;$C114)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B115" s="57"/>
+      <c r="C115" s="39"/>
+      <c r="D115" s="39"/>
+      <c r="E115" s="58"/>
+      <c r="F115" s="59"/>
+      <c r="J115" s="60" t="str">
+        <f aca="false">IF(OR($B115="",$C115=""),"",$B115&amp;"|"&amp;$C115)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B116" s="57"/>
+      <c r="C116" s="39"/>
+      <c r="D116" s="39"/>
+      <c r="E116" s="58"/>
+      <c r="F116" s="59"/>
+      <c r="J116" s="60" t="str">
+        <f aca="false">IF(OR($B116="",$C116=""),"",$B116&amp;"|"&amp;$C116)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B117" s="57"/>
+      <c r="C117" s="39"/>
+      <c r="D117" s="39"/>
+      <c r="E117" s="58"/>
+      <c r="F117" s="59"/>
+      <c r="J117" s="60" t="str">
+        <f aca="false">IF(OR($B117="",$C117=""),"",$B117&amp;"|"&amp;$C117)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B118" s="57"/>
+      <c r="C118" s="39"/>
+      <c r="D118" s="39"/>
+      <c r="E118" s="58"/>
+      <c r="F118" s="59"/>
+      <c r="J118" s="60" t="str">
+        <f aca="false">IF(OR($B118="",$C118=""),"",$B118&amp;"|"&amp;$C118)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B119" s="57"/>
+      <c r="C119" s="39"/>
+      <c r="D119" s="39"/>
+      <c r="E119" s="58"/>
+      <c r="F119" s="59"/>
+      <c r="J119" s="60" t="str">
+        <f aca="false">IF(OR($B119="",$C119=""),"",$B119&amp;"|"&amp;$C119)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B120" s="57"/>
+      <c r="C120" s="39"/>
+      <c r="D120" s="39"/>
+      <c r="E120" s="58"/>
+      <c r="F120" s="59"/>
+      <c r="J120" s="60" t="str">
+        <f aca="false">IF(OR($B120="",$C120=""),"",$B120&amp;"|"&amp;$C120)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B121" s="57"/>
+      <c r="C121" s="39"/>
+      <c r="D121" s="39"/>
+      <c r="E121" s="58"/>
+      <c r="F121" s="59"/>
+      <c r="J121" s="60" t="str">
+        <f aca="false">IF(OR($B121="",$C121=""),"",$B121&amp;"|"&amp;$C121)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B122" s="57"/>
+      <c r="C122" s="39"/>
+      <c r="D122" s="39"/>
+      <c r="E122" s="58"/>
+      <c r="F122" s="59"/>
+      <c r="J122" s="60" t="str">
+        <f aca="false">IF(OR($B122="",$C122=""),"",$B122&amp;"|"&amp;$C122)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B123" s="57"/>
+      <c r="C123" s="39"/>
+      <c r="D123" s="39"/>
+      <c r="E123" s="58"/>
+      <c r="F123" s="59"/>
+      <c r="J123" s="60" t="str">
+        <f aca="false">IF(OR($B123="",$C123=""),"",$B123&amp;"|"&amp;$C123)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B124" s="57"/>
+      <c r="C124" s="39"/>
+      <c r="D124" s="39"/>
+      <c r="E124" s="58"/>
+      <c r="F124" s="59"/>
+      <c r="J124" s="60" t="str">
+        <f aca="false">IF(OR($B124="",$C124=""),"",$B124&amp;"|"&amp;$C124)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B125" s="57"/>
+      <c r="C125" s="39"/>
+      <c r="D125" s="39"/>
+      <c r="E125" s="58"/>
+      <c r="F125" s="59"/>
+      <c r="J125" s="60" t="str">
+        <f aca="false">IF(OR($B125="",$C125=""),"",$B125&amp;"|"&amp;$C125)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B126" s="57"/>
+      <c r="C126" s="39"/>
+      <c r="D126" s="39"/>
+      <c r="E126" s="58"/>
+      <c r="F126" s="59"/>
+      <c r="J126" s="60" t="str">
+        <f aca="false">IF(OR($B126="",$C126=""),"",$B126&amp;"|"&amp;$C126)</f>
         <v/>
       </c>
     </row>
@@ -4063,44 +4288,44 @@
     <mergeCell ref="B38:L39"/>
     <mergeCell ref="B41:L41"/>
     <mergeCell ref="B42:L43"/>
-    <mergeCell ref="J45:J46"/>
-    <mergeCell ref="K45:K46"/>
-    <mergeCell ref="L45:L46"/>
-    <mergeCell ref="J47:J48"/>
-    <mergeCell ref="K47:K48"/>
-    <mergeCell ref="L47:L48"/>
-    <mergeCell ref="J49:J50"/>
-    <mergeCell ref="K49:K50"/>
-    <mergeCell ref="L49:L50"/>
-    <mergeCell ref="J51:J52"/>
-    <mergeCell ref="K51:K52"/>
-    <mergeCell ref="L51:L52"/>
-    <mergeCell ref="J53:J54"/>
-    <mergeCell ref="K53:K54"/>
-    <mergeCell ref="L53:L54"/>
-    <mergeCell ref="J55:J56"/>
-    <mergeCell ref="K55:K56"/>
-    <mergeCell ref="L55:L56"/>
-    <mergeCell ref="J57:J58"/>
-    <mergeCell ref="K57:K58"/>
-    <mergeCell ref="L57:L58"/>
-    <mergeCell ref="J59:J60"/>
-    <mergeCell ref="K59:K60"/>
-    <mergeCell ref="L59:L60"/>
-    <mergeCell ref="J61:J62"/>
-    <mergeCell ref="K61:K62"/>
-    <mergeCell ref="L61:L62"/>
-    <mergeCell ref="J63:J64"/>
-    <mergeCell ref="K63:K64"/>
-    <mergeCell ref="L63:L64"/>
-    <mergeCell ref="J65:J66"/>
-    <mergeCell ref="K65:K66"/>
-    <mergeCell ref="L65:L66"/>
-    <mergeCell ref="J67:J68"/>
-    <mergeCell ref="K67:K68"/>
-    <mergeCell ref="L67:L68"/>
-    <mergeCell ref="B71:L71"/>
-    <mergeCell ref="B72:L73"/>
+    <mergeCell ref="J45:J47"/>
+    <mergeCell ref="K45:K47"/>
+    <mergeCell ref="L45:L47"/>
+    <mergeCell ref="J48:J50"/>
+    <mergeCell ref="K48:K50"/>
+    <mergeCell ref="L48:L50"/>
+    <mergeCell ref="J51:J53"/>
+    <mergeCell ref="K51:K53"/>
+    <mergeCell ref="L51:L53"/>
+    <mergeCell ref="J54:J56"/>
+    <mergeCell ref="K54:K56"/>
+    <mergeCell ref="L54:L56"/>
+    <mergeCell ref="J57:J59"/>
+    <mergeCell ref="K57:K59"/>
+    <mergeCell ref="L57:L59"/>
+    <mergeCell ref="J60:J62"/>
+    <mergeCell ref="K60:K62"/>
+    <mergeCell ref="L60:L62"/>
+    <mergeCell ref="J63:J65"/>
+    <mergeCell ref="K63:K65"/>
+    <mergeCell ref="L63:L65"/>
+    <mergeCell ref="J66:J68"/>
+    <mergeCell ref="K66:K68"/>
+    <mergeCell ref="L66:L68"/>
+    <mergeCell ref="J69:J71"/>
+    <mergeCell ref="K69:K71"/>
+    <mergeCell ref="L69:L71"/>
+    <mergeCell ref="J72:J74"/>
+    <mergeCell ref="K72:K74"/>
+    <mergeCell ref="L72:L74"/>
+    <mergeCell ref="J75:J77"/>
+    <mergeCell ref="K75:K77"/>
+    <mergeCell ref="L75:L77"/>
+    <mergeCell ref="J78:J80"/>
+    <mergeCell ref="K78:K80"/>
+    <mergeCell ref="L78:L80"/>
+    <mergeCell ref="B83:L83"/>
+    <mergeCell ref="B84:L85"/>
   </mergeCells>
   <conditionalFormatting sqref="C8:I8 C10:I10 C12:I12 C14:I14 C16:I16 C18:I18">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
@@ -4181,42 +4406,42 @@
       <formula>$B25="TMMRUN"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="B45:B68">
+  <conditionalFormatting sqref="B45:B80">
     <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
-      <formula>OR($B45="CDGRUN",$B44="CDGRUN")</formula>
+      <formula>OR($B45="CDGRUN",$B44="CDGRUN",$B43="CDGRUN")</formula>
     </cfRule>
     <cfRule type="expression" priority="28" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
-      <formula>OR($B45="CDGDZA",$B44="CDGDZA")</formula>
+      <formula>OR($B45="CDGDZA",$B44="CDGDZA",$B43="CDGDZA")</formula>
     </cfRule>
     <cfRule type="expression" priority="29" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
-      <formula>OR($B45="BKKRUN",$B44="BKKRUN")</formula>
+      <formula>OR($B45="BKKRUN",$B44="BKKRUN",$B43="BKKRUN")</formula>
     </cfRule>
     <cfRule type="expression" priority="30" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
-      <formula>OR($B45="DZARUN",$B44="DZARUN")</formula>
+      <formula>OR($B45="DZARUN",$B44="DZARUN",$B43="DZARUN")</formula>
     </cfRule>
     <cfRule type="expression" priority="31" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
-      <formula>OR($B45="MRURUN",$B44="MRURUN")</formula>
+      <formula>OR($B45="MRURUN",$B44="MRURUN",$B43="MRURUN")</formula>
     </cfRule>
     <cfRule type="expression" priority="32" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
-      <formula>OR($B45="NOSRUN",$B44="NOSRUN")</formula>
+      <formula>OR($B45="NOSRUN",$B44="NOSRUN",$B43="NOSRUN")</formula>
     </cfRule>
     <cfRule type="expression" priority="33" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
-      <formula>OR($B45="RUNTNR",$B44="RUNTNR")</formula>
+      <formula>OR($B45="RUNTNR",$B44="RUNTNR",$B43="RUNTNR")</formula>
     </cfRule>
     <cfRule type="expression" priority="34" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
-      <formula>OR($B45="JNBRUN",$B44="JNBRUN")</formula>
+      <formula>OR($B45="JNBRUN",$B44="JNBRUN",$B43="JNBRUN")</formula>
     </cfRule>
     <cfRule type="expression" priority="35" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
-      <formula>OR($B45="CPTRUN",$B44="CPTRUN")</formula>
+      <formula>OR($B45="CPTRUN",$B44="CPTRUN",$B43="CPTRUN")</formula>
     </cfRule>
     <cfRule type="expression" priority="36" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
-      <formula>OR($B45="DIERUN",$B44="DIERUN")</formula>
+      <formula>OR($B45="DIERUN",$B44="DIERUN",$B43="DIERUN")</formula>
     </cfRule>
     <cfRule type="expression" priority="37" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
-      <formula>OR($B45="RRGRUN",$B44="RRGRUN")</formula>
+      <formula>OR($B45="RRGRUN",$B44="RRGRUN",$B43="RRGRUN")</formula>
     </cfRule>
     <cfRule type="expression" priority="38" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
-      <formula>OR($B45="TMMRUN",$B44="TMMRUN")</formula>
+      <formula>OR($B45="TMMRUN",$B44="TMMRUN",$B43="TMMRUN")</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="7">
@@ -4225,26 +4450,26 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="false" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C5" type="list">
-      <formula1>$B$45:$B$68</formula1>
+      <formula1>$B$45:$B$80</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Choisir un type avion dans la liste, ou laisser vide s'il n'y a pas de vol ce jour-la." errorStyle="stop" errorTitle="Type avion invalide" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C45:I68" type="list">
+    <dataValidation allowBlank="true" error="Choisir un type avion dans la liste, ou laisser vide s'il n'y a pas de vol ce jour-la." errorStyle="stop" errorTitle="Type avion invalide" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C45:I80" type="list">
       <formula1>$P$45:$P$47</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C75:C114" type="list">
-      <formula1>$B$45:$B$68</formula1>
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="C87:C126" type="list">
+      <formula1>$B$45:$B$80</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D75:D114" type="list">
+    <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D87:D126" type="list">
       <formula1>$P$45:$P$47</formula1>
       <formula2>0</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="Nombre de rotations : entier entre 1 et 20." errorStyle="stop" errorTitle="Valeur invalide" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E75:E114" type="whole">
+    <dataValidation allowBlank="true" error="Nombre de rotations : entier entre 1 et 20." errorStyle="stop" errorTitle="Valeur invalide" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="E87:E126" type="whole">
       <formula1>1</formula1>
       <formula2>20</formula2>
     </dataValidation>
-    <dataValidation allowBlank="true" error="La date est hors de l'annee avril 2027 - mars 2028 : le vol ne sera visible dans aucun mois." errorStyle="warning" errorTitle="Date hors annee d'exploitation" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B75:B114" type="date">
+    <dataValidation allowBlank="true" error="La date est hors de l'annee avril 2027 - mars 2028 : le vol ne sera visible dans aucun mois." errorStyle="warning" errorTitle="Date hors annee d'exploitation" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="B87:B126" type="date">
       <formula1>DATE(2027,4,1)</formula1>
       <formula2>DATE(2028,3,31)</formula2>
     </dataValidation>

--- a/Programme_vols_mensuel_2027-2028.xlsx
+++ b/Programme_vols_mensuel_2027-2028.xlsx
@@ -315,7 +315,7 @@
     <t xml:space="preserve">Nb de semaines calendaires du mois</t>
   </si>
   <si>
-    <t xml:space="preserve">Lecture : 1re ligne = les rotations qui PARTENT ce jour-la ("2xA320" = deux rotations A320)  |  2e ligne "&lt; 787" = les RETOURS du jour  |  "(+787)" ou "(-787)" encadre en rouge = ajout ou retrait saisi sur la feuille Vols additionnels.</t>
+    <t xml:space="preserve">Lecture : 1re ligne = les rotations qui PARTENT ce jour-la ("2xA320" = deux rotations A320)  |  2e ligne "&lt; 787" = les RETOURS du jour  |  cellule encadree en VERT = vol AJOUTE "(+787)", encadree en ROUGE = vol RETIRE "(-787)", saisis sur la feuille Vols additionnels.</t>
   </si>
   <si>
     <t xml:space="preserve">77W : code du mois precedent</t>
@@ -1767,7 +1767,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="19">
     <dxf>
       <border diagonalUp="false" diagonalDown="false">
         <left style="medium">
@@ -1781,6 +1781,23 @@
         </top>
         <bottom style="medium">
           <color rgb="FFC00000"/>
+        </bottom>
+        <diagonal/>
+      </border>
+    </dxf>
+    <dxf>
+      <border diagonalUp="false" diagonalDown="false">
+        <left style="medium">
+          <color rgb="FF00B050"/>
+        </left>
+        <right style="medium">
+          <color rgb="FF00B050"/>
+        </right>
+        <top style="medium">
+          <color rgb="FF00B050"/>
+        </top>
+        <bottom style="medium">
+          <color rgb="FF00B050"/>
         </bottom>
         <diagonal/>
       </border>
@@ -2017,6 +2034,13 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFE2EFDA"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -2025,7 +2049,7 @@
       <rgbColor rgb="FFC00000"/>
       <rgbColor rgb="FF00FF00"/>
       <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFF2E4D8"/>
+      <rgbColor rgb="FFC6E0B4"/>
       <rgbColor rgb="FFFF00FF"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800000"/>
@@ -2041,12 +2065,12 @@
       <rgbColor rgb="FFFFF2CC"/>
       <rgbColor rgb="FFF2F2F2"/>
       <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFE7E6E6"/>
+      <rgbColor rgb="FFFCE4E4"/>
       <rgbColor rgb="FF0563C1"/>
       <rgbColor rgb="FFD9D2E9"/>
       <rgbColor rgb="FF000080"/>
       <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFCE4E4"/>
+      <rgbColor rgb="FFF2E4D8"/>
       <rgbColor rgb="FF00FFFF"/>
       <rgbColor rgb="FF800080"/>
       <rgbColor rgb="FF800000"/>
@@ -2054,22 +2078,22 @@
       <rgbColor rgb="FF0000FF"/>
       <rgbColor rgb="FF00CCFF"/>
       <rgbColor rgb="FFD9E2F3"/>
-      <rgbColor rgb="FFC6E0B4"/>
+      <rgbColor rgb="FFE2EFDA"/>
       <rgbColor rgb="FFFFE699"/>
       <rgbColor rgb="FF9DC3E6"/>
       <rgbColor rgb="FFF4B183"/>
       <rgbColor rgb="FFB7DEE8"/>
       <rgbColor rgb="FFFFC7CE"/>
       <rgbColor rgb="FF2E75B6"/>
-      <rgbColor rgb="FF33CCCC"/>
       <rgbColor rgb="FFA9D08E"/>
+      <rgbColor rgb="FF70AD47"/>
       <rgbColor rgb="FFFFD966"/>
-      <rgbColor rgb="FFFF9900"/>
+      <rgbColor rgb="FFE7E6E6"/>
       <rgbColor rgb="FFED7D31"/>
       <rgbColor rgb="FF595959"/>
       <rgbColor rgb="FFA6A6A6"/>
       <rgbColor rgb="FF1F3864"/>
-      <rgbColor rgb="FF70AD47"/>
+      <rgbColor rgb="FF00B050"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF375623"/>
       <rgbColor rgb="FF833C0C"/>
@@ -6747,80 +6771,83 @@
   </mergeCells>
   <conditionalFormatting sqref="C8:I8 C10:I10 C12:I12 C14:I14 C16:I16 C18:I18">
     <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="0">
-      <formula>ISNUMBER(SEARCH("(",C8))</formula>
+      <formula>ISNUMBER(SEARCH("(-",C8))</formula>
     </cfRule>
     <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+      <formula>ISNUMBER(SEARCH("(+",C8))</formula>
+    </cfRule>
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>AND($C$5="CDGRUN",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>AND($C$5="CDGDZA",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>AND($C$5="BKKRUN",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>AND($C$5="DZARUN",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>AND($C$5="MRURUN",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>AND($C$5="NOSRUN",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>AND($C$5="RUNTNR",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>AND($C$5="JNBRUN",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>AND($C$5="CPTRUN",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>AND($C$5="DIERUN",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>AND($C$5="RRGRUN",C8&lt;&gt;"")</formula>
     </cfRule>
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>AND($C$5="TMMRUN",C8&lt;&gt;"")</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B25:B36">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="1">
+    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
       <formula>$B25="CDGRUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="16" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="2">
+    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
       <formula>$B25="CDGDZA"</formula>
     </cfRule>
-    <cfRule type="expression" priority="17" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="3">
+    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
       <formula>$B25="BKKRUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="18" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="4">
+    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
       <formula>$B25="DZARUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="19" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="5">
+    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
       <formula>$B25="MRURUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="20" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="6">
+    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
       <formula>$B25="NOSRUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="21" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="7">
+    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
       <formula>$B25="RUNTNR"</formula>
     </cfRule>
-    <cfRule type="expression" priority="22" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="8">
+    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
       <formula>$B25="JNBRUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="23" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="9">
+    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
       <formula>$B25="CPTRUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="24" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="10">
+    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
       <formula>$B25="DIERUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="25" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="11">
+    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
       <formula>$B25="RRGRUN"</formula>
     </cfRule>
-    <cfRule type="expression" priority="26" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="12">
+    <cfRule type="expression" priority="27" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
       <formula>$B25="TMMRUN"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -17475,70 +17502,70 @@
     <mergeCell ref="L475:L477"/>
   </mergeCells>
   <conditionalFormatting sqref="D13:J48 D52:J87 D91:J126 D130:J165 D169:J204 D208:J243 D247:J282 D286:J321 D325:J360 D364:J399 D403:J438 D442:J477">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="13">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
       <formula>LEN(D13)&gt;1</formula>
     </cfRule>
-    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="14">
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
       <formula>D13&lt;&gt;""</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B11:L11">
-    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="4" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>$C$6="avril 2027"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B50:L50">
-    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="5" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>$C$6="mai 2027"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B89:L89">
-    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="6" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>$C$6="juin 2027"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B128:L128">
-    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="7" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>$C$6="juillet 2027"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B167:L167">
-    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="8" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>$C$6="aout 2027"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B206:L206">
-    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="9" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>$C$6="septembre 2027"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B245:L245">
-    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="10" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>$C$6="octobre 2027"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B284:L284">
-    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="11" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>$C$6="novembre 2027"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B323:L323">
-    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="12" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>$C$6="decembre 2027"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B362:L362">
-    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="13" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>$C$6="janvier 2028"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B401:L401">
-    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="14" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>$C$6="fevrier 2028"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="B440:L440">
-    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="15">
+    <cfRule type="expression" priority="15" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
       <formula>$C$6="mars 2028"</formula>
     </cfRule>
   </conditionalFormatting>
@@ -19183,8 +19210,11 @@
     <mergeCell ref="B2:G4"/>
   </mergeCells>
   <conditionalFormatting sqref="B7:G66">
-    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="16">
+    <cfRule type="expression" priority="2" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="17">
       <formula>$E7&lt;0</formula>
+    </cfRule>
+    <cfRule type="expression" priority="3" aboveAverage="0" equalAverage="0" bottom="0" percent="0" rank="0" text="" dxfId="18">
+      <formula>$E7&gt;0</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="5">
